--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,57 +525,57 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -761,37 +761,37 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9673996913580254</v>
+        <v>-21467361.1111111</v>
       </c>
       <c r="U2" t="n">
         <v>-0.5290895061728413</v>
       </c>
       <c r="V2" t="n">
+        <v>-0.9643367566498202</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-4.041770926062227</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-27339071.97269149</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-1.188310185185185</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5.481085751106946</v>
+      </c>
+      <c r="AA2" t="n">
         <v>-2.392785493827162</v>
       </c>
-      <c r="W2" t="n">
-        <v>-21467361.1111111</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.9643367566498202</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>-3.464930555555554</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>1.263340021912427</v>
       </c>
-      <c r="AA2" t="n">
-        <v>-1.188310185185185</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-5.481085751106946</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-27339071.97269149</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-4.041770926062227</v>
+        <v>0.9673996913580254</v>
       </c>
       <c r="AE2" t="n">
         <v>1.651140094643594</v>
@@ -892,37 +892,37 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.308207070707027</v>
+        <v>53211254.20875421</v>
       </c>
       <c r="U3" t="n">
         <v>-2.240446127946129</v>
       </c>
       <c r="V3" t="n">
+        <v>1.739018428574349</v>
+      </c>
+      <c r="W3" t="n">
+        <v>8.721836734172271</v>
+      </c>
+      <c r="X3" t="n">
+        <v>57261198.95546704</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.542171717171717</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10.77358227481584</v>
+      </c>
+      <c r="AA3" t="n">
         <v>7.488173400673404</v>
       </c>
-      <c r="W3" t="n">
-        <v>53211254.20875421</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.739018428574349</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>9.462878787878807</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>-0.8960641423635138</v>
       </c>
-      <c r="AA3" t="n">
-        <v>1.542171717171717</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>10.77358227481584</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>57261198.95546704</v>
-      </c>
       <c r="AD3" t="n">
-        <v>8.721836734172271</v>
+        <v>-1.308207070707027</v>
       </c>
       <c r="AE3" t="n">
         <v>-2.129850321462168</v>
@@ -1030,37 +1030,37 @@
         <v>-1</v>
       </c>
       <c r="T4" t="n">
-        <v>5.278356481481524</v>
+        <v>-23228472.22222222</v>
       </c>
       <c r="U4" t="n">
         <v>-2.435763888888886</v>
       </c>
       <c r="V4" t="n">
+        <v>-0.2603361958818617</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.151501379060392</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-10675560.09931385</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.8981481481481477</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-2.436867981841857</v>
+      </c>
+      <c r="AA4" t="n">
         <v>-6.582754629629633</v>
       </c>
-      <c r="W4" t="n">
-        <v>-23228472.22222222</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.2603361958818617</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>-4.822916666666657</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>2.408901312718086</v>
       </c>
-      <c r="AA4" t="n">
-        <v>-0.8981481481481477</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-2.436867981841857</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-10675560.09931385</v>
-      </c>
       <c r="AD4" t="n">
-        <v>-2.151501379060392</v>
+        <v>5.278356481481524</v>
       </c>
       <c r="AE4" t="n">
         <v>0.9503994360902297</v>
@@ -1168,37 +1168,37 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.778935185185162</v>
+        <v>-1036111.111111111</v>
       </c>
       <c r="U5" t="n">
         <v>-1.541666666666668</v>
       </c>
       <c r="V5" t="n">
+        <v>0.1050673217905496</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1.576698485861385</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-527661.9736612202</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.004629629629629539</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.6851613911757255</v>
+      </c>
+      <c r="AA5" t="n">
         <v>-1.625000000000014</v>
       </c>
-      <c r="W5" t="n">
-        <v>-1036111.111111111</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.1050673217905496</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>0.4166666666666572</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>0.6852096467857791</v>
       </c>
-      <c r="AA5" t="n">
-        <v>0.004629629629629539</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.6851613911757255</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-527661.9736612202</v>
-      </c>
       <c r="AD5" t="n">
-        <v>-1.576698485861385</v>
+        <v>-2.778935185185162</v>
       </c>
       <c r="AE5" t="n">
         <v>-1.282833491015992</v>
@@ -1306,37 +1306,37 @@
         <v>-1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.308207070707027</v>
+        <v>-53211254.20875421</v>
       </c>
       <c r="U6" t="n">
         <v>2.240446127946129</v>
       </c>
       <c r="V6" t="n">
+        <v>-1.739018428574349</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-8.721836734172271</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-57261198.95546704</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.542171717171717</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-10.77358227481584</v>
+      </c>
+      <c r="AA6" t="n">
         <v>-7.488173400673404</v>
       </c>
-      <c r="W6" t="n">
-        <v>-53211254.20875421</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.739018428574349</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>-9.462878787878807</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>0.8960641423635138</v>
       </c>
-      <c r="AA6" t="n">
-        <v>-1.542171717171717</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-10.77358227481584</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-57261198.95546704</v>
-      </c>
       <c r="AD6" t="n">
-        <v>-8.721836734172271</v>
+        <v>1.308207070707027</v>
       </c>
       <c r="AE6" t="n">
         <v>2.129850321462168</v>
@@ -1444,37 +1444,37 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.867708333333297</v>
+        <v>17979561.23737374</v>
       </c>
       <c r="U7" t="n">
         <v>-3.136458333333334</v>
       </c>
       <c r="V7" t="n">
+        <v>0.2682422098147215</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9457345087851508</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11186211.25158292</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3762941919191918</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.906691981105595</v>
+      </c>
+      <c r="AA7" t="n">
         <v>3.729135101010101</v>
       </c>
-      <c r="W7" t="n">
-        <v>17979561.23737374</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.2682422098147215</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>5.603124999999977</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>0.2910971227475443</v>
       </c>
-      <c r="AA7" t="n">
-        <v>0.3762941919191918</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.906691981105595</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11186211.25158292</v>
-      </c>
       <c r="AD7" t="n">
-        <v>0.9457345087851508</v>
+        <v>1.867708333333297</v>
       </c>
       <c r="AE7" t="n">
         <v>-4.51046917978411</v>
@@ -1582,40 +1582,40 @@
         <v>-2</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6892361111111143</v>
+        <v>-35803392.85714285</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.206597222222225</v>
+        <v>-3.332837301587304</v>
       </c>
       <c r="V8" t="n">
-        <v>-10.08159722222223</v>
+        <v>-1.229528378753207</v>
       </c>
       <c r="W8" t="n">
-        <v>-35668888.88888888</v>
+        <v>-8.178311490187951</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.239402116126945</v>
+        <v>-34956176.54664494</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.381944444444443</v>
+        <v>-1.59796626984127</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.1664886421422693</v>
+        <v>-8.913535035711803</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.595486111111111</v>
+        <v>-10.23189484126983</v>
       </c>
       <c r="AB8" t="n">
-        <v>-8.735777858678304</v>
+        <v>-8.29389880952381</v>
       </c>
       <c r="AC8" t="n">
-        <v>-35055056.96264707</v>
+        <v>0.05962512712937951</v>
       </c>
       <c r="AD8" t="n">
-        <v>-8.178752744839727</v>
+        <v>-0.6941964285714448</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.3225403346970808</v>
+        <v>0.4587943219379085</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.04722447691197695</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.580523000284018</v>
+      </c>
       <c r="X9" t="n">
-        <v>0.04722447691197695</v>
+        <v>6105587.759105681</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
+        <v>4.22146141236216</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
         <v>-0.4713968731432203</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="n">
-        <v>4.22146141236216</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6105587.759105681</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4.580523000284018</v>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
         <v>-0.5998769714762346</v>
       </c>
@@ -1842,37 +1842,37 @@
         <v>-1</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.331398809523847</v>
+        <v>-3528839.285714285</v>
       </c>
       <c r="U10" t="n">
         <v>-3.417063492063498</v>
       </c>
       <c r="V10" t="n">
+        <v>-0.499713564262124</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-2.549894942201277</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-6063772.852581156</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.008035714285714</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-4.83139505767636</v>
+      </c>
+      <c r="AA10" t="n">
         <v>-2.89771825396825</v>
       </c>
-      <c r="W10" t="n">
-        <v>-3528839.285714285</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.499713564262124</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>-1.542509920634942</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>-4.420193306155426</v>
       </c>
-      <c r="AA10" t="n">
-        <v>-1.008035714285714</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-4.83139505767636</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-6063772.852581156</v>
-      </c>
       <c r="AD10" t="n">
-        <v>-2.549894942201277</v>
+        <v>-5.331398809523847</v>
       </c>
       <c r="AE10" t="n">
         <v>1.029229816189705</v>
@@ -1980,37 +1980,37 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1567460317459961</v>
+        <v>4040674.603174603</v>
       </c>
       <c r="U11" t="n">
         <v>3.351851851851851</v>
       </c>
       <c r="V11" t="n">
+        <v>0.1910443722943722</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.046884214819016</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2979518.986448334</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3888888888888888</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.9335913482652671</v>
+      </c>
+      <c r="AA11" t="n">
         <v>3.785052910052912</v>
       </c>
-      <c r="W11" t="n">
-        <v>4040674.603174603</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1910443722943722</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>0.9660052910052883</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>-0.8949773354665069</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0.3888888888888888</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.9335913482652671</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2979518.986448334</v>
-      </c>
       <c r="AD11" t="n">
-        <v>3.046884214819016</v>
+        <v>0.1567460317459961</v>
       </c>
       <c r="AE11" t="n">
         <v>1.763488142292491</v>
@@ -2118,37 +2118,37 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3255952380952181</v>
+        <v>-13656706.34920635</v>
       </c>
       <c r="U12" t="n">
         <v>2.818650793650789</v>
       </c>
       <c r="V12" t="n">
+        <v>0.9011201577312842</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9128792883476819</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-4934973.836311791</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.521031746031746</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.853105022520083</v>
+      </c>
+      <c r="AA12" t="n">
         <v>-2.153174603174591</v>
       </c>
-      <c r="W12" t="n">
-        <v>-13656706.34920635</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.9011201577312842</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>-3.971031746031727</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>4.754544479405041</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0.521031746031746</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-1.853105022520083</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-4934973.836311791</v>
-      </c>
       <c r="AD12" t="n">
-        <v>0.9128792883476819</v>
+        <v>-0.3255952380952181</v>
       </c>
       <c r="AE12" t="n">
         <v>4.153374207711305</v>
@@ -2256,37 +2256,37 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6975308641974891</v>
+        <v>11175043.40277778</v>
       </c>
       <c r="U13" t="n">
         <v>-0.9961033950617271</v>
       </c>
       <c r="V13" t="n">
+        <v>0.2329739092606744</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.616392965014299</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7836670.359273762</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1936342592592595</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.505077517117954</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.742631172839495</v>
       </c>
-      <c r="W13" t="n">
-        <v>11175043.40277778</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.2329739092606744</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>2.854513888888889</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>-2.964161662139588</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0.1936342592592595</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.505077517117954</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7836670.359273762</v>
-      </c>
       <c r="AD13" t="n">
-        <v>3.616392965014299</v>
+        <v>-0.6975308641974891</v>
       </c>
       <c r="AE13" t="n">
         <v>0.6824135083326262</v>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,62 +525,62 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -761,40 +761,40 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>-21467361.1111111</v>
+        <v>-2.419444444444451</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5290895061728413</v>
+        <v>-1.161458333333333</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9643367566498202</v>
+        <v>-21506423.6111111</v>
       </c>
       <c r="W2" t="n">
-        <v>-4.041770926062227</v>
+        <v>-4.32085766176661</v>
       </c>
       <c r="X2" t="n">
-        <v>-27339071.97269149</v>
+        <v>-0.4923611111111121</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.188310185185185</v>
+        <v>-5.514267180244261</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5.481085751106946</v>
+        <v>-3.532638888888883</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.392785493827162</v>
+        <v>0.8888888888888857</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.464930555555554</v>
+        <v>1.32488093878419</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.263340021912427</v>
+        <v>1.462141300681566</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9673996913580254</v>
+        <v>-0.9712162129778061</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.651140094643594</v>
+        <v>-27772493.67217936</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -892,40 +892,40 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>53211254.20875421</v>
+        <v>7.441329966329974</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.240446127946129</v>
+        <v>1.543813131313131</v>
       </c>
       <c r="V3" t="n">
-        <v>1.739018428574349</v>
+        <v>53272491.58249159</v>
       </c>
       <c r="W3" t="n">
-        <v>8.721836734172271</v>
+        <v>8.775206975042508</v>
       </c>
       <c r="X3" t="n">
-        <v>57261198.95546704</v>
+        <v>-2.353198653198653</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.542171717171717</v>
+        <v>10.77279833653189</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.77358227481584</v>
+        <v>9.494823232323242</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.488173400673404</v>
+        <v>-1.056439393939371</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.462878787878807</v>
+        <v>-0.8567215405209083</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8960641423635138</v>
+        <v>-2.122968314580163</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.308207070707027</v>
+        <v>1.738151240207161</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.129850321462168</v>
+        <v>57290736.74406733</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1030,40 +1030,40 @@
         <v>-1</v>
       </c>
       <c r="T4" t="n">
+        <v>-6.582754629629633</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.8981481481481477</v>
+      </c>
+      <c r="V4" t="n">
         <v>-23228472.22222222</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-2.435763888888886</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.2603361958818617</v>
       </c>
       <c r="W4" t="n">
         <v>-2.151501379060392</v>
       </c>
       <c r="X4" t="n">
+        <v>-2.435763888888886</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-2.436867981841857</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-4.822916666666657</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.278356481481524</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.408901312718086</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9503994360902297</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.2603361958818617</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-10675560.09931385</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.8981481481481477</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-2.436867981841857</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-6.582754629629633</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-4.822916666666657</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.408901312718086</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>5.278356481481524</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.9503994360902297</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1168,40 +1168,40 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>-1.625000000000014</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.004629629629629539</v>
+      </c>
+      <c r="V5" t="n">
         <v>-1036111.111111111</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
+        <v>-1.47101967000863</v>
+      </c>
+      <c r="X5" t="n">
         <v>-1.541666666666668</v>
       </c>
-      <c r="V5" t="n">
-        <v>0.1050673217905496</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1.576698485861385</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-527661.9736612202</v>
-      </c>
       <c r="Y5" t="n">
-        <v>0.004629629629629539</v>
+        <v>0.7088429544311907</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6851613911757255</v>
+        <v>0.4166666666666572</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.625000000000014</v>
+        <v>-2.778935185185162</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4166666666666572</v>
+        <v>0.7229488648605695</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6852096467857791</v>
+        <v>-1.154303930682605</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.778935185185162</v>
+        <v>0.119714048206695</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.282833491015992</v>
+        <v>-488837.8917514947</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1306,40 +1306,40 @@
         <v>-1</v>
       </c>
       <c r="T6" t="n">
-        <v>-53211254.20875421</v>
+        <v>-7.441329966329974</v>
       </c>
       <c r="U6" t="n">
-        <v>2.240446127946129</v>
+        <v>-1.543813131313131</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.739018428574349</v>
+        <v>-53272491.58249159</v>
       </c>
       <c r="W6" t="n">
-        <v>-8.721836734172271</v>
+        <v>-8.775206975042508</v>
       </c>
       <c r="X6" t="n">
-        <v>-57261198.95546704</v>
+        <v>2.353198653198653</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.542171717171717</v>
+        <v>-10.77279833653189</v>
       </c>
       <c r="Z6" t="n">
-        <v>-10.77358227481584</v>
+        <v>-9.494823232323242</v>
       </c>
       <c r="AA6" t="n">
-        <v>-7.488173400673404</v>
+        <v>1.056439393939371</v>
       </c>
       <c r="AB6" t="n">
-        <v>-9.462878787878807</v>
+        <v>0.8567215405209083</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8960641423635138</v>
+        <v>2.122968314580163</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.308207070707027</v>
+        <v>-1.738151240207161</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.129850321462168</v>
+        <v>-57290736.74406733</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1444,40 +1444,40 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>3.729135101010101</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3762941919191918</v>
+      </c>
+      <c r="V7" t="n">
         <v>17979561.23737374</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-3.136458333333334</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.2682422098147215</v>
       </c>
       <c r="W7" t="n">
         <v>0.9457345087851508</v>
       </c>
       <c r="X7" t="n">
+        <v>-3.136458333333334</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.906691981105595</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.603124999999977</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.867708333333297</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2910971227475443</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-4.51046917978411</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.2682422098147215</v>
+      </c>
+      <c r="AE7" t="n">
         <v>11186211.25158292</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.3762941919191918</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.906691981105595</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.729135101010101</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>5.603124999999977</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.2910971227475443</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.867708333333297</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-4.51046917978411</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1582,40 +1582,40 @@
         <v>-2</v>
       </c>
       <c r="T8" t="n">
+        <v>-10.23189484126983</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.59796626984127</v>
+      </c>
+      <c r="V8" t="n">
         <v>-35803392.85714285</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-3.332837301587304</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.229528378753207</v>
       </c>
       <c r="W8" t="n">
         <v>-8.178311490187951</v>
       </c>
       <c r="X8" t="n">
+        <v>-3.332837301587304</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-8.913535035711803</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-8.29389880952381</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.6941964285714448</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.05962512712937951</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.4587943219379085</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.229528378753207</v>
+      </c>
+      <c r="AE8" t="n">
         <v>-34956176.54664494</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.59796626984127</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-8.913535035711803</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-10.23189484126983</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-8.29389880952381</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.05962512712937951</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.6941964285714448</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.4587943219379085</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1717,27 +1717,27 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>4.511213908640372</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>4.200855333392113</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>-0.6284451251362952</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.699943693969427</v>
+      </c>
+      <c r="AD9" t="n">
         <v>0.04722447691197695</v>
       </c>
-      <c r="W9" t="n">
-        <v>4.580523000284018</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6105587.759105681</v>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="n">
-        <v>4.22146141236216</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>-0.4713968731432203</v>
-      </c>
-      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>-0.5998769714762346</v>
+        <v>6111332.894025909</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1842,40 +1842,40 @@
         <v>-1</v>
       </c>
       <c r="T10" t="n">
+        <v>-2.89771825396825</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.008035714285714</v>
+      </c>
+      <c r="V10" t="n">
         <v>-3528839.285714285</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-3.417063492063498</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.499713564262124</v>
       </c>
       <c r="W10" t="n">
         <v>-2.549894942201277</v>
       </c>
       <c r="X10" t="n">
+        <v>-3.417063492063498</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-4.83139505767636</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.542509920634942</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-5.331398809523847</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-4.420193306155426</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.029229816189705</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.499713564262124</v>
+      </c>
+      <c r="AE10" t="n">
         <v>-6063772.852581156</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1.008035714285714</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-4.83139505767636</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-2.89771825396825</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-1.542509920634942</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-4.420193306155426</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-5.331398809523847</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.029229816189705</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1980,40 +1980,40 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
+        <v>3.785052910052912</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3888888888888888</v>
+      </c>
+      <c r="V11" t="n">
         <v>4040674.603174603</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.351851851851851</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.1910443722943722</v>
       </c>
       <c r="W11" t="n">
         <v>3.046884214819016</v>
       </c>
       <c r="X11" t="n">
+        <v>3.351851851851851</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.9335913482652671</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.9660052910052883</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1567460317459961</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.8949773354665069</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.763488142292491</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1910443722943722</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2979518.986448334</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.3888888888888888</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.9335913482652671</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.785052910052912</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.9660052910052883</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.8949773354665069</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.1567460317459961</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.763488142292491</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2118,40 +2118,40 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>-2.153174603174591</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.521031746031746</v>
+      </c>
+      <c r="V12" t="n">
         <v>-13656706.34920635</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.818650793650789</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.9011201577312842</v>
       </c>
       <c r="W12" t="n">
         <v>0.9128792883476819</v>
       </c>
       <c r="X12" t="n">
+        <v>2.818650793650789</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.853105022520083</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-3.971031746031727</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.3255952380952181</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.754544479405041</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.153374207711305</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9011201577312842</v>
+      </c>
+      <c r="AE12" t="n">
         <v>-4934973.836311791</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.521031746031746</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-1.853105022520083</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-2.153174603174591</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-3.971031746031727</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.754544479405041</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.3255952380952181</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>4.153374207711305</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2256,40 +2256,40 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>11175043.40277778</v>
+        <v>2.715972222222206</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9961033950617271</v>
+        <v>0.2204861111111112</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2329739092606744</v>
+        <v>11135980.90277778</v>
       </c>
       <c r="W13" t="n">
-        <v>3.616392965014299</v>
+        <v>3.337306229309917</v>
       </c>
       <c r="X13" t="n">
-        <v>7836670.359273762</v>
+        <v>-0.9593749999999979</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1936342592592595</v>
+        <v>2.471896087980639</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.505077517117954</v>
+        <v>2.78680555555556</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.742631172839495</v>
+        <v>-0.7760416666666288</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.854513888888889</v>
+        <v>-2.902620745267825</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.964161662139588</v>
+        <v>0.4934147143705978</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.6975308641974891</v>
+        <v>0.2260944529326885</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.6824135083326262</v>
+        <v>7403248.659785885</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,62 +525,62 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -761,40 +761,40 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>-21467361.1111111</v>
+        <v>-1.161458333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5290895061728413</v>
+        <v>-5.514267180244261</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9643367566498202</v>
+        <v>-0.4923611111111121</v>
       </c>
       <c r="W2" t="n">
-        <v>-4.041770926062227</v>
+        <v>1.32488093878419</v>
       </c>
       <c r="X2" t="n">
-        <v>-27339071.97269149</v>
+        <v>0.8888888888888857</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.188310185185185</v>
+        <v>1.462141300681566</v>
       </c>
       <c r="Z2" t="n">
-        <v>-5.481085751106946</v>
+        <v>-27772493.67217936</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.392785493827162</v>
+        <v>-3.532638888888883</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.464930555555554</v>
+        <v>-0.9712162129778061</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.263340021912427</v>
+        <v>-4.32085766176661</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9673996913580254</v>
+        <v>-21506423.6111111</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.651140094643594</v>
+        <v>-2.419444444444451</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -892,40 +892,40 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>53211254.20875421</v>
+        <v>1.543813131313131</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.240446127946129</v>
+        <v>10.77279833653189</v>
       </c>
       <c r="V3" t="n">
-        <v>1.739018428574349</v>
+        <v>-2.353198653198653</v>
       </c>
       <c r="W3" t="n">
-        <v>8.721836734172271</v>
+        <v>-0.8567215405209083</v>
       </c>
       <c r="X3" t="n">
-        <v>57261198.95546704</v>
+        <v>-1.056439393939371</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.542171717171717</v>
+        <v>-2.122968314580163</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.77358227481584</v>
+        <v>57290736.74406733</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.488173400673404</v>
+        <v>9.494823232323242</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.462878787878807</v>
+        <v>1.738151240207161</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8960641423635138</v>
+        <v>8.775206975042508</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.308207070707027</v>
+        <v>53272491.58249159</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.129850321462168</v>
+        <v>7.441329966329974</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -954,35 +954,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45531.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23000</v>
+        <v>14505</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1009,61 +1009,61 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="S4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>-23228472.22222222</v>
+        <v>-1.395833333333333</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.435763888888886</v>
+        <v>-9.882520045584968</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2603361958818617</v>
+        <v>3.137152777777775</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.151501379060392</v>
+        <v>-0.2293853251376277</v>
       </c>
       <c r="X4" t="n">
-        <v>-10675560.09931385</v>
+        <v>-2.027777777777771</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.8981481481481477</v>
+        <v>5.372321511122998</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.436867981841857</v>
+        <v>-35126973.43707177</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6.582754629629633</v>
+        <v>-9.041666666666657</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4.822916666666657</v>
+        <v>-0.9310865117751561</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.408901312718086</v>
+        <v>-4.805220334267844</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.278356481481524</v>
+        <v>-38190104.16666666</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9503994360902297</v>
+        <v>-5.878472222222214</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1092,35 +1092,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>27618</v>
+        <v>26020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1147,61 +1147,61 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>IilCZTta</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="Q5" t="n">
         <v>-2</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-1036111.111111111</v>
+        <v>-0.7585227272727275</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.541666666666668</v>
+        <v>-3.426756213212172</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1050673217905496</v>
+        <v>-0.4852272727272755</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.576698485861385</v>
+        <v>-2.345946626398245</v>
       </c>
       <c r="X5" t="n">
-        <v>-527661.9736612202</v>
+        <v>-2.004450757575796</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004629629629629539</v>
+        <v>1.804339190763177</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6851613911757255</v>
+        <v>-3964303.761090806</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.625000000000014</v>
+        <v>-2.551041666666663</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4166666666666572</v>
+        <v>-0.5125799993817224</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6852096467857791</v>
+        <v>-1.093367566965128</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.778935185185162</v>
+        <v>-4466205.808080807</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.282833491015992</v>
+        <v>-1.988825757575768</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1230,35 +1230,35 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45530.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26020</v>
+        <v>23000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1285,61 +1285,61 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>-53211254.20875421</v>
+        <v>0.12962962962963</v>
       </c>
       <c r="U6" t="n">
-        <v>2.240446127946129</v>
+        <v>1.811517911590471</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.739018428574349</v>
+        <v>-0.777777777777775</v>
       </c>
       <c r="W6" t="n">
-        <v>-8.721836734172271</v>
+        <v>3.143628812170846</v>
       </c>
       <c r="X6" t="n">
-        <v>-57261198.95546704</v>
+        <v>2.852513227513271</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.542171717171717</v>
+        <v>2.613205850522029</v>
       </c>
       <c r="Z6" t="n">
-        <v>-10.77358227481584</v>
+        <v>2505591.51523947</v>
       </c>
       <c r="AA6" t="n">
-        <v>-7.488173400673404</v>
+        <v>0.682142857142864</v>
       </c>
       <c r="AB6" t="n">
-        <v>-9.462878787878807</v>
+        <v>0.4534998927800784</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8960641423635138</v>
+        <v>2.828061945471958</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.308207070707027</v>
+        <v>1817658.730158731</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.129850321462168</v>
+        <v>0.5806878306878218</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1368,35 +1368,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45529.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40000</v>
+        <v>70460</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1428,56 +1428,56 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>A7v4ruhp</t>
         </is>
       </c>
       <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>17979561.23737374</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.136458333333334</v>
+        <v>0.6530505318069117</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2682422098147215</v>
+        <v>3.682986111111109</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9457345087851508</v>
+        <v>2.402982747256033</v>
       </c>
       <c r="X7" t="n">
-        <v>11186211.25158292</v>
+        <v>-2.509374999999977</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3762941919191918</v>
+        <v>2.997365236140219</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.906691981105595</v>
+        <v>4063482.522108767</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.729135101010101</v>
+        <v>0.9451388888888914</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.603124999999977</v>
+        <v>0.7851672853542635</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2910971227475443</v>
+        <v>3.459842053716983</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.867708333333297</v>
+        <v>8091805.555555556</v>
       </c>
       <c r="AE7" t="n">
-        <v>-4.51046917978411</v>
+        <v>3.653125000000003</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1506,35 +1506,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45529.59375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49430</v>
+        <v>19840</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1561,61 +1561,61 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-25</v>
+        <v>-4</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="S8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-35803392.85714285</v>
+        <v>-0.8710317460317458</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.332837301587304</v>
+        <v>-2.6758216873706</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.229528378753207</v>
+        <v>-4.145502645502642</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.178311490187951</v>
+        <v>-2.191311896135261</v>
       </c>
       <c r="X8" t="n">
-        <v>-34956176.54664494</v>
+        <v>0.08531746031749776</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.59796626984127</v>
+        <v>-4.582303528295377</v>
       </c>
       <c r="Z8" t="n">
-        <v>-8.913535035711803</v>
+        <v>-7162214.242581091</v>
       </c>
       <c r="AA8" t="n">
-        <v>-10.23189484126983</v>
+        <v>-1.554894179894191</v>
       </c>
       <c r="AB8" t="n">
-        <v>-8.29389880952381</v>
+        <v>-1.020833333333333</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.05962512712937951</v>
+        <v>-5.479484773982065</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.6941964285714448</v>
+        <v>-7338293.650793651</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4587943219379085</v>
+        <v>-5.142195767195773</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1644,35 +1644,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">alvendiz l 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23516</v>
+        <v>12454</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1699,46 +1699,50 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Qkg2vOrk</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1</v>
+      </c>
       <c r="R9" t="n">
-        <v>5</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.04722447691197695</v>
-      </c>
+      <c r="U9" t="n">
+        <v>-2.702676175075098</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>4.580523000284018</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6105587.759105681</v>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+        <v>3.056050078564226</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>0.2376479389502677</v>
+      </c>
       <c r="Z9" t="n">
-        <v>4.22146141236216</v>
+        <v>-3920682.739674807</v>
       </c>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>-0.1278139875671509</v>
+      </c>
       <c r="AC9" t="n">
-        <v>-0.4713968731432203</v>
+        <v>-4.725072917853112</v>
       </c>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="n">
-        <v>-0.5998769714762346</v>
-      </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
@@ -1766,35 +1770,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45529.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32392</v>
+        <v>83186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1821,61 +1825,61 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-4</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="S10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>-3528839.285714285</v>
+        <v>1.662373737373737</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.417063492063498</v>
+        <v>12.92492184619216</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.499713564262124</v>
+        <v>-0.06620370370369955</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.549894942201277</v>
+        <v>0.006600717286687541</v>
       </c>
       <c r="X10" t="n">
-        <v>-6063772.852581156</v>
+        <v>2.110290404040398</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.008035714285714</v>
+        <v>-0.7058655745913924</v>
       </c>
       <c r="Z10" t="n">
-        <v>-4.83139505767636</v>
+        <v>62718826.63722156</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.89771825396825</v>
+        <v>11.5517676767677</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.542509920634942</v>
+        <v>1.669038653447516</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.420193306155426</v>
+        <v>13.55647518599821</v>
       </c>
       <c r="AD10" t="n">
-        <v>-5.331398809523847</v>
+        <v>59898021.88552189</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.029229816189705</v>
+        <v>13.04069865319866</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1904,35 +1908,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24791</v>
+        <v>40000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1959,61 +1963,61 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="P11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7</v>
-      </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4040674.603174603</v>
+        <v>-0.5215488215488213</v>
       </c>
       <c r="U11" t="n">
-        <v>3.351851851851851</v>
+        <v>-6.496314675662504</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1910443722943722</v>
+        <v>1.245833333333334</v>
       </c>
       <c r="W11" t="n">
-        <v>3.046884214819016</v>
+        <v>-1.146638065507915</v>
       </c>
       <c r="X11" t="n">
-        <v>2979518.986448334</v>
+        <v>0.8018518518518931</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3888888888888888</v>
+        <v>2.489528256743728</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.9335913482652671</v>
+        <v>-13806125.69270238</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.785052910052912</v>
+        <v>-7.045833333333306</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9660052910052883</v>
+        <v>-0.591201622155906</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.8949773354665069</v>
+        <v>-4.376535560087362</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1567460317459961</v>
+        <v>-20724873.73737374</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.763488142292491</v>
+        <v>-7.282954545454544</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2042,35 +2046,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>60721</v>
+        <v>16500</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2097,61 +2101,61 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>A7v4ruhp</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T12" t="n">
-        <v>-13656706.34920635</v>
+        <v>0.01388888888888884</v>
       </c>
       <c r="U12" t="n">
-        <v>2.818650793650789</v>
+        <v>1.896356777360069</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9011201577312842</v>
+        <v>-2.670138888888889</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9128792883476819</v>
+        <v>4.456887009189643</v>
       </c>
       <c r="X12" t="n">
-        <v>-4934973.836311791</v>
+        <v>3.692708333333286</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.521031746031746</v>
+        <v>-4.40359492481203</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.853105022520083</v>
+        <v>-48768.89489348419</v>
       </c>
       <c r="AA12" t="n">
-        <v>-2.153174603174591</v>
+        <v>2.722222222222214</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3.971031746031727</v>
+        <v>-0.2662241541353385</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.754544479405041</v>
+        <v>-2.852943556808683</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.3255952380952181</v>
+        <v>5547699.65277778</v>
       </c>
       <c r="AE12" t="n">
-        <v>4.153374207711305</v>
+        <v>0.7430555555555571</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2180,35 +2184,28 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45519.58333333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>53331</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2235,61 +2232,61 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>AD5WKzFn</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>11175043.40277778</v>
+        <v>1.161458333333333</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9961033950617271</v>
+        <v>5.514267180244261</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2329739092606744</v>
+        <v>0.4923611111111121</v>
       </c>
       <c r="W13" t="n">
-        <v>3.616392965014299</v>
+        <v>-1.32488093878419</v>
       </c>
       <c r="X13" t="n">
-        <v>7836670.359273762</v>
+        <v>-0.8888888888888857</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1936342592592595</v>
+        <v>-1.462141300681566</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.505077517117954</v>
+        <v>27772493.67217936</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.742631172839495</v>
+        <v>3.532638888888883</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.854513888888889</v>
+        <v>0.9712162129778061</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.964161662139588</v>
+        <v>4.32085766176661</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.6975308641974891</v>
+        <v>21506423.6111111</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.6824135083326262</v>
+        <v>2.419444444444451</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2315,6 +2312,1784 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>13</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.03522727272727266</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.09354031385282724</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.9397727272727288</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3533582736707501</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.059090909090912</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.237405129592631</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>91181.06286075059</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3874999999999886</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.06772307553557555</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.670386384448889</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1591136.363636363</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1.196590909090901</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45527.6875</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>AD5WKzFn</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5252314814814814</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.9034625773459766</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.077777777777779</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1848956530552641</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1679398148148152</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-2.499829423569587</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2388399.745851336</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.316319444444446</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.01701671324517573</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.9437603125727776</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4054236.11111111</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.190046296296302</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45527.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2837301587301588</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.014134483937113</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.509920634920636</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.5408581111870774</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.043650793650812</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.237669457735254</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1218853.169856459</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.835714285714289</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.1021807359307358</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.461604579630915</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-948293.6507936511</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.992063492063494</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45523.6875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>148</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.8981481481481477</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-2.436867981841857</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-2.435763888888886</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.408901312718086</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.278356481481524</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.9503994360902297</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10675560.09931385</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-4.822916666666657</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.2603361958818617</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-2.151501379060392</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-23228472.22222222</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-6.582754629629633</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45523.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>IilCZTta</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.004629629629629539</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.7088429544311907</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.541666666666668</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.7229488648605695</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-2.778935185185162</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.154303930682605</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-488837.8917514947</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.4166666666666572</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.119714048206695</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.47101967000863</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1036111.111111111</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-1.625000000000014</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>-16</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.543813131313131</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-10.77279833653189</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.353198653198653</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.8567215405209083</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.056439393939371</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.122968314580163</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-57290736.74406733</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-9.494823232323242</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.738151240207161</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-8.775206975042508</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-53272491.58249159</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-7.441329966329974</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.3762941919191918</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.906691981105595</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-3.136458333333334</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.2910971227475443</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.867708333333297</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-4.51046917978411</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>11186211.25158292</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5.603124999999977</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2682422098147215</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.9457345087851508</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17979561.23737374</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.729135101010101</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>148</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>-25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-9</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.59796626984127</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-8.913535035711803</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-3.332837301587304</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.05962512712937951</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.6941964285714448</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.4587943219379085</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-34956176.54664494</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-8.29389880952381</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-1.229528378753207</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-8.178311490187951</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-35803392.85714285</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-10.23189484126983</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alvendiz l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>148</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Qkg2vOrk</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>4.200855333392113</v>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-0.6284451251362952</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>-0.699943693969427</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6111332.894025909</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>0.04722447691197695</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.511213908640372</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>148</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.008035714285714</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-4.83139505767636</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-3.417063492063498</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-4.420193306155426</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-5.331398809523847</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.029229816189705</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6063772.852581156</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-1.542509920634942</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.499713564262124</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-2.549894942201277</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-3528839.285714285</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-2.89771825396825</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>148</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.3888888888888888</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.9335913482652671</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.351851851851851</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.8949773354665069</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.1567460317459961</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.763488142292491</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2979518.986448334</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.9660052910052883</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.1910443722943722</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.046884214819016</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4040674.603174603</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3.785052910052912</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>148</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.521031746031746</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-1.853105022520083</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.818650793650789</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.754544479405041</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.3255952380952181</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4.153374207711305</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-4934973.836311791</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-3.971031746031727</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.9011201577312842</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.9128792883476819</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-13656706.34920635</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-2.153174603174591</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>148</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2204861111111112</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.471896087980639</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.9593749999999979</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-2.902620745267825</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.7760416666666288</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.4934147143705978</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7403248.659785885</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.78680555555556</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.2260944529326885</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.337306229309917</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>11135980.90277778</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.715972222222206</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,62 +525,62 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -761,25 +761,25 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
+        <v>-0.4923611111111121</v>
+      </c>
+      <c r="U2" t="n">
         <v>-1.161458333333333</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>-21506423.6111111</v>
+      </c>
+      <c r="W2" t="n">
         <v>-5.514267180244261</v>
       </c>
-      <c r="V2" t="n">
-        <v>-0.4923611111111121</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1.32488093878419</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
+        <v>-2.419444444444451</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.8888888888888857</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.462141300681566</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-27772493.67217936</v>
       </c>
       <c r="AA2" t="n">
         <v>-3.532638888888883</v>
@@ -791,10 +791,10 @@
         <v>-4.32085766176661</v>
       </c>
       <c r="AD2" t="n">
-        <v>-21506423.6111111</v>
+        <v>-27772493.67217936</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2.419444444444451</v>
+        <v>1.462141300681566</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -892,25 +892,25 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
+        <v>-2.353198653198653</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.543813131313131</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>53272491.58249159</v>
+      </c>
+      <c r="W3" t="n">
         <v>10.77279833653189</v>
       </c>
-      <c r="V3" t="n">
-        <v>-2.353198653198653</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>-0.8567215405209083</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
+        <v>7.441329966329974</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-1.056439393939371</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2.122968314580163</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>57290736.74406733</v>
       </c>
       <c r="AA3" t="n">
         <v>9.494823232323242</v>
@@ -922,10 +922,10 @@
         <v>8.775206975042508</v>
       </c>
       <c r="AD3" t="n">
-        <v>53272491.58249159</v>
+        <v>57290736.74406733</v>
       </c>
       <c r="AE3" t="n">
-        <v>7.441329966329974</v>
+        <v>-2.122968314580163</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -954,35 +954,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45527.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1009,61 +1009,61 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>AD5WKzFn</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-18</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>-6</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.395833333333333</v>
+        <v>2.077777777777779</v>
       </c>
       <c r="U4" t="n">
-        <v>-9.882520045584968</v>
+        <v>0.5252314814814814</v>
       </c>
       <c r="V4" t="n">
-        <v>3.137152777777775</v>
+        <v>4054236.11111111</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2293853251376277</v>
+        <v>0.9034625773459766</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.027777777777771</v>
+        <v>0.1848956530552641</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.372321511122998</v>
+        <v>2.190046296296302</v>
       </c>
       <c r="Z4" t="n">
-        <v>-35126973.43707177</v>
+        <v>-0.1679398148148152</v>
       </c>
       <c r="AA4" t="n">
-        <v>-9.041666666666657</v>
+        <v>1.316319444444446</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.9310865117751561</v>
+        <v>-0.01701671324517573</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.805220334267844</v>
+        <v>-0.9437603125727776</v>
       </c>
       <c r="AD4" t="n">
-        <v>-38190104.16666666</v>
+        <v>2388399.745851336</v>
       </c>
       <c r="AE4" t="n">
-        <v>-5.878472222222214</v>
+        <v>-2.499829423569587</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1092,35 +1092,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26020</v>
+        <v>24791</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1147,61 +1147,61 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>-11</v>
       </c>
       <c r="Q5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S5" t="n">
         <v>-2</v>
       </c>
-      <c r="R5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
       <c r="T5" t="n">
-        <v>-0.7585227272727275</v>
+        <v>4.509920634920636</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.426756213212172</v>
+        <v>0.2837301587301588</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4852272727272755</v>
+        <v>-948293.6507936511</v>
       </c>
       <c r="W5" t="n">
-        <v>-2.345946626398245</v>
+        <v>1.014134483937113</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.004450757575796</v>
+        <v>-0.5408581111870774</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.804339190763177</v>
+        <v>3.992063492063494</v>
       </c>
       <c r="Z5" t="n">
-        <v>-3964303.761090806</v>
+        <v>1.043650793650812</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2.551041666666663</v>
+        <v>0.835714285714289</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.5125799993817224</v>
+        <v>0.1021807359307358</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.093367566965128</v>
+        <v>2.461604579630915</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4466205.808080807</v>
+        <v>1218853.169856459</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.988825757575768</v>
+        <v>1.237669457735254</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1230,15 +1230,15 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45523.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1290,56 +1290,56 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.12962962962963</v>
+        <v>-2.435763888888886</v>
       </c>
       <c r="U6" t="n">
-        <v>1.811517911590471</v>
+        <v>-0.8981481481481477</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.777777777777775</v>
+        <v>-23228472.22222222</v>
       </c>
       <c r="W6" t="n">
-        <v>3.143628812170846</v>
+        <v>-2.436867981841857</v>
       </c>
       <c r="X6" t="n">
-        <v>2.852513227513271</v>
+        <v>2.408901312718086</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.613205850522029</v>
+        <v>-6.582754629629633</v>
       </c>
       <c r="Z6" t="n">
-        <v>2505591.51523947</v>
+        <v>5.278356481481524</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.682142857142864</v>
+        <v>-4.822916666666657</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4534998927800784</v>
+        <v>-0.2603361958818617</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.828061945471958</v>
+        <v>-2.151501379060392</v>
       </c>
       <c r="AD6" t="n">
-        <v>1817658.730158731</v>
+        <v>-10675560.09931385</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.5806878306878218</v>
+        <v>0.9503994360902297</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1368,35 +1368,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45523.58333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70460</v>
+        <v>27618</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1423,61 +1423,61 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>IilCZTta</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>A7v4ruhp</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.066666666666667</v>
+        <v>-1.541666666666668</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6530505318069117</v>
+        <v>0.004629629629629539</v>
       </c>
       <c r="V7" t="n">
-        <v>3.682986111111109</v>
+        <v>-1036111.111111111</v>
       </c>
       <c r="W7" t="n">
-        <v>2.402982747256033</v>
+        <v>0.7088429544311907</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.509374999999977</v>
+        <v>0.7229488648605695</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.997365236140219</v>
+        <v>-1.625000000000014</v>
       </c>
       <c r="Z7" t="n">
-        <v>4063482.522108767</v>
+        <v>-2.778935185185162</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9451388888888914</v>
+        <v>0.4166666666666572</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7851672853542635</v>
+        <v>0.119714048206695</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.459842053716983</v>
+        <v>-1.47101967000863</v>
       </c>
       <c r="AD7" t="n">
-        <v>8091805.555555556</v>
+        <v>-488837.8917514947</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.653125000000003</v>
+        <v>-1.154303930682605</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1506,11 +1506,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45522.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,21 +1520,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19840</v>
+        <v>26020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1570,52 +1570,52 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>-16</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-4</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S8" t="n">
         <v>-1</v>
       </c>
-      <c r="R8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
-        <v>-0.8710317460317458</v>
+        <v>2.353198653198653</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.6758216873706</v>
+        <v>-1.543813131313131</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.145502645502642</v>
+        <v>-53272491.58249159</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.191311896135261</v>
+        <v>-10.77279833653189</v>
       </c>
       <c r="X8" t="n">
-        <v>0.08531746031749776</v>
+        <v>0.8567215405209083</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.582303528295377</v>
+        <v>-7.441329966329974</v>
       </c>
       <c r="Z8" t="n">
-        <v>-7162214.242581091</v>
+        <v>1.056439393939371</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.554894179894191</v>
+        <v>-9.494823232323242</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.020833333333333</v>
+        <v>-1.738151240207161</v>
       </c>
       <c r="AC8" t="n">
-        <v>-5.479484773982065</v>
+        <v>-8.775206975042508</v>
       </c>
       <c r="AD8" t="n">
-        <v>-7338293.650793651</v>
+        <v>-57290736.74406733</v>
       </c>
       <c r="AE8" t="n">
-        <v>-5.142195767195773</v>
+        <v>2.122968314580163</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1644,35 +1644,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45522.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12454</v>
+        <v>40000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1699,50 +1699,62 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-3.136458333333334</v>
+      </c>
       <c r="U9" t="n">
-        <v>-2.702676175075098</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
+        <v>0.3762941919191918</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17979561.23737374</v>
+      </c>
       <c r="W9" t="n">
-        <v>3.056050078564226</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
+        <v>4.906691981105595</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.2910971227475443</v>
+      </c>
       <c r="Y9" t="n">
-        <v>0.2376479389502677</v>
+        <v>3.729135101010101</v>
       </c>
       <c r="Z9" t="n">
-        <v>-3920682.739674807</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
+        <v>1.867708333333297</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.603124999999977</v>
+      </c>
       <c r="AB9" t="n">
-        <v>-0.1278139875671509</v>
+        <v>0.2682422098147215</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.725072917853112</v>
-      </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+        <v>0.9457345087851508</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11186211.25158292</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-4.51046917978411</v>
+      </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
@@ -1770,35 +1782,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45529.5</v>
+        <v>45521.6875</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>83186</v>
+        <v>49430</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1825,61 +1837,61 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>-25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="R10" t="n">
-        <v>18</v>
+        <v>-9</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.662373737373737</v>
+        <v>-3.332837301587304</v>
       </c>
       <c r="U10" t="n">
-        <v>12.92492184619216</v>
+        <v>-1.59796626984127</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.06620370370369955</v>
+        <v>-35803392.85714285</v>
       </c>
       <c r="W10" t="n">
-        <v>0.006600717286687541</v>
+        <v>-8.913535035711803</v>
       </c>
       <c r="X10" t="n">
-        <v>2.110290404040398</v>
+        <v>0.05962512712937951</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.7058655745913924</v>
+        <v>-10.23189484126983</v>
       </c>
       <c r="Z10" t="n">
-        <v>62718826.63722156</v>
+        <v>-0.6941964285714448</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.5517676767677</v>
+        <v>-8.29389880952381</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.669038653447516</v>
+        <v>-1.229528378753207</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.55647518599821</v>
+        <v>-8.178311490187951</v>
       </c>
       <c r="AD10" t="n">
-        <v>59898021.88552189</v>
+        <v>-34956176.54664494</v>
       </c>
       <c r="AE10" t="n">
-        <v>13.04069865319866</v>
+        <v>0.4587943219379085</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1908,35 +1920,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">alvendiz l 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>23516</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1963,61 +1975,45 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>Qkg2vOrk</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.5215488215488213</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-6.496314675662504</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.245833333333334</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>-1.146638065507915</v>
+        <v>4.200855333392113</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8018518518518931</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.489528256743728</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-13806125.69270238</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-7.045833333333306</v>
-      </c>
+        <v>-0.6284451251362952</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>-0.591201622155906</v>
+        <v>0.04722447691197695</v>
       </c>
       <c r="AC11" t="n">
-        <v>-4.376535560087362</v>
+        <v>4.511213908640372</v>
       </c>
       <c r="AD11" t="n">
-        <v>-20724873.73737374</v>
+        <v>6111332.894025909</v>
       </c>
       <c r="AE11" t="n">
-        <v>-7.282954545454544</v>
+        <v>-0.699943693969427</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2046,35 +2042,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>hnqZAAAk</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45520.6875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>16500</v>
+        <v>32392</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2101,12 +2097,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2122,40 +2118,40 @@
         <v>-1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01388888888888884</v>
+        <v>-3.417063492063498</v>
       </c>
       <c r="U12" t="n">
-        <v>1.896356777360069</v>
+        <v>-1.008035714285714</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.670138888888889</v>
+        <v>-3528839.285714285</v>
       </c>
       <c r="W12" t="n">
-        <v>4.456887009189643</v>
+        <v>-4.83139505767636</v>
       </c>
       <c r="X12" t="n">
-        <v>3.692708333333286</v>
+        <v>-4.420193306155426</v>
       </c>
       <c r="Y12" t="n">
-        <v>-4.40359492481203</v>
+        <v>-2.89771825396825</v>
       </c>
       <c r="Z12" t="n">
-        <v>-48768.89489348419</v>
+        <v>-5.331398809523847</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.722222222222214</v>
+        <v>-1.542509920634942</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2662241541353385</v>
+        <v>-0.499713564262124</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.852943556808683</v>
+        <v>-2.549894942201277</v>
       </c>
       <c r="AD12" t="n">
-        <v>5547699.65277778</v>
+        <v>-6063772.852581156</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.7430555555555571</v>
+        <v>1.029229816189705</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2184,28 +2180,35 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>nDzACNof</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45520.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24791</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2232,61 +2235,61 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.161458333333333</v>
+        <v>3.351851851851851</v>
       </c>
       <c r="U13" t="n">
-        <v>5.514267180244261</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4923611111111121</v>
+        <v>4040674.603174603</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.32488093878419</v>
+        <v>0.9335913482652671</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8888888888888857</v>
+        <v>-0.8949773354665069</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.462141300681566</v>
+        <v>3.785052910052912</v>
       </c>
       <c r="Z13" t="n">
-        <v>27772493.67217936</v>
+        <v>0.1567460317459961</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.532638888888883</v>
+        <v>0.9660052910052883</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9712162129778061</v>
+        <v>0.1910443722943722</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.32085766176661</v>
+        <v>3.046884214819016</v>
       </c>
       <c r="AD13" t="n">
-        <v>21506423.6111111</v>
+        <v>2979518.986448334</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.419444444444451</v>
+        <v>1.763488142292491</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2315,35 +2318,35 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>QyafIhIF</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45519.6875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23516</v>
+        <v>60721</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2370,61 +2373,61 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>A7v4ruhp</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03522727272727266</v>
+        <v>2.818650793650789</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09354031385282724</v>
+        <v>0.521031746031746</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9397727272727288</v>
+        <v>-13656706.34920635</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3533582736707501</v>
+        <v>-1.853105022520083</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.059090909090912</v>
+        <v>4.754544479405041</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.237405129592631</v>
+        <v>-2.153174603174591</v>
       </c>
       <c r="Z14" t="n">
-        <v>91181.06286075059</v>
+        <v>-0.3255952380952181</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3874999999999886</v>
+        <v>-3.971031746031727</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.06772307553557555</v>
+        <v>0.9011201577312842</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1.670386384448889</v>
+        <v>0.9128792883476819</v>
       </c>
       <c r="AD14" t="n">
-        <v>1591136.363636363</v>
+        <v>-4934973.836311791</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.196590909090901</v>
+        <v>4.153374207711305</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2453,35 +2456,35 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45519.58333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>42714</v>
+        <v>53331</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2508,61 +2511,61 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>p2dFnNso</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5252314814814814</v>
+        <v>-0.9593749999999979</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9034625773459766</v>
+        <v>0.2204861111111112</v>
       </c>
       <c r="V15" t="n">
-        <v>2.077777777777779</v>
+        <v>11135980.90277778</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1848956530552641</v>
+        <v>2.471896087980639</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1679398148148152</v>
+        <v>-2.902620745267825</v>
       </c>
       <c r="Y15" t="n">
-        <v>-2.499829423569587</v>
+        <v>2.715972222222206</v>
       </c>
       <c r="Z15" t="n">
-        <v>2388399.745851336</v>
+        <v>-0.7760416666666288</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.316319444444446</v>
+        <v>2.78680555555556</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.01701671324517573</v>
+        <v>0.2260944529326885</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.9437603125727776</v>
+        <v>3.337306229309917</v>
       </c>
       <c r="AD15" t="n">
-        <v>4054236.11111111</v>
+        <v>7403248.659785885</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.190046296296302</v>
+        <v>0.4934147143705978</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2588,1508 +2591,6 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45527.58333333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>148</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>-11</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.2837301587301588</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.014134483937113</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.509920634920636</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-0.5408581111870774</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.043650793650812</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.237669457735254</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1218853.169856459</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.835714285714289</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.1021807359307358</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.461604579630915</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-948293.6507936511</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>3.992063492063494</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>E1Xs9lu2</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45523.6875</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>148</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.8981481481481477</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-2.436867981841857</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-2.435763888888886</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.408901312718086</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.278356481481524</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.9503994360902297</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-10675560.09931385</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-4.822916666666657</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-0.2603361958818617</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-2.151501379060392</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-23228472.22222222</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-6.582754629629633</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ITdtTrn2</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45523.58333333334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vega a  c 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>148</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>IilCZTta</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.004629629629629539</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.7088429544311907</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1.541666666666668</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.7229488648605695</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.778935185185162</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-1.154303930682605</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-488837.8917514947</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.4166666666666572</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.119714048206695</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-1.47101967000863</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-1036111.111111111</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>-1.625000000000014</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>M3h3GWnS</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45522.6875</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>148</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>-16</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-1.543813131313131</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-10.77279833653189</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.353198653198653</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.8567215405209083</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.056439393939371</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.122968314580163</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-57290736.74406733</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-9.494823232323242</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-1.738151240207161</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-8.775206975042508</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-53272491.58249159</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>-7.441329966329974</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Eax2EqHs</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45522.58333333334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>148</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.3762941919191918</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.906691981105595</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-3.136458333333334</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.2910971227475443</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.867708333333297</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>-4.51046917978411</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>11186211.25158292</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5.603124999999977</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.2682422098147215</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.9457345087851508</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17979561.23737374</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>3.729135101010101</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KbKTWiX8</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45521.6875</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villanueva j  i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>148</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>-25</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-9</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-1.59796626984127</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-8.913535035711803</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-3.332837301587304</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.05962512712937951</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.6941964285714448</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.4587943219379085</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>-34956176.54664494</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-8.29389880952381</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-1.229528378753207</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>-8.178311490187951</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-35803392.85714285</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>-10.23189484126983</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>ruUIA1G6</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45521.58333333334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alvendiz l 
-  esp </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>148</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Qkg2vOrk</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>5</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="n">
-        <v>4.200855333392113</v>
-      </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="n">
-        <v>-0.6284451251362952</v>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="n">
-        <v>-0.699943693969427</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6111332.894025909</v>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="n">
-        <v>0.04722447691197695</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.511213908640372</v>
-      </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hnqZAAAk</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45520.6875</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villanueva j  i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>32392</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>148</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-1.008035714285714</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-4.83139505767636</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-3.417063492063498</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-4.420193306155426</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-5.331398809523847</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.029229816189705</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-6063772.852581156</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-1.542509920634942</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.499713564262124</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-2.549894942201277</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>-3528839.285714285</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-2.89771825396825</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>nDzACNof</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45520.58333333334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maeso f 
-  esp </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>148</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.3888888888888888</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.9335913482652671</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.351851851851851</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-0.8949773354665069</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.1567460317459961</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.763488142292491</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2979518.986448334</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.9660052910052883</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.1910443722943722</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.046884214819016</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4040674.603174603</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>3.785052910052912</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>QyafIhIF</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45519.6875</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>148</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>A7v4ruhp</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.521031746031746</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-1.853105022520083</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.818650793650789</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4.754544479405041</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-0.3255952380952181</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>4.153374207711305</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-4934973.836311791</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>-3.971031746031727</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0.9011201577312842</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.9128792883476819</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-13656706.34920635</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>-2.153174603174591</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>hO0nKEm3</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45519.58333333334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>148</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>p2dFnNso</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.2204861111111112</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.471896087980639</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-0.9593749999999979</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-2.902620745267825</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-0.7760416666666288</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.4934147143705978</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>7403248.659785885</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.78680555555556</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.2260944529326885</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.337306229309917</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>11135980.90277778</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.715972222222206</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,57 +525,57 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -761,40 +761,40 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4923611111111121</v>
+        <v>-3.32664141414142</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.161458333333333</v>
+        <v>-4.876545828649739</v>
       </c>
       <c r="V2" t="n">
-        <v>-21506423.6111111</v>
+        <v>1.336111111111109</v>
       </c>
       <c r="W2" t="n">
-        <v>-5.514267180244261</v>
+        <v>-2.893694456279775</v>
       </c>
       <c r="X2" t="n">
-        <v>1.32488093878419</v>
+        <v>0.9902171695628681</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.419444444444451</v>
+        <v>-2.288131313131331</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8888888888888857</v>
+        <v>-1.237247474747475</v>
       </c>
       <c r="AA2" t="n">
-        <v>-3.532638888888883</v>
+        <v>-0.6672979797979792</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.9712162129778061</v>
+        <v>-22687674.4741646</v>
       </c>
       <c r="AC2" t="n">
-        <v>-4.32085766176661</v>
+        <v>-20563876.26262626</v>
       </c>
       <c r="AD2" t="n">
-        <v>-27772493.67217936</v>
+        <v>-0.8427141374922797</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.462141300681566</v>
+        <v>1.864397889332054</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -892,40 +892,40 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.353198653198653</v>
+        <v>9.694128787878796</v>
       </c>
       <c r="U3" t="n">
-        <v>1.543813131313131</v>
+        <v>10.64862560426756</v>
       </c>
       <c r="V3" t="n">
-        <v>53272491.58249159</v>
+        <v>-1.630707644628103</v>
       </c>
       <c r="W3" t="n">
-        <v>10.77279833653189</v>
+        <v>8.52165666898523</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8567215405209083</v>
+        <v>-0.9058584328719803</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.441329966329974</v>
+        <v>7.873120408631777</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.056439393939371</v>
+        <v>1.518267906336088</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.494823232323242</v>
+        <v>-2.242455808080813</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.738151240207161</v>
+        <v>55620288.03105158</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.775206975042508</v>
+        <v>53827586.6620753</v>
       </c>
       <c r="AD3" t="n">
-        <v>57290736.74406733</v>
+        <v>1.727284665980838</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.122968314580163</v>
+        <v>-2.15857352081435</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -954,35 +954,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45529.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42714</v>
+        <v>19840</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1009,61 +1009,61 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.077777777777779</v>
+        <v>-1.706790123456798</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5252314814814814</v>
+        <v>-2.871234550473673</v>
       </c>
       <c r="V4" t="n">
-        <v>4054236.11111111</v>
+        <v>0.06018518518521887</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9034625773459766</v>
+        <v>-5.401178006775837</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1848956530552641</v>
+        <v>-2.845776789635465</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.190046296296302</v>
+        <v>-5.35956790123457</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1679398148148152</v>
+        <v>-0.8719135802469136</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.316319444444446</v>
+        <v>-4.1358024691358</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.01701671324517573</v>
+        <v>-6744724.857268337</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.9437603125727776</v>
+        <v>-8074228.395061728</v>
       </c>
       <c r="AD4" t="n">
-        <v>2388399.745851336</v>
+        <v>-1.023333333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.499829423569587</v>
+        <v>-4.658901985695465</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1092,35 +1092,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45527.58333333334</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24791</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1147,61 +1147,49 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.509920634920636</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>0.2837301587301588</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-948293.6507936511</v>
-      </c>
+        <v>-2.851841390753165</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1.014134483937113</v>
+        <v>-5.092905948269802</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5408581111870774</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.992063492063494</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.043650793650812</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.835714285714289</v>
-      </c>
+        <v>2.737127180689953</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0.1021807359307358</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.461604579630915</v>
-      </c>
+        <v>-4093510.271743448</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>1218853.169856459</v>
+        <v>-0.1322511900537209</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.237669457735254</v>
+        <v>-0.246940785237161</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1230,35 +1218,35 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45529.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23000</v>
+        <v>83186</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1285,61 +1273,61 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.435763888888886</v>
+        <v>11.6410563973064</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8981481481481477</v>
+        <v>12.75337355116122</v>
       </c>
       <c r="V6" t="n">
-        <v>-23228472.22222222</v>
+        <v>1.716066919191888</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.436867981841857</v>
+        <v>13.0254831770731</v>
       </c>
       <c r="X6" t="n">
-        <v>2.408901312718086</v>
+        <v>-0.647612277165905</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.582754629629633</v>
+        <v>13.17530513468014</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.278356481481524</v>
+        <v>1.597874579124579</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.822916666666657</v>
+        <v>-0.4044086700336678</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.2603361958818617</v>
+        <v>60830890.92254016</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.151501379060392</v>
+        <v>60235043.13973065</v>
       </c>
       <c r="AD6" t="n">
-        <v>-10675560.09931385</v>
+        <v>1.652809220649778</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9503994360902297</v>
+        <v>-0.7786833643032054</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1368,35 +1356,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27618</v>
+        <v>40000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1423,12 +1411,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>IilCZTta</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1438,46 +1426,46 @@
         <v>-2</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.541666666666668</v>
+        <v>-7.188535353535343</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004629629629629539</v>
+        <v>-6.371491137938165</v>
       </c>
       <c r="V7" t="n">
-        <v>-1036111.111111111</v>
+        <v>1.3085858585859</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7088429544311907</v>
+        <v>-3.80204795297945</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7229488648605695</v>
+        <v>-1.084363377014427</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.625000000000014</v>
+        <v>-7.474898989898975</v>
       </c>
       <c r="Z7" t="n">
-        <v>-2.778935185185162</v>
+        <v>-0.5764646464646463</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4166666666666572</v>
+        <v>1.073232323232322</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.119714048206695</v>
+        <v>-12923912.95998865</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.47101967000863</v>
+        <v>-21849015.15151515</v>
       </c>
       <c r="AD7" t="n">
-        <v>-488837.8917514947</v>
+        <v>-0.5557941256402732</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.154303930682605</v>
+        <v>2.842057195654938</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1506,35 +1494,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26020</v>
+        <v>16500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1566,56 +1554,56 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="R8" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="S8" t="n">
         <v>-1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.353198653198653</v>
+        <v>2.746874999999989</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.543813131313131</v>
+        <v>1.880894945697577</v>
       </c>
       <c r="V8" t="n">
-        <v>-53272491.58249159</v>
+        <v>3.918055555555497</v>
       </c>
       <c r="W8" t="n">
-        <v>-10.77279833653189</v>
+        <v>-2.599973893065993</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8567215405209083</v>
+        <v>4.198366750208891</v>
       </c>
       <c r="Y8" t="n">
-        <v>-7.441329966329974</v>
+        <v>0.79131944444444</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.056439393939371</v>
+        <v>0.05312500000000009</v>
       </c>
       <c r="AA8" t="n">
-        <v>-9.494823232323242</v>
+        <v>-2.417013888888892</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.738151240207161</v>
+        <v>139508.6936090225</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8.775206975042508</v>
+        <v>5431484.375000002</v>
       </c>
       <c r="AD8" t="n">
-        <v>-57290736.74406733</v>
+        <v>-0.2967888471177944</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.122968314580163</v>
+        <v>-4.446685463659151</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1644,11 +1632,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1656,23 +1644,16 @@
   esp </t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>40000</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1699,7 +1680,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>AD5WKzFn</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1708,52 +1689,52 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
+        <v>30</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
       <c r="T9" t="n">
-        <v>-3.136458333333334</v>
+        <v>3.32664141414142</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3762941919191918</v>
+        <v>4.876545828649739</v>
       </c>
       <c r="V9" t="n">
-        <v>17979561.23737374</v>
+        <v>-1.336111111111109</v>
       </c>
       <c r="W9" t="n">
-        <v>4.906691981105595</v>
+        <v>2.893694456279775</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2910971227475443</v>
+        <v>-0.9902171695628681</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.729135101010101</v>
+        <v>2.288131313131331</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.867708333333297</v>
+        <v>1.237247474747475</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.603124999999977</v>
+        <v>0.6672979797979792</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2682422098147215</v>
+        <v>22687674.4741646</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.9457345087851508</v>
+        <v>20563876.26262626</v>
       </c>
       <c r="AD9" t="n">
-        <v>11186211.25158292</v>
+        <v>0.8427141374922797</v>
       </c>
       <c r="AE9" t="n">
-        <v>-4.51046917978411</v>
+        <v>-1.864397889332054</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1782,35 +1763,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45528.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49430</v>
+        <v>23516</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1837,61 +1818,61 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>p2dFnNso</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-25</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-9</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.332837301587304</v>
+        <v>0.3424242424242436</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.59796626984127</v>
+        <v>0.3296731467186191</v>
       </c>
       <c r="V10" t="n">
-        <v>-35803392.85714285</v>
+        <v>0.06294765840220862</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.913535035711803</v>
+        <v>-1.31710709324345</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05962512712937951</v>
+        <v>0.2032777688080785</v>
       </c>
       <c r="Y10" t="n">
-        <v>-10.23189484126983</v>
+        <v>-0.4433884297520621</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.6941964285714448</v>
+        <v>-0.1027548209366389</v>
       </c>
       <c r="AA10" t="n">
-        <v>-8.29389880952381</v>
+        <v>-0.3287878787878817</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.229528378753207</v>
+        <v>474474.8682153989</v>
       </c>
       <c r="AC10" t="n">
-        <v>-8.178311490187951</v>
+        <v>1598388.429752065</v>
       </c>
       <c r="AD10" t="n">
-        <v>-34956176.54664494</v>
+        <v>-0.04724911732487502</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4587943219379085</v>
+        <v>-1.160647867844837</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1920,35 +1901,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45527.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">alvendiz l 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23516</v>
+        <v>42714</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1975,45 +1956,61 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>AD5WKzFn</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Qkg2vOrk</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>1.289166666666674</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.067305086031368</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.8325000000000387</v>
+      </c>
       <c r="W11" t="n">
-        <v>4.200855333392113</v>
+        <v>-0.6154249167248906</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6284451251362952</v>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+        <v>0.2944744934586652</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.239999999999995</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5377777777777777</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.881666666666664</v>
+      </c>
       <c r="AB11" t="n">
-        <v>0.04722447691197695</v>
+        <v>2443062.79185015</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.511213908640372</v>
+        <v>4566166.666666668</v>
       </c>
       <c r="AD11" t="n">
-        <v>6111332.894025909</v>
+        <v>-0.01524380537874936</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.699943693969427</v>
+        <v>-2.321451703106877</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2042,35 +2039,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>32392</v>
+        <v>24791</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2097,61 +2094,61 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R12" t="n">
         <v>-1</v>
       </c>
       <c r="S12" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.417063492063498</v>
+        <v>1.048456790123439</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.008035714285714</v>
+        <v>0.5223501591444091</v>
       </c>
       <c r="V12" t="n">
-        <v>-3528839.285714285</v>
+        <v>0.5785493827160337</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.83139505767636</v>
+        <v>2.638409729558063</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.420193306155426</v>
+        <v>-0.2728977056967494</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.89771825396825</v>
+        <v>3.57037037037037</v>
       </c>
       <c r="Z12" t="n">
-        <v>-5.331398809523847</v>
+        <v>0.2788580246913579</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.542509920634942</v>
+        <v>4.149074074074068</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.499713564262124</v>
+        <v>1400889.74157156</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.549894942201277</v>
+        <v>-1133086.419753088</v>
       </c>
       <c r="AD12" t="n">
-        <v>-6063772.852581156</v>
+        <v>0.09820739866194406</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.029229816189705</v>
+        <v>1.710747806154508</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2180,35 +2177,35 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45523.6875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>24791</v>
+        <v>23000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2235,61 +2232,61 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T13" t="n">
-        <v>3.351851851851851</v>
+        <v>-4.892901234567901</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3888888888888888</v>
+        <v>-2.528522163251267</v>
       </c>
       <c r="V13" t="n">
-        <v>4040674.603174603</v>
+        <v>5.713888888888931</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9335913482652671</v>
+        <v>-2.424117769914972</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8949773354665069</v>
+        <v>2.448509939063371</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.785052910052912</v>
+        <v>-6.36666666666666</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1567460317459961</v>
+        <v>-0.8981481481481481</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9660052910052883</v>
+        <v>-1.907098765432099</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1910443722943722</v>
+        <v>-10772003.63500663</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.046884214819016</v>
+        <v>-23546882.71604938</v>
       </c>
       <c r="AD13" t="n">
-        <v>2979518.986448334</v>
+        <v>-0.363546734483267</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.763488142292491</v>
+        <v>0.5376806599832946</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2318,35 +2315,35 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45523.58333333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60721</v>
+        <v>27618</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2373,61 +2370,61 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>IilCZTta</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>A7v4ruhp</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>-7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.818650793650789</v>
+        <v>0.285648148148141</v>
       </c>
       <c r="U14" t="n">
-        <v>0.521031746031746</v>
+        <v>0.7782221369997302</v>
       </c>
       <c r="V14" t="n">
-        <v>-13656706.34920635</v>
+        <v>-2.870833333333337</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.853105022520083</v>
+        <v>-1.438561790537904</v>
       </c>
       <c r="X14" t="n">
-        <v>4.754544479405041</v>
+        <v>0.8457683486175824</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.153174603174591</v>
+        <v>-1.567129629629648</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.3255952380952181</v>
+        <v>0.06759259259259265</v>
       </c>
       <c r="AA14" t="n">
-        <v>-3.971031746031727</v>
+        <v>-1.00925925925926</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9011201577312842</v>
+        <v>-508646.3866335191</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.9128792883476819</v>
+        <v>-995011.5740740737</v>
       </c>
       <c r="AD14" t="n">
-        <v>-4934973.836311791</v>
+        <v>0.0892136747375718</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.153374207711305</v>
+        <v>-1.326403119279956</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2456,35 +2453,35 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45519.58333333334</v>
+        <v>45522.6875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53331</v>
+        <v>26020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2511,61 +2508,61 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9593749999999979</v>
+        <v>-9.694128787878796</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2204861111111112</v>
+        <v>-10.64862560426756</v>
       </c>
       <c r="V15" t="n">
-        <v>11135980.90277778</v>
+        <v>1.630707644628103</v>
       </c>
       <c r="W15" t="n">
-        <v>2.471896087980639</v>
+        <v>-8.52165666898523</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.902620745267825</v>
+        <v>0.9058584328719803</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.715972222222206</v>
+        <v>-7.873120408631777</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.7760416666666288</v>
+        <v>-1.518267906336088</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.78680555555556</v>
+        <v>2.242455808080813</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2260944529326885</v>
+        <v>-55620288.03105158</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.337306229309917</v>
+        <v>-53827586.6620753</v>
       </c>
       <c r="AD15" t="n">
-        <v>7403248.659785885</v>
+        <v>-1.727284665980838</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4934147143705978</v>
+        <v>2.15857352081435</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2591,6 +2588,956 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5.889924242424229</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.620331939862837</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.917803030302991</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5686943891348903</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.2779282032485639</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.080454545454529</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.4306313131313133</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-2.863510101010103</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10516625.20617254</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>18982209.5959596</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.2525014157594252</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-4.727783713235659</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>148</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>-25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-8.237499999999997</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-8.316249685531488</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.19305555555556</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-7.56225144847987</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.2778216414000099</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-9.51666666666668</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1.580555555555555</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-2.948611111111109</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-31136091.58025724</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-34474027.77777778</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1.11865694149135</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.296591284810912</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alvendiz l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Qkg2vOrk</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>4.490437673709735</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>5.179135821966696</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.6214568814446295</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>6343878.163582514</v>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>0.05785032868366202</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.05125013421582025</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.487314814814809</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-4.815067736962348</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-5.162253086419753</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-2.624915953761018</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-4.566879282605441</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-3.097098765432094</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1.051666666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-3.656666666666666</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-6028527.943900673</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-3999993.827160494</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.4973070832937569</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.050388683869642</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.102160493827142</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.691418533157659</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.06327160493822248</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.043668988016819</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.6210323734237022</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.949074074074062</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.4135802469135801</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.42592592592592</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2915925.795219273</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4251080.246913578</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.1628354978354978</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.944325867369347</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>148</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-3.751913580246907</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.688198303730346</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.34925925925927</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.181732002106727</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.990302250190695</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-1.934691358024679</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.5185802469135805</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.657283950617281</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-4490931.450001813</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-12529716.04938272</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8942294595183611</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>4.321746985216663</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>148</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.859816919191914</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.556922601056243</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.458333333333286</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.582836656581421</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-3.130019471796402</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.717771464646447</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1568497474747477</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.083617424242423</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8241953.004852978</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11144361.58459596</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.2437058238075447</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.6549628387706754</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE32"/>
+  <dimension ref="A1:BE30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,69 +717,74 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45536.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>148</v>
       </c>
       <c r="H2" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>-42</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-2</v>
-      </c>
       <c r="Q2" t="n">
-        <v>-12</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -787,67 +792,103 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-0.5499999999999999</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>74.01736111111111</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>74.25231481481481</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.8003062945826112</v>
+      </c>
       <c r="AM2" t="n">
-        <v>0.9385767047645004</v>
+        <v>0.9721275252525254</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.8511941443275497</v>
+        <v>-2.582092972816664</v>
       </c>
       <c r="AO2" t="n">
-        <v>-24441052.16555215</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.6615319865319869</v>
-      </c>
+        <v>6.728271881627151</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-1.255555555555556</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+        <v>50038648.55247092</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.658457120365</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>53072821.96969697</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-3.497699214365866</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-4.859859225778933</v>
-      </c>
+        <v>-3.788931141957477</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-2.874470259424029</v>
+        <v>7.190593434343427</v>
       </c>
       <c r="AX2" t="n">
-        <v>-21506467.45230078</v>
+        <v>0.1103219696969688</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-2.622699214365895</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.018383706146821</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>1.507856341189665</v>
-      </c>
+        <v>-2.34513888888889</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>8.486395202020191</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -855,137 +896,178 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45536.59375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>148</v>
       </c>
       <c r="H3" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>16</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>76.21597222222223</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>72.77006172839505</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.5423458184327754</v>
+      </c>
       <c r="AM3" t="n">
-        <v>-1.42239059120044</v>
+        <v>-0.3832267115600447</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.65278918649134</v>
+        <v>0.16494745592572</v>
       </c>
       <c r="AO3" t="n">
-        <v>52862094.51466928</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-2.221243686868693</v>
-      </c>
+        <v>-3.402319075851679</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>1.577737603305785</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+        <v>-11026334.76653178</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-2.871044137022395</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-13001295.59483726</v>
+      </c>
       <c r="AT3" t="n">
-        <v>9.659406565656568</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.23294783034615</v>
-      </c>
+        <v>3.66178775330954</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>8.03600319802473</v>
+        <v>-3.110869809203137</v>
       </c>
       <c r="AX3" t="n">
-        <v>55245023.53076217</v>
+        <v>1.554938271604897</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>7.955569903581278</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-2.062633810899364</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-1.360126836547266</v>
-      </c>
+        <v>0.5663580246913504</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>-3.175123456790132</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -993,11 +1075,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1007,18 +1089,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1045,7 +1127,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1054,117 +1136,117 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="P4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>12</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="W4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI4" t="n">
         <v>-4</v>
       </c>
-      <c r="U4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.5499999999999999</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>74.01736111111111</v>
+        <v>75.91872704315887</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.25231481481481</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>78.27916666666667</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.5044226535007594</v>
+      </c>
       <c r="AM4" t="n">
-        <v>-3.788931141957477</v>
+        <v>0.6455555555555554</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8003062945826112</v>
+        <v>1.492613209280655</v>
       </c>
       <c r="AO4" t="n">
-        <v>50038648.55247092</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-2.34513888888889</v>
-      </c>
+        <v>0.8710293690321294</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0.9721275252525254</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+        <v>-2956440.539755186</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.5854433184410368</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-10162083.33333333</v>
+      </c>
       <c r="AT4" t="n">
-        <v>8.486395202020191</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.658457120365</v>
-      </c>
+        <v>3.993386503342776</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>6.728271881627151</v>
+        <v>-0.7255555555555446</v>
       </c>
       <c r="AX4" t="n">
-        <v>53072821.96969697</v>
+        <v>2.84361111111113</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>7.190593434343427</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-2.582092972816664</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>0.1103219696969688</v>
-      </c>
+        <v>2.939722222222219</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>-2.420000000000002</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1172,32 +1254,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1224,126 +1306,126 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
         <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-2</v>
+        <v>-0.05999999999999994</v>
       </c>
       <c r="U5" t="n">
-        <v>-6</v>
+        <v>-1.06</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="Y5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-35</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>35</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-3</v>
-      </c>
       <c r="AI5" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76.21597222222223</v>
+        <v>77.01580176767676</v>
       </c>
       <c r="AK5" t="n">
-        <v>72.77006172839505</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>79.44165088383838</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.1313420991446299</v>
+      </c>
       <c r="AM5" t="n">
-        <v>3.66178775330954</v>
+        <v>-0.03125</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.5423458184327754</v>
+        <v>-2.654923355237663</v>
       </c>
       <c r="AO5" t="n">
-        <v>-11026334.76653178</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0.5663580246913504</v>
-      </c>
+        <v>-2.497496839246068</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>-0.3832267115600447</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+        <v>-2220547.09299988</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.8755408730304453</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-6254513.888888888</v>
+      </c>
       <c r="AT5" t="n">
-        <v>-3.175123456790132</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-2.871044137022395</v>
-      </c>
+        <v>2.135010721020961</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-3.402319075851679</v>
+        <v>-3.700231481481481</v>
       </c>
       <c r="AX5" t="n">
-        <v>-13001295.59483726</v>
+        <v>2.425347222222257</v>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>-3.110869809203137</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.16494745592572</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>1.554938271604897</v>
-      </c>
+        <v>-1.327546296296294</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>-1.344328703703695</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1351,32 +1433,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1403,126 +1485,126 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="P6" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.58</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75.91872704315887</v>
+        <v>77.10081037649218</v>
       </c>
       <c r="AK6" t="n">
-        <v>78.27916666666667</v>
-      </c>
-      <c r="AL6" t="inlineStr"/>
+        <v>73.78958333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.1385479797979798</v>
+      </c>
       <c r="AM6" t="n">
-        <v>3.993386503342776</v>
+        <v>-0.2199074074074072</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.5044226535007594</v>
+        <v>0.580319819069814</v>
       </c>
       <c r="AO6" t="n">
-        <v>-2956440.539755186</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.939722222222219</v>
-      </c>
+        <v>-0.6329467754467828</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>0.6455555555555554</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+        <v>810333.2431457443</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.165044677544671</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2318364.197530866</v>
+      </c>
       <c r="AT6" t="n">
-        <v>-2.420000000000002</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.5854433184410368</v>
-      </c>
+        <v>0.5864076201576438</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>0.8710293690321294</v>
+        <v>-0.6844135802469253</v>
       </c>
       <c r="AX6" t="n">
-        <v>-10162083.33333333</v>
+        <v>0.4637345679012697</v>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>-0.7255555555555446</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.492613209280655</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>2.84361111111113</v>
-      </c>
+        <v>-0.196759259259256</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>-0.3305555555555628</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1530,32 +1612,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45536.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1582,126 +1664,126 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P7" t="n">
         <v>-1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V7" t="n">
         <v>-1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-5</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="Y7" t="n">
-        <v>-12</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="Z7" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.6666666666666667</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.05999999999999994</v>
+        <v>-2</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.06</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>77.01580176767676</v>
+        <v>76.89466891133557</v>
       </c>
       <c r="AK7" t="n">
-        <v>79.44165088383838</v>
-      </c>
-      <c r="AL7" t="inlineStr"/>
+        <v>78.0382304526749</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.5494921613708554</v>
+      </c>
       <c r="AM7" t="n">
-        <v>2.135010721020961</v>
+        <v>-0.4611111111111112</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1313420991446299</v>
+        <v>-3.655845314854957</v>
       </c>
       <c r="AO7" t="n">
-        <v>-2220547.09299988</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-1.327546296296294</v>
-      </c>
+        <v>-5.595392114218456</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>-0.03125</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+        <v>-4398124.948712629</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-2.900945801548104</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-705486.1111111119</v>
+      </c>
       <c r="AT7" t="n">
-        <v>-1.344328703703695</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.8755408730304453</v>
-      </c>
+        <v>-2.558798273332854</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>-2.497496839246068</v>
+        <v>-4.46250000000002</v>
       </c>
       <c r="AX7" t="n">
-        <v>-6254513.888888888</v>
+        <v>-4.032638888888926</v>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>-3.700231481481481</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-2.654923355237663</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>2.425347222222257</v>
-      </c>
+        <v>-4.183333333333337</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
+        <v>-1.486805555555563</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1709,32 +1791,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45536.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1766,121 +1848,103 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD8" t="n">
         <v>-1</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI8" t="n">
         <v>3</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>77.10081037649218</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
-        <v>73.78958333333333</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>0.5864076201576438</v>
-      </c>
+        <v>79.39898148148148</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.09683498319861972</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-0.1385479797979798</v>
+        <v>-0.8552556787428713</v>
       </c>
       <c r="AO8" t="n">
-        <v>810333.2431457443</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.196759259259256</v>
-      </c>
+        <v>-6.011691773607751</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>-0.2199074074074072</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>-5470173.764896095</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-3.796264054690027</v>
+      </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>-0.3305555555555628</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-0.165044677544671</v>
-      </c>
+        <v>0.8002993242333218</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>-0.6329467754467828</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>2318364.197530866</v>
-      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>-0.6844135802469253</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.580319819069814</v>
-      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>0.4637345679012697</v>
-      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1888,32 +1952,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45535.59375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1940,126 +2004,126 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
         <v>-2</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.9800000000000001</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>-1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE9" t="n">
         <v>-2</v>
       </c>
-      <c r="Y9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF9" t="n">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
         <v>-2</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>76.89466891133557</v>
+        <v>77.55202861952861</v>
       </c>
       <c r="AK9" t="n">
-        <v>78.0382304526749</v>
-      </c>
-      <c r="AL9" t="inlineStr"/>
+        <v>78.31224279835391</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.2740940255994437</v>
+      </c>
       <c r="AM9" t="n">
-        <v>-2.558798273332854</v>
+        <v>-0.1861111111111111</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.5494921613708554</v>
+        <v>-1.884180865860433</v>
       </c>
       <c r="AO9" t="n">
-        <v>-4398124.948712629</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-4.183333333333337</v>
-      </c>
+        <v>-3.237414733815655</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>-0.4611111111111112</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>-2377412.516376525</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.515458839406207</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-2758888.888888889</v>
+      </c>
       <c r="AT9" t="n">
-        <v>-1.486805555555563</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-2.900945801548104</v>
-      </c>
+        <v>-0.7823659321415164</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-5.595392114218456</v>
+        <v>-3.390277777777783</v>
       </c>
       <c r="AX9" t="n">
-        <v>-705486.1111111119</v>
+        <v>3.444444444444457</v>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>-4.46250000000002</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-3.655845314854957</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>-4.032638888888926</v>
-      </c>
+        <v>-1.930555555555554</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>-1.218055555555551</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2067,32 +2131,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2119,107 +2183,125 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="O10" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-3</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.7200000000000001</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-1</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
       </c>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>75.8383744855967</v>
+      </c>
       <c r="AK10" t="n">
-        <v>79.39898148148148</v>
-      </c>
-      <c r="AL10" t="inlineStr"/>
+        <v>75.15777777777777</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.5600559536307037</v>
+      </c>
       <c r="AM10" t="n">
-        <v>0.7201828523695326</v>
+        <v>-0.9763888888888885</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.09723370728155434</v>
+        <v>-1.819191117867803</v>
       </c>
       <c r="AO10" t="n">
-        <v>-5500666.865578802</v>
+        <v>-3.155544864288487</v>
       </c>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="n">
-        <v>-3.892210264268215</v>
-      </c>
+      <c r="AQ10" t="n">
+        <v>-6537895.522017898</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.640355548640642</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-10351452.02020202</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.9570194825413409</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>-6.06168350532181</v>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+        <v>-3.453409090909091</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.124368686868706</v>
+      </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="n">
-        <v>-0.9248473856516348</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>-3.227272727272727</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>-1.721464646464639</v>
+      </c>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2228,32 +2310,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45535.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2280,126 +2362,126 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="P11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R11" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-13</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="n">
         <v>-1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.9800000000000001</v>
       </c>
       <c r="AF11" t="n">
         <v>-2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>77.55202861952861</v>
+        <v>75.32941919191919</v>
       </c>
       <c r="AK11" t="n">
-        <v>78.31224279835391</v>
-      </c>
-      <c r="AL11" t="inlineStr"/>
+        <v>77.94165088383838</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.062489911230068</v>
+      </c>
       <c r="AM11" t="n">
-        <v>-0.5919654767961902</v>
+        <v>1.545634920634921</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.2698998527379914</v>
+        <v>-2.484913496407476</v>
       </c>
       <c r="AO11" t="n">
-        <v>-2405755.827409174</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-1.930555555555554</v>
-      </c>
+        <v>8.660079717034833</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
-        <v>-0.1861111111111111</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
+        <v>35931123.14045717</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>10.30605043647915</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>41141672.17813051</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-1.218055555555551</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-1.583599674265798</v>
-      </c>
+        <v>0.2556124101883768</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="n">
-        <v>-3.20351590150689</v>
+        <v>10.74845679012347</v>
       </c>
       <c r="AX11" t="n">
-        <v>-2758888.888888889</v>
+        <v>1.915123456790127</v>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
-        <v>-3.390277777777783</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>-1.793313097667294</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="n">
-        <v>3.444444444444457</v>
-      </c>
+        <v>0.233465608465611</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>9.925044091710745</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
@@ -2407,32 +2489,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45533.6875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2459,126 +2541,126 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O12" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
         <v>-17</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AC12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AI12" t="n">
         <v>6</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.2000000000000001</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>75.8383744855967</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="AK12" t="n">
-        <v>75.15777777777777</v>
-      </c>
-      <c r="AL12" t="inlineStr"/>
+        <v>73.54861111111111</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-1.623066759540545</v>
+      </c>
       <c r="AM12" t="n">
-        <v>0.9570194825413409</v>
+        <v>-1.828030303030303</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.5600559536307037</v>
+        <v>1.184039411441823</v>
       </c>
       <c r="AO12" t="n">
-        <v>-6537895.522017898</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-3.227272727272727</v>
-      </c>
+        <v>-9.309962174534462</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="n">
-        <v>-0.976388888888889</v>
-      </c>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
+        <v>-54370197.62963701</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-11.39010498137316</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-54687752.52525253</v>
+      </c>
       <c r="AT12" t="n">
-        <v>-1.721464646464639</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-1.640355548640642</v>
-      </c>
+        <v>-0.9901019827340463</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="n">
-        <v>-3.155544864288487</v>
+        <v>-8.817329545454541</v>
       </c>
       <c r="AX12" t="n">
-        <v>-10351452.02020202</v>
+        <v>-2.386363636363626</v>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
-        <v>-3.453409090909091</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-1.819191117867803</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="n">
-        <v>3.124368686868678</v>
-      </c>
+        <v>-0.54548611111111</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>-8.774589646464648</v>
+      </c>
+      <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
@@ -2586,32 +2668,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.5</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2638,34 +2720,34 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-2</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2674,16 +2756,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2692,72 +2774,72 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.18</v>
+        <v>-3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>75.32941919191919</v>
+        <v>82.12083333333332</v>
       </c>
       <c r="AK13" t="n">
-        <v>77.94165088383838</v>
-      </c>
-      <c r="AL13" t="inlineStr"/>
+        <v>75.81662075298438</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.08418143514253362</v>
+      </c>
       <c r="AM13" t="n">
-        <v>0.2556124101883768</v>
+        <v>0.1575</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.062489911230068</v>
+        <v>-1.930347828817503</v>
       </c>
       <c r="AO13" t="n">
-        <v>35931123.14045717</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.233465608465611</v>
-      </c>
+        <v>1.740469823845118</v>
+      </c>
+      <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="n">
-        <v>1.545634920634921</v>
-      </c>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
+        <v>6631837.745095611</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.756868522400552</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>13535750</v>
+      </c>
       <c r="AT13" t="n">
-        <v>9.925044091710745</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>10.30605043647915</v>
-      </c>
+        <v>-1.755138802527256</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="n">
-        <v>8.660079717034833</v>
+        <v>3.947499999999991</v>
       </c>
       <c r="AX13" t="n">
-        <v>41141672.17813051</v>
+        <v>-0.2524999999999977</v>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
-        <v>10.74845679012347</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-2.484913496407476</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="n">
-        <v>1.915123456790127</v>
-      </c>
+        <v>-1.689999999999998</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
+        <v>4.642499999999998</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2765,32 +2847,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2817,34 +2899,34 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>0.89</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2853,90 +2935,90 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.03000000000000003</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75.11111111111111</v>
+        <v>73.52777777777777</v>
       </c>
       <c r="AK14" t="n">
-        <v>73.54861111111111</v>
-      </c>
-      <c r="AL14" t="inlineStr"/>
+        <v>75.97829861111111</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.6392108977978546</v>
+      </c>
       <c r="AM14" t="n">
-        <v>-0.9901019827340463</v>
+        <v>0.7057575757575756</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.623066759540545</v>
+        <v>0.7292855656928872</v>
       </c>
       <c r="AO14" t="n">
-        <v>-54370197.62963701</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.54548611111111</v>
-      </c>
+        <v>4.704384718383565</v>
+      </c>
+      <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="n">
-        <v>-1.828030303030303</v>
-      </c>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
+        <v>12707030.41014096</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.959744226343204</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>20833510.1010101</v>
+      </c>
       <c r="AT14" t="n">
-        <v>-8.774589646464648</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-11.39010498137316</v>
-      </c>
+        <v>-0.3250470956706977</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="n">
-        <v>-9.309962174534462</v>
+        <v>7.836178451178441</v>
       </c>
       <c r="AX14" t="n">
-        <v>-54687752.52525253</v>
+        <v>-0.4916666666667027</v>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
-        <v>-8.817329545454541</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.184039411441823</v>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="n">
-        <v>-2.386363636363626</v>
-      </c>
+        <v>2.12962962962963</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>5.060925925925929</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
@@ -2944,32 +3026,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2996,47 +3078,47 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V15" t="n">
         <v>2</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" t="n">
         <v>-1</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9</v>
-      </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
@@ -3044,78 +3126,78 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AH15" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>82.12083333333332</v>
+        <v>78.38499999999999</v>
       </c>
       <c r="AK15" t="n">
-        <v>75.81662075298438</v>
-      </c>
-      <c r="AL15" t="inlineStr"/>
+        <v>75.26762626262627</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.8565750443227222</v>
+      </c>
       <c r="AM15" t="n">
-        <v>-1.755138802527256</v>
+        <v>1.331944444444444</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.08418143514253362</v>
+        <v>0.07593279470215109</v>
       </c>
       <c r="AO15" t="n">
-        <v>6631837.745095611</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-1.689999999999998</v>
-      </c>
+        <v>7.497665606094401</v>
+      </c>
+      <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
+        <v>17495615.25975458</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.713294728147659</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>29062083.33333333</v>
+      </c>
       <c r="AT15" t="n">
-        <v>4.642499999999998</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.756868522400552</v>
-      </c>
+        <v>1.337529453690451</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="n">
-        <v>1.740469823845118</v>
+        <v>10.19027777777777</v>
       </c>
       <c r="AX15" t="n">
-        <v>13535750</v>
+        <v>-2.86250000000004</v>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
-        <v>3.947499999999991</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-1.930347828817503</v>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="n">
-        <v>-0.2524999999999977</v>
-      </c>
+        <v>1.761111111111109</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>8.347222222222214</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
@@ -3123,32 +3205,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3175,22 +3257,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O16" t="n">
+        <v>-13</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -3199,102 +3281,102 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
         <v>-9</v>
       </c>
-      <c r="U16" t="n">
-        <v>13</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>73.52777777777777</v>
+        <v>77.97839506172841</v>
       </c>
       <c r="AK16" t="n">
-        <v>75.97829861111111</v>
-      </c>
-      <c r="AL16" t="inlineStr"/>
+        <v>75.12191358024693</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.3019595504105532</v>
+      </c>
       <c r="AM16" t="n">
-        <v>-0.3250470956706977</v>
+        <v>0.3305555555555555</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.6392108977978546</v>
+        <v>1.420610963904451</v>
       </c>
       <c r="AO16" t="n">
-        <v>12707030.41014096</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.12962962962963</v>
-      </c>
+        <v>4.888087826862488</v>
+      </c>
+      <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="n">
-        <v>0.7057575757575756</v>
-      </c>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
+        <v>8752072.242987916</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.763966217328317</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>13166881.31313132</v>
+      </c>
       <c r="AT16" t="n">
-        <v>5.060925925925929</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.959744226343204</v>
-      </c>
+        <v>1.491723021489179</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="n">
-        <v>4.704384718383565</v>
+        <v>7.109090909090909</v>
       </c>
       <c r="AX16" t="n">
-        <v>20833510.1010101</v>
+        <v>1.750757575757575</v>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
-        <v>7.836178451178441</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0.7292855656928872</v>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="n">
-        <v>-0.4916666666667027</v>
-      </c>
+        <v>2.683838383838385</v>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>4.407702020202024</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
@@ -3302,32 +3384,32 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3354,22 +3436,22 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -3378,102 +3460,88 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH17" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>-9</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3</v>
-      </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.38499999999999</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>75.26762626262627</v>
-      </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="n">
-        <v>1.147128998345124</v>
-      </c>
+        <v>77.94165088383838</v>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>0.1561890118681915</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="n">
-        <v>0.85238087146127</v>
+        <v>-0.5815863227733473</v>
       </c>
       <c r="AO17" t="n">
-        <v>17523958.57078723</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.761111111111109</v>
-      </c>
+        <v>1.438038710495945</v>
+      </c>
+      <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="n">
-        <v>1.331944444444445</v>
-      </c>
-      <c r="AR17" t="inlineStr"/>
+        <v>393518.1819552199</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.756123002098235</v>
+      </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>8.347222222222214</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.78143556300725</v>
-      </c>
+        <v>-1.42331814248422</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="n">
-        <v>7.463766773785636</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>29062083.33333333</v>
-      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="n">
-        <v>10.19027777777777</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-0.0149349734909876</v>
-      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="n">
-        <v>-2.862500000000011</v>
-      </c>
+      <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
@@ -3481,32 +3549,32 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45531.6875</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3533,111 +3601,125 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG18" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AH18" t="n">
         <v>-6</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>-1</v>
-      </c>
       <c r="AI18" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>77.94165088383838</v>
-      </c>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
+        <v>76.8233024691358</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>75.33371212121212</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.8736192094201245</v>
+      </c>
       <c r="AM18" t="n">
-        <v>-1.343201670620431</v>
+        <v>-1.425</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.1565877359511261</v>
+        <v>5.645822895172905</v>
       </c>
       <c r="AO18" t="n">
-        <v>424011.2826379272</v>
+        <v>-3.979176267414289</v>
       </c>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="n">
-        <v>1.852069211676422</v>
-      </c>
+      <c r="AQ18" t="n">
+        <v>-33021359.38691231</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-9.417339565879743</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-37458209.87654321</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.5736062993257747</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="n">
-        <v>1.488030442210004</v>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+        <v>-5.969290123456787</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-2.198456790123458</v>
+      </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="n">
-        <v>-0.5119946158645838</v>
-      </c>
-      <c r="BC18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>2.735185185185184</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
+        <v>-8.90540123456789</v>
+      </c>
       <c r="BD18" t="inlineStr"/>
       <c r="BE18" t="n">
         <v>0</v>
@@ -3646,32 +3728,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3698,126 +3780,126 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>-0.83</v>
       </c>
       <c r="U19" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="V19" t="n">
         <v>-1</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-33</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5</v>
+        <v>-17</v>
       </c>
       <c r="AC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
         <v>-1</v>
       </c>
-      <c r="AD19" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>-1.68</v>
-      </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="AI19" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>77.97839506172841</v>
+        <v>80.26875</v>
       </c>
       <c r="AK19" t="n">
-        <v>75.12191358024693</v>
-      </c>
-      <c r="AL19" t="inlineStr"/>
+        <v>76.02083333333334</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.539049712264754</v>
+      </c>
       <c r="AM19" t="n">
-        <v>1.491723021489179</v>
+        <v>-0.7090128558310373</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.3019595504105532</v>
+        <v>1.567366921711017</v>
       </c>
       <c r="AO19" t="n">
-        <v>8752072.242987916</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.683838383838385</v>
-      </c>
+        <v>-1.234391320685631</v>
+      </c>
+      <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="n">
-        <v>0.3305555555555555</v>
-      </c>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
+        <v>-4194475.333983446</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-3.599223717248464</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-4151423.783287421</v>
+      </c>
       <c r="AT19" t="n">
-        <v>4.407702020202024</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.763966217328317</v>
-      </c>
+        <v>-1.891053375337691</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="n">
-        <v>4.888087826862488</v>
+        <v>-1.842823691460069</v>
       </c>
       <c r="AX19" t="n">
-        <v>13166881.31313132</v>
+        <v>-1.61024563820024</v>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
-        <v>7.109090909090909</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.420610963904451</v>
-      </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="n">
-        <v>1.750757575757575</v>
-      </c>
+        <v>-0.3197979797979755</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
+        <v>-2.438914141414145</v>
+      </c>
+      <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
@@ -3825,32 +3907,32 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45530.6875</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3877,126 +3959,126 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>-3</v>
-      </c>
       <c r="AI20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>76.8233024691358</v>
+        <v>79.49638888888889</v>
       </c>
       <c r="AK20" t="n">
-        <v>75.33371212121212</v>
-      </c>
-      <c r="AL20" t="inlineStr"/>
+        <v>71.55833333333332</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.4291888031129516</v>
+      </c>
       <c r="AM20" t="n">
-        <v>-0.5736062993257747</v>
+        <v>0.1759259259259263</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.8736192094201245</v>
+        <v>2.041814680417616</v>
       </c>
       <c r="AO20" t="n">
-        <v>-33021359.38691231</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.735185185185184</v>
-      </c>
+        <v>2.663421778599798</v>
+      </c>
+      <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="n">
-        <v>-1.425</v>
-      </c>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
+        <v>2350723.212191575</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.950186551494596</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1974266.975308644</v>
+      </c>
       <c r="AT20" t="n">
-        <v>-8.90540123456789</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>-9.417339565879743</v>
-      </c>
+        <v>2.571847494181128</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="n">
-        <v>-3.979176267414289</v>
+        <v>0.8989197530864175</v>
       </c>
       <c r="AX20" t="n">
-        <v>-37458209.87654321</v>
+        <v>3.578317901234641</v>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
-        <v>-5.969290123456787</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>5.645822895172905</v>
-      </c>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="n">
-        <v>-2.198456790123458</v>
-      </c>
+        <v>-0.1759259259259203</v>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
+        <v>0.84652777777778</v>
+      </c>
+      <c r="BD20" t="inlineStr"/>
       <c r="BE20" t="n">
         <v>0</v>
       </c>
@@ -4004,32 +4086,32 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45529.6875</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4056,126 +4138,118 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.4399999999999999</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI21" t="n">
         <v>-11</v>
       </c>
-      <c r="P21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>-17</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>80.26875</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>76.02083333333334</v>
-      </c>
-      <c r="AL21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>0.7960786904387993</v>
+      </c>
       <c r="AM21" t="n">
-        <v>-1.891053375337691</v>
+        <v>1.084166666666666</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.539049712264754</v>
+        <v>2.975799457082601</v>
       </c>
       <c r="AO21" t="n">
-        <v>-4194475.333983446</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>-0.3197979797979755</v>
-      </c>
+        <v>4.004139307133983</v>
+      </c>
+      <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="n">
-        <v>-0.7090128558310373</v>
-      </c>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
+        <v>5800395.040243404</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.8617386710595696</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8933000</v>
+      </c>
       <c r="AT21" t="n">
-        <v>-2.438914141414145</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>-3.599223717248464</v>
-      </c>
+        <v>1.716483942165723</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
       <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="n">
-        <v>-1.234391320685631</v>
+        <v>3.735833333333332</v>
       </c>
       <c r="AX21" t="n">
-        <v>-4151423.783287421</v>
+        <v>-2.039166666666688</v>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
-        <v>-1.842823691460069</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.567366921711017</v>
-      </c>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="n">
-        <v>-1.61024563820024</v>
-      </c>
+        <v>3.438611111111108</v>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
+        <v>1.176944444444445</v>
+      </c>
+      <c r="BD21" t="inlineStr"/>
       <c r="BE21" t="n">
         <v>0</v>
       </c>
@@ -4183,32 +4257,32 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45529.59375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4235,126 +4309,118 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.6399999999999999</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.7999999999999999</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC22" t="n">
         <v>3</v>
       </c>
-      <c r="R22" t="n">
-        <v>3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AD22" t="n">
         <v>-2</v>
       </c>
-      <c r="U22" t="n">
-        <v>-13</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AE22" t="n">
         <v>2</v>
       </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.1699999999999999</v>
-      </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="AI22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>79.49638888888889</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>71.55833333333332</v>
-      </c>
-      <c r="AL22" t="inlineStr"/>
+        <v>-7</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>-0.954102564102564</v>
+      </c>
       <c r="AM22" t="n">
-        <v>2.571847494181128</v>
+        <v>-0.8871527777777777</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.4291888031129516</v>
+        <v>-4.052976916612504</v>
       </c>
       <c r="AO22" t="n">
-        <v>2350723.212191575</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>-0.1759259259259203</v>
-      </c>
+        <v>-5.079187132153379</v>
+      </c>
+      <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="n">
-        <v>0.1759259259259263</v>
-      </c>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
+        <v>-6552096.170165966</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-2.856106987977711</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-7869444.444444444</v>
+      </c>
       <c r="AT22" t="n">
-        <v>0.84652777777778</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.950186551494596</v>
-      </c>
+        <v>-2.644022403670562</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
       <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="n">
-        <v>2.663421778599798</v>
+        <v>-5.326967592592595</v>
       </c>
       <c r="AX22" t="n">
-        <v>1974266.975308644</v>
+        <v>0.1493055555555998</v>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
-        <v>0.8989197530864175</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>2.041814680417616</v>
-      </c>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="n">
-        <v>3.578317901234641</v>
-      </c>
+        <v>-4.218171296296294</v>
+      </c>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="n">
+        <v>-1.632523148148152</v>
+      </c>
+      <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="n">
         <v>0</v>
       </c>
@@ -4362,32 +4428,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4414,118 +4480,106 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>0.14</v>
       </c>
       <c r="U23" t="n">
+        <v>-0.05999999999999983</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH23" t="n">
         <v>-5</v>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>-11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>-0.4399999999999999</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3</v>
-      </c>
       <c r="AI23" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="n">
-        <v>1.716483942165723</v>
-      </c>
+      <c r="AL23" t="n">
+        <v>-0.1265574101494147</v>
+      </c>
+      <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="n">
-        <v>0.7960786904387993</v>
+        <v>0.02333872071466914</v>
       </c>
       <c r="AO23" t="n">
-        <v>5800395.040243404</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.438611111111108</v>
-      </c>
+        <v>-4.737732797098019</v>
+      </c>
+      <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="n">
-        <v>1.084166666666667</v>
-      </c>
-      <c r="AR23" t="inlineStr"/>
+        <v>-3962070.649928365</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>-2.63910690366302</v>
+      </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
-        <v>1.176944444444445</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0.8617386710595696</v>
-      </c>
+        <v>3.212791898167808</v>
+      </c>
+      <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="n">
-        <v>4.004139307133983</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>8933000</v>
-      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="n">
-        <v>3.735833333333332</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>2.975799457082601</v>
-      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="n">
-        <v>-2.039166666666659</v>
-      </c>
+      <c r="BD23" t="inlineStr"/>
       <c r="BE23" t="n">
         <v>0</v>
       </c>
@@ -4533,32 +4587,32 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45529.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4585,118 +4639,122 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>-4</v>
+        <v>26</v>
       </c>
       <c r="P24" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
+        <v>18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
         <v>-2</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>12</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="Y24" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="n">
-        <v>-9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
         <v>3</v>
       </c>
-      <c r="AB24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-0.6399999999999999</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>-0.7999999999999999</v>
-      </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AG24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>-2</v>
       </c>
       <c r="AI24" t="n">
         <v>2</v>
       </c>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
+      <c r="AJ24" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.593435157821768</v>
+      </c>
       <c r="AM24" t="n">
-        <v>-2.644022403670562</v>
+        <v>1.69658189033189</v>
       </c>
       <c r="AN24" t="n">
-        <v>-0.954102564102564</v>
+        <v>-0.6257918093831449</v>
       </c>
       <c r="AO24" t="n">
-        <v>-6552096.170165966</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>-4.218171296296294</v>
-      </c>
+        <v>12.60965626113654</v>
+      </c>
+      <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="n">
-        <v>-0.8871527777777777</v>
-      </c>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
+        <v>57938750.09761015</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>12.27308888293794</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>61985173.16017316</v>
+      </c>
       <c r="AT24" t="n">
-        <v>-1.632523148148152</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>-2.856106987977711</v>
-      </c>
+        <v>-0.7993717729495415</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
       <c r="AV24" t="inlineStr"/>
       <c r="AW24" t="n">
-        <v>-5.079187132153379</v>
+        <v>13.230523989899</v>
       </c>
       <c r="AX24" t="n">
-        <v>-7869444.444444444</v>
+        <v>2.211016414141397</v>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
-        <v>-5.326967592592595</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>-4.052976916612504</v>
-      </c>
-      <c r="BC24" t="inlineStr"/>
-      <c r="BD24" t="n">
-        <v>0.1493055555555998</v>
-      </c>
+        <v>-0.2407242063492063</v>
+      </c>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="n">
+        <v>11.77235750360749</v>
+      </c>
+      <c r="BD24" t="inlineStr"/>
       <c r="BE24" t="n">
         <v>0</v>
       </c>
@@ -4704,32 +4762,32 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4756,105 +4814,121 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="P25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
       <c r="R25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4299999999999999</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.8300000000000001</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE25" t="n">
         <v>-1</v>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AF25" t="n">
         <v>-9</v>
       </c>
-      <c r="AA25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>-0.05999999999999983</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>-1</v>
-      </c>
       <c r="AG25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-0.2529793233082711</v>
+      </c>
       <c r="AM25" t="n">
-        <v>3.132675426304019</v>
+        <v>0.03919753086419764</v>
       </c>
       <c r="AN25" t="n">
-        <v>-0.1269561342323493</v>
+        <v>-4.363352130325808</v>
       </c>
       <c r="AO25" t="n">
-        <v>-3992563.750611072</v>
+        <v>-2.576640559732652</v>
       </c>
       <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="n">
-        <v>-2.735053113241207</v>
-      </c>
+      <c r="AQ25" t="n">
+        <v>118937.2650375934</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.958513993316629</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5191658.950617285</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4.000271512113613</v>
+      </c>
+      <c r="AU25" t="inlineStr"/>
       <c r="AV25" t="inlineStr"/>
       <c r="AW25" t="n">
-        <v>-4.787724528812078</v>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+        <v>0.6591049382715966</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.596604938271554</v>
+      </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
-      <c r="BB25" t="n">
-        <v>-0.04625298619409435</v>
-      </c>
-      <c r="BC25" t="inlineStr"/>
+      <c r="BA25" t="n">
+        <v>-2.386419753086425</v>
+      </c>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="n">
+        <v>2.519598765432093</v>
+      </c>
       <c r="BD25" t="inlineStr"/>
       <c r="BE25" t="n">
         <v>0</v>
@@ -4863,32 +4937,32 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45529.5</v>
+        <v>45528.6875</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4915,122 +4989,122 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>26</v>
+        <v>-7</v>
       </c>
       <c r="P26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>18</v>
-      </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-8</v>
+        <v>-1.29</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
-      </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+        <v>-0.93</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>-20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE26" t="n">
         <v>-2</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.58</v>
-      </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>76.55555555555556</v>
+        <v>71.44444444444444</v>
       </c>
       <c r="AK26" t="n">
-        <v>72.11111111111111</v>
-      </c>
-      <c r="AL26" t="inlineStr"/>
+        <v>75.125</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.563460520723948</v>
+      </c>
       <c r="AM26" t="n">
-        <v>-0.7993717729495415</v>
+        <v>-0.6085353535353535</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.593435157821768</v>
+        <v>2.644118720391095</v>
       </c>
       <c r="AO26" t="n">
-        <v>57938750.09761015</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>-0.2407242063492063</v>
-      </c>
+        <v>-4.063093249934681</v>
+      </c>
+      <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="n">
-        <v>1.69658189033189</v>
-      </c>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
+        <v>-13522684.54794589</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>-6.345016969745231</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>-20951843.43434343</v>
+      </c>
       <c r="AT26" t="n">
-        <v>11.77235750360749</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>12.27308888293794</v>
-      </c>
+        <v>-1.12084969094559</v>
+      </c>
+      <c r="AU26" t="inlineStr"/>
       <c r="AV26" t="inlineStr"/>
       <c r="AW26" t="n">
-        <v>12.60965626113654</v>
+        <v>-7.160252525252517</v>
       </c>
       <c r="AX26" t="n">
-        <v>61985173.16017316</v>
+        <v>1.4027777777778</v>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
-        <v>13.230523989899</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>-0.6257918093831449</v>
-      </c>
-      <c r="BC26" t="inlineStr"/>
-      <c r="BD26" t="n">
-        <v>2.211016414141397</v>
-      </c>
+        <v>1.022222222222222</v>
+      </c>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="n">
+        <v>-6.912777777777777</v>
+      </c>
+      <c r="BD26" t="inlineStr"/>
       <c r="BE26" t="n">
         <v>0</v>
       </c>
@@ -5038,32 +5112,32 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5090,122 +5164,120 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>-4</v>
+        <v>43</v>
       </c>
       <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>30</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-2</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="AG27" t="n">
         <v>-1</v>
       </c>
-      <c r="R27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="n">
+      <c r="AH27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI27" t="n">
         <v>-3</v>
       </c>
-      <c r="Y27" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>-0.4299999999999999</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>-0.8300000000000001</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>77.11111111111111</v>
-      </c>
+      <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="n">
-        <v>77.66666666666667</v>
-      </c>
-      <c r="AL27" t="inlineStr"/>
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.8511941443275497</v>
+      </c>
       <c r="AM27" t="n">
-        <v>4.000271512113613</v>
+        <v>1.255555555555556</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.2529793233082711</v>
+        <v>-2.018383706146821</v>
       </c>
       <c r="AO27" t="n">
-        <v>118937.2650375934</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>-2.386419753086425</v>
-      </c>
+        <v>2.874470259424029</v>
+      </c>
+      <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="n">
-        <v>0.03919753086419764</v>
-      </c>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
+        <v>24441052.16555215</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.859859225778933</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>21506467.45230078</v>
+      </c>
       <c r="AT27" t="n">
-        <v>2.519598765432093</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.958513993316629</v>
-      </c>
+        <v>-0.9385767047645004</v>
+      </c>
+      <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="n">
-        <v>-2.576640559732652</v>
+        <v>2.622699214365895</v>
       </c>
       <c r="AX27" t="n">
-        <v>5191658.950617285</v>
+        <v>-1.507856341189665</v>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
-        <v>0.6591049382715966</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>-4.363352130325808</v>
-      </c>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="n">
-        <v>3.596604938271554</v>
-      </c>
+        <v>0.6615319865319869</v>
+      </c>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="n">
+        <v>3.497699214365866</v>
+      </c>
+      <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="n">
         <v>0</v>
       </c>
@@ -5213,32 +5285,32 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45528.5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5265,22 +5337,22 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5289,98 +5361,96 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>-6</v>
+        <v>0.7700000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-6</v>
-      </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+        <v>0.11</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
       <c r="X28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>11</v>
-      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI28" t="n">
         <v>-3</v>
       </c>
-      <c r="AI28" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>71.44444444444444</v>
-      </c>
+      <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="AL28" t="inlineStr"/>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-0.0495543763785391</v>
+      </c>
       <c r="AM28" t="n">
-        <v>-0.930449235600264</v>
+        <v>-0.09404269972451806</v>
       </c>
       <c r="AN28" t="n">
-        <v>-0.5592663478624957</v>
+        <v>-1.129632302174169</v>
       </c>
       <c r="AO28" t="n">
-        <v>-13551027.85897854</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.022222222222222</v>
-      </c>
+        <v>-1.377107872191615</v>
+      </c>
+      <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="n">
-        <v>-0.6085353535353535</v>
-      </c>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
+        <v>519078.128643021</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.4277985132889484</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>777757.116620753</v>
+      </c>
       <c r="AT28" t="n">
-        <v>-6.912777777777777</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>-6.413157804604822</v>
-      </c>
+        <v>-0.3471943254778296</v>
+      </c>
+      <c r="AU28" t="inlineStr"/>
       <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="n">
-        <v>-4.029194417625916</v>
+        <v>-1.379120752984377</v>
       </c>
       <c r="AX28" t="n">
-        <v>-20951843.43434343</v>
+        <v>-0.9808654729108923</v>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
-        <v>-7.160252525252517</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>2.734986488584234</v>
-      </c>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="n">
-        <v>1.4027777777778</v>
-      </c>
+        <v>-0.9299242424242458</v>
+      </c>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="n">
+        <v>0.2164141414141483</v>
+      </c>
+      <c r="BD28" t="inlineStr"/>
       <c r="BE28" t="n">
         <v>0</v>
       </c>
@@ -5388,32 +5458,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45527.6875</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5440,120 +5510,126 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>11</v>
+      </c>
+      <c r="R29" t="n">
         <v>2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>30</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3</v>
-      </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-2</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+        <v>-0.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
       <c r="X29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI29" t="n">
         <v>5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>-0.1200000000000001</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>-1</v>
-      </c>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="n">
-        <v>74.66666666666667</v>
-      </c>
-      <c r="AL29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="n">
+        <v>0.02086730573236162</v>
+      </c>
       <c r="AM29" t="n">
-        <v>-0.9385767047645004</v>
+        <v>0.4072222222222219</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.8511941443275497</v>
+        <v>-1.899229480884649</v>
       </c>
       <c r="AO29" t="n">
-        <v>24441052.16555215</v>
+        <v>-0.6848693611693335</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.6615319865319869</v>
+        <v>-44500000</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.255555555555556</v>
-      </c>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
+        <v>2135007.236294594</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.056193974920248</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3717763.88888889</v>
+      </c>
       <c r="AT29" t="n">
-        <v>3.497699214365866</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.859859225778933</v>
-      </c>
-      <c r="AV29" t="inlineStr"/>
+        <v>0.2528078267920364</v>
+      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>-236</v>
+      </c>
       <c r="AW29" t="n">
-        <v>2.874470259424029</v>
+        <v>1.638611111111103</v>
       </c>
       <c r="AX29" t="n">
-        <v>21506467.45230078</v>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+        <v>-0.5234722222222388</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>-233</v>
+      </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
-        <v>2.622699214365895</v>
+        <v>1.228888888888886</v>
       </c>
       <c r="BB29" t="n">
-        <v>-2.018383706146821</v>
-      </c>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="n">
-        <v>-1.507856341189665</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.045416666666654</v>
+      </c>
+      <c r="BD29" t="inlineStr"/>
       <c r="BE29" t="n">
         <v>0</v>
       </c>
@@ -5561,32 +5637,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45528.5</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5613,463 +5689,133 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X30" t="n">
         <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="n">
-        <v>4</v>
       </c>
       <c r="Y30" t="n">
         <v>-3</v>
       </c>
-      <c r="Z30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>-26</v>
-      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.7700000000000001</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.11</v>
+        <v>-6</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="AL30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>0.1203033582579038</v>
+      </c>
       <c r="AM30" t="n">
-        <v>-0.3471943254778296</v>
+        <v>0.285185185185185</v>
       </c>
       <c r="AN30" t="n">
-        <v>-0.0495543763785391</v>
+        <v>1.614030634437341</v>
       </c>
       <c r="AO30" t="n">
-        <v>519078.128643021</v>
+        <v>2.931970335618658</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.9299242424242458</v>
+        <v>-41400000</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.09404269972451806</v>
-      </c>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
+        <v>2047401.736521054</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.9507592500535083</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>-1268780.864197532</v>
+      </c>
       <c r="AT30" t="n">
-        <v>0.2164141414141483</v>
+        <v>-0.01304922084827354</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.4277985132889484</v>
-      </c>
-      <c r="AV30" t="inlineStr"/>
+        <v>4.100000000000001</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>-234</v>
+      </c>
       <c r="AW30" t="n">
-        <v>-1.377107872191615</v>
+        <v>3.563580246913602</v>
       </c>
       <c r="AX30" t="n">
-        <v>777757.116620753</v>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
+        <v>0.4543209876542846</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-225</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.1000000000000001</v>
+      </c>
       <c r="BA30" t="n">
-        <v>-1.379120752984377</v>
+        <v>4.359259259259257</v>
       </c>
       <c r="BB30" t="n">
-        <v>-1.129632302174169</v>
-      </c>
-      <c r="BC30" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.6402777777777828</v>
+      </c>
       <c r="BD30" t="n">
-        <v>-0.9808654729108923</v>
+        <v>4.099999999999994</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45527.6875</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>148</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>9</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>11</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>4</v>
-      </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.7999999999999999</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
-        <v>0.2528078267920364</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0.02086730573236162</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>2135007.236294594</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.228888888888886</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.4072222222222219</v>
-      </c>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="n">
-        <v>1.045416666666654</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.056193974920248</v>
-      </c>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="n">
-        <v>-0.6848693611693335</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>3717763.88888889</v>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="n">
-        <v>1.638611111111103</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>-1.899229480884649</v>
-      </c>
-      <c r="BC31" t="inlineStr"/>
-      <c r="BD31" t="n">
-        <v>-0.5234722222222388</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45527.58333333334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>148</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>-11</v>
-      </c>
-      <c r="P32" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>10</v>
-      </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="n">
-        <v>-0.01304922084827354</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0.1203033582579038</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>2047401.736521054</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>4.359259259259257</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.285185185185185</v>
-      </c>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="n">
-        <v>0.6402777777777828</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0.9507592500535083</v>
-      </c>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="n">
-        <v>2.931970335618658</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>-1268780.864197532</v>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="n">
-        <v>3.563580246913602</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.614030634437341</v>
-      </c>
-      <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="n">
-        <v>0.4543209876542846</v>
-      </c>
-      <c r="BE32" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE5"/>
+  <dimension ref="A1:BE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,92 +620,92 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,136 +769,126 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-7</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.93</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>-11</v>
+        <v>-0.5499999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>-0.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
         <v>-6</v>
       </c>
       <c r="AI2" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>71.44444444444444</v>
+        <v>73.98495370370371</v>
       </c>
       <c r="AK2" t="n">
-        <v>75.125</v>
+        <v>74.25231481481481</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.644118720391095</v>
+        <v>-2.582092972816664</v>
       </c>
       <c r="AM2" t="n">
-        <v>-4.063093249934681</v>
+        <v>0.8003062945826112</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.6085353535353535</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-4</v>
-      </c>
+        <v>0.9721275252525254</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>1.4027777777778</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.022222222222222</v>
-      </c>
+        <v>53072821.96969697</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-20951843.43434343</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-13522684.54794589</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
+        <v>-2.34513888888889</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-6.345016969745231</v>
+        <v>8.486395202020191</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>50038648.55247092</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-10</v>
-      </c>
+        <v>7.190593434343427</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>-0.563460520723948</v>
+        <v>-3.788931141957477</v>
       </c>
       <c r="BA2" t="n">
-        <v>-6.912777777777777</v>
+        <v>0.1103219696969688</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1.12084969094559</v>
+        <v>6.728271881627151</v>
       </c>
       <c r="BC2" t="n">
-        <v>-4600000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-7.160252525252517</v>
-      </c>
+        <v>7.658457120365</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -906,15 +896,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
@@ -931,7 +921,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -967,121 +957,113 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF3" t="n">
         <v>-2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>-0.4299999999999999</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.8300000000000001</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AG3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-2</v>
       </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-9</v>
-      </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="AJ3" t="n">
         <v>77.11111111111111</v>
       </c>
       <c r="AK3" t="n">
-        <v>77.66666666666667</v>
+        <v>73.18981481481481</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.363352130325808</v>
+        <v>0.16494745592572</v>
       </c>
       <c r="AM3" t="n">
-        <v>-2.576640559732652</v>
+        <v>-0.5423458184327754</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.03919753086419764</v>
+        <v>-0.3832267115600447</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>3.596604938271554</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-2.386419753086425</v>
-      </c>
+        <v>-13001295.59483726</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>5191658.950617285</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>118937.2650375934</v>
-      </c>
+        <v>0.5663580246913504</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>1.958513993316629</v>
+        <v>-3.175123456790132</v>
       </c>
       <c r="AW3" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>-74</v>
-      </c>
+        <v>-11026334.76653178</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-3.110869809203137</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-0.2529793233082711</v>
+        <v>3.66178775330954</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.519598765432093</v>
+        <v>1.554938271604897</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.000271512113613</v>
+        <v>-3.402319075851679</v>
       </c>
       <c r="BC3" t="n">
-        <v>-550000</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0.6591049382715966</v>
-      </c>
+        <v>-2.871044137022395</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1089,32 +1071,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,134 +1123,126 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>43</v>
+        <v>-2</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
-        <v>2.03</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1200000000000001</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1300000000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.4299999999999999</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>4</v>
       </c>
-      <c r="Y4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-2</v>
-      </c>
       <c r="AI4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>-7.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>75.87819865319865</v>
+      </c>
       <c r="AK4" t="n">
-        <v>74.66666666666667</v>
+        <v>78.27916666666667</v>
       </c>
       <c r="AL4" t="n">
-        <v>-2.018383706146821</v>
+        <v>1.695573783427797</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.874470259424029</v>
+        <v>0.5189072549136153</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.255555555555556</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-5.25</v>
-      </c>
+        <v>0.5959090909090907</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-1.507856341189665</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.6615319865319869</v>
-      </c>
+        <v>-10365118.68686868</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>21506467.45230078</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>24441052.16555215</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>2.631035353535353</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>4.859859225778933</v>
+        <v>-2.42886363636363</v>
       </c>
       <c r="AW4" t="n">
-        <v>-142</v>
+        <v>-2857123.335347591</v>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-148</v>
-      </c>
+        <v>-0.9673232323232241</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>0.8511941443275497</v>
+        <v>3.817938367774815</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.497699214365866</v>
+        <v>2.931919191919206</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.9385767047645004</v>
+        <v>0.9971520470749908</v>
       </c>
       <c r="BC4" t="n">
-        <v>87000000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.622699214365895</v>
-      </c>
+        <v>-0.5806107990661928</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1276,187 +1250,3560 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>148</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.05999999999999994</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>77.01580176767676</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>79.44165088383838</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-2.654923355237663</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.1313420991446299</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.03125</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>-6254513.888888888</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>-1.327546296296294</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-1.344328703703695</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-2220547.09299988</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-3.700231481481481</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>2.135010721020961</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.425347222222257</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-2.497496839246068</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.8755408730304453</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>148</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>77.47027777777777</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>74.01041666666667</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2923361991543771</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.1657254361799816</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.2199074074074072</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>2318364.197530866</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-0.196759259259256</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>-0.3305555555555628</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>362490.4483143119</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.6844135802469253</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>0.4955978365069598</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.4637345679012697</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.9026788867697917</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.2216315250406069</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>148</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.1849999999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>78.59328703703703</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>77.15174897119341</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-3.683217708933654</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.5850128077546808</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.4494949494949496</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>-513251.2626262642</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-4.231060606060609</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>-1.401830808080817</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-4409620.674276489</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-4.422348484848499</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>-2.654992712395966</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-3.966224747474797</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-5.666011767944823</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-2.965940801759288</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>81.75883838383838</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.8527942247263951</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.09275264209474754</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>-5340827.246183546</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>0.7476910473427552</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>-5.935140932104758</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-3.714371863946155</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.9800000000000001</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>76.78263888888888</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>79.47839506172841</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-1.884180865860433</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.2740940255994437</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.1861111111111111</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>-2758888.888888889</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-1.930555555555554</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>-1.218055555555551</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-2377412.516376525</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-3.390277777777783</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>-0.7823659321415164</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.444444444444457</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-3.237414733815655</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-1.515458839406207</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.3750000000000001</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>73.13257575757575</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>75.15777777777777</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-1.899082913000164</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.5645632577627127</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.9863425925925922</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>-10345833.33333333</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>-3.24583333333333</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-1.719212962962956</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-6727195.715738622</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-3.527546296296293</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>1.078657028965125</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.175925925925952</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-3.293618387789195</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-1.649625922416661</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>28</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75.03287037037036</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>77.94165088383838</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-2.687312435328348</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.9687998058563656</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.560185185185185</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>41152469.13580246</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0.4398148148148167</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>9.896604938271594</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>33102331.92932426</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.84567901234568</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0.4935943374267424</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.898919753086403</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.652848040420849</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>9.542369286475605</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.184039411441823</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1.623066759540545</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.828030303030303</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>-54687752.52525253</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-0.54548611111111</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>-8.774589646464648</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-54370197.62963701</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-8.817329545454541</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>-0.9901019827340463</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-2.386363636363626</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-9.309962174534462</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-11.39010498137316</v>
+      </c>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>ETdxjU8a</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.7649999999999999</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>82.12083333333332</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="n">
+        <v>-1.776468892097657</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.08323282567119694</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>13535750</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-1.689999999999998</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>4.642499999999998</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6785259.052323735</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.947499999999991</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>-1.657788942791029</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.2524999999999977</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.95118055251038</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.777739772362708</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>11</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>78.38499999999999</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.07593279470215109</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.8565750443227222</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.331944444444444</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>29062083.33333333</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>1.761111111111109</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>8.347222222222214</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>17495615.25975458</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10.19027777777777</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>1.337529453690451</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-2.86250000000004</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.497665606094401</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.713294728147659</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>148</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>75.97829861111111</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.7292855656928872</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.6392108977978546</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.7057575757575756</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="n">
+        <v>20833510.1010101</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>2.12962962962963</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>5.060925925925929</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>12707030.41014096</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.836178451178441</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>-0.3250470956706977</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.4916666666667027</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.704384718383565</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.959744226343204</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>77.94165088383838</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>-0.6440096664132717</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.1568369706879418</v>
+      </c>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>440869.7286897043</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>-1.519312467405655</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>1.433329246979667</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.885241004812485</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>1.251424577874975</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.2984094452738448</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.3089856902356902</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="n">
+        <v>12980265.15151515</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>2.713005050505053</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>4.324978956228961</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8491919.609548189</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.994802188552185</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="n">
+        <v>1.731717582532639</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.735900673400693</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.755256978545532</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.780961902426185</v>
+      </c>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>-0.585</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.4650000000000001</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>5.910645177733702</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.7805770628661723</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-1.425</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-236750000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-37458209.87654321</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.735185185185184</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-201</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-8.90540123456789</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-30239919.72251388</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-5.969290123456787</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-0.7155939016427055</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-2.198456790123458</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-2.967235127284027</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-8.782776418590444</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-198</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>148</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H19" t="n">
         <v>1481</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>20242025</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>25GxoIxN</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-11</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.9450000000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.1950000000000001</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>1.361944893547399</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.557616654781482</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.6550505050505049</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-10600000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-3724663.299663303</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.01742424242424079</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-2.364562289562301</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-4423139.057103589</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-1.539478114478115</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-1.662996962879163</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-1.557491582491593</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-1.437064840231486</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-3.68594842736718</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>148</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.4349999999999999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.024376982197836</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.435626184648138</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.1759259259259263</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1974266.975308644</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>-0.1759259259259203</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>158</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>0.84652777777778</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2138649.889871128</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.8989197530864175</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>2.556224994710107</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.578317901234641</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.669777374484667</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.953199895298113</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>155</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>148</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>-0.4399999999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>2.975799457082601</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.7960786904387993</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.084166666666666</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-2400000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8933000</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>3.438611111111108</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="n">
+        <v>1.176944444444445</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5800395.040243404</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.735833333333332</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>1.716483942165723</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-2.039166666666688</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.004139307133983</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.8617386710595696</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-126</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>148</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>-0.6399999999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.7999999999999999</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>-4.052976916612504</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.954102564102564</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.8871527777777777</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-26650000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-7869444.444444444</v>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>-4.218171296296294</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-230</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>-1.632523148148152</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>-6552096.170165966</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>-5.326967592592595</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="n">
+        <v>-2.644022403670562</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.1493055555555998</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-5.079187132153379</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-2.856106987977711</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>-216</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>148</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>0.7700000000000001</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.05999999999999983</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="n">
+        <v>0.02333872071466914</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-0.1265574101494147</v>
+      </c>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="n">
+        <v>-13800000</v>
+      </c>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="n">
+        <v>-3962070.649928365</v>
+      </c>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="n">
+        <v>3.212791898167808</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="n">
+        <v>-4.737732797098019</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-2.63910690366302</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>148</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
         <v>26</v>
       </c>
-      <c r="AA5" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.5633684657432205</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.592787199002018</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.711132154882155</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>266200000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>61995970.11784512</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>-0.03437500000000071</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>354</v>
+      </c>
+      <c r="AT24" t="n">
         <v>4</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AU24" t="n">
+        <v>8.400000000000006</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11.74391835016834</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>57891398.55087567</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13.32774621212121</v>
+      </c>
+      <c r="AY24" t="n">
         <v>-3</v>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-1.129632302174169</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1.377107872191615</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.09404269972451806</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2.333333333333343</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.9808654729108923</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.9299242424242458</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>777757.116620753</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>519078.128643021</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.333333333333332</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.4277985132889484</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>151</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>139</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.0495543763785391</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.2164141414141483</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.3471943254778296</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8300000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-1.379120752984377</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="AZ24" t="n">
+        <v>-0.7033774480281068</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.194812710437674</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>12.61436572465281</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>12.14397088022369</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>342</v>
+      </c>
+      <c r="BE24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE24"/>
+  <dimension ref="A1:BE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
@@ -769,12 +769,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -793,102 +793,100 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3</v>
       </c>
-      <c r="X2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.5499999999999999</v>
-      </c>
       <c r="AA2" t="n">
-        <v>-0.57</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>26</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4</v>
+        <v>-0.02499999999999991</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="AH2" t="n">
-        <v>-6</v>
+        <v>14.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1</v>
+        <v>-14.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>73.98495370370371</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>74.25231481481481</v>
-      </c>
+        <v>74.37847222222223</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-2.582092972816664</v>
+        <v>-2.390702160493827</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8003062945826112</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.9721275252525254</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>53072821.96969697</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>0.7762524755945817</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>54177230.63973063</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>7.364053731762056</v>
+      </c>
       <c r="AR2" t="n">
-        <v>-2.34513888888889</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>-4.080846492688636</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.1779250841750866</v>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>8.486395202020191</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>50038648.55247092</v>
-      </c>
+        <v>7.376735910288545</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>7.190593434343427</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>-3.788931141957477</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.1103219696969688</v>
-      </c>
+        <v>6.708602143470571</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>48602586.34640213</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>6.728271881627151</v>
+        <v>8.673284932659925</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.658457120365</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+        <v>-2.152552053209956</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.012454405162738</v>
+      </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -904,7 +902,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
@@ -948,12 +946,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -972,98 +970,102 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="U3" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y3" t="n">
         <v>-1</v>
       </c>
-      <c r="V3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-0.48</v>
+        <v>-3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.78</v>
+        <v>-1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-35</v>
+        <v>-0.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>35</v>
+        <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6</v>
+        <v>-0.93</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2</v>
+        <v>-26.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5</v>
+        <v>26.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77.11111111111111</v>
+        <v>76.44444444444444</v>
       </c>
       <c r="AK3" t="n">
         <v>73.18981481481481</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.16494745592572</v>
+        <v>0.5104797979797979</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.5423458184327754</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-0.3832267115600447</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>-13001295.59483726</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>-0.5566780167570684</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-13224286.3292011</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-3.311971992653795</v>
+      </c>
       <c r="AR3" t="n">
-        <v>0.5663580246913504</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>3.230413109069247</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.236111111111086</v>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-3.175123456790132</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-11026334.76653178</v>
-      </c>
+        <v>-2.817615882141581</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-3.110869809203137</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>3.66178775330954</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.554938271604897</v>
-      </c>
+        <v>-3.218774917440925</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-10817766.45442282</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-3.402319075851679</v>
+        <v>-3.314520202020191</v>
       </c>
       <c r="BC3" t="n">
-        <v>-2.871044137022395</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>0.1938916265991359</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.3861685032139575</v>
+      </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1147,102 +1149,102 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1300000000000001</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.4299999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI4" t="n">
         <v>5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.1300000000000001</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.4299999999999999</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-7.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>75.87819865319865</v>
       </c>
       <c r="AK4" t="n">
-        <v>78.27916666666667</v>
+        <v>74.4375</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.695573783427797</v>
+        <v>2.631035353535353</v>
       </c>
       <c r="AM4" t="n">
         <v>0.5189072549136153</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0.5959090909090907</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
         <v>-10365118.68686868</v>
       </c>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>-0.9673232323232241</v>
+      </c>
       <c r="AR4" t="n">
-        <v>2.631035353535353</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>3.817938367774815</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.931919191919206</v>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
+        <v>-0.5806107990661928</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>0.9971520470749908</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-2857123.335347591</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="n">
         <v>-2.42886363636363</v>
       </c>
-      <c r="AW4" t="n">
-        <v>-2857123.335347591</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-0.9673232323232241</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>3.817938367774815</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.931919191919206</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.9971520470749908</v>
-      </c>
       <c r="BC4" t="n">
-        <v>-0.5806107990661928</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+        <v>1.695573783427797</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.5959090909090907</v>
+      </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1258,7 +1260,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
@@ -1302,12 +1304,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1326,102 +1328,102 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>-1</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.05999999999999994</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>12</v>
-      </c>
       <c r="AD5" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-6</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6666666666666667</v>
+        <v>-4.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>-0.35</v>
       </c>
       <c r="AG5" t="n">
-        <v>-7</v>
+        <v>-0.7249999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5</v>
+        <v>-16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>-12</v>
+        <v>16.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77.01580176767676</v>
+        <v>77.23445821854912</v>
       </c>
       <c r="AK5" t="n">
-        <v>79.44165088383838</v>
+        <v>79.5283810325477</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2.654923355237663</v>
+        <v>-1.327546296296294</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.1313420991446299</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.03125</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
+        <v>-0.1323889213003129</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
         <v>-6254513.888888888</v>
       </c>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>-3.700231481481481</v>
+      </c>
       <c r="AR5" t="n">
-        <v>-1.327546296296294</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>2.077715374088314</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.425347222222257</v>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
+        <v>0.7145609668241946</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>-2.520235221825416</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-2399934.586709849</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
         <v>-1.344328703703695</v>
       </c>
-      <c r="AW5" t="n">
-        <v>-2220547.09299988</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-3.700231481481481</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="n">
-        <v>2.135010721020961</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.425347222222257</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-2.497496839246068</v>
-      </c>
       <c r="BC5" t="n">
-        <v>0.8755408730304453</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+        <v>-2.559887032900036</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.03125</v>
+      </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1505,52 +1507,52 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>-0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="Z6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.375</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AG6" t="n">
         <v>-0.07999999999999996</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AH6" t="n">
         <v>-3</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AI6" t="n">
         <v>3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-1</v>
       </c>
       <c r="AJ6" t="n">
         <v>77.47027777777777</v>
@@ -1559,48 +1561,48 @@
         <v>74.01041666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.2923361991543771</v>
+        <v>-0.196759259259256</v>
       </c>
       <c r="AM6" t="n">
         <v>-0.1657254361799816</v>
       </c>
-      <c r="AN6" t="n">
-        <v>-0.2199074074074072</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
         <v>2318364.197530866</v>
       </c>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>-0.6844135802469253</v>
+      </c>
       <c r="AR6" t="n">
-        <v>-0.196759259259256</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+        <v>0.4955978365069598</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.4637345679012697</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
+        <v>-0.2216315250406069</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-0.9026788867697917</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>362490.4483143119</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
         <v>-0.3305555555555628</v>
       </c>
-      <c r="AW6" t="n">
-        <v>362490.4483143119</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.6844135802469253</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="n">
-        <v>0.4955978365069598</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.4637345679012697</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.9026788867697917</v>
-      </c>
       <c r="BC6" t="n">
-        <v>-0.2216315250406069</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
+        <v>0.2923361991543771</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.2199074074074072</v>
+      </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1608,7 +1610,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1616,24 +1618,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1660,124 +1662,106 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
         <v>-1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>9</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="Y7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>-1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.1849999999999999</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.666666666666667</v>
-      </c>
       <c r="AF7" t="n">
-        <v>4</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>-5</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>78.59328703703703</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
-        <v>77.15174897119341</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-3.683217708933654</v>
-      </c>
+        <v>81.75883838383838</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
-        <v>-0.5850128077546808</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-0.4494949494949496</v>
-      </c>
+        <v>-0.08898469951101551</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>-513251.2626262642</v>
-      </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>-4.231060606060609</v>
+        <v>0.6555375384419619</v>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>-1.401830808080817</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-4409620.674276489</v>
-      </c>
+        <v>-3.553373629079886</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-4.422348484848499</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="n">
-        <v>-2.654992712395966</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-3.966224747474797</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-5.666011767944823</v>
-      </c>
+        <v>-5.758743774929926</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-5106239.328347735</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>-2.965940801759288</v>
+        <v>-0.9594229686721967</v>
       </c>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
@@ -1787,7 +1771,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1795,24 +1779,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1839,108 +1823,126 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.405</v>
+        <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.405</v>
+        <v>-0.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5.5</v>
+        <v>-1</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.3333333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.5</v>
+        <v>-0.1849999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.5</v>
+        <v>1.07</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>78.59328703703703</v>
+      </c>
       <c r="AK8" t="n">
-        <v>81.75883838383838</v>
+        <v>77.15174897119341</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.8527942247263951</v>
+        <v>-4.231060606060609</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.09275264209474754</v>
+        <v>-0.5850128077546808</v>
       </c>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>-513251.2626262642</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>-4.422348484848499</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-2.654992712395966</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-3.966224747474797</v>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>-5340827.246183546</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="n">
-        <v>0.7476910473427552</v>
-      </c>
+      <c r="AV8" t="n">
+        <v>-2.965940801759288</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-5.666011767944823</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-4409620.674276489</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-5.935140932104758</v>
+        <v>-1.401830808080817</v>
       </c>
       <c r="BC8" t="n">
-        <v>-3.714371863946155</v>
-      </c>
-      <c r="BD8" t="inlineStr"/>
+        <v>-3.683217708933654</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.4494949494949496</v>
+      </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1956,7 +1958,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
@@ -2000,7 +2002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2024,102 +2026,102 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-2</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="V9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.24</v>
+        <v>-0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.9800000000000001</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-21</v>
+        <v>0.5</v>
       </c>
       <c r="AD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.3100000000000001</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF9" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-2</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>76.78263888888888</v>
+        <v>77.56342592592593</v>
       </c>
       <c r="AK9" t="n">
-        <v>79.47839506172841</v>
+        <v>77.6522633744856</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.884180865860433</v>
+        <v>-2.025757575757577</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.2740940255994437</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-0.1861111111111111</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>-2758888.888888889</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
+        <v>-0.2742971148326216</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>-2775782.828282829</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>-3.431818181818173</v>
+      </c>
       <c r="AR9" t="n">
-        <v>-1.930555555555554</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+        <v>-0.462483751091554</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.505808080808094</v>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>-1.218055555555551</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-2377412.516376525</v>
-      </c>
+        <v>-1.557325990948755</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>-3.390277777777783</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="n">
-        <v>-0.7823659321415164</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.444444444444457</v>
-      </c>
+        <v>-3.360098043135466</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-2540222.784128066</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-3.237414733815655</v>
+        <v>-1.217171717171709</v>
       </c>
       <c r="BC9" t="n">
-        <v>-1.515458839406207</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
+        <v>-1.874172308975428</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.2007575757575757</v>
+      </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2203,102 +2205,102 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
         <v>-1</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AC10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V10" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>0.3750000000000001</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AH10" t="n">
         <v>-3</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AI10" t="n">
         <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1</v>
       </c>
       <c r="AJ10" t="n">
         <v>73.13257575757575</v>
       </c>
       <c r="AK10" t="n">
-        <v>75.15777777777777</v>
+        <v>71.93055555555556</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.899082913000164</v>
+        <v>-3.24583333333333</v>
       </c>
       <c r="AM10" t="n">
         <v>-0.5645632577627127</v>
       </c>
-      <c r="AN10" t="n">
-        <v>-0.9863425925925922</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
         <v>-10345833.33333333</v>
       </c>
-      <c r="AQ10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>-3.527546296296293</v>
+      </c>
       <c r="AR10" t="n">
-        <v>-3.24583333333333</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+        <v>1.078657028965125</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.175925925925952</v>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
+        <v>-1.649625922416661</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-3.293618387789195</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-6727195.715738622</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="n">
         <v>-1.719212962962956</v>
       </c>
-      <c r="AW10" t="n">
-        <v>-6727195.715738622</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-3.527546296296293</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="n">
-        <v>1.078657028965125</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.175925925925952</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-3.293618387789195</v>
-      </c>
       <c r="BC10" t="n">
-        <v>-1.649625922416661</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
+        <v>-1.899082913000164</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.9863425925925922</v>
+      </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
@@ -2314,7 +2316,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
@@ -2363,7 +2365,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -2385,99 +2387,99 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC11" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1.515</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-18.5</v>
-      </c>
       <c r="AD11" t="n">
-        <v>0.6666666666666667</v>
+        <v>3.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-6.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>-4.5</v>
+        <v>1.415</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3</v>
+        <v>-23</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75.03287037037036</v>
+        <v>75.04671717171716</v>
       </c>
       <c r="AK11" t="n">
-        <v>77.94165088383838</v>
+        <v>78.72222222222223</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.687312435328348</v>
+        <v>0.4656084656084687</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.9687998058563656</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.560185185185185</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="n">
-        <v>41152469.13580246</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
+        <v>0.9776386478669989</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>40941225.74955908</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>10.6770282186949</v>
+      </c>
       <c r="AR11" t="n">
-        <v>0.4398148148148167</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+        <v>0.6461755110807701</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.790123456790127</v>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>9.896604938271594</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>33102331.92932426</v>
-      </c>
+        <v>9.563937431639999</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>10.84567901234568</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="n">
-        <v>0.4935943374267424</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.898919753086403</v>
-      </c>
+        <v>7.567654246420233</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>33056369.72962</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>7.652848040420849</v>
+        <v>9.800044091710745</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.542369286475605</v>
-      </c>
-      <c r="BD11" t="inlineStr"/>
+        <v>-2.67601783025032</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.563492063492063</v>
+      </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
@@ -2493,7 +2495,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
@@ -2537,12 +2539,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -2561,102 +2563,100 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.03000000000000003</v>
+        <v>-1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>-17</v>
+        <v>-0.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>-0.5700000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>-10.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>75.11111111111111</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
-        <v>73.5</v>
+        <v>74.09027777777777</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.184039411441823</v>
+        <v>-0.4999228395061728</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1.623066759540545</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1.828030303030303</v>
-      </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="n">
-        <v>-54687752.52525253</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
+        <v>-1.576164586595301</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>-55792161.19528619</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-8.99078984287317</v>
+      </c>
       <c r="AR12" t="n">
-        <v>-0.54548611111111</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+        <v>-0.770222581706264</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-2.453966750841744</v>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="n">
-        <v>-8.774589646464648</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-54370197.62963701</v>
-      </c>
+        <v>-10.98992227743879</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>-8.817329545454541</v>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="n">
-        <v>-0.9901019827340463</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-2.386363636363626</v>
-      </c>
+        <v>-8.997151760399291</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-52413734.85811156</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>-9.309962174534462</v>
+        <v>-8.961479377104382</v>
       </c>
       <c r="BC12" t="n">
-        <v>-11.39010498137316</v>
-      </c>
-      <c r="BD12" t="inlineStr"/>
+        <v>0.9984773870250301</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-1.868357182940516</v>
+      </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
@@ -2740,100 +2740,94 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
         <v>0.5</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-3</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AA13" t="n">
         <v>1</v>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AF13" t="n">
         <v>-0.155</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AG13" t="n">
         <v>0.7649999999999999</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AH13" t="n">
         <v>7.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AI13" t="n">
         <v>-7.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>82.12083333333332</v>
-      </c>
+      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>-1.776468892097657</v>
+        <v>-1.689999999999998</v>
       </c>
       <c r="AM13" t="n">
         <v>0.08323282567119694</v>
       </c>
-      <c r="AN13" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
         <v>13535750</v>
       </c>
-      <c r="AQ13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>3.947499999999991</v>
+      </c>
       <c r="AR13" t="n">
-        <v>-1.689999999999998</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+        <v>-1.657788942791029</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.2524999999999977</v>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="n">
+        <v>3.777739772362708</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>1.95118055251038</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6785259.052323735</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="n">
         <v>4.642499999999998</v>
       </c>
-      <c r="AW13" t="n">
-        <v>6785259.052323735</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.947499999999991</v>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="n">
-        <v>-1.657788942791029</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-0.2524999999999977</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.95118055251038</v>
-      </c>
       <c r="BC13" t="n">
-        <v>3.777739772362708</v>
-      </c>
-      <c r="BD13" t="inlineStr"/>
+        <v>-1.776468892097657</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.1575</v>
+      </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2841,7 +2835,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2849,24 +2843,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2893,22 +2887,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -2917,98 +2911,114 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" t="n">
         <v>3</v>
       </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="n">
-        <v>0.71</v>
-      </c>
       <c r="AA14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>-9</v>
+        <v>0.425</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>-4</v>
+        <v>-28.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>78.38499999999999</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>71.44444444444444</v>
-      </c>
+        <v>75.125</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.07593279470215109</v>
+        <v>2.20664983164983</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.8565750443227222</v>
+        <v>0.6447371798162314</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.331944444444444</v>
-      </c>
-      <c r="AO14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>20663418.27364555</v>
+      </c>
       <c r="AP14" t="n">
-        <v>29062083.33333333</v>
-      </c>
-      <c r="AQ14" t="inlineStr"/>
+        <v>232</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.839286807468611</v>
+      </c>
       <c r="AR14" t="n">
-        <v>1.761111111111109</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
+        <v>-0.08489129909455073</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.4444444444444855</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>254</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="AV14" t="n">
-        <v>8.347222222222214</v>
+        <v>3.887646266372613</v>
       </c>
       <c r="AW14" t="n">
-        <v>17495615.25975458</v>
+        <v>51400000</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.19027777777777</v>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+        <v>4.420652774288087</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12623815.52437057</v>
+      </c>
       <c r="AZ14" t="n">
-        <v>1.337529453690451</v>
+        <v>3</v>
       </c>
       <c r="BA14" t="n">
-        <v>-2.86250000000004</v>
+        <v>-1.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.497665606094401</v>
+        <v>4.991835016835012</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.713294728147659</v>
-      </c>
-      <c r="BD14" t="inlineStr"/>
+        <v>0.6463202112359596</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.7097796143250685</v>
+      </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
@@ -3016,7 +3026,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -3024,24 +3034,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,22 +3078,22 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>IJEltJ2H</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -3092,98 +3102,110 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3</v>
-      </c>
-      <c r="W15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1</v>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-30</v>
-      </c>
       <c r="AD15" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AE15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1749999999999999</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>75.28472222222223</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.761111111111109</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.8613094428898413</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1</v>
       </c>
-      <c r="AF15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="AO15" t="n">
+        <v>29062083.33333333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10.19027777777777</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.387150006748499</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-2.86250000000004</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU15" t="n">
         <v>1</v>
       </c>
-      <c r="AI15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>75.97829861111111</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.7292855656928872</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.6392108977978546</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0.7057575757575756</v>
-      </c>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="n">
-        <v>20833510.1010101</v>
-      </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="n">
-        <v>2.12962962962963</v>
-      </c>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="n">
-        <v>5.060925925925929</v>
+        <v>7.706330520990434</v>
       </c>
       <c r="AW15" t="n">
-        <v>12707030.41014096</v>
+        <v>22600000</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.836178451178441</v>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+        <v>7.561455849415879</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>17533832.52036706</v>
+      </c>
       <c r="AZ15" t="n">
-        <v>-0.3250470956706977</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.4916666666667027</v>
+        <v>-7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.704384718383565</v>
+        <v>8.347222222222214</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.959744226343204</v>
-      </c>
-      <c r="BD15" t="inlineStr"/>
+        <v>0.1258213290300212</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.331944444444444</v>
+      </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
@@ -3199,7 +3221,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
@@ -3243,12 +3265,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -3267,86 +3289,94 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB16" t="n">
         <v>-1</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AC16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
         <v>-1</v>
       </c>
-      <c r="W16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>-6</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>77.94165088383838</v>
+        <v>78.72222222222223</v>
       </c>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="n">
-        <v>-0.6440096664132717</v>
-      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
-        <v>0.1568369706879418</v>
+        <v>0.1442301860935764</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
+      <c r="AP16" t="n">
+        <v>69</v>
+      </c>
       <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>-1.579740132158889</v>
+      </c>
       <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>69</v>
+      </c>
       <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>1.702674624781821</v>
+      </c>
       <c r="AW16" t="n">
-        <v>440869.7286897043</v>
-      </c>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
+        <v>1400000</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.342125883805451</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>252244.0105581549</v>
+      </c>
       <c r="AZ16" t="n">
-        <v>-1.519312467405655</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="n">
-        <v>1.433329246979667</v>
-      </c>
+      <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="n">
-        <v>1.885241004812485</v>
+        <v>-0.5486755275454982</v>
       </c>
       <c r="BD16" t="inlineStr"/>
       <c r="BE16" t="n">
@@ -3364,7 +3394,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
@@ -3432,100 +3462,114 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U17" t="n">
         <v>-1</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.5</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AA17" t="n">
         <v>-3.5</v>
       </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0.14</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AG17" t="n">
         <v>-1.015</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AH17" t="n">
         <v>9.5</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
         <v>-9.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-3.5</v>
       </c>
       <c r="AJ17" t="n">
         <v>74.66666666666667</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>1.251424577874975</v>
+        <v>2.713005050505053</v>
       </c>
       <c r="AM17" t="n">
         <v>0.2984094452738448</v>
       </c>
       <c r="AN17" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12980265.15151515</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.994802188552185</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.731717582532639</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.735900673400693</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-1.899999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.780961902426185</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.755256978545532</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8491919.609548189</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.849999999999994</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.324978956228961</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.251424577874975</v>
+      </c>
+      <c r="BD17" t="n">
         <v>0.3089856902356902</v>
       </c>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="n">
-        <v>12980265.15151515</v>
-      </c>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="n">
-        <v>2.713005050505053</v>
-      </c>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="n">
-        <v>4.324978956228961</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8491919.609548189</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>6.994802188552185</v>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="n">
-        <v>1.731717582532639</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.735900673400693</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.755256978545532</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.780961902426185</v>
-      </c>
-      <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
@@ -3541,7 +3585,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
@@ -3585,7 +3629,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3609,109 +3653,113 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB18" t="n">
         <v>-1</v>
       </c>
-      <c r="W18" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
-        <v>-0.585</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.4650000000000001</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-29.5</v>
-      </c>
       <c r="AC18" t="n">
-        <v>29.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>-1.21</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>0.02500000000000013</v>
       </c>
       <c r="AH18" t="n">
-        <v>-1.5</v>
+        <v>-20.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>4</v>
+        <v>20.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>77.66666666666667</v>
+        <v>75.83333333333334</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>5.910645177733702</v>
+        <v>2.830387205387208</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.7805770628661723</v>
+        <v>-0.7851083722001135</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1.425</v>
+        <v>-2</v>
       </c>
       <c r="AO18" t="n">
+        <v>-37441315.93714926</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-198</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-5.927749719416397</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-1.085096635750716</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-2.259820426487096</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-201</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-8.733945059890672</v>
+      </c>
+      <c r="AW18" t="n">
         <v>-236750000</v>
       </c>
-      <c r="AP18" t="n">
-        <v>-37458209.87654321</v>
-      </c>
-      <c r="AQ18" t="n">
+      <c r="AX18" t="n">
+        <v>-2.908342061285694</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-30115326.71537483</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>-2</v>
       </c>
-      <c r="AR18" t="n">
-        <v>2.735185185185184</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>-201</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="BA18" t="n">
         <v>2.75</v>
       </c>
-      <c r="AV18" t="n">
-        <v>-8.90540123456789</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>-30239919.72251388</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>-5.969290123456787</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-0.7155939016427055</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>-2.198456790123458</v>
-      </c>
       <c r="BB18" t="n">
-        <v>-2.967235127284027</v>
+        <v>-8.906285072951732</v>
       </c>
       <c r="BC18" t="n">
-        <v>-8.782776418590444</v>
+        <v>5.850748086520827</v>
       </c>
       <c r="BD18" t="n">
-        <v>-198</v>
+        <v>-1.410353535353536</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -3728,7 +3776,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
@@ -3796,113 +3844,107 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB19" t="n">
         <v>-1</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AC19" t="n">
         <v>-1</v>
       </c>
-      <c r="V19" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AD19" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF19" t="n">
         <v>-0.9450000000000001</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AG19" t="n">
         <v>0.1950000000000001</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AH19" t="n">
         <v>-11.5</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AI19" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>1.361944893547399</v>
+        <v>-0.01742424242424079</v>
       </c>
       <c r="AM19" t="n">
         <v>-0.557616654781482</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="n">
+        <v>-3724663.299663303</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>69</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1.539478114478115</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-1.662996962879163</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-1.557491582491593</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>81</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-3.68594842736718</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-1.437064840231486</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-4423139.057103589</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>-2.364562289562301</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.361944893547399</v>
+      </c>
+      <c r="BD19" t="n">
         <v>-0.6550505050505049</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>-10600000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>-3724663.299663303</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>-0.01742424242424079</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>-2.364562289562301</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>-4423139.057103589</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>-1.539478114478115</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-1.662996962879163</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>-1.557491582491593</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-1.437064840231486</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>-3.68594842736718</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>-9</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -3919,7 +3961,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
@@ -3987,823 +4029,109 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="U20" t="n">
         <v>0.5</v>
       </c>
       <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-0.5</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AA20" t="n">
         <v>3.5</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF20" t="n">
         <v>-0.175</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AG20" t="n">
         <v>0.4349999999999999</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AH20" t="n">
         <v>-14.5</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AI20" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.5</v>
       </c>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
         <v>72</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.024376982197836</v>
+        <v>-0.1759259259259203</v>
       </c>
       <c r="AM20" t="n">
         <v>0.435626184648138</v>
       </c>
-      <c r="AN20" t="n">
-        <v>0.1759259259259263</v>
-      </c>
+      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
-        <v>31000000</v>
+        <v>1974266.975308644</v>
       </c>
       <c r="AP20" t="n">
-        <v>1974266.975308644</v>
-      </c>
-      <c r="AQ20" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.8989197530864175</v>
+      </c>
       <c r="AR20" t="n">
-        <v>-0.1759259259259203</v>
+        <v>2.556224994710107</v>
       </c>
       <c r="AS20" t="n">
+        <v>3.578317901234641</v>
+      </c>
+      <c r="AT20" t="n">
         <v>158</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="n">
+        <v>1.953199895298113</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.669777374484667</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>2138649.889871128</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="n">
         <v>0.84652777777778</v>
       </c>
-      <c r="AW20" t="n">
-        <v>2138649.889871128</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0.8989197530864175</v>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="n">
-        <v>2.556224994710107</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.578317901234641</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>2.669777374484667</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.953199895298113</v>
+        <v>2.024376982197836</v>
       </c>
       <c r="BD20" t="n">
-        <v>155</v>
+        <v>0.1759259259259263</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45529.6875</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>148</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Ii1Om118</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="n">
-        <v>-0.4399999999999999</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="n">
-        <v>2.975799457082601</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.7960786904387993</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.084166666666666</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>-2400000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>8933000</v>
-      </c>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="n">
-        <v>3.438611111111108</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>-156</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="n">
-        <v>1.176944444444445</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5800395.040243404</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.735833333333332</v>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="n">
-        <v>1.716483942165723</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>-2.039166666666688</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.004139307133983</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.8617386710595696</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>-126</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45529.59375</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>148</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="n">
-        <v>-0.6399999999999999</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>-0.7999999999999999</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
-        <v>-4.052976916612504</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>-0.954102564102564</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>-0.8871527777777777</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>-26650000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>-7869444.444444444</v>
-      </c>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="n">
-        <v>-4.218171296296294</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>-230</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="n">
-        <v>-1.632523148148152</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>-6552096.170165966</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>-5.326967592592595</v>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="n">
-        <v>-2.644022403670562</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0.1493055555555998</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>-5.079187132153379</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>-2.856106987977711</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>-216</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45529.58333333334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>148</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-0.05999999999999983</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="n">
-        <v>0.02333872071466914</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>-0.1265574101494147</v>
-      </c>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="n">
-        <v>-13800000</v>
-      </c>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="n">
-        <v>-3962070.649928365</v>
-      </c>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="n">
-        <v>3.212791898167808</v>
-      </c>
-      <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="n">
-        <v>-4.737732797098019</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>-2.63910690366302</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>148</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>26</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>18</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3</v>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="n">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>76.55555555555556</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>72.11111111111111</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>-0.5633684657432205</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.592787199002018</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.711132154882155</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>266200000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>61995970.11784512</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>-0.03437500000000071</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>354</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.400000000000006</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11.74391835016834</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>57891398.55087567</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>13.32774621212121</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>-0.7033774480281068</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.194812710437674</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>12.61436572465281</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>12.14397088022369</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>342</v>
-      </c>
-      <c r="BE24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -793,25 +793,25 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>-0.3333333333333334</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="X2" t="n">
-        <v>-3.5</v>
+        <v>-0.02499999999999991</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="AA2" t="n">
         <v>2</v>
@@ -823,70 +823,70 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2</v>
       </c>
-      <c r="AF2" t="n">
-        <v>-0.02499999999999991</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.04000000000000004</v>
-      </c>
       <c r="AH2" t="n">
-        <v>14.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>-14.5</v>
+        <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>74.37847222222223</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
+        <v>-2.152552053209956</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.012454405162738</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
         <v>-2.390702160493827</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>0.1779250841750866</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>48602586.34640213</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.673284932659925</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.364053731762056</v>
+      </c>
+      <c r="AX2" t="n">
         <v>0.7762524755945817</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
+      <c r="AY2" t="n">
+        <v>7.376735910288545</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>54177230.63973063</v>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>7.364053731762056</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-4.080846492688636</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.1779250841750866</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>7.376735910288545</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>6.708602143470571</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>48602586.34640213</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>8.673284932659925</v>
+        <v>-4.080846492688636</v>
       </c>
       <c r="BC2" t="n">
-        <v>-2.152552053209956</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.012454405162738</v>
-      </c>
+        <v>6.708602143470571</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -970,28 +970,28 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="V3" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="V3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1</v>
+        <v>-0.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3.5</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.5</v>
+        <v>-7.5</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.5</v>
@@ -1000,22 +1000,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>-7.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.4199999999999999</v>
+        <v>-3.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.93</v>
+        <v>-1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>-26.5</v>
+        <v>-2</v>
       </c>
       <c r="AI3" t="n">
-        <v>26.5</v>
+        <v>-1</v>
       </c>
       <c r="AJ3" t="n">
         <v>76.44444444444444</v>
@@ -1024,48 +1024,48 @@
         <v>73.18981481481481</v>
       </c>
       <c r="AL3" t="n">
+        <v>0.1938916265991359</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.3861685032139575</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
         <v>0.5104797979797979</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>1.236111111111086</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>-10817766.45442282</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-3.314520202020191</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-3.311971992653795</v>
+      </c>
+      <c r="AX3" t="n">
         <v>-0.5566780167570684</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
+      <c r="AY3" t="n">
+        <v>-2.817615882141581</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>-13224286.3292011</v>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>-3.311971992653795</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.230413109069247</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.236111111111086</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-2.817615882141581</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-3.218774917440925</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-10817766.45442282</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-3.314520202020191</v>
+        <v>3.230413109069247</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1938916265991359</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-0.3861685032139575</v>
-      </c>
+        <v>-3.218774917440925</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1149,28 +1149,28 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" t="n">
         <v>-0.3333333333333334</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="V4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="X4" t="n">
-        <v>8.5</v>
+        <v>0.1300000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0.4299999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>-7.5</v>
       </c>
       <c r="AB4" t="n">
         <v>0.5</v>
@@ -1179,22 +1179,22 @@
         <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>-7.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1300000000000001</v>
+        <v>5</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.4299999999999999</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5</v>
+        <v>8.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>75.87819865319865</v>
@@ -1203,48 +1203,48 @@
         <v>74.4375</v>
       </c>
       <c r="AL4" t="n">
+        <v>1.695573783427797</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.5959090909090907</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
         <v>2.631035353535353</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>2.931919191919206</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>-2857123.335347591</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-2.42886363636363</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.9673232323232241</v>
+      </c>
+      <c r="AX4" t="n">
         <v>0.5189072549136153</v>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
+      <c r="AY4" t="n">
+        <v>-0.5806107990661928</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>-10365118.68686868</v>
       </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>-0.9673232323232241</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.817938367774815</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.931919191919206</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>-0.5806107990661928</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>0.9971520470749908</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-2857123.335347591</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>-2.42886363636363</v>
+        <v>3.817938367774815</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.695573783427797</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.5959090909090907</v>
-      </c>
+        <v>0.9971520470749908</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-16.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1340,16 +1340,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>7.5</v>
+        <v>-0.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2.5</v>
+        <v>-0.7249999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>-3.5</v>
+        <v>-6</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AB5" t="n">
         <v>-1</v>
@@ -1358,22 +1358,22 @@
         <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.35</v>
+        <v>-3.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.7249999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>-16.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>16.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>77.23445821854912</v>
@@ -1382,48 +1382,48 @@
         <v>79.5283810325477</v>
       </c>
       <c r="AL5" t="n">
+        <v>-2.559887032900036</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.03125</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
         <v>-1.327546296296294</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>2.425347222222257</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>-2399934.586709849</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-1.344328703703695</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-3.700231481481481</v>
+      </c>
+      <c r="AX5" t="n">
         <v>-0.1323889213003129</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
+      <c r="AY5" t="n">
+        <v>0.7145609668241946</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>-6254513.888888888</v>
       </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>-3.700231481481481</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.077715374088314</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.425347222222257</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>0.7145609668241946</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>-2.520235221825416</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-2399934.586709849</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-1.344328703703695</v>
+        <v>2.077715374088314</v>
       </c>
       <c r="BC5" t="n">
-        <v>-2.559887032900036</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.03125</v>
-      </c>
+        <v>-2.520235221825416</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1507,28 +1507,28 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>0.375</v>
       </c>
       <c r="Y6" t="n">
-        <v>-7</v>
+        <v>-0.07999999999999996</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="AB6" t="n">
         <v>-1.5</v>
@@ -1537,22 +1537,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.07999999999999996</v>
+        <v>-0.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="AJ6" t="n">
         <v>77.47027777777777</v>
@@ -1561,48 +1561,48 @@
         <v>74.01041666666667</v>
       </c>
       <c r="AL6" t="n">
+        <v>0.2923361991543771</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.2199074074074072</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
         <v>-0.196759259259256</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>0.4637345679012697</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>362490.4483143119</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.3305555555555628</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.6844135802469253</v>
+      </c>
+      <c r="AX6" t="n">
         <v>-0.1657254361799816</v>
       </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
+      <c r="AY6" t="n">
+        <v>-0.2216315250406069</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>2318364.197530866</v>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>-0.6844135802469253</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.4955978365069598</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.4637345679012697</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>-0.2216315250406069</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>-0.9026788867697917</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>362490.4483143119</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-0.3305555555555628</v>
+        <v>0.4955978365069598</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.2923361991543771</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.2199074074074072</v>
-      </c>
+        <v>-0.9026788867697917</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1682,28 +1682,28 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>-1</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.5</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
@@ -1712,56 +1712,56 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.7849999999999999</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.02000000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
         <v>81.75883838383838</v>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-0.08898469951101551</v>
-      </c>
+      <c r="AL7" t="n">
+        <v>-0.9594229686721967</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>0.6555375384419619</v>
-      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>-3.553373629079886</v>
-      </c>
+      <c r="AU7" t="n">
+        <v>-5106239.328347735</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-5.758743774929926</v>
+        <v>-0.08898469951101551</v>
       </c>
       <c r="AY7" t="n">
-        <v>-5106239.328347735</v>
+        <v>-3.553373629079886</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>0.6555375384419619</v>
+      </c>
       <c r="BC7" t="n">
-        <v>-0.9594229686721967</v>
+        <v>-5.758743774929926</v>
       </c>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
@@ -1847,25 +1847,25 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V8" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>-0.1849999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
         <v>-0.5</v>
@@ -1877,22 +1877,22 @@
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AF8" t="n">
-        <v>-0.1849999999999999</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="AJ8" t="n">
         <v>78.59328703703703</v>
@@ -1901,48 +1901,48 @@
         <v>77.15174897119341</v>
       </c>
       <c r="AL8" t="n">
+        <v>-3.683217708933654</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.4494949494949496</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
         <v>-4.231060606060609</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-3.966224747474797</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>-4409620.674276489</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-1.401830808080817</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-4.422348484848499</v>
+      </c>
+      <c r="AX8" t="n">
         <v>-0.5850128077546808</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
+      <c r="AY8" t="n">
+        <v>-2.965940801759288</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>-513251.2626262642</v>
       </c>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>-4.422348484848499</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-2.654992712395966</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-3.966224747474797</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-2.965940801759288</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="n">
-        <v>-5.666011767944823</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-4409620.674276489</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-1.401830808080817</v>
+        <v>-2.654992712395966</v>
       </c>
       <c r="BC8" t="n">
-        <v>-3.683217708933654</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-0.4494949494949496</v>
-      </c>
+        <v>-5.666011767944823</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -2026,28 +2026,28 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V9" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="X9" t="n">
-        <v>-8.5</v>
+        <v>-0.07999999999999996</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.5</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="AB9" t="n">
         <v>-1</v>
@@ -2056,22 +2056,22 @@
         <v>0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.07999999999999996</v>
+        <v>-0.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.3100000000000001</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-1.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>77.56342592592593</v>
@@ -2080,48 +2080,48 @@
         <v>77.6522633744856</v>
       </c>
       <c r="AL9" t="n">
+        <v>-1.874172308975428</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.2007575757575757</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
         <v>-2.025757575757577</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>3.505808080808094</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>-2540222.784128066</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-1.217171717171709</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-3.431818181818173</v>
+      </c>
+      <c r="AX9" t="n">
         <v>-0.2742971148326216</v>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
+      <c r="AY9" t="n">
+        <v>-1.557325990948755</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>-2775782.828282829</v>
       </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>-3.431818181818173</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-0.462483751091554</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.505808080808094</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>-1.557325990948755</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>-3.360098043135466</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-2540222.784128066</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-1.217171717171709</v>
+        <v>-0.462483751091554</v>
       </c>
       <c r="BC9" t="n">
-        <v>-1.874172308975428</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-0.2007575757575757</v>
-      </c>
+        <v>-3.360098043135466</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2205,28 +2205,28 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
         <v>-0.3333333333333334</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="V10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>4</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>-1</v>
@@ -2235,22 +2235,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>-2.5</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.3750000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
         <v>73.13257575757575</v>
@@ -2259,48 +2259,48 @@
         <v>71.93055555555556</v>
       </c>
       <c r="AL10" t="n">
+        <v>-1.899082913000164</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.9863425925925922</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
         <v>-3.24583333333333</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>3.175925925925952</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>-6727195.715738622</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-1.719212962962956</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-3.527546296296293</v>
+      </c>
+      <c r="AX10" t="n">
         <v>-0.5645632577627127</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
+      <c r="AY10" t="n">
+        <v>-1.649625922416661</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>-10345833.33333333</v>
       </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>-3.527546296296293</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.078657028965125</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.175925925925952</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-1.649625922416661</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>-3.293618387789195</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-6727195.715738622</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>-1.719212962962956</v>
+        <v>1.078657028965125</v>
       </c>
       <c r="BC10" t="n">
-        <v>-1.899082913000164</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-0.9863425925925922</v>
-      </c>
+        <v>-3.293618387789195</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
@@ -2384,28 +2384,28 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-23</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>-1</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" t="n">
-        <v>-4.5</v>
+        <v>1.415</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="Z11" t="n">
         <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.5</v>
+        <v>-6.5</v>
       </c>
       <c r="AB11" t="n">
         <v>1.5</v>
@@ -2414,22 +2414,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>3.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.415</v>
-      </c>
       <c r="AG11" t="n">
-        <v>0.02000000000000002</v>
+        <v>-3.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>-4.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>-23</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
         <v>75.04671717171716</v>
@@ -2438,48 +2438,48 @@
         <v>78.72222222222223</v>
       </c>
       <c r="AL11" t="n">
+        <v>-2.67601783025032</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.563492063492063</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
         <v>0.4656084656084687</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>1.790123456790127</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>33056369.72962</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.800044091710745</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>10.6770282186949</v>
+      </c>
+      <c r="AX11" t="n">
         <v>0.9776386478669989</v>
       </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
+      <c r="AY11" t="n">
+        <v>9.563937431639999</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>40941225.74955908</v>
       </c>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
-        <v>10.6770282186949</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.6461755110807701</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.790123456790127</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>9.563937431639999</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>7.567654246420233</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>33056369.72962</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>9.800044091710745</v>
+        <v>0.6461755110807985</v>
       </c>
       <c r="BC11" t="n">
-        <v>-2.67601783025032</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.563492063492063</v>
-      </c>
+        <v>7.567654246420233</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
@@ -2563,28 +2563,28 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V12" t="n">
         <v>-1.5</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>1.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
-        <v>3.5</v>
+        <v>-0.5700000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
         <v>-0.5</v>
@@ -2593,70 +2593,70 @@
         <v>1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.5700000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9099999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>-10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
         <v>74.09027777777777</v>
       </c>
       <c r="AL12" t="n">
+        <v>0.9984773870250301</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1.868357182940516</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
         <v>-0.4999228395061728</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-2.453966750841744</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>-52413734.85811156</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-8.961479377104382</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-8.99078984287317</v>
+      </c>
+      <c r="AX12" t="n">
         <v>-1.576164586595301</v>
       </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="n">
+      <c r="AY12" t="n">
+        <v>-10.98992227743879</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>-55792161.19528619</v>
       </c>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="n">
-        <v>-8.99078984287317</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-0.770222581706264</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-2.453966750841744</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>-10.98992227743879</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>-8.997151760399291</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-52413734.85811156</v>
-      </c>
-      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>-8.961479377104382</v>
+        <v>-0.770222581706264</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.9984773870250301</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-1.868357182940516</v>
-      </c>
+        <v>-8.997151760399291</v>
+      </c>
+      <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
@@ -2740,24 +2740,28 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="V13" t="n">
         <v>-1</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>0.5</v>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>-5</v>
+        <v>-0.155</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0.7649999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2765,69 +2769,65 @@
       <c r="AC13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>-0.155</v>
+        <v>-3</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.7649999999999999</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>7.5</v>
+        <v>-5</v>
       </c>
       <c r="AI13" t="n">
-        <v>-7.5</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
+        <v>-1.776468892097657</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
         <v>-1.689999999999998</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-0.2524999999999977</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>6785259.052323735</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.642499999999998</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.947499999999991</v>
+      </c>
+      <c r="AX13" t="n">
         <v>0.08323282567119694</v>
       </c>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="n">
+      <c r="AY13" t="n">
+        <v>3.777739772362708</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>13535750</v>
       </c>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>3.947499999999991</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-1.657788942791029</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-0.2524999999999977</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="n">
-        <v>3.777739772362708</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="n">
-        <v>1.95118055251038</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>6785259.052323735</v>
-      </c>
-      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="n">
-        <v>4.642499999999998</v>
+        <v>-1.657788942791029</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.776468892097657</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0.1575</v>
-      </c>
+        <v>1.95118055251038</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2911,28 +2911,28 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="V14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
       <c r="X14" t="n">
-        <v>-3.5</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>7</v>
+        <v>0.425</v>
       </c>
       <c r="Z14" t="n">
         <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
         <v>0.5</v>
@@ -2941,83 +2941,83 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>3</v>
       </c>
-      <c r="AE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.8300000000000001</v>
-      </c>
       <c r="AG14" t="n">
-        <v>0.425</v>
+        <v>0.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>28.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>-28.5</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
         <v>75.125</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
+        <v>0.6463202112359596</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.7097796143250685</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>51400000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AP14" t="n">
         <v>2.20664983164983</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AQ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.4444444444444855</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>254</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>12623815.52437057</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.991835016835012</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.839286807468611</v>
+      </c>
+      <c r="AX14" t="n">
         <v>0.6447371798162314</v>
       </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
+      <c r="AY14" t="n">
+        <v>3.887646266372613</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>20663418.27364555</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="BA14" t="n">
         <v>232</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>7.839286807468611</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="BB14" t="n">
         <v>-0.08489129909455073</v>
       </c>
-      <c r="AS14" t="n">
-        <v>-0.4444444444444855</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>254</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.887646266372613</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>51400000</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BC14" t="n">
         <v>4.420652774288087</v>
       </c>
-      <c r="AY14" t="n">
-        <v>12623815.52437057</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.991835016835012</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.6463202112359596</v>
-      </c>
       <c r="BD14" t="n">
-        <v>0.7097796143250685</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3102,24 +3102,28 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="V15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>-2</v>
       </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
-        <v>-1</v>
+        <v>0.1749999999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>-10.5</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
@@ -3127,84 +3131,80 @@
       <c r="AC15" t="n">
         <v>1</v>
       </c>
-      <c r="AD15" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-2</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.1749999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06999999999999995</v>
+        <v>-0.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>11.5</v>
+        <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>-11.5</v>
+        <v>-10.5</v>
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="n">
         <v>75.28472222222223</v>
       </c>
       <c r="AL15" t="n">
+        <v>0.1258213290300212</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.331944444444444</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>22600000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.761111111111109</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-2.86250000000004</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>17533832.52036706</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.347222222222214</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>10.19027777777777</v>
+      </c>
+      <c r="AX15" t="n">
         <v>0.8613094428898413</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AY15" t="n">
+        <v>7.706330520990434</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>29062083.33333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.387150006748499</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7.561455849415879</v>
+      </c>
+      <c r="BD15" t="n">
         <v>1</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>29062083.33333333</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10.19027777777777</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.387150006748499</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-2.86250000000004</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7.706330520990434</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>22600000</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.561455849415879</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>17533832.52036706</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.347222222222214</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.1258213290300212</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.331944444444444</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -3289,25 +3289,25 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V16" t="n">
         <v>-0.5</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>1</v>
       </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
-        <v>3.5</v>
+        <v>-0.71</v>
       </c>
       <c r="Y16" t="n">
-        <v>-3</v>
+        <v>-0.1200000000000001</v>
       </c>
       <c r="Z16" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0.5</v>
@@ -3322,61 +3322,61 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG16" t="n">
         <v>0.5</v>
       </c>
-      <c r="AF16" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>-0.1200000000000001</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AJ16" t="n">
         <v>78.72222222222223</v>
       </c>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="n">
+      <c r="AL16" t="n">
+        <v>-0.5486755275454982</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>69</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>252244.0105581549</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
         <v>0.1442301860935764</v>
       </c>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
+        <v>1.702674624781821</v>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="n">
         <v>69</v>
       </c>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="n">
-        <v>-1.579740132158889</v>
-      </c>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="n">
-        <v>69</v>
-      </c>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="n">
-        <v>1.702674624781821</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BB16" t="n">
+        <v>-1.579740132158918</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.342125883805451</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>252244.0105581549</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="n">
-        <v>-0.5486755275454982</v>
       </c>
       <c r="BD16" t="inlineStr"/>
       <c r="BE16" t="n">
@@ -3462,25 +3462,25 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="V17" t="n">
         <v>0.5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>-1</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>0.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1</v>
+        <v>-1.015</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
       <c r="AA17" t="n">
         <v>-3.5</v>
@@ -3492,83 +3492,83 @@
         <v>-1</v>
       </c>
       <c r="AD17" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>-3.5</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-1.015</v>
-      </c>
       <c r="AH17" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>-9.5</v>
+        <v>-1</v>
       </c>
       <c r="AJ17" t="n">
         <v>74.66666666666667</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
+        <v>1.251424577874975</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.3089856902356902</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.849999999999994</v>
+      </c>
+      <c r="AP17" t="n">
         <v>2.713005050505053</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AQ17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.735900673400693</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-1.899999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8491919.609548189</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.324978956228961</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6.994802188552185</v>
+      </c>
+      <c r="AX17" t="n">
         <v>0.2984094452738448</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AY17" t="n">
+        <v>3.780961902426185</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12980265.15151515</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.731717582532639</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.755256978545532</v>
+      </c>
+      <c r="BD17" t="n">
         <v>0.1000000000000001</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>12980265.15151515</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6.994802188552185</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.731717582532639</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.735900673400693</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>-1.899999999999999</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.780961902426185</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>4.755256978545532</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8491919.609548189</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.849999999999994</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.324978956228961</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.251424577874975</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0.3089856902356902</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -3653,28 +3653,28 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V18" t="n">
         <v>-1</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.5</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>-1.21</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>0.02500000000000013</v>
       </c>
       <c r="Z18" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB18" t="n">
         <v>-1</v>
@@ -3683,83 +3683,83 @@
         <v>-0.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>-1.21</v>
+        <v>-3</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.02500000000000013</v>
+        <v>0.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>-20.5</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>20.5</v>
+        <v>4</v>
       </c>
       <c r="AJ18" t="n">
         <v>75.83333333333334</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
+        <v>5.850748086520827</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-1.410353535353536</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-236750000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP18" t="n">
         <v>2.830387205387208</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AQ18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-2.259820426487096</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-201</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-30115326.71537483</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-8.906285072951732</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-5.927749719416397</v>
+      </c>
+      <c r="AX18" t="n">
         <v>-0.7851083722001135</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AY18" t="n">
+        <v>-8.733945059890672</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-37441315.93714926</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-198</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-1.085096635750716</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-2.908342061285694</v>
+      </c>
+      <c r="BD18" t="n">
         <v>-2</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>-37441315.93714926</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-198</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>-5.927749719416397</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-1.085096635750716</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>-2.259820426487096</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>-201</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>-8.733945059890672</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>-236750000</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>-2.908342061285694</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>-30115326.71537483</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-8.906285072951732</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.850748086520827</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>-1.410353535353536</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -3844,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-11.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3856,16 +3856,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-6</v>
+        <v>-0.9450000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>-2.5</v>
+        <v>0.1950000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AB19" t="n">
         <v>-1</v>
@@ -3874,78 +3874,78 @@
         <v>-1</v>
       </c>
       <c r="AD19" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.9450000000000001</v>
+        <v>-3.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.1950000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>-11.5</v>
+        <v>-6</v>
       </c>
       <c r="AI19" t="n">
-        <v>11.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AJ19" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
+        <v>1.361944893547399</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.6550505050505049</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="n">
         <v>-0.01742424242424079</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-1.557491582491593</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>81</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>-4423139.057103589</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-2.364562289562301</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-1.539478114478115</v>
+      </c>
+      <c r="AX19" t="n">
         <v>-0.557616654781482</v>
       </c>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="n">
+      <c r="AY19" t="n">
+        <v>-3.68594842736718</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>-3724663.299663303</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="BA19" t="n">
         <v>69</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>-1.539478114478115</v>
-      </c>
-      <c r="AR19" t="n">
+      <c r="BB19" t="n">
         <v>-1.662996962879163</v>
       </c>
-      <c r="AS19" t="n">
-        <v>-1.557491582491593</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>81</v>
-      </c>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="n">
-        <v>-3.68594842736718</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="AX19" t="n">
+      <c r="BC19" t="n">
         <v>-1.437064840231486</v>
       </c>
-      <c r="AY19" t="n">
-        <v>-4423139.057103589</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="n">
-        <v>-2.364562289562301</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.361944893547399</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>-0.6550505050505049</v>
-      </c>
+      <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
@@ -4029,28 +4029,28 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V20" t="n">
         <v>-1</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.5</v>
+        <v>-0.175</v>
       </c>
       <c r="Y20" t="n">
-        <v>-4</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
         <v>-0.5</v>
@@ -4059,78 +4059,78 @@
         <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.175</v>
+        <v>-0.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.4349999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>-14.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>14.5</v>
+        <v>-4</v>
       </c>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
         <v>72</v>
       </c>
       <c r="AL20" t="n">
+        <v>2.024376982197836</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.1759259259259263</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="n">
         <v>-0.1759259259259203</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AQ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.578317901234641</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>158</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>2138649.889871128</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.84652777777778</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.8989197530864175</v>
+      </c>
+      <c r="AX20" t="n">
         <v>0.435626184648138</v>
       </c>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="n">
+      <c r="AY20" t="n">
+        <v>1.953199895298113</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>1974266.975308644</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="BA20" t="n">
         <v>155</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>0.8989197530864175</v>
-      </c>
-      <c r="AR20" t="n">
+      <c r="BB20" t="n">
         <v>2.556224994710107</v>
       </c>
-      <c r="AS20" t="n">
-        <v>3.578317901234641</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>158</v>
-      </c>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="n">
-        <v>1.953199895298113</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="AX20" t="n">
+      <c r="BC20" t="n">
         <v>2.669777374484667</v>
       </c>
-      <c r="AY20" t="n">
-        <v>2138649.889871128</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA20" t="inlineStr"/>
-      <c r="BB20" t="n">
-        <v>0.84652777777778</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.024376982197836</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0.1759259259259263</v>
-      </c>
+      <c r="BD20" t="inlineStr"/>
       <c r="BE20" t="n">
         <v>0</v>
       </c>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE20"/>
+  <dimension ref="A1:BE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,74 +535,74 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,92 +615,92 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -799,19 +799,19 @@
         <v>-14.5</v>
       </c>
       <c r="V2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>-0.3333333333333334</v>
       </c>
-      <c r="X2" t="n">
-        <v>-0.02499999999999991</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.04000000000000004</v>
-      </c>
       <c r="Z2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
         <v>2</v>
@@ -829,63 +829,63 @@
         <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>-0.02499999999999991</v>
       </c>
       <c r="AG2" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>74.37847222222223</v>
       </c>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-2.152552053209956</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1.012454405162738</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>6.708602143470571</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.7762524755945817</v>
+      </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
         <v>-2.390702160493827</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
+        <v>-2.152552053209956</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.673284932659925</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.364053731762056</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.376735910288545</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>54177230.63973063</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.012454405162738</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>48602586.34640213</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
         <v>0.1779250841750866</v>
       </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>48602586.34640213</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.673284932659925</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.364053731762056</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.7762524755945817</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.376735910288545</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>54177230.63973063</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
+      <c r="BA2" t="n">
         <v>-4.080846492688636</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6.708602143470571</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
@@ -976,22 +976,22 @@
         <v>26.5</v>
       </c>
       <c r="V3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X3" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="X3" t="n">
-        <v>-0.4199999999999999</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.93</v>
-      </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>-3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>-7.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AB3" t="n">
         <v>-0.5</v>
@@ -999,23 +999,19 @@
       <c r="AC3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-3.5</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.5</v>
+        <v>-0.93</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>76.44444444444444</v>
@@ -1023,48 +1019,48 @@
       <c r="AK3" t="n">
         <v>73.18981481481481</v>
       </c>
-      <c r="AL3" t="n">
-        <v>0.1938916265991359</v>
-      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-0.3861685032139575</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>-3.359743532159541</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.5478721004511522</v>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
         <v>0.5104797979797979</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
+        <v>0.1945662297737378</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-3.314520202020191</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-3.311971992653795</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-2.946950297725991</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-13224286.3292011</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.3861685032139575</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-10897442.54569267</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
         <v>1.236111111111086</v>
       </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>-10817766.45442282</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-3.314520202020191</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-3.311971992653795</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.5566780167570684</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-2.817615882141581</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-13224286.3292011</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>3.230413109069247</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-3.218774917440925</v>
-      </c>
+      <c r="BA3" t="n">
+        <v>3.180027106183218</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1081,7 +1077,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
@@ -1125,7 +1121,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1149,101 +1145,101 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-5</v>
+        <v>-4.5</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3333333333333334</v>
+        <v>4.666666666666666</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6666666666666667</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4299999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>-7.5</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="AB4" t="n">
         <v>0.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>5</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>-0.1983333333333333</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.5</v>
+        <v>3.666666666666668</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-3.333333333333334</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75.87819865319865</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.4375</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.695573783427797</v>
-      </c>
+        <v>74.625</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>0.5959090909090907</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>1.115854204947638</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.5104561874837146</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>2.631035353535353</v>
+        <v>2.424999999999997</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>2.931919191919206</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>1.82164188580597</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-2.470202020202024</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-1.159595959595961</v>
+      </c>
       <c r="AU4" t="n">
-        <v>-2857123.335347591</v>
+        <v>-0.4458524948227591</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.42886363636363</v>
+        <v>-10485858.58585859</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.9673232323232241</v>
+        <v>0.5489898989898989</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.5189072549136153</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-0.5806107990661928</v>
-      </c>
+        <v>-2738606.632370936</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>-10365118.68686868</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>3.817938367774815</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.9971520470749908</v>
-      </c>
+        <v>2.780808080808129</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.732023607477856</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1252,7 +1248,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1260,24 +1256,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1304,22 +1300,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>-1</v>
@@ -1328,34 +1324,34 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-16.5</v>
+        <v>-2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>16.5</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.35</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.7249999999999999</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="Z5" t="n">
-        <v>-6</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="AA5" t="n">
-        <v>-4.5</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1364,65 +1360,65 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3.5</v>
+        <v>-0.2883333333333336</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.5</v>
+        <v>-1.085</v>
       </c>
       <c r="AH5" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.5</v>
+        <v>-5.166666666666666</v>
       </c>
       <c r="AJ5" t="n">
-        <v>77.23445821854912</v>
+        <v>77.4584595959596</v>
       </c>
       <c r="AK5" t="n">
-        <v>79.5283810325477</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-2.559887032900036</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-0.03125</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>-1.248050402756292</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.2005991285403048</v>
+      </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-1.327546296296294</v>
+        <v>-0.05555555555555358</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>2.425347222222257</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>0.08763000071823512</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.02611111111110631</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.2736111111111086</v>
+      </c>
       <c r="AU5" t="n">
-        <v>-2399934.586709849</v>
+        <v>-0.5239231329672407</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.344328703703695</v>
+        <v>2923888.88888889</v>
       </c>
       <c r="AW5" t="n">
-        <v>-3.700231481481481</v>
+        <v>-0.1499999999999999</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1323889213003129</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.7145609668241946</v>
-      </c>
+        <v>-91227.38678804785</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-6254513.888888888</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>2.077715374088314</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-2.520235221825416</v>
-      </c>
+        <v>0.02083333333334281</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.8466295523648455</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1431,7 +1427,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1439,24 +1435,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1483,22 +1479,22 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
         <v>-1</v>
@@ -1507,101 +1503,101 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-3</v>
+        <v>-16.5</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>16.5</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6666666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3333333333333333</v>
+        <v>-2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.07999999999999996</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>-3.5</v>
       </c>
       <c r="AA6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB6" t="n">
         <v>-1</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AC6" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.5</v>
+        <v>-0.7249999999999999</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.5</v>
+        <v>-6</v>
       </c>
       <c r="AI6" t="n">
-        <v>-7</v>
+        <v>-4.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>77.47027777777777</v>
+        <v>77.23445821854912</v>
       </c>
       <c r="AK6" t="n">
-        <v>74.01041666666667</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.2923361991543771</v>
-      </c>
+        <v>79.5283810325477</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
-        <v>-0.2199074074074072</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>-2.520235221825416</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.1323889213003129</v>
+      </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>-0.196759259259256</v>
+        <v>-1.327546296296294</v>
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>0.4637345679012697</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+        <v>-2.559887032900036</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-1.344328703703695</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-3.700231481481481</v>
+      </c>
       <c r="AU6" t="n">
-        <v>362490.4483143119</v>
+        <v>0.7145609668241946</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.3305555555555628</v>
+        <v>-6254513.888888888</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.6844135802469253</v>
+        <v>-0.03125</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1657254361799816</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.2216315250406069</v>
-      </c>
+        <v>-2399934.586709849</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>2318364.197530866</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>0.4955978365069598</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.9026788867697917</v>
-      </c>
+        <v>2.425347222222257</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.077715374088314</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1610,7 +1606,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1618,24 +1614,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1662,54 +1658,58 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-5</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="W7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7849999999999999</v>
+        <v>-2</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.02000000000000002</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.5</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1</v>
+        <v>-0.833333333333333</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1718,51 +1718,63 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>-1.103333333333333</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.5</v>
+        <v>0.4066666666666663</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>-3.833333333333334</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
-        <v>81.75883838383838</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-0.9594229686721967</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>78.59328703703703</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>-5.365184124323932</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.5866775546669298</v>
+      </c>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>-4.31527777777778</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-3.460787117333521</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-1.559027777777786</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-4.662500000000023</v>
+      </c>
       <c r="AU7" t="n">
-        <v>-5106239.328347735</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
+        <v>-2.811125819328751</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-524125</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.4472222222222224</v>
+      </c>
       <c r="AX7" t="n">
-        <v>-0.08898469951101551</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-3.553373629079886</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>0.6555375384419619</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-5.758743774929926</v>
-      </c>
+        <v>-4514242.264548455</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>-4.129861111111154</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-2.393453363040123</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1771,7 +1783,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1779,24 +1791,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,58 +1835,54 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-5.833333333333336</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.833333333333336</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>-1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.1849999999999999</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.5</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1883,65 +1891,51 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1</v>
+        <v>0.5199999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.5</v>
+        <v>0.04833333333333334</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>78.59328703703703</v>
-      </c>
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
-        <v>77.15174897119341</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-3.683217708933654</v>
-      </c>
+        <v>81.3625</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
-        <v>-0.4494949494949496</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>-5.614641823370334</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.09480598091279235</v>
+      </c>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>-4.231060606060609</v>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>-3.966224747474797</v>
+        <v>-0.885685353205762</v>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>-4409620.674276489</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-1.401830808080817</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-4.422348484848499</v>
-      </c>
+        <v>-3.543625943200254</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>-0.5850128077546808</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-2.965940801759288</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-513251.2626262642</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>-2.654992712395966</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-5.666011767944823</v>
-      </c>
+        <v>-5148183.272510162</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>0.4560792277897576</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2032,22 +2026,22 @@
         <v>-1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.333333333333333</v>
+        <v>-8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.07999999999999996</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.3100000000000001</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>-0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>-1</v>
@@ -2055,72 +2049,68 @@
       <c r="AC9" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>-0.5</v>
+        <v>-0.07999999999999996</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>-8.5</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>77.56342592592593</v>
       </c>
       <c r="AK9" t="n">
-        <v>77.6522633744856</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-1.874172308975428</v>
-      </c>
+        <v>75.83333333333334</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
-        <v>-0.2007575757575757</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>-3.486956366933128</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.2849473316501179</v>
+      </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>-2.025757575757577</v>
+        <v>-2.107007575757578</v>
       </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>3.505808080808094</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+        <v>-2.002262658508794</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1.099116161616152</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-3.449179292929287</v>
+      </c>
       <c r="AU9" t="n">
-        <v>-2540222.784128066</v>
+        <v>-1.565496834606748</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.217171717171709</v>
+        <v>-2655366.161616162</v>
       </c>
       <c r="AW9" t="n">
-        <v>-3.431818181818173</v>
+        <v>-0.1764520202020201</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.2742971148326216</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-1.557325990948755</v>
-      </c>
+        <v>-2634222.718085721</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>-2775782.828282829</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>-0.462483751091554</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-3.360098043135466</v>
-      </c>
+        <v>3.351641414141426</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.4300577681692346</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2137,7 +2127,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
@@ -2186,7 +2176,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -2205,101 +2195,101 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.1300000000000001</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5550000000000002</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-3</v>
       </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.3750000000000001</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AI10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>73.13257575757575</v>
+        <v>73.01249999999999</v>
       </c>
       <c r="AK10" t="n">
-        <v>71.93055555555556</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-1.899082913000164</v>
-      </c>
+        <v>75.01909722222223</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
-        <v>-0.9863425925925922</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>-3.239963394691486</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.5404124618781707</v>
+      </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
         <v>-3.24583333333333</v>
       </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
+        <v>-1.828824535326923</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-1.719212962962956</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-3.527546296296293</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-1.619866139715711</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-10345833.33333333</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.9863425925925922</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-6848416.756307965</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
         <v>3.175925925925952</v>
       </c>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="n">
-        <v>-6727195.715738622</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-1.719212962962956</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-3.527546296296293</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-0.5645632577627127</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-1.649625922416661</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-10345833.33333333</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="n">
-        <v>1.078657028965125</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-3.293618387789195</v>
-      </c>
+      <c r="BA10" t="n">
+        <v>1.073376648870493</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2390,22 +2380,22 @@
         <v>-23</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>1.415</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02000000000000002</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="Z11" t="n">
         <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>-6.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AB11" t="n">
         <v>1.5</v>
@@ -2414,71 +2404,69 @@
         <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="AH11" t="n">
         <v>3.5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-4.5</v>
-      </c>
       <c r="AI11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>75.04671717171716</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="n">
         <v>78.72222222222223</v>
       </c>
-      <c r="AL11" t="n">
-        <v>-2.67601783025032</v>
-      </c>
+      <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
-        <v>1.563492063492063</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>7.66294905052186</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.9767363137928735</v>
+      </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>0.4656084656084687</v>
+        <v>0.5995370370370381</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>1.790123456790127</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+        <v>-2.687312435328348</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.799382716049379</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10.63040123456791</v>
+      </c>
       <c r="AU11" t="n">
-        <v>33056369.72962</v>
+        <v>9.631835375941691</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800044091710745</v>
+        <v>40887422.83950617</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.6770282186949</v>
+        <v>1.576388888888889</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.9776386478669989</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.563937431639999</v>
-      </c>
+        <v>33107490.65948299</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="n">
-        <v>40941225.74955908</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>0.6461755110807985</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.567654246420233</v>
-      </c>
+        <v>1.998456790123441</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.8132191570515772</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2569,22 +2557,22 @@
         <v>10.5</v>
       </c>
       <c r="V12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
         <v>-1.5</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>1.5</v>
       </c>
-      <c r="X12" t="n">
-        <v>-0.5700000000000001</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.9099999999999999</v>
-      </c>
       <c r="Z12" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
         <v>-0.5</v>
@@ -2599,64 +2587,78 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.5</v>
+        <v>-0.5700000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
         <v>74.09027777777777</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.9984773870250301</v>
+        <v>-106</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1.868357182940516</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
+        <v>-8.997151760399291</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.576164586595301</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
       <c r="AP12" t="n">
         <v>-0.4999228395061728</v>
       </c>
-      <c r="AQ12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-223200000</v>
+      </c>
       <c r="AR12" t="n">
+        <v>0.9984773870250301</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-8.961479377104382</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-8.99078984287317</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-10.98992227743879</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-55792161.19528619</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-1.868357182940516</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-52413734.85811156</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>-2.453966750841744</v>
       </c>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="n">
-        <v>-52413734.85811156</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-8.961479377104382</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-8.99078984287317</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-1.576164586595301</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-10.98992227743879</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-55792161.19528619</v>
-      </c>
-      <c r="BA12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>-0.770222581706264</v>
+      </c>
       <c r="BB12" t="n">
-        <v>-0.770222581706264</v>
+        <v>-1.166666666666657</v>
       </c>
       <c r="BC12" t="n">
-        <v>-8.997151760399291</v>
-      </c>
-      <c r="BD12" t="inlineStr"/>
+        <v>-117</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-2.166666666666667</v>
+      </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
@@ -2716,7 +2718,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2740,94 +2742,112 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.5</v>
+        <v>-6</v>
       </c>
       <c r="V13" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.155</v>
+        <v>-1.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7649999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.605</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AH13" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AA13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-5</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>-1.776468892097657</v>
+        <v>-12</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
+        <v>1.946334765539575</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.09381709696355034</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
       <c r="AP13" t="n">
-        <v>-1.689999999999998</v>
-      </c>
-      <c r="AQ13" t="inlineStr"/>
+        <v>-1.774999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-4800000</v>
+      </c>
       <c r="AR13" t="n">
-        <v>-0.2524999999999977</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
+        <v>-1.660807282597901</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.50454545454545</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.736363636363635</v>
+      </c>
       <c r="AU13" t="n">
-        <v>6785259.052323735</v>
+        <v>3.78260687729508</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.642499999999998</v>
+        <v>12802954.54545455</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.947499999999991</v>
+        <v>0.09772727272727266</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.08323282567119694</v>
+        <v>6410943.707044608</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.777739772362708</v>
+        <v>-3.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13535750</v>
-      </c>
-      <c r="BA13" t="inlineStr"/>
+        <v>0.4863636363636203</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-1.901403366529195</v>
+      </c>
       <c r="BB13" t="n">
-        <v>-1.657788942791029</v>
+        <v>1.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.95118055251038</v>
-      </c>
-      <c r="BD13" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2835,7 +2855,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2843,24 +2863,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2887,22 +2907,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -2911,114 +2931,110 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>28.5</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>-28.5</v>
+        <v>-4.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.5</v>
+        <v>-8</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8300000000000001</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.425</v>
+        <v>-2.5</v>
       </c>
       <c r="Z14" t="n">
         <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.1100000000000001</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="AK14" t="inlineStr"/>
+        <v>78.125</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>75.28472222222223</v>
+      </c>
       <c r="AL14" t="n">
-        <v>0.6463202112359596</v>
+        <v>-74</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.7097796143250685</v>
+        <v>7.634659180115833</v>
       </c>
       <c r="AN14" t="n">
-        <v>51400000</v>
+        <v>0.8478088638227956</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1.75</v>
+        <v>-1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.20664983164983</v>
+        <v>1.84236111111111</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3</v>
+        <v>-4900000</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.4444444444444855</v>
+        <v>0.1836533008901462</v>
       </c>
       <c r="AS14" t="n">
-        <v>254</v>
+        <v>8.229166666666657</v>
       </c>
       <c r="AT14" t="n">
-        <v>-7.5</v>
+        <v>10.20763888888888</v>
       </c>
       <c r="AU14" t="n">
-        <v>12623815.52437057</v>
+        <v>7.684741581947478</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.991835016835012</v>
+        <v>28941666.66666667</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.839286807468611</v>
+        <v>1.307638888888889</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.6447371798162314</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.887646266372613</v>
-      </c>
+        <v>17749053.49489406</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="n">
-        <v>20663418.27364555</v>
+        <v>-2.708333333333371</v>
       </c>
       <c r="BA14" t="n">
-        <v>232</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-0.08489129909455073</v>
-      </c>
+        <v>1.360004403920811</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>4.420652774288087</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
+        <v>-75</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
@@ -3026,7 +3042,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -3034,24 +3050,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3078,22 +3094,22 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -3102,109 +3118,113 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>11.5</v>
+        <v>28.5</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.5</v>
+        <v>-28.5</v>
       </c>
       <c r="V15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7</v>
+      </c>
+      <c r="X15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.1749999999999999</v>
-      </c>
       <c r="Y15" t="n">
-        <v>0.06999999999999995</v>
+        <v>-0.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>-1.5</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2</v>
+        <v>0.5</v>
       </c>
       <c r="AB15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>4.420652774288087</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.6447371798162314</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.20664983164983</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.6463202112359596</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.991835016835012</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.839286807468611</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.887646266372613</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>20663418.27364555</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.7097796143250685</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12623815.52437057</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0.4444444444444855</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.08489129909455073</v>
+      </c>
+      <c r="BB15" t="n">
         <v>2</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="n">
-        <v>75.28472222222223</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.1258213290300212</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.331944444444444</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>22600000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.761111111111109</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-2.86250000000004</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>17533832.52036706</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8.347222222222214</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>10.19027777777777</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.8613094428898413</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.706330520990434</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>29062083.33333333</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.387150006748499</v>
-      </c>
       <c r="BC15" t="n">
-        <v>7.561455849415879</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -3213,7 +3233,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -3221,24 +3241,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3265,22 +3285,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-2</v>
+        <v>-13</v>
       </c>
       <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -3289,35 +3309,35 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="U16" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
         <v>-1</v>
       </c>
-      <c r="V16" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
       <c r="X16" t="n">
-        <v>-0.71</v>
+        <v>0.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.1200000000000001</v>
+        <v>-1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
         <v>-1</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
@@ -3325,60 +3345,78 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="AH16" t="n">
         <v>-2</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AI16" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>78.72222222222223</v>
+        <v>74.66666666666667</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
-        <v>-0.5486755275454982</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4.469392963916917</v>
+      </c>
       <c r="AN16" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
+        <v>0.2921046526956566</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.797222222222224</v>
+      </c>
       <c r="AQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR16" t="inlineStr"/>
+        <v>44300000</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.160938165461669</v>
+      </c>
       <c r="AS16" t="n">
-        <v>69</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
+        <v>4.48217592592593</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.234953703703709</v>
+      </c>
       <c r="AU16" t="n">
-        <v>252244.0105581549</v>
-      </c>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
+        <v>3.569567246659005</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12991138.88888889</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.306712962962963</v>
+      </c>
       <c r="AX16" t="n">
-        <v>0.1442301860935764</v>
+        <v>8277223.284306661</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.702674624781821</v>
-      </c>
-      <c r="AZ16" t="inlineStr"/>
+        <v>-2.666666666666668</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.899537037037049</v>
+      </c>
       <c r="BA16" t="n">
-        <v>69</v>
+        <v>1.738647046140585</v>
       </c>
       <c r="BB16" t="n">
-        <v>-1.579740132158918</v>
+        <v>1.666666666666657</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.342125883805451</v>
-      </c>
-      <c r="BD16" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
@@ -3386,7 +3424,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3394,24 +3432,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3438,22 +3476,22 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -3462,34 +3500,34 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>-9.5</v>
+        <v>-1</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="W17" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="X17" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.015</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
         <v>-2</v>
       </c>
       <c r="AA17" t="n">
-        <v>-3.5</v>
+        <v>0.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3498,640 +3536,61 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-1</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>74.66666666666667</v>
+        <v>78.72222222222223</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>1.251424577874975</v>
+        <v>69</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.3089856902356902</v>
+        <v>1.127238932065822</v>
       </c>
       <c r="AN17" t="n">
-        <v>38000000</v>
+        <v>0.1443550082059795</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.849999999999994</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.713005050505053</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="n">
-        <v>-1</v>
+        <v>1400000</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.735900673400693</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>-1.899999999999999</v>
-      </c>
+        <v>-0.68144282149348</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="n">
-        <v>8491919.609548189</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.324978956228961</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>6.994802188552185</v>
-      </c>
+        <v>1.668769567752818</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="n">
-        <v>0.2984094452738448</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.780961902426185</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12980265.15151515</v>
-      </c>
+        <v>161319.2873010277</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
-        <v>-64</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.731717582532639</v>
-      </c>
+        <v>-1.831450656014454</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="n">
-        <v>4.755256978545532</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0.1000000000000001</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45531.6875</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>148</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>-18</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.02500000000000013</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>75.83333333333334</v>
-      </c>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="n">
-        <v>5.850748086520827</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>-1.410353535353536</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>-236750000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.830387205387208</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-2.259820426487096</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>-201</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>-30115326.71537483</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>-8.906285072951732</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>-5.927749719416397</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>-0.7851083722001135</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>-8.733945059890672</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-37441315.93714926</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>-198</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-1.085096635750716</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>-2.908342061285694</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45531.58333333334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>148</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>-11</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.9450000000000001</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.1950000000000001</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="n">
-        <v>1.361944893547399</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>-0.6550505050505049</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="n">
-        <v>-0.01742424242424079</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>-1.557491582491593</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>81</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="n">
-        <v>-4423139.057103589</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>-2.364562289562301</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>-1.539478114478115</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>-0.557616654781482</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>-3.68594842736718</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-3724663.299663303</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>69</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-1.662996962879163</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>-1.437064840231486</v>
-      </c>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45530.6875</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>148</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.175</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.4349999999999999</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="n">
-        <v>72</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.024376982197836</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.1759259259259263</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="n">
-        <v>-0.1759259259259203</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>3.578317901234641</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>158</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="n">
-        <v>2138649.889871128</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0.84652777777778</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.8989197530864175</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0.435626184648138</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.953199895298113</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1974266.975308644</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>155</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>2.556224994710107</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.669777374484667</v>
-      </c>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE6"/>
+  <dimension ref="A1:BE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.6875</v>
+        <v>45551.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
+          <t xml:space="preserve">campo de futbol de vallecas
   madrid </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,22 +769,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -793,113 +793,101 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.333333333333332</v>
+        <v>-0.4075</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>-0.01583333333333314</v>
       </c>
       <c r="V2" t="n">
-        <v>11.66666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="W2" t="n">
-        <v>-11.66666666666666</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5</v>
+        <v>1.083333333333334</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5</v>
+        <v>2.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6666666666666667</v>
+        <v>-1.583333333333336</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3333333333333334</v>
+        <v>1.583333333333336</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2</v>
+        <v>4.083333333333334</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>3.416666666666666</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4283333333333332</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.04166666666666674</v>
+        <v>-0.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.166666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>74.09027777777777</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>75.83333333333334</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>76.31018518518518</v>
+      </c>
       <c r="AL2" t="n">
-        <v>7.288095384148022</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-2.111918381326284</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7.426603334936658</v>
-      </c>
+        <v>0.1729166666666668</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>121</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>54795048.1000481</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1.333333333333332</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>231850000</v>
-      </c>
+        <v>0.287037037037037</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>1.061908770242104</v>
+        <v>-1.684374999999989</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.7461284329705387</v>
+        <v>2.937499999999986</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1806036556036759</v>
+        <v>3.547916666666669</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>-1066093.75</v>
       </c>
       <c r="AW2" t="n">
-        <v>-2.262477954144618</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>118</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.649327390445819</v>
-      </c>
+        <v>-1.101851851851848</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>47976328.74983203</v>
+        <v>-5.842592592592553</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.166666666666667</v>
+        <v>-4667592.592592597</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.695358345358329</v>
+        <v>1.675925925925924</v>
       </c>
       <c r="BC2" t="n">
-        <v>-4.177374270466402</v>
+        <v>-2.425925925925938</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1.833333333333343</v>
+        <v>-1.588541666666629</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -908,32 +896,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.59375</v>
+        <v>45550.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,134 +948,124 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8333333333333339</v>
+        <v>0.9125000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-8</v>
+        <v>-0.8825000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-22.16666666666666</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>22.16666666666666</v>
+        <v>-2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5</v>
+        <v>-2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1</v>
+        <v>-3.25</v>
       </c>
       <c r="AB3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG3" t="n">
         <v>-2</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.3099999999999998</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.9316666666666668</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
       <c r="AH3" t="n">
-        <v>-2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>76.44444444444444</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>73.4375</v>
-      </c>
+        <v>78.67361111111111</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-2.834920912969324</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.332766413428466</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-3.361971992653807</v>
-      </c>
+        <v>0.6894349845201238</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>-157</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-13303831.78374655</v>
-      </c>
+        <v>1.125</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>-49000000</v>
-      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-0.4134412304866852</v>
+        <v>5.270059339525289</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.5028766918193799</v>
+        <v>7.915127278981771</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.131565656565641</v>
+        <v>2.189448959408328</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2</v>
+        <v>17905796.48262814</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.4127525252525253</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-168</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-2.997943715814273</v>
-      </c>
+        <v>9.527777777777771</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-10211939.79087173</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>0.3749999999999147</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>19386527.77777778</v>
+      </c>
       <c r="BB3" t="n">
-        <v>-3.232702020202012</v>
+        <v>5.465277777777779</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.129062918855425</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>5.499999999999986</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.8924514103887304</v>
+      </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1095,32 +1073,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.58333333334</v>
+        <v>45550.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1147,139 +1125,111 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P4" t="n">
         <v>-2</v>
       </c>
-      <c r="P4" t="n">
-        <v>-4</v>
-      </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.666666666666668</v>
+        <v>-0.1308333333333332</v>
       </c>
       <c r="U4" t="n">
-        <v>1.333333333333332</v>
+        <v>0.968333333333333</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.666666666666664</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="W4" t="n">
-        <v>4.666666666666664</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.6666666666666666</v>
+        <v>8.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3333333333333335</v>
+        <v>-8.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.333333333333332</v>
+        <v>0.5833333333333339</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.08666666666666645</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2233333333333335</v>
+        <v>0.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>76.59999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>76.44444444444444</v>
+        <v>71.55555555555556</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.2830819320521982</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.432464396628482</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-1.050505050505066</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-10131540.4040404</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>39600000</v>
-      </c>
+        <v>-0.2029961997067256</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>0.5512626262626261</v>
+        <v>-2.953326205957794</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.4914085684360956</v>
+        <v>-1.175257344994193</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.464898989899041</v>
+        <v>0.6001905258484221</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.509090909090908</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.9323044213978591</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-2667957.281721584</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-2.436111111111117</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.012543087997358</v>
-      </c>
+        <v>-6409753.565148303</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>-6.100267276583082</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1288,32 +1238,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
+        <v>45550.46875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1340,139 +1290,111 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.7508333333333328</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.07333333333333336</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-2.083333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-6.666666666666666</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.583333333333334</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.166666666666666</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-4.083333333333334</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF5" t="n">
         <v>-1</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-5.333333333333332</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-7</v>
-      </c>
-      <c r="W5" t="n">
-        <v>7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.7866666666666668</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.5033333333333334</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-2</v>
-      </c>
       <c r="AG5" t="n">
-        <v>-0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76.77777777777777</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>72</v>
-      </c>
+        <v>76.44444444444444</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-0.5615092943301505</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-0.05128488564317735</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.6967592592592524</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-156</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3198765.432098769</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-10400000</v>
-      </c>
+        <v>-0.2479739010989008</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-0.2145061728395061</v>
+        <v>-0.9441620879120904</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.2101741247463174</v>
+        <v>3.244642857142878</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.222993827160451</v>
+        <v>4.694402472527472</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.05169753086419604</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-1.393753498432645</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-268883.6922510052</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.6339506172839435</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.8615260259645368</v>
-      </c>
+        <v>-9607123.969780218</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>2.25</v>
+        <v>-1.91689560439562</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1481,185 +1403,1042 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.5</v>
+        <v>45550.375</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>148</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-12.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>72</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>78.72222222222223</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.3344362745098035</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>0.3611111111111109</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>1.079554738562081</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.195445261437911</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.026307189542479</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6052964.154411766</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.337962962962962</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>1.398148148148124</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5770833.333333334</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.152777777777782</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.546296296296291</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.804268790849676</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>148</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.0525</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>74.09027777777777</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.6458580581355351</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>-1.313888888888888</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-4.403522746818027</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-6.167475060199507</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-1.953290548675611</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-23905601.05456656</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-6.045138888888886</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>-0.8909722222222172</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-48193611.11111111</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.2888888888888879</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-6.06527777777778</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.108794504643981</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3858333333333331</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.9758333333333333</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.833333333333334</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-3.583333333333332</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>77.29629629629629</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.6996527777777777</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>0.157407407407407</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>3.204922385620918</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.97953431372548</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.104881535947715</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4252769.607843135</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.31481481481481</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>5.407407407407305</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3337152.777777778</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.236111111111114</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.537037037037052</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.2268586601307163</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.46875</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>hxt57t2q</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="G9" t="n">
         <v>148</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H9" t="n">
         <v>1481</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>20242025</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.08500000000000019</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75.23148148148148</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>78.0625</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-1.266417982816961</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.3804355925292668</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.053925492721937</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-675864.2818095214</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.3611111111111143</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>2.1527777777778</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>912500</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.291666666666671</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.9444444444444429</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.06445855163923397</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.6275000000000001</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.7649999999999999</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>78.40833333333333</v>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="n">
+        <v>-0.4820929586409468</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-3.724549992061597</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-1.045880963721515</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.214970826387233</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-3575633.980312774</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>2.461231840914508</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45548.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="P6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-8.000000000000002</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-10</v>
-      </c>
-      <c r="W6" t="n">
-        <v>10</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3.999999999999998</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.6666666666666661</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.03000000000000003</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1.076666666666667</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>78.0625</v>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
-        <v>0.4549296890111094</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-2.354801209632406</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-3.53422619047619</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-6502480.158730159</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>-13800000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.03571428571428581</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-0.1212001101115017</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.372023809523824</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.053075396825395</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-2.512765418901068</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-2446684.42777787</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>-1.846726190476176</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.305623829269479</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3650000000000002</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2358333333333336</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.08333333333333348</v>
+      </c>
+      <c r="X11" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.916666666666664</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-2.916666666666664</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4166666666666661</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.5833333333333334</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="n">
+        <v>72.96527777777777</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.3676391676778676</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>5.814255898040727</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.166326591365291</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-2.546014829683553</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2259067.470949243</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>1.504266794437086</v>
+      </c>
+      <c r="BE11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE11"/>
+  <dimension ref="A1:BE27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45551.66666666666</v>
+        <v>45559.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
+          <t xml:space="preserve">estadio santiago bernabeu
   madrid </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,126 +769,126 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.7650000000000001</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC2" t="n">
         <v>-2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.4075</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.01583333333333314</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.4166666666666665</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.083333333333334</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-1.583333333333336</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.583333333333336</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4.083333333333334</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.416666666666666</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.83333333333334</v>
+        <v>76.48148148148148</v>
       </c>
       <c r="AK2" t="n">
-        <v>76.31018518518518</v>
+        <v>75.75648148148149</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1729166666666668</v>
+        <v>-2.357231171820956</v>
       </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>0.287037037037037</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>37056307.03803958</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>78646022.72727273</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>1.186081932773109</v>
+      </c>
       <c r="AS2" t="n">
-        <v>-1.684374999999989</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.937499999999986</v>
-      </c>
+        <v>2.201641414141392</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>3.547916666666669</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-1066093.75</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-1.101851851851848</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
+        <v>2.304545454545455</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>1.518308080808076</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>13.54507575757575</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>-5.842592592592553</v>
+        <v>9.0427536719816</v>
       </c>
       <c r="BA2" t="n">
-        <v>-4667592.592592597</v>
+        <v>1.77137647569149</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.675925925925924</v>
+        <v>7.770779784585912</v>
       </c>
       <c r="BC2" t="n">
-        <v>-2.425925925925938</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-1.588541666666629</v>
-      </c>
+        <v>12.27020202020202</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -896,32 +896,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.66666666666</v>
+        <v>45559.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -948,124 +948,126 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9125000000000001</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8825000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="V3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2</v>
       </c>
-      <c r="W3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-2</v>
-      </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78.67361111111111</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>75.04618055555557</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>75.87615740740742</v>
+      </c>
       <c r="AL3" t="n">
-        <v>0.6894349845201238</v>
+        <v>0.2173611111111029</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>5594626.73611111</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7641180.555555555</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>0.5298611111111107</v>
+      </c>
       <c r="AS3" t="n">
-        <v>5.270059339525289</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.915127278981771</v>
-      </c>
+        <v>4.476388888888891</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>2.189448959408328</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17905796.48262814</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>9.527777777777771</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
+        <v>0.3472222222222219</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>0.2145833333333371</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.697222222222237</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>0.3749999999999147</v>
+        <v>4.715624999999989</v>
       </c>
       <c r="BA3" t="n">
-        <v>19386527.77777778</v>
+        <v>2.262500000000003</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.465277777777779</v>
+        <v>3.565972222222229</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.499999999999986</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0.8924514103887304</v>
-      </c>
+        <v>4.825000000000017</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1073,32 +1075,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
+        <v>45559.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1125,22 +1127,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="P4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>-1</v>
@@ -1149,88 +1151,102 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1308333333333332</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.968333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.4599999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>-1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>1.333333333333334</v>
+        <v>0.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.75</v>
+        <v>-0.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8.75</v>
+        <v>0.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5833333333333339</v>
+        <v>6.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3333333333333334</v>
+        <v>-1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.75</v>
+        <v>-2</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>-8.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>79.48055555555555</v>
+      </c>
       <c r="AK4" t="n">
-        <v>71.55555555555556</v>
+        <v>75.8641975308642</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.2029961997067256</v>
+        <v>1.129032210050013</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>-905835.9678891795</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-705972.222222222</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>0.04155354449472104</v>
+      </c>
       <c r="AS4" t="n">
-        <v>-2.953326205957794</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-1.175257344994193</v>
-      </c>
+        <v>-1.016666666666623</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>0.6001905258484221</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-6409753.565148303</v>
-      </c>
+        <v>0.09583333333333321</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>-6.100267276583082</v>
-      </c>
+      <c r="AX4" t="n">
+        <v>-3.255555555555556</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-4.231944444444437</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.9351544514566967</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.4224306878621924</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-1.088448142414862</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-2.216666666666654</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1238,32 +1254,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.46875</v>
+        <v>45558.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1290,112 +1306,126 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.2349999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5049999999999999</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.7508333333333328</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.07333333333333336</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-2.083333333333333</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-6.666666666666666</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.583333333333334</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.166666666666666</v>
-      </c>
       <c r="AC5" t="n">
-        <v>-4.083333333333334</v>
+        <v>3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>76.44444444444444</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>77.32460016835017</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75.26597222222222</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-0.2479739010989008</v>
+        <v>0.9298436041082709</v>
       </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>17449023.65390601</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6128518.518518519</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>0.4921763149704323</v>
+      </c>
       <c r="AS5" t="n">
-        <v>-0.9441620879120904</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.244642857142878</v>
-      </c>
+        <v>-3.10277777777776</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>4.694402472527472</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-9607123.969780218</v>
-      </c>
+        <v>0.5629629629629631</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>-1.91689560439562</v>
-      </c>
+      <c r="AX5" t="n">
+        <v>1.175925925925924</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2.029629629629625</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.100645813881115</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-3.132170090258327</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.897012138188614</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.090740740740742</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1403,32 +1433,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>QiF6bS1N</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.375</v>
+        <v>45557.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1455,126 +1485,126 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>-17</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="R6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.28</v>
-      </c>
       <c r="V6" t="n">
-        <v>2.75</v>
+        <v>-1.256666666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.5</v>
+        <v>0.8933333333333334</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.25</v>
+        <v>-1.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>-12.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5.25</v>
+        <v>-5.666666666666666</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.25</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.25</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>72</v>
+        <v>75.01875</v>
       </c>
       <c r="AK6" t="n">
-        <v>78.72222222222223</v>
+        <v>76.40925925925926</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3344362745098035</v>
+        <v>-2.651137820512787</v>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>0.3611111111111109</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>-21829383.01282051</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-25995370.37037037</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-0.6598878205128205</v>
+      </c>
       <c r="AS6" t="n">
-        <v>1.079554738562081</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.195445261437911</v>
-      </c>
+        <v>-2.510185185185179</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>2.026307189542479</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6052964.154411766</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.337962962962962</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+        <v>-0.7296296296296299</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1.648148148148145</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-6.118518518518513</v>
+      </c>
       <c r="AZ6" t="n">
-        <v>1.398148148148124</v>
+        <v>-5.398573717948707</v>
       </c>
       <c r="BA6" t="n">
-        <v>5770833.333333334</v>
+        <v>1.947916666666664</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.152777777777782</v>
+        <v>-6.834871794871788</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.546296296296291</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.804268790849676</v>
-      </c>
+        <v>-7.275925925925932</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1582,32 +1612,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jckS1tiI</t>
+          <t>pxdwg6Pp</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.66666666666</v>
+        <v>45557.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1634,126 +1664,126 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-19</v>
+        <v>-22</v>
       </c>
       <c r="P7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R7" t="n">
         <v>-3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>-1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-1.0525</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.46</v>
+        <v>5</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.75</v>
+        <v>-0.2799999999999996</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5</v>
+        <v>1.273333333333333</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.75</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.25</v>
+        <v>0.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>-3.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.25</v>
+        <v>0.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.25</v>
+        <v>-5.666666666666666</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.75</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-23.99999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>73.66666666666667</v>
+        <v>73.90694444444445</v>
       </c>
       <c r="AK7" t="n">
-        <v>74.09027777777777</v>
+        <v>75.0925925925926</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.6458580581355351</v>
+        <v>-0.0701792542253088</v>
       </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>-1.313888888888888</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>-12677422.43228263</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-35128125</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-0.05342502891844969</v>
+      </c>
       <c r="AS7" t="n">
-        <v>-4.403522746818027</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-6.167475060199507</v>
-      </c>
+        <v>6.375</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>-1.953290548675611</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-23905601.05456656</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-6.045138888888886</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
+        <v>-1.25</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-5.75</v>
+      </c>
       <c r="AZ7" t="n">
-        <v>-0.8909722222222172</v>
+        <v>3.04857255317782</v>
       </c>
       <c r="BA7" t="n">
-        <v>-48193611.11111111</v>
+        <v>4.096569749694751</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.2888888888888879</v>
+        <v>-1.529304430949168</v>
       </c>
       <c r="BC7" t="n">
-        <v>-6.06527777777778</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.108794504643981</v>
-      </c>
+        <v>-6.5</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1761,32 +1791,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>OAmz0KLU</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.5625</v>
+        <v>45557.46875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1813,22 +1843,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1837,102 +1867,102 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3858333333333331</v>
+        <v>-3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9758333333333333</v>
+        <v>-3.666666666666667</v>
       </c>
       <c r="V8" t="n">
-        <v>5.5</v>
+        <v>-1.236666666666667</v>
       </c>
       <c r="W8" t="n">
-        <v>2.833333333333333</v>
+        <v>-1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>4.166666666666666</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.833333333333334</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-9.75</v>
+        <v>-0.1499999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.25</v>
+        <v>-3</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.583333333333332</v>
+        <v>-7.666666666666666</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.4166666666666667</v>
+        <v>-2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.166666666666667</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.5</v>
+        <v>5.666666666666668</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5</v>
+        <v>-5.333333333333336</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.333333333333336</v>
       </c>
       <c r="AJ8" t="n">
-        <v>76.8</v>
+        <v>74.88310185185186</v>
       </c>
       <c r="AK8" t="n">
-        <v>77.29629629629629</v>
+        <v>72.70462962962962</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6996527777777777</v>
+        <v>3.290391531413235</v>
       </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>0.157407407407407</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>5186041.441895736</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>12623148.14814815</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-0.09890663601963912</v>
+      </c>
       <c r="AS8" t="n">
-        <v>3.204922385620918</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.97953431372548</v>
-      </c>
+        <v>3.134259259259267</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>3.104881535947715</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4252769.607843135</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.31481481481481</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
+        <v>-0.03240740740740744</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-0.722222222222225</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.490740740740748</v>
+      </c>
       <c r="AZ8" t="n">
-        <v>5.407407407407305</v>
+        <v>1.081875644994838</v>
       </c>
       <c r="BA8" t="n">
-        <v>3337152.777777778</v>
+        <v>-2.195678534571723</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.236111111111114</v>
+        <v>2.800361197110433</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.537037037037052</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.2268586601307163</v>
-      </c>
+        <v>3.888888888888886</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1940,32 +1970,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>dCNk2A2b</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.46875</v>
+        <v>45557.375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1992,159 +2022,155 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08500000000000019</v>
+        <v>-2.166666666666667</v>
       </c>
       <c r="U9" t="n">
-        <v>0.46</v>
+        <v>-2.833333333333333</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5</v>
+        <v>-0.04999999999999993</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>-0.7033333333333334</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.25</v>
+        <v>-0.5499999999999998</v>
       </c>
       <c r="Y9" t="n">
-        <v>5</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>-0.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>-6</v>
+        <v>-0.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>-6</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>-9.333333333333334</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.75</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.75</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.75</v>
+        <v>3.666666666666666</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-5.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75.23148148148148</v>
+        <v>76.84282407407407</v>
       </c>
       <c r="AK9" t="n">
-        <v>78.0625</v>
+        <v>75.37083333333334</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>-0.9027593493537722</v>
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>843027.9589906139</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4939236.11111111</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-0.04946741854636594</v>
+      </c>
       <c r="AS9" t="n">
-        <v>-1.266417982816961</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.3804355925292668</v>
-      </c>
+        <v>-1.138888888888857</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>2.053925492721937</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-675864.2818095214</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.3611111111111143</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
+        <v>0.2256944444444444</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>0.6076388888888893</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.281250000000014</v>
+      </c>
       <c r="AZ9" t="n">
-        <v>2.1527777777778</v>
+        <v>0.06078001375989572</v>
       </c>
       <c r="BA9" t="n">
-        <v>912500</v>
+        <v>-1.709447638704603</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.291666666666671</v>
+        <v>2.348860509115923</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.9444444444444429</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-0.06445855163923397</v>
-      </c>
+        <v>2.256944444444443</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>ImLNuMV7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.375</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2171,112 +2197,126 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-4</v>
+        <v>36</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6275000000000001</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7649999999999999</v>
+        <v>-3</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.5</v>
+        <v>-0.9566666666666667</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-5</v>
+        <v>-0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.75</v>
+        <v>-0.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-8.000000000000002</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.25</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.75</v>
+        <v>-1.666666666666668</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.75</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>20.33333333333334</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-20.33333333333334</v>
       </c>
       <c r="AJ10" t="n">
-        <v>78.40833333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr"/>
+        <v>75.96296296296296</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>76.83090277777778</v>
+      </c>
       <c r="AL10" t="n">
-        <v>-0.4820929586409468</v>
+        <v>-3.95251425131454</v>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>37269285.61830434</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>77952272.72727273</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>1.186081932773109</v>
+      </c>
       <c r="AS10" t="n">
-        <v>-3.724549992061597</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-1.045880963721515</v>
-      </c>
+        <v>-1.069191919191837</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="n">
-        <v>2.214970826387233</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-3575633.980312774</v>
-      </c>
+        <v>2.304545454545455</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>2.461231840914508</v>
-      </c>
+      <c r="AX10" t="n">
+        <v>-0.03030303030303827</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13.45479797979797</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>8.865612100103192</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.1589172072337703</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>9.082488543663089</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12.08964646464646</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
@@ -2284,161 +2324,3005 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.8933333333333336</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.666666666666668</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>81.46111111111111</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>77.72013888888888</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.981608893557393</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>-4564215.642507002</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-8109861.11111111</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>-0.3200367647058822</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.7638888888888573</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>-2.431944444444447</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-5.694444444444443</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-3.421419817927173</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0.9387254901960844</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-3.188926820728298</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-3.911111111111097</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4233333333333335</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-5.666666666666668</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-13.33333333333333</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75.99814814814815</v>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="n">
+        <v>-0.02714347378625348</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>-516989.1921427818</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-0.03712943510737632</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>-1.566904865859968</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.2089099894343711</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.6035160606077739</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.009999999999999898</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.8766666666666665</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.2999999999999998</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.000000000000001</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>77.64282407407407</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>76.88522727272728</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.001494238046092</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>-9951312.752622981</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-21699236.11111111</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-0.3783561231510146</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.01527777777772599</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>-0.7500000000000004</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>-1.15902777777778</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-8.594444444444463</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-3.014016812865506</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.7927459580323379</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-3.531989594083257</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-7.469444444444463</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.3566666666666665</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.333333333333332</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-17.33333333333334</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>17.33333333333334</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>76.86111111111111</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>75.38472222222222</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-1.569928025191132</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>-5692000.534188033</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-6730138.888888888</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>-0.5888888888888888</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-5.318055555555503</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>-0.3749999999999996</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-2.915277777777774</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-4.425961538461522</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-2.862488753936127</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-3.718314215024748</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-3.425000000000011</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>148</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.2333333333333334</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.2533333333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.6666666666666679</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>74.4820987654321</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>76.33333333333334</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-1.990083162451583</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>-9235917.848598771</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-17939814.81481481</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>-0.2450899977215766</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-2.421296296296362</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>-0.2488425925925926</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>0.5682870370370381</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-6.054398148148152</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-3.405482456140348</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.315256892230575</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-5.272587719298258</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-6.956018518518519</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.3450000000000002</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>78.8549558080808</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>76.38611111111112</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.384033613445354</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="n">
+        <v>18698108.07656396</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8787615.740740743</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>0.6405228758169932</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.4444444444444287</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>0.5740740740740744</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>1.68981481481481</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.949074074074062</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.782726423902886</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.2606909430438833</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.856349206349208</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.115740740740748</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45552.58333333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.04499999999999993</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.2949999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>77.19400252525253</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>76.62064393939394</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.158339476141379</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="n">
+        <v>-6275648.979474832</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-13343333.33333333</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>-0.2890373400822319</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.172222222222189</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>-0.4194444444444447</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>1.458333333333332</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-2.650000000000006</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.6104044834307842</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.622044899831277</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-3.573755467099133</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-4.155555555555566</v>
+      </c>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45551.66666666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.4075</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.01583333333333314</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.416666666666666</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-1.333333333333336</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.333333333333336</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>75.94444444444444</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>76.21666666666667</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.8507754822577169</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>-1873107.343266254</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-4487037.037037037</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0.1487556561085972</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-4.965740740740728</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="n">
+        <v>0.2856481481481479</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>2.663425925925925</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.6949074074073991</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.286894945225058</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.486458829483208</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-2.173303911645633</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-3.364814814814821</v>
+      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>148</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9125000000000001</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.8825000000000001</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>78.71111111111111</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>0.6713301282050566</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="n">
+        <v>20862111.63744344</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>22214305.55555556</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>0.7670899321266966</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-1.438888888888926</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>0.9194444444444445</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>4.270833333333336</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.655555555555551</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>8.620623114630462</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.960972850678736</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.750016025641017</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6.127777777777766</v>
+      </c>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>148</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.1308333333333332</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.968333333333333</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-2.083333333333334</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="n">
+        <v>76.33333333333334</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-5.286622587938382</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="n">
+        <v>-6577286.03268077</v>
+      </c>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>-0.2078663295768557</v>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>-1.199607994344845</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.6391515648094632</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-2.948456076087666</v>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>148</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.7508333333333328</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.07333333333333336</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>77.25185185185184</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>73.25925925925925</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-1.566536710838193</v>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="n">
+        <v>-11927151.37497307</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-23408611.11111111</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>-0.181602160094807</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.722222222222229</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>-1.141666666666667</v>
+      </c>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>1.31388888888889</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-1.625</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.600572344322345</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.028496687136396</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-1.150393234216764</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-3.25555555555556</v>
+      </c>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>148</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.3650000000000002</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-12.25</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>73.41666666666667</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>77.03402777777778</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.694893790849676</v>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="n">
+        <v>5633427.798202617</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6074236.111111111</v>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>0.3344362745098035</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-0.07546296296291644</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>1.649768518518524</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.30740740740741</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.205167483660134</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.026307189542479</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.122263071895432</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>3.099074074074082</v>
+      </c>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>148</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.0525</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>73.6388888888889</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>75.15185185185184</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.708303847854893</v>
+      </c>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="n">
+        <v>-27007620.48733968</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-57857828.28282829</v>
+      </c>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>-0.7486980318443164</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>-1.375252525252506</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>-1.526767676767677</v>
+      </c>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="n">
+        <v>0.1136363636363669</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>-6.732575757575745</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>-6.318400320654561</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-1.964133679787704</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>-4.086448197700136</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-6.200757575757564</v>
+      </c>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>148</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.3858333333333331</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.9733333333333332</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.833333333333334</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-3.583333333333332</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>-10.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>75.75833333333334</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.5147058823528994</v>
+      </c>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="n">
+        <v>3168047.385620913</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1944375</v>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>0.5888888888888888</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.97777777777776</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>0.02777777777777746</v>
+      </c>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="n">
+        <v>-1.888888888888889</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.6722222222222172</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.773284313725469</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.826062091503275</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>2.567075163398698</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.536111111111126</v>
+      </c>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45549.46875</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>148</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.08500000000000019</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>76.45069444444445</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>77.99074074074075</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.595283079493584</v>
+      </c>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="n">
+        <v>-212978.5802647644</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>693750</v>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.270833333333229</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="n">
+        <v>1.548611111111114</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.09027777777777146</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.1771415718784084</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.93029368292526</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>-1.311708759077177</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.1805555555555571</v>
+      </c>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45549.375</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>148</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.7150000000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.7649999999999999</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>78.46700336700337</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>75.19444444444444</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.2681149990360723</v>
+      </c>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="n">
+        <v>-2957638.859434913</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4191736.111111112</v>
+      </c>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>-0.3909825311141102</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>-2.091666666666669</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>0.1083333333333334</v>
+      </c>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.808333333333337</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-0.8303745474798205</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.984060846560844</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-3.341017608122883</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-0.3222222222222229</v>
+      </c>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>YeqTho8m</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45548.66666666666</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio benito villamarin
   sevilla </t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>vJbTeCGP</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G27" t="n">
         <v>148</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H27" t="n">
         <v>1481</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>20242025</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
         <v>5</v>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.08333333333333348</v>
+      </c>
+      <c r="V27" t="n">
         <v>0.3650000000000002</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W27" t="n">
         <v>0.2358333333333336</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.08333333333333348</v>
-      </c>
-      <c r="X11" t="n">
-        <v>6.333333333333334</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.916666666666664</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-2.916666666666664</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.4166666666666661</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-2.833333333333334</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="X27" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.5833333333333334</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.8333333333333339</v>
+      </c>
+      <c r="AD27" t="n">
         <v>-0.4166666666666667</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE27" t="n">
         <v>0.25</v>
       </c>
-      <c r="AF11" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="n">
-        <v>72.96527777777777</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0.3676391676778676</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
-        <v>5.814255898040727</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.166326591365291</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-2.546014829683553</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2259067.470949243</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="n">
-        <v>1.504266794437086</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="AF27" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>3.833333333333336</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-3.833333333333336</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>81.61363636363637</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>72.61666666666667</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.481274264091581</v>
+      </c>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>19541136.03555457</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>13726851.85185185</v>
+      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>0.5910554572706272</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>-1.583333333333286</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>0.7997685185185188</v>
+      </c>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="n">
+        <v>2.297453703703699</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6.230324074074076</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>4.843506437662782</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-1.44875669566072</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7.205209715465131</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.37268518518519</v>
+      </c>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE7"/>
+  <dimension ref="A1:BE32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,74 +535,74 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45552.58333333334</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -774,134 +774,106 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06350000000000011</v>
+        <v>-0.345</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.194</v>
+        <v>-1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.15</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.9</v>
+        <v>-23.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.05000000000000071</v>
+        <v>23.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>-11.6</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>11.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>78.46700336700337</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>73.6388888888889</v>
-      </c>
+        <v>74.39236111111111</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.4039377289377306</v>
       </c>
       <c r="AM2" t="n">
-        <v>-6.733333333333348</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>145</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-5721939.720215573</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.436740667027042</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-14109111.11111111</v>
-      </c>
+        <v>2.426138262322482</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>2.137777777777728</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.7567007797270833</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-18900000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.305555555555554</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>131</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.4244444444444451</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-0.2853733189182108</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-3.161930070273741</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.302664872966773</v>
-      </c>
+        <v>1.743888567572782</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-1.866666666666667</v>
+        <v>2.533526926290108</v>
       </c>
       <c r="BB2" t="n">
-        <v>-2.953333333333347</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-4.368888888888904</v>
-      </c>
+        <v>0.4638961185013815</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>2920038.397275239</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -910,32 +882,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45551.66666666666</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
+          <t xml:space="preserve">metropolitano stadium
   madrid </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -962,139 +934,125 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="P3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4075</v>
+        <v>0.1750000000000003</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.01583333333333314</v>
+        <v>-0.6749999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.75</v>
+        <v>-4.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.416666666666666</v>
+        <v>-0.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4166666666666665</v>
+        <v>-4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.333333333333334</v>
+        <v>-6</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.333333333333336</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.333333333333336</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75.94444444444444</v>
+        <v>76.28973765432099</v>
       </c>
       <c r="AK3" t="n">
-        <v>76.21666666666667</v>
+        <v>74.21064814814815</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.5</v>
+        <v>1.328293862999743</v>
       </c>
       <c r="AM3" t="n">
-        <v>-2</v>
+        <v>-1.382369503045979</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>-47064242.42424242</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1873107.343266254</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.486458829483208</v>
-      </c>
+        <v>1.363636363636363</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-4487037.037037037</v>
+        <v>-4.543232323232317</v>
       </c>
       <c r="AR3" t="n">
-        <v>-4.965740740740728</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.286894945225058</v>
-      </c>
+        <v>0.4694948091124616</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>3350000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.663425925925925</v>
-      </c>
+        <v>-1.048484848484848</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.2856481481481479</v>
-      </c>
+        <v>-3.908080808080811</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>0.1487556561085972</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-2.173303911645633</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-0.8507754822577169</v>
-      </c>
+        <v>-1.28262626262628</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>2.117429766312057</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.6949074074073991</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-3.364814814814821</v>
-      </c>
+        <v>-0.3056580870110284</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-15367775.03991107</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1103,32 +1061,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.66666666666</v>
+        <v>45564.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1155,137 +1113,125 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.8899999999999999</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.4800000000000002</v>
+      </c>
+      <c r="V4" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.9125000000000001</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.8825000000000001</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.75</v>
-      </c>
       <c r="W4" t="n">
-        <v>-1.25</v>
+        <v>-5.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2</v>
+        <v>-0.9500000000000002</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.75</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>-1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>-1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.75</v>
+        <v>9.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.25</v>
+        <v>-9.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>-0.8</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3</v>
+        <v>0.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>78.71111111111111</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>77.45129734848486</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>78.01454545454546</v>
+      </c>
       <c r="AL4" t="n">
-        <v>0.5</v>
+        <v>-1.721716948342337</v>
       </c>
       <c r="AM4" t="n">
-        <v>-6.666666666666657</v>
+        <v>6.879482351154181</v>
       </c>
       <c r="AN4" t="n">
-        <v>-309</v>
+        <v>11019097.22222222</v>
       </c>
       <c r="AO4" t="n">
-        <v>20862111.63744344</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.960972850678736</v>
-      </c>
+        <v>2.090277777777771</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>22214305.55555556</v>
+        <v>2.975694444444443</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.438888888888926</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.620623114630462</v>
-      </c>
+        <v>4.83455295993997</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-29200000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.270833333333336</v>
-      </c>
+        <v>0.8159722222222223</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>-300</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.9194444444444445</v>
-      </c>
+        <v>5.548611111111114</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>0.7670899321266966</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.750016025641017</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.6713301282050566</v>
-      </c>
+        <v>-2.9826388888888</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-2.333333333333332</v>
+        <v>0.8957082992686765</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.655555555555551</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.127777777777766</v>
-      </c>
+        <v>0.6382868937048503</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>-4</v>
+        <v>18058116.92779185</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1294,32 +1240,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5625</v>
+        <v>45564.46875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1346,22 +1292,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P5" t="n">
         <v>-1</v>
       </c>
-      <c r="P5" t="n">
-        <v>-2</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>-1</v>
@@ -1370,95 +1316,101 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1308333333333332</v>
+        <v>0.395</v>
       </c>
       <c r="U5" t="n">
-        <v>0.968333333333333</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3333333333333334</v>
+        <v>-4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>-1.5</v>
       </c>
       <c r="X5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-2.083333333333334</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.333333333333334</v>
-      </c>
       <c r="AB5" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.416666666666667</v>
+        <v>-6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>-10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>75.98117283950616</v>
+      </c>
       <c r="AK5" t="n">
-        <v>76.33333333333334</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+        <v>73.89798611111112</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-1.64406850459482</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.3486549707602506</v>
+      </c>
       <c r="AN5" t="n">
-        <v>-166</v>
+        <v>11380555.55555556</v>
       </c>
       <c r="AO5" t="n">
-        <v>-6577286.03268077</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0.6391515648094632</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>-1.199607994344845</v>
-      </c>
+        <v>0.5083333333333329</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>2.274999999999991</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.1242773600668556</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>-68000000</v>
+        <v>-0.0222222222222217</v>
       </c>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-165</v>
+        <v>3.11666666666666</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-0.2078663295768557</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-2.948456076087666</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-5.286622587938382</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
+        <v>-1.688888888888869</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>2.214414065466741</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.2626080352396143</v>
+      </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>-2</v>
+        <v>5487254.955570746</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1467,11 +1419,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.46875</v>
+        <v>45564.375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1481,18 +1433,18 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1519,139 +1471,125 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4449999999999998</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.7508333333333328</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.07333333333333336</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="Y6" t="n">
-        <v>-0.5</v>
+        <v>-4.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.416666666666666</v>
+        <v>-0.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.416666666666667</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>-7.666666666666666</v>
+        <v>4.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.333333333333334</v>
+        <v>-4.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>-9.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>77.25185185185184</v>
+        <v>76.49083333333334</v>
       </c>
       <c r="AK6" t="n">
-        <v>73.25925925925925</v>
+        <v>74.89670138888889</v>
       </c>
       <c r="AL6" t="n">
-        <v>-2</v>
+        <v>1.055892672858612</v>
       </c>
       <c r="AM6" t="n">
-        <v>-2</v>
+        <v>-2.473009361639399</v>
       </c>
       <c r="AN6" t="n">
-        <v>-200</v>
+        <v>-9260333.333333336</v>
       </c>
       <c r="AO6" t="n">
-        <v>-11927151.37497307</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4.028496687136396</v>
-      </c>
+        <v>1.334074074074074</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>-23408611.11111111</v>
+        <v>-3.743703703703702</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.722222222222229</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.600572344322345</v>
-      </c>
+        <v>-1.009065678903141</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>-301100000</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.31388888888889</v>
-      </c>
+        <v>0.04944444444444462</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-213</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.141666666666667</v>
-      </c>
+        <v>-2.609259259259261</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-0.181602160094807</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-1.150393234216764</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-1.566536710838193</v>
-      </c>
+        <v>-1.815740740740722</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>-4.25</v>
+        <v>0.7117656887316457</v>
       </c>
       <c r="BB6" t="n">
-        <v>-1.625</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-3.25555555555556</v>
-      </c>
+        <v>-0.06743980048159637</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>-2</v>
+        <v>-2279787.765983583</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1660,193 +1598,4654 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45550.375</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>148</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>-28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.725</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>73.81018518518518</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>73.46267361111111</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4.190964515360804</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-3.586411815738444</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-30812500</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.137499999999999</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-4.950000000000003</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.5583628755145895</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>-1.3875</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>-3.087500000000006</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>3.974999999999994</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>-3.953020447045219</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.5458321709250498</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>-15769402.28328173</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.005000000000000004</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.2850000000000001</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>76.43266414141414</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>78.50879629629628</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.402170622635019</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.950869453044362</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>13925416.66666666</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.993055555555557</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.655412796697632</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0.5694444444444449</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>7.027777777777786</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-0.8472222222222285</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>0.6368601651186623</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.3270149638802891</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>6943619.319745444</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>79.39555555555555</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>76.02100694444445</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.767821476768848</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.6743841246472897</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.337499999999999</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>1.703472222222217</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.041297693534531</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0.2201388888888889</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>2.814583333333331</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-3.360416666666623</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>-4.567445493103435</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.1499890022258445</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>535313.0728920195</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.195</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.5499999999999998</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.4500000000000002</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>76.87881944444445</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>80.23987373737374</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.298583343256329</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.988164443915224</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>4984635.416666666</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.715277777777779</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>1.100694444444443</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.1119717823026605</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0.3541666666666665</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>2.677083333333329</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>0.121527777777743</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>1.250676897277117</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>1769991.971468075</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.1899999999999999</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>77.63148148148149</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>76.34953703703704</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-2.450105820105819</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.621587301587283</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-7547166.666666668</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-2.622777777777774</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-2.973333333333329</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-3.731203703703699</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>-0.3311111111111109</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-5.60888888888887</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>-1.867777777777746</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>-1.402142857142849</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.09478835978835942</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>-4295364.351851853</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.9200000000000004</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.9433333333333334</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.9166666666666665</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>74.77592592592593</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>77.16145833333334</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1988235294117651</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-4.890706636500752</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-24537222.22222222</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.9592592592592553</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-5.939259259259273</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-5.724703619909505</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>-0.8105555555555557</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>-7.089259259259265</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>0.2353703703704184</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>1.189948215183534</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.4477543991955759</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>-17656606.58622423</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.1266666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.166666666666666</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.833333333333332</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.8333333333333339</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>7.666666666666664</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-7.666666666666664</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="n">
+        <v>77.45129734848486</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.9764789991570204</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-4.802770831679496</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-2.506230697407176</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>-3.573462927681192</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.5564340243519807</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>-14152452.09554807</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.151666666666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.833333333333334</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>80.68954545454545</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>75.15277777777779</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.3413002202475859</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-4.502849781797167</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-2559375</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.791666666666671</v>
+      </c>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>-2.055555555555557</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-4.072210830105575</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-1.263888888888886</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-1.819444444444514</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>0.1442277021224072</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0.545748987854251</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>-6825703.229519019</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>148</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.683333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.2833333333333334</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.666666666666668</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>16.16666666666666</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-16.16666666666666</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>73.05092592592592</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>76.13009259259259</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-2.601062405731525</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>3.942268368886005</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>33396614.58333334</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-2.958333333333336</v>
+      </c>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>7.635416666666671</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.9309339312648035</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>1.145833333333333</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>4.427083333333329</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>-1.40625</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>0.7213613714716871</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.6170604395604393</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>17579201.4046003</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.4466666666666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-7.000000000000001</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>75.17152777777778</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>81.63555555555556</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-2.99437683575454</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4.454815545651471</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>11832555.55555556</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-3.725277777777773</v>
+      </c>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>5.036527777777778</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.4914261615577402</v>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>-0.03902777777777788</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>2.054861111111109</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>4.390972222222217</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="n">
+        <v>2.910887654657017</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.2460571961578153</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>5794944.000272173</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>18</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6866666666666668</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.2066666666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.6666666666666679</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>75.30555555555556</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>77.57916666666668</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.9489193623713774</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>7.54026019130508</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>76764659.09090909</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.718308080808079</v>
+      </c>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>12.18156565656567</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8.065112028494383</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>2.261818181818182</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>13.52280303030302</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>1.813459595959557</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>-2.551239482911285</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.100683728036669</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>38344772.90315893</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4899999999999999</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.6100000000000001</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10.33333333333334</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-10.33333333333334</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>75.48020833333334</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>76.31944444444444</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.408571428571427</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3.899444444444427</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>7598222.222222222</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.3727777777777774</v>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>4.697777777777787</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.405357142857127</v>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0.3527777777777774</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>4.664999999999992</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>4.221666666666636</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>0.4219841269840856</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.4710317460317457</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>5590570.436507935</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>148</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>15</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.4733333333333334</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.4666666666666661</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-3.666666666666668</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>79.74444444444444</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>75.54166666666667</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-1.168353907014897</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.9374251805985523</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-705972.222222222</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-3.255555555555556</v>
+      </c>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>-2.216666666666654</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-1.600755140112724</v>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0.09583333333333321</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-4.231944444444437</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>-1.016666666666623</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="n">
+        <v>1.004980154004897</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.001663888227355637</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>-1612461.171972164</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>148</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.1233333333333335</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.333333333333329</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-7.333333333333329</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>77.97506313131315</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>75.89629629629628</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-2.955760643438662</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>5.103018084426765</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5033763.888888888</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.7013888888888893</v>
+      </c>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>1.455694444444447</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.684975101151579</v>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0.4626388888888893</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>1.779722222222233</v>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-2.675972222222185</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="n">
+        <v>0.215920192638464</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.4862763116942683</v>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>13588084.30963029</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>148</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.2375</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.7950000000000002</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>78.71111111111111</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.137307692307694</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-6.872512820512824</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-27109444.44444445</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.431944444444444</v>
+      </c>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="n">
+        <v>-7.23208333333335</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-5.207064102564104</v>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>-0.8209722222222224</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="n">
+        <v>-6.534861111111113</v>
+      </c>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>-2.339861111111077</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="n">
+        <v>-2.432705128205129</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-0.6263717948717948</v>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="n">
+        <v>-21171762.82051282</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>148</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-22</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.3874999999999997</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-20.25</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>73.52777777777777</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>74.51851851851852</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>4.434398656898662</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1.880586401902178</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-35128125</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>3.253143756827981</v>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="n">
+        <v>-0.641857689094536</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-0.07131145170618836</v>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="n">
+        <v>-13080509.37439753</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>8pvUZFhf</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G23" t="n">
+        <v>148</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.7275000000000003</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.6625000000000001</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>74.98425925925926</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>72.75833333333334</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-2.051542827657379</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>2.682788957688345</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>12947500</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-0.926851851851854</v>
+      </c>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="n">
+        <v>4.000925925925927</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.138000515995884</v>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="n">
+        <v>3.506481481481487</v>
+      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="n">
+        <v>2.862962962962939</v>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="n">
+        <v>2.632313225130559</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>-0.1116253088157113</v>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="n">
+        <v>5375083.153516587</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>148</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1508333333333333</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4966666666666667</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.416666666666666</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-2.083333333333333</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>4.916666666666668</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>77.29398148148148</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>74.82152777777779</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-1.945282784166295</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>2.377170700816237</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4643663.194444444</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.5388888888888914</v>
+      </c>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="n">
+        <v>2.39791666666666</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>-0.3982168238108699</v>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0.1819444444444445</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="n">
+        <v>2.41180555555556</v>
+      </c>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="n">
+        <v>-1.42986111111108</v>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="n">
+        <v>-0.4502537510219611</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>-0.04866484392800174</v>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="n">
+        <v>500070.0016250517</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>148</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>36</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>27</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.7775000000000001</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.8200000000000001</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-18.75</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>74.52777777777777</v>
+      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="n">
+        <v>-0.9271337657870156</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>8.993263562203197</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>76070909.09090909</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.1696969696969646</v>
+      </c>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="n">
+        <v>12.00101010101011</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>8.065216952809834</v>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>2.261818181818182</v>
+      </c>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="n">
+        <v>13.43252525252525</v>
+      </c>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="n">
+        <v>-1.457373737373672</v>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="n">
+        <v>-4.02564776468796</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.130683728036669</v>
+      </c>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="n">
+        <v>38901792.13100711</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>148</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.7749999999999999</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5750000000000004</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.9166666666666665</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>82.33333333333333</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>77.72013888888888</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-1.297179222566221</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-3.333597596933515</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-7560750.000000002</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-2.149722222222227</v>
+      </c>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="n">
+        <v>-3.873333333333321</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>-4.042399012236473</v>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>-0.1449999999999998</v>
+      </c>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="n">
+        <v>-5.349999999999994</v>
+      </c>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="n">
+        <v>-0.908333333333303</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="n">
+        <v>-1.020374834144178</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-0.3718188854489164</v>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="n">
+        <v>-5632849.122192737</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>148</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.06749999999999989</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.6150000000000002</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>75.75624999999999</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>0.160503587399873</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.7203128484862162</v>
+      </c>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>-0.95089231374061</v>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="n">
+        <v>-0.7776358316605751</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-0.01062460071747995</v>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="n">
+        <v>231145.488391039</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>148</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H28" t="n">
         <v>1481</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>20242025</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.3650000000000002</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.2274999999999999</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.25</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AD28" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AE28" t="n">
         <v>-0.25</v>
       </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-5.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AF28" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>78.675</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>76.78155303030303</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.9391967664258658</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-3.655591675266578</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-21656277.77777777</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1.31722222222222</v>
+      </c>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="n">
+        <v>-7.342222222222233</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>-3.0137134502924</v>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>-0.755555555555556</v>
+      </c>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="n">
+        <v>-8.562222222222218</v>
+      </c>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="n">
+        <v>0.2699999999999818</v>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="n">
+        <v>1.091195390436894</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>-0.3426848985208117</v>
+      </c>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="n">
+        <v>-9293300.202098384</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>148</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.9166666666666665</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>79.23611111111111</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>75.81874999999999</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-2.068562431720327</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-3.601318038686443</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-6730138.888888888</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="n">
+        <v>-3.425000000000011</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>-3.823626373626368</v>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>-0.3749999999999996</v>
+      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>-2.915277777777774</v>
+      </c>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="n">
+        <v>-5.318055555555503</v>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="n">
+        <v>-1.174037658248125</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>-0.4982539682539682</v>
+      </c>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="n">
+        <v>-5208219.474969474</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>148</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.7524999999999999</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.1475</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Y30" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AC30" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>73.74444444444445</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>76.33333333333334</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.222205513784459</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-5.338979266347707</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-17769722.22222222</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.9805555555555543</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>-6.99722222222222</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>-3.661658692185014</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>-0.1805555555555558</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>-89</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>-5.766666666666666</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>-47700000</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>-2.077777777777811</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>-1.687521075415788</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>-0.2169810890863522</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>-9425552.460697196</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>148</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.5733333333333336</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.2333333333333332</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="W31" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>-3.000000000000002</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.666666666666664</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-8.666666666666664</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>79.61363636363637</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.452919523072385</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>4.43831453634084</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>6728211.805555556</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.9236111111111072</v>
+      </c>
+      <c r="AP31" t="n">
         <v>2</v>
       </c>
-      <c r="AG7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-12.25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>73.41666666666667</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>77.03402777777778</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AQ31" t="n">
+        <v>2.055555555555557</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.946419817927179</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>181</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.4618055555555558</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>163</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.961805555555557</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>37225000</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.1666666666666856</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>-3.199999999999989</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.119439683768235</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.6382868937048503</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.8666666666666669</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>15731105.7284756</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45552.58333333334</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>148</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.172</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.200000000000001</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-0.3999999999999986</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-2.799999999999999</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-4.799999999999999</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-9.600000000000001</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0.2</v>
       </c>
-      <c r="AM7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>300</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>5633427.798202617</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.026307189542479</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6074236.111111111</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.07546296296291644</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.205167483660134</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.649768518518524</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>284</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.3344362745098035</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.122263071895432</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-0.694893790849676</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-2.600000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.30740740740741</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.099074074074082</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
+      <c r="AI32" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>78.46700336700337</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>76.59280303030303</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3.389302586531684</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-3.034004373679295</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-14109111.11111111</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.305555555555554</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-4.368888888888904</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.7174902534112988</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-0.4244444444444451</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>68</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>-2.953333333333347</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>-21700000</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>2.137777777777728</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>-6.333333333333343</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.493338247579743</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>-0.2478965387324523</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>-4997935.850246533</v>
+      </c>
+      <c r="BE32" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP10"/>
+  <dimension ref="A1:DP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -955,72 +955,72 @@
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
@@ -1032,32 +1032,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1084,301 +1084,297 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8399999999999999</v>
+        <v>0.6885714285714287</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1214285714285713</v>
+        <v>-0.3857142857142855</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.524</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09799999999999986</v>
+        <v>-0.1840000000000004</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2857142857142856</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U2" t="n">
+        <v>-0.7142857142857144</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.7333333333333334</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.571428571428572</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5333333333333337</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1428571428571423</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.200000000000001</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.466666666666667</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="V2" t="n">
-        <v>-0.2666666666666666</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-3.142857142857143</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.4666666666666663</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-6.857142857142856</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.2857142857142847</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-4.066666666666668</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1.600000000000001</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-0.7142857142857142</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.2857142857142858</v>
-      </c>
       <c r="AH2" t="n">
-        <v>-0.8</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.2857142857142856</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1428571428571428</v>
+        <v>-1.428571428571428</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.2666666666666666</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.822343224679901</v>
+        <v>-2.034314495028782</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.59143475572047</v>
+        <v>3.123851148851149</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3922600651565</v>
+        <v>-1.950862637362638</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.75034151034151</v>
+        <v>1.035535261839611</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-36.60000000000001</v>
+        <v>-20.80000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>45.8</v>
+        <v>7.200000000000003</v>
       </c>
       <c r="AX2" t="n">
-        <v>-26.61538461538461</v>
+        <v>-15.69230769230769</v>
       </c>
       <c r="AY2" t="n">
-        <v>28</v>
+        <v>11.15384615384616</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-25</v>
+        <v>-3.399999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>-1.399999999999999</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>-16.92307692307693</v>
+        <v>0.8461538461538467</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.6923076923076934</v>
+        <v>18.84615384615385</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3</v>
+        <v>-7.285714285714285</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.714285714285712</v>
+        <v>-2.857142857142854</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1.266666666666666</v>
+        <v>-11.06666666666667</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.066666666666663</v>
+        <v>-3.133333333333333</v>
       </c>
       <c r="BH2" t="n">
-        <v>-13.57142857142857</v>
+        <v>-15.14285714285715</v>
       </c>
       <c r="BI2" t="n">
-        <v>13.57142857142857</v>
+        <v>15.14285714285715</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-10.66666666666667</v>
+        <v>-13.06666666666666</v>
       </c>
       <c r="BK2" t="n">
-        <v>10.66666666666667</v>
+        <v>13.06666666666666</v>
       </c>
       <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>0.1257142857142857</v>
+        <v>0.1685714285714285</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.1642857142857143</v>
+        <v>0.5285714285714285</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.276</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.09799999999999993</v>
+        <v>0.1173333333333333</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.8809523809523807</v>
+        <v>1</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.8952380952380949</v>
-      </c>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.1428571428571423</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="CC2" t="n">
-        <v>-3.142857142857144</v>
+        <v>0.7142857142857153</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.466666666666667</v>
+        <v>0.8666666666666671</v>
       </c>
       <c r="CE2" t="n">
-        <v>-1.200000000000001</v>
+        <v>0.2000000000000011</v>
       </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr"/>
       <c r="CH2" t="inlineStr"/>
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="n">
-        <v>0.003340163581037951</v>
+        <v>-0.03170512089554403</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.02123992540509204</v>
+        <v>0.0307723137296308</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.008195299532143305</v>
+        <v>-0.03290441104613708</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.008746191925054582</v>
+        <v>0.03492332572775557</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.2857142857142858</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1642857142857143</v>
+        <v>-0.5285714285714285</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.1257142857142857</v>
+        <v>-0.1685714285714285</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.09799999999999993</v>
+        <v>-0.1173333333333333</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.276</v>
+        <v>-0.5166666666666666</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.29</v>
+        <v>-0.3600000000000001</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.29</v>
+        <v>0.3600000000000001</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0.3739999999999999</v>
+        <v>0.3993333333333333</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.3739999999999999</v>
+        <v>-0.3993333333333333</v>
       </c>
       <c r="CZ2" t="n">
-        <v>77.25222222222223</v>
+        <v>76.11559829059829</v>
       </c>
       <c r="DA2" t="n">
-        <v>75.56241582491582</v>
+        <v>76.52563131313131</v>
       </c>
       <c r="DB2" t="n">
-        <v>-1.281385281385298</v>
+        <v>157</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.2027003738558335</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-3.888455988456002</v>
-      </c>
+        <v>17920.47950759251</v>
+      </c>
+      <c r="DD2" t="inlineStr"/>
       <c r="DE2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-258</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-134701.443001443</v>
-      </c>
+        <v>1.500334648029252</v>
+      </c>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
       <c r="DH2" t="n">
-        <v>-66446.71466488691</v>
+        <v>2</v>
       </c>
       <c r="DI2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.060068880699077</v>
+        <v>0.75</v>
       </c>
       <c r="DK2" t="n">
-        <v>-5.25</v>
+        <v>-23750</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="DM2" t="n">
-        <v>-127750</v>
+        <v>2.757691301891896</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.567821067821068</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1.360771126632471</v>
-      </c>
+        <v>0.1261600794163833</v>
+      </c>
+      <c r="DO2" t="inlineStr"/>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
@@ -1386,32 +1382,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1438,300 +1434,300 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5371428571428571</v>
+        <v>-0.8399999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.055714285714286</v>
+        <v>-0.1214285714285713</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2690196078431371</v>
+        <v>-0.524</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1759607843137254</v>
+        <v>-0.09799999999999986</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1833333333333333</v>
+        <v>-0.2666666666666666</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1166666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>-3.142857142857143</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.714285714285715</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.933333333333334</v>
+        <v>-3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.04999999999999982</v>
+        <v>-0.4666666666666663</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.142857142857144</v>
+        <v>-6.857142857142856</v>
       </c>
       <c r="AC3" t="n">
-        <v>-7.714285714285714</v>
+        <v>-0.2857142857142847</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.966666666666667</v>
+        <v>-4.066666666666668</v>
       </c>
       <c r="AE3" t="n">
-        <v>-2.083333333333332</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="AF3" t="n">
+        <v>-0.7142857142857142</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.2857142857142858</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AG3" t="n">
-        <v>-0.5714285714285714</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.2666666666666666</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.2166666666666667</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>0.2857142857142858</v>
+        <v>-0.2857142857142856</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1500000000000001</v>
+        <v>-0.2666666666666666</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1499999999999999</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1.770281452048369</v>
+        <v>2.822343224679901</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.745486663873761</v>
+        <v>1.59143475572047</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.7707600927337772</v>
+        <v>1.3922600651565</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.348876820312304</v>
+        <v>1.75034151034151</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>20.2</v>
+        <v>-36.60000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.400000000000006</v>
+        <v>45.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5726495726495813</v>
+        <v>-26.61538461538461</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.230769230769226</v>
+        <v>28</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27.6</v>
+        <v>-25</v>
       </c>
       <c r="BA3" t="n">
-        <v>-2.200000000000003</v>
+        <v>-1.399999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.64957264957265</v>
+        <v>-16.92307692307693</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.952991452991455</v>
+        <v>-0.6923076923076934</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.714285714285708</v>
+        <v>-3</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.4285714285714306</v>
+        <v>3.714285714285712</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.300000000000004</v>
+        <v>-1.266666666666666</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.3833333333333329</v>
+        <v>2.066666666666663</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.85714285714285</v>
+        <v>-13.57142857142857</v>
       </c>
       <c r="BI3" t="n">
-        <v>-11.85714285714285</v>
+        <v>13.57142857142857</v>
       </c>
       <c r="BJ3" t="n">
-        <v>4.68333333333333</v>
+        <v>-10.66666666666667</v>
       </c>
       <c r="BK3" t="n">
-        <v>-4.68333333333333</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="n">
-        <v>-0.5371428571428571</v>
+        <v>0.1257142857142857</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.4842857142857143</v>
+        <v>-0.1642857142857143</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.06117647058823535</v>
+        <v>-0.276</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.3014509803921568</v>
+        <v>0.09799999999999993</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.5714285714285716</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.8809523809523807</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.9166666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.04999999999999982</v>
+        <v>0.8952380952380949</v>
       </c>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.857142857142856</v>
+        <v>-0.1428571428571423</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.1428571428571459</v>
+        <v>-3.142857142857144</v>
       </c>
       <c r="CD3" t="n">
-        <v>-1.75</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1333333333333329</v>
+        <v>-1.200000000000001</v>
       </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
       <c r="CH3" t="inlineStr"/>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="n">
-        <v>-0.0009254475193338357</v>
+        <v>0.003340163581037951</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.04791991598381529</v>
+        <v>0.02123992540509204</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.008012871480320136</v>
+        <v>0.008195299532143305</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.007041766262958236</v>
+        <v>0.008746191925054582</v>
       </c>
       <c r="CN3" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="CO3" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="CO3" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
       <c r="CP3" t="n">
-        <v>-0.1833333333333333</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1833333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.4842857142857143</v>
+        <v>0.1642857142857143</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.5371428571428571</v>
+        <v>-0.1257142857142857</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.3014509803921568</v>
+        <v>-0.09799999999999993</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.06117647058823535</v>
+        <v>0.276</v>
       </c>
       <c r="CV3" t="n">
-        <v>-1.021428571428571</v>
+        <v>0.29</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.021428571428571</v>
+        <v>-0.29</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.3626274509803921</v>
+        <v>-0.3739999999999999</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.3626274509803921</v>
+        <v>0.3739999999999999</v>
       </c>
       <c r="CZ3" t="n">
-        <v>77.25481902356903</v>
+        <v>77.25222222222223</v>
       </c>
       <c r="DA3" t="n">
-        <v>73.59467592592593</v>
+        <v>75.56241582491582</v>
       </c>
       <c r="DB3" t="n">
-        <v>-2.630555555555475</v>
+        <v>-173</v>
       </c>
       <c r="DC3" t="n">
-        <v>3.36374437334743</v>
+        <v>-66446.71466488691</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.906944444444449</v>
+        <v>-1.281385281385298</v>
       </c>
       <c r="DE3" t="n">
-        <v>2</v>
+        <v>0.2027003738558335</v>
       </c>
       <c r="DF3" t="n">
-        <v>165</v>
+        <v>1.567821067821068</v>
       </c>
       <c r="DG3" t="n">
-        <v>27802.77777777777</v>
+        <v>-3.888455988456002</v>
       </c>
       <c r="DH3" t="n">
-        <v>31384.1136135475</v>
+        <v>-2</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.666666666666668</v>
+        <v>-5</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.7678837324402821</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.666666666666671</v>
+        <v>-120666.6666666667</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.6666666666666572</v>
+        <v>1</v>
       </c>
       <c r="DM3" t="n">
-        <v>18000</v>
+        <v>1.060068880699077</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.851388888888881</v>
+        <v>1.360771126632471</v>
       </c>
       <c r="DO3" t="n">
-        <v>-1.038183271713784</v>
+        <v>-134701.443001443</v>
       </c>
       <c r="DP3" t="n">
         <v>0</v>
@@ -1740,32 +1736,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45564.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1792,304 +1788,300 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.05857142857142872</v>
+        <v>0.5371428571428571</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.05571428571428583</v>
+        <v>-1.055714285714286</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2847083333333333</v>
+        <v>0.2690196078431371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.09579166666666672</v>
+        <v>-0.1759607843137254</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4285714285714286</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1208333333333333</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.07916666666666661</v>
+        <v>-0.1166666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.571428571428571</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1</v>
+        <v>-2.714285714285715</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.5291666666666668</v>
+        <v>1.933333333333334</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.295833333333333</v>
+        <v>-0.04999999999999982</v>
       </c>
       <c r="AB4" t="n">
-        <v>-5.714285714285714</v>
+        <v>5.142857142857144</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1</v>
+        <v>-7.714285714285714</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.808333333333334</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.4625000000000004</v>
+        <v>-2.083333333333332</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.2857142857142858</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.2041666666666666</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.7142857142857144</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="AK4" t="n">
         <v>-0.5714285714285714</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.55</v>
+        <v>0.1500000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-0.1499999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.491528114742401</v>
+        <v>-1.770281452048369</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.41698063840921</v>
+        <v>2.745486663873761</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.910733241431771</v>
+        <v>-0.7707600927337772</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8642909574086044</v>
+        <v>1.348876820312304</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>23.20000000000002</v>
+        <v>20.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.400000000000006</v>
+        <v>1.400000000000006</v>
       </c>
       <c r="AX4" t="n">
-        <v>31.81318681318682</v>
+        <v>0.5726495726495813</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.05494505494506541</v>
+        <v>9.230769230769226</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-5.800000000000004</v>
+        <v>27.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.200000000000003</v>
+        <v>-2.200000000000003</v>
       </c>
       <c r="BB4" t="n">
-        <v>12.08791208791209</v>
+        <v>10.64957264957265</v>
       </c>
       <c r="BC4" t="n">
-        <v>-2.098901098901102</v>
+        <v>6.952991452991455</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2.428571428571431</v>
+        <v>8.714285714285708</v>
       </c>
       <c r="BE4" t="n">
-        <v>3</v>
+        <v>-0.4285714285714306</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.05833333333333</v>
+        <v>4.300000000000004</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.5083333333333329</v>
+        <v>0.3833333333333329</v>
       </c>
       <c r="BH4" t="n">
-        <v>-10</v>
+        <v>11.85714285714285</v>
       </c>
       <c r="BI4" t="n">
-        <v>10</v>
+        <v>-11.85714285714285</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.9874999999999972</v>
+        <v>4.68333333333333</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.9874999999999972</v>
+        <v>-4.68333333333333</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>0.63</v>
+        <v>-0.5371428571428571</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0.23</v>
+        <v>0.4842857142857143</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.5847083333333334</v>
+        <v>-0.06117647058823535</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.108375</v>
+        <v>0.3014509803921568</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0.4285714285714284</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.4285714285714288</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.875</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.2708333333333335</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>0.25</v>
+        <v>-1</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.08333333333333331</v>
+        <v>1</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0.4285714285714306</v>
+        <v>2.857142857142856</v>
       </c>
       <c r="CC4" t="n">
-        <v>-2.142857142857144</v>
+        <v>-0.1428571428571459</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.8583333333333325</v>
+        <v>-1.75</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.6083333333333325</v>
+        <v>-0.1333333333333329</v>
       </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
       <c r="CH4" t="inlineStr"/>
       <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="n">
-        <v>-0.009217170619331291</v>
+        <v>-0.0009254475193338357</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.02270822911424415</v>
+        <v>-0.04791991598381529</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.003651736827716842</v>
+        <v>0.008012871480320136</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0005207966501886638</v>
+        <v>-0.007041766262958236</v>
       </c>
       <c r="CN4" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CO4" t="n">
         <v>-0.1428571428571428</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.04583333333333334</v>
+        <v>-0.1833333333333333</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.2041666666666667</v>
+        <v>-0.1833333333333333</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.23</v>
+        <v>-0.4842857142857143</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0.63</v>
+        <v>0.5371428571428571</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.108375</v>
+        <v>-0.3014509803921568</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.5847083333333334</v>
+        <v>0.06117647058823535</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.8600000000000001</v>
+        <v>-1.021428571428571</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.8600000000000001</v>
+        <v>1.021428571428571</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.6930833333333333</v>
+        <v>-0.3626274509803921</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0.6930833333333333</v>
+        <v>0.3626274509803921</v>
       </c>
       <c r="CZ4" t="n">
-        <v>75.81342592592593</v>
+        <v>77.25481902356903</v>
       </c>
       <c r="DA4" t="n">
-        <v>75.90694444444445</v>
+        <v>73.59467592592593</v>
       </c>
       <c r="DB4" t="n">
-        <v>-1.668518518518539</v>
+        <v>93</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.2451335377782016</v>
+        <v>31384.1136135475</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.678148148148139</v>
+        <v>-2.630555555555475</v>
       </c>
       <c r="DE4" t="n">
-        <v>-2</v>
+        <v>3.36374437334743</v>
       </c>
       <c r="DF4" t="n">
-        <v>-151</v>
+        <v>1.851388888888881</v>
       </c>
       <c r="DG4" t="n">
-        <v>2038.518518518515</v>
+        <v>4.906944444444449</v>
       </c>
       <c r="DH4" t="n">
-        <v>490.9188555805158</v>
+        <v>1</v>
       </c>
       <c r="DI4" t="n">
-        <v>-1</v>
+        <v>6.666666666666671</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.29413683370862</v>
+        <v>1.666666666666668</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.333333333333329</v>
+        <v>19000</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.666666666666657</v>
+        <v>-3.833333333333343</v>
       </c>
       <c r="DM4" t="n">
-        <v>-666.6666666666642</v>
+        <v>-0.7678837324402821</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0.1062962962962928</v>
+        <v>-1.038183271713784</v>
       </c>
       <c r="DO4" t="n">
-        <v>-1.104828582844277</v>
+        <v>27802.77777777777</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
@@ -2098,32 +2090,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.375</v>
+        <v>45564.46875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2150,304 +2142,304 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.332857142857143</v>
+        <v>-0.05857142857142872</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4085714285714287</v>
+        <v>-0.05571428571428583</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.222</v>
+        <v>-0.2847083333333333</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1286666666666669</v>
+        <v>-0.09579166666666672</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.1208333333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.07916666666666661</v>
       </c>
       <c r="X5" t="n">
-        <v>1.714285714285714</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5714285714285712</v>
+        <v>-1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5333333333333332</v>
+        <v>-0.5291666666666668</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2666666666666666</v>
+        <v>-1.295833333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7142857142857153</v>
+        <v>-5.714285714285714</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7142857142857135</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.6666666666666661</v>
+        <v>-1.808333333333334</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.2000000000000011</v>
+        <v>-0.4625000000000004</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.2000000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4666666666666668</v>
+        <v>-0.2041666666666666</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.142857142857143</v>
+        <v>0.7142857142857144</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.1333333333333335</v>
+        <v>0.55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.2666666666666666</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.6634302205730771</v>
+        <v>2.491528114742401</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.850233945252742</v>
+        <v>1.41698063840921</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.339222870527218</v>
+        <v>1.910733241431771</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.05827741144304577</v>
+        <v>0.8642909574086044</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-9.799999999999997</v>
+        <v>23.20000000000002</v>
       </c>
       <c r="AW5" t="n">
-        <v>23.60000000000001</v>
+        <v>2.400000000000006</v>
       </c>
       <c r="AX5" t="n">
-        <v>-4.15384615384616</v>
+        <v>31.81318681318682</v>
       </c>
       <c r="AY5" t="n">
-        <v>18.84615384615384</v>
+        <v>-0.05494505494506541</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-10.2</v>
+        <v>-5.800000000000004</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.400000000000006</v>
+        <v>5.200000000000003</v>
       </c>
       <c r="BB5" t="n">
-        <v>-5.46153846153846</v>
+        <v>12.08791208791209</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.230769230769226</v>
+        <v>-2.098901098901102</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.7142857142857153</v>
+        <v>-2.428571428571431</v>
       </c>
       <c r="BE5" t="n">
-        <v>-1.285714285714285</v>
+        <v>3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.799999999999997</v>
+        <v>1.05833333333333</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.599999999999994</v>
+        <v>0.5083333333333329</v>
       </c>
       <c r="BH5" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-4.399999999999999</v>
+        <v>-0.9874999999999972</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.399999999999999</v>
+        <v>0.9874999999999972</v>
       </c>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>0.5242857142857142</v>
+        <v>0.63</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1628571428571429</v>
+        <v>-0.23</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0220000000000001</v>
+        <v>0.5847083333333334</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.5953333333333333</v>
+        <v>-0.108375</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1190476190476191</v>
+        <v>-0.4285714285714284</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.07142857142857162</v>
+        <v>-0.4285714285714288</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2142857142857142</v>
+        <v>-0.875</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.2708333333333335</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.3333333333333334</v>
+        <v>0.08333333333333331</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.2857142857142847</v>
+        <v>-0.4285714285714306</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.142857142857141</v>
+        <v>-2.142857142857144</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.266666666666667</v>
+        <v>0.8583333333333325</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.066666666666668</v>
+        <v>0.6083333333333325</v>
       </c>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="inlineStr"/>
       <c r="CI5" t="inlineStr"/>
       <c r="CJ5" t="n">
-        <v>0.008041519219204374</v>
+        <v>-0.009217170619331291</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.03060205977597281</v>
+        <v>0.02270822911424415</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.005728090949074657</v>
+        <v>0.003651736827716842</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.003233568779033053</v>
+        <v>0.0005207966501886638</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.04583333333333334</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.06666666666666665</v>
+        <v>-0.2041666666666667</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.1628571428571429</v>
+        <v>0.23</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.5242857142857142</v>
+        <v>-0.63</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.5953333333333333</v>
+        <v>0.108375</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0220000000000001</v>
+        <v>-0.5847083333333334</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.3614285714285714</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.3614285714285714</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.5733333333333333</v>
+        <v>0.6930833333333333</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.5733333333333333</v>
+        <v>-0.6930833333333333</v>
       </c>
       <c r="CZ5" t="n">
-        <v>75.40757575757576</v>
+        <v>75.81342592592593</v>
       </c>
       <c r="DA5" t="n">
-        <v>76.93124999999999</v>
+        <v>75.90694444444445</v>
       </c>
       <c r="DB5" t="n">
-        <v>-1.872916666666669</v>
+        <v>84</v>
       </c>
       <c r="DC5" t="n">
-        <v>-1.631050909506229</v>
+        <v>490.9188555805158</v>
       </c>
       <c r="DD5" t="n">
-        <v>-2.253240740740736</v>
+        <v>-1.668518518518539</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.2451335377782016</v>
       </c>
       <c r="DF5" t="n">
-        <v>22</v>
+        <v>-0.1062962962962928</v>
       </c>
       <c r="DG5" t="n">
-        <v>-7898.611111111117</v>
+        <v>2.678148148148139</v>
       </c>
       <c r="DH5" t="n">
-        <v>-10991.53708962422</v>
+        <v>1</v>
       </c>
       <c r="DI5" t="n">
-        <v>5</v>
+        <v>1.333333333333329</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.2381243431000257</v>
+        <v>-1</v>
       </c>
       <c r="DK5" t="n">
-        <v>11</v>
+        <v>-7916.666666666664</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666572</v>
       </c>
       <c r="DM5" t="n">
-        <v>14000</v>
+        <v>2.29413683370862</v>
       </c>
       <c r="DN5" t="n">
-        <v>2.008333333333326</v>
+        <v>-1.104828582844277</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.555957303790116</v>
+        <v>2038.518518518515</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -2456,32 +2448,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45564.375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2508,1722 +2500,306 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A7eo6U2U</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.27</v>
+        <v>0.332857142857143</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3899999999999999</v>
+        <v>0.4085714285714287</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.9393333333333334</v>
+        <v>-0.222</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001333333333332964</v>
+        <v>-0.1286666666666669</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.428571428571428</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U6" t="n">
-        <v>1.142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7333333333333334</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.428571428571429</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.142857142857143</v>
+        <v>0.5714285714285712</v>
       </c>
       <c r="Z6" t="n">
-        <v>-3.733333333333333</v>
+        <v>0.5333333333333332</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2000000000000002</v>
+        <v>-0.2666666666666666</v>
       </c>
       <c r="AB6" t="n">
-        <v>-8.428571428571427</v>
+        <v>0.7142857142857153</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.428571428571429</v>
+        <v>0.7142857142857135</v>
       </c>
       <c r="AD6" t="n">
-        <v>-6.133333333333335</v>
+        <v>-0.6666666666666661</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.533333333333333</v>
+        <v>-0.2000000000000011</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.6</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.4666666666666668</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.142857142857143</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1.466666666666667</v>
+        <v>-0.1333333333333335</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.133333333333333</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.025310559006212</v>
+        <v>0.6634302205730771</v>
       </c>
       <c r="AO6" t="n">
-        <v>-2.732015370250664</v>
+        <v>-1.850233945252742</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.734594120318758</v>
+        <v>1.339222870527218</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.360054107112931</v>
+        <v>-0.05827741144304577</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-22</v>
+        <v>-9.799999999999997</v>
       </c>
       <c r="AW6" t="n">
-        <v>35</v>
+        <v>23.60000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>-18.15384615384616</v>
+        <v>-4.15384615384616</v>
       </c>
       <c r="AY6" t="n">
-        <v>30.46153846153847</v>
+        <v>18.84615384615384</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-9.399999999999999</v>
+        <v>-10.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.600000000000001</v>
+        <v>1.400000000000006</v>
       </c>
       <c r="BB6" t="n">
-        <v>-5.230769230769226</v>
+        <v>-5.46153846153846</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.15384615384615</v>
+        <v>3.230769230769226</v>
       </c>
       <c r="BD6" t="n">
-        <v>-3.142857142857146</v>
+        <v>-0.7142857142857153</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.14285714285714</v>
+        <v>-1.285714285714285</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1.733333333333334</v>
+        <v>1.799999999999997</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.666666666666668</v>
+        <v>2.599999999999994</v>
       </c>
       <c r="BH6" t="n">
-        <v>-20.28571428571428</v>
+        <v>-2</v>
       </c>
       <c r="BI6" t="n">
-        <v>20.28571428571428</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-18.46666666666667</v>
+        <v>-4.399999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>18.46666666666667</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="n">
-        <v>-0.872857142857143</v>
+        <v>0.5242857142857142</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.4671428571428571</v>
+        <v>0.1628571428571429</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.6606666666666667</v>
+        <v>0.0220000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.5986666666666667</v>
+        <v>0.5953333333333333</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.6190476190476193</v>
+        <v>0.1190476190476191</v>
       </c>
       <c r="BU6" t="n">
-        <v>-1.119047619047619</v>
+        <v>0.07142857142857162</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.004761904761904745</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0428571428571427</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="BX6" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.714285714285714</v>
+        <v>-0.2857142857142847</v>
       </c>
       <c r="CC6" t="n">
-        <v>-2.857142857142858</v>
+        <v>4.142857142857141</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.4666666666666668</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="CE6" t="n">
-        <v>-1.133333333333333</v>
+        <v>1.066666666666668</v>
       </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="inlineStr"/>
       <c r="CI6" t="inlineStr"/>
       <c r="CJ6" t="n">
-        <v>0.01890316798211535</v>
+        <v>0.008041519219204374</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.02381722460680223</v>
+        <v>0.03060205977597281</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.005949286873919601</v>
+        <v>0.005728090949074657</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.01490355206441994</v>
+        <v>-0.003233568779033053</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.4671428571428571</v>
+        <v>-0.1628571428571429</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.872857142857143</v>
+        <v>-0.5242857142857142</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.5986666666666667</v>
+        <v>-0.5953333333333333</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.6606666666666667</v>
+        <v>-0.0220000000000001</v>
       </c>
       <c r="CV6" t="n">
-        <v>-1.34</v>
+        <v>0.3614285714285714</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.34</v>
+        <v>-0.3614285714285714</v>
       </c>
       <c r="CX6" t="n">
-        <v>-1.259333333333333</v>
+        <v>-0.5733333333333333</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.259333333333333</v>
+        <v>0.5733333333333333</v>
       </c>
       <c r="CZ6" t="n">
-        <v>75.396626984127</v>
+        <v>75.40757575757576</v>
       </c>
       <c r="DA6" t="n">
-        <v>75.6799422799423</v>
+        <v>76.93124999999999</v>
       </c>
       <c r="DB6" t="n">
-        <v>4.233333333333348</v>
+        <v>97</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.084374843054619</v>
+        <v>-10991.53708962422</v>
       </c>
       <c r="DD6" t="n">
-        <v>-3.141666666666666</v>
+        <v>-1.87291666666664</v>
       </c>
       <c r="DE6" t="n">
-        <v>-5</v>
+        <v>-1.631050909506229</v>
       </c>
       <c r="DF6" t="n">
-        <v>-448</v>
+        <v>2.008333333333326</v>
       </c>
       <c r="DG6" t="n">
-        <v>-85150</v>
+        <v>-2.253240740740736</v>
       </c>
       <c r="DH6" t="n">
-        <v>-40754.06204992118</v>
+        <v>1</v>
       </c>
       <c r="DI6" t="n">
-        <v>-5.166666666666668</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-4.003943176460893</v>
+        <v>6.833333333333332</v>
       </c>
       <c r="DK6" t="n">
-        <v>-22.16666666666667</v>
+        <v>16166.66666666667</v>
       </c>
       <c r="DL6" t="n">
-        <v>-4</v>
+        <v>-2.833333333333343</v>
       </c>
       <c r="DM6" t="n">
-        <v>-149500</v>
+        <v>0.2381243431000257</v>
       </c>
       <c r="DN6" t="n">
-        <v>2.008333333333336</v>
+        <v>0.555957303790116</v>
       </c>
       <c r="DO6" t="n">
-        <v>4.738529075597853</v>
+        <v>-7898.611111111117</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>148</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3514285714285713</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.1514285714285719</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.1336666666666665</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.1176666666666668</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1.142857142857143</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.1125</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.2250000000000001</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.4285714285714288</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.4285714285714284</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.3250000000000002</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.6291666666666669</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.428571428571427</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.571428571428571</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.3708333333333336</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1.541666666666666</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.2857142857142858</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.4285714285714286</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.07916666666666672</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.4375</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.2541666666666667</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-0.2708333333333333</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-2.211440940012368</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.4850143903715338</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.6958698586272116</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.203741351241351</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>-5.433333333333323</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-8.666666666666671</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11.85714285714286</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-20.07142857142857</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-4.133333333333333</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.066666666666663</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.0714285714285694</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-7.928571428571431</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.714285714285715</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-1.142857142857139</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.616666666666667</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.216666666666669</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>11.42857142857142</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-11.42857142857142</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10.14166666666667</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-10.14166666666667</v>
-      </c>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="n">
-        <v>-0.6371428571428571</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-0.2771428571428572</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.05450000000000002</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>-0.3198333333333332</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.4285714285714288</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>-0.1428571428571432</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0.7333333333333334</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.571428571428571</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>3.000000000000002</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>2.920833333333334</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>-0.7208333333333332</v>
-      </c>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
-      <c r="CI7" t="inlineStr"/>
-      <c r="CJ7" t="n">
-        <v>-0.02696334541591025</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.0007566466600049948</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0.001917237729385617</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>-0.00593367521899741</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0.08750000000000002</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0.09166666666666667</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0.2771428571428572</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>0.6371428571428571</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0.3198333333333332</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>-0.05450000000000002</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>0.3743333333333332</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>-0.3743333333333332</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>76.5771103896104</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>77.5858024691358</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>-1.11944444444444</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>2.39884927655271</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>7.030555555555551</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>-153</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>18177.77777777778</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>5370.058110963684</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>0.5777742676017397</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>-2750</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>2.777777777777786</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-0.4218735739910038</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45563.46875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>148</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.3371428571428572</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.08714285714285697</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.304625</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.08650000000000002</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.142857142857143</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.2083333333333333</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.1916666666666667</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.8571428571428568</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.7142857142857144</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.3166666666666669</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.857142857142857</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.7142857142857153</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>5.383333333333333</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.4166666666666661</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.01249999999999996</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.2583333333333333</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.4285714285714287</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-0.4285714285714284</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-0.1166666666666667</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.2833333333333334</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-0.8587334933973585</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-0.7047464440321582</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.7852846749292826</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.3219508963258959</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-3.200000000000003</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-4.200000000000003</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.835164835164832</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-10.07692307692308</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>12.74175824175824</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-3.791208791208796</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.714285714285715</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.857142857142861</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.5625</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.857142857142861</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>-3.857142857142861</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>6.375</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>-6.375</v>
-      </c>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="n">
-        <v>0.2342857142857143</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>-0.2300000000000001</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>-0.317125</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.1718333333333333</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0.7142857142857144</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0.2232142857142856</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0.09821428571428559</v>
-      </c>
-      <c r="BX8" t="inlineStr"/>
-      <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>2.571428571428569</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>-0.2857142857142847</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>1.600000000000001</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
-      <c r="CJ8" t="n">
-        <v>0.01166160594712073</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>-0.007479740465221409</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.01356725292310521</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>-0.01291182587977613</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>-0.2857142857142857</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>-0.04583333333333334</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.2300000000000001</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>-0.2342857142857143</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>-0.1718333333333333</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0.317125</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>0.4642857142857143</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>-0.4642857142857143</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>-0.4889583333333334</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0.4889583333333334</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>76.40493827160493</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>71.63292929292929</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>-2.879629629629619</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>2.894062773610827</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>2.273148148148152</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>68</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>118.0555555555547</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>5200.824175824175</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>-5.033045554478235</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>1.898148148148152</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.79344046132212</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45563.375</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>148</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.3828571428571427</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.06999999999999984</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.2726666666666666</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1386666666666665</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.7142857142857143</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.5333333333333332</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.4666666666666666</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.285714285714286</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.1428571428571432</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-1.066666666666666</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.2857142857142865</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-1.428571428571429</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-1.142857142857143</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.5714285714285715</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.8666666666666666</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.8571428571428572</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.4285714285714286</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.3732142857142851</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>3.463038548752834</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.477582477435418</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2.928033448033448</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>1.799999999999997</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11.53846153846155</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-1.307692307692307</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-1.399999999999999</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-6.769230769230766</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-4.692307692307693</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>8.857142857142854</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.142857142857139</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.466666666666661</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.399999999999999</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1.571428571428569</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>-1.571428571428569</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>5.266666666666673</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>-5.266666666666673</v>
-      </c>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>-0.6414285714285717</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>-0.5940000000000001</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>-0.3386666666666668</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.2857142857142856</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-0.7142857142857144</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.06666666666666643</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>-0.08333333333333331</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>2.428571428571431</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>2.571428571428573</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>3.800000000000001</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.9999999999999982</v>
-      </c>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr"/>
-      <c r="CH9" t="inlineStr"/>
-      <c r="CI9" t="inlineStr"/>
-      <c r="CJ9" t="n">
-        <v>-0.04200339644036094</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>-0.01497352166237614</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.002580398549703454</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>-0.003271242942632709</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.6414285714285717</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.3386666666666668</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.5940000000000001</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>-0.1185714285714285</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>0.1185714285714285</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>-0.2553333333333333</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>0.2553333333333333</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>76.97454086317724</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>77.71883417508417</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.1689814814814383</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1.172312899518772</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>3.324074074074076</v>
-      </c>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
-      <c r="DG9" t="n">
-        <v>9060.185185185184</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>7787.266337034136</v>
-      </c>
-      <c r="DI9" t="inlineStr"/>
-      <c r="DJ9" t="n">
-        <v>0.6971295603261751</v>
-      </c>
-      <c r="DK9" t="inlineStr"/>
-      <c r="DL9" t="inlineStr"/>
-      <c r="DM9" t="inlineStr"/>
-      <c r="DN9" t="n">
-        <v>3.018518518518515</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.2704318772043237</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45562.66666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>148</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.2885714285714285</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.4728571428571426</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.07750000000000001</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.10625</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.1428571428571429</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.1875</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-2.142857142857143</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.8571428571428577</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-1.142857142857142</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.1875</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.4285714285714285</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.428571428571428</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-0.8571428571428571</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.8571428571428572</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>3.928123541906881</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-0.712981807968196</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.948881881474592</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-20.43333333333332</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.900000000000006</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-6.852380952380955</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-13.04285714285714</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.633333333333333</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-6.266666666666666</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.128571428571433</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-4.685714285714283</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.571428571428569</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-0.1428571428571388</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-2.285714285714285</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.285714285714285</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>3.9375</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>-3.9375</v>
-      </c>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0.9557142857142857</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0.14375</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.6875</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>-0.1666666666666666</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>2.857142857142856</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>1.714285714285715</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>-0.0625</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr"/>
-      <c r="CH10" t="inlineStr"/>
-      <c r="CI10" t="inlineStr"/>
-      <c r="CJ10" t="n">
-        <v>0.03881778941592356</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>-0.005729486363026434</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0.001004904926037734</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0.006916858149454558</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>-0.9557142857142857</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>-0.14375</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>-1.095714285714286</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>1.095714285714286</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>-0.003750000000000045</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>0.003750000000000045</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>72.02361111111111</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>77.64429713804714</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>-2.098412698412659</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>-3.410530250747641</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>-5.245634920634913</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>-165</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>-11890.87301587301</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>-5941.837145486208</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>-1.200504042196627</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>-5.133333333333326</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>-14200</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>-2.469841269841268</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>-1.950990009530376</v>
-      </c>
-      <c r="DP10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP6"/>
+  <dimension ref="A1:DJ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,12 +505,12 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_30_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_goals_(xg)_against</t>
+          <t>dif_mean_last_30_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_points</t>
+          <t>dif_mean_last_30_matches_expected_points</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_expected_points_against</t>
+          <t>dif_mean_last_30_matches_expected_points_against</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal</t>
+          <t>dif_mean_last_30_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_30_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+          <t>dif_mean_last_30_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals</t>
+          <t>dif_mean_last_30_matches_goals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals_against</t>
+          <t>dif_mean_last_30_matches_goals_against</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points</t>
+          <t>dif_mean_last_30_matches_points</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points_against</t>
+          <t>dif_mean_last_30_matches_points_against</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio</t>
+          <t>dif_mean_last_30_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+          <t>dif_mean_last_30_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPS</t>
+          <t>dif_mean_last_30_matches_PPS</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPS_against</t>
+          <t>dif_mean_last_30_matches_PPS_against</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacks</t>
+          <t>dif_mean_last_30_matches_attacks</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacks_against</t>
+          <t>dif_mean_last_30_matches_attacks_against</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+          <t>dif_mean_last_30_matches_dangerous_attacks_against</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls</t>
+          <t>dif_mean_last_30_matches_dead_balls</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls_against</t>
+          <t>dif_mean_last_30_matches_dead_balls_against</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession</t>
+          <t>dif_mean_last_30_matches_ball_possession</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_ball_possession_against</t>
+          <t>dif_mean_last_30_matches_ball_possession_against</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_total_passes</t>
+          <t>dif_mean_last_30_matches_total_passes</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_total_passes_against</t>
+          <t>dif_mean_last_30_matches_total_passes_against</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
@@ -765,197 +765,197 @@
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacking_efficiency</t>
+          <t>dif_mean_last_30_matches_yellow_cards</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_attacking_efficiency_against</t>
+          <t>dif_mean_last_30_matches_yellow_cards_against</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_attacking_efficiency</t>
+          <t>dif_mean_last_180_matches_yellow_cards</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_attacking_efficiency_against</t>
+          <t>dif_mean_last_180_matches_yellow_cards_against</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards</t>
+          <t>dif_mean_last_30_matches_red_cards</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+          <t>dif_mean_last_30_matches_red_cards_against</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_yellow_cards</t>
+          <t>dif_mean_last_180_matches_red_cards</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_yellow_cards_against</t>
+          <t>dif_mean_last_180_matches_red_cards_against</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards</t>
+          <t>dif_mean_last_30_matches_defensive_actions</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards_against</t>
+          <t>dif_mean_last_30_matches_defensive_actions_against</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_red_cards</t>
+          <t>dif_mean_last_180_matches_defensive_actions</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_red_cards_against</t>
+          <t>dif_mean_last_180_matches_defensive_actions_against</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_defensive_actions</t>
+          <t>dif_mean_last_30_matches_PPDA</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+          <t>dif_mean_last_30_matches_PPDA_against</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_defensive_actions</t>
+          <t>dif_mean_last_180_matches_PPDA</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_defensive_actions_against</t>
+          <t>dif_mean_last_180_matches_PPDA_against</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
+          <t>dif_mean_last_30_matches_KGP</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPDA_against</t>
+          <t>dif_mean_last_30_matches_KGP_against</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_PPDA</t>
+          <t>dif_mean_last_180_matches_KGP</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_PPDA_against</t>
+          <t>dif_mean_last_180_matches_KGP_against</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_KGP</t>
+          <t>dif_mean_last_30_matches_clean_sheet</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_KGP_against</t>
+          <t>dif_mean_last_30_matches_clean_sheet_against</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_KGP</t>
+          <t>dif_mean_last_180_matches_clean_sheet</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_KGP_against</t>
+          <t>dif_mean_last_180_matches_clean_sheet_against</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_clean_sheet</t>
+          <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_clean_sheet</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_clean_sheet_against</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_defensive_efficiency</t>
+          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_defensive_efficiency_against</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_defensive_efficiency</t>
+          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_defensive_efficiency_against</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_efficiency</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_efficiency_against</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_efficiency</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_efficiency_against</t>
+          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_180_matches_mean_rat_player_start_home_against</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="DA1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_rat_player_miss</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="DC1" s="1" t="inlineStr">
@@ -965,99 +965,69 @@
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_value_player_start</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_miss</t>
+          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45584.46875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1084,330 +1054,274 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>UsfeP2jC</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6885714285714287</v>
+        <v>-0.3800000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3857142857142855</v>
+        <v>0.4366666666666666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7499999999999999</v>
+        <v>-0.3399999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1840000000000004</v>
+        <v>0.3964285714285711</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7142857142857144</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.8</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7333333333333334</v>
+        <v>0.6</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.571428571428572</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5333333333333337</v>
+        <v>-1.928571428571428</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.199999999999999</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>-5.666666666666668</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1428571428571423</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.200000000000001</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.466666666666667</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.8571428571428572</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.266666666666667</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AL2" t="n">
         <v>-0.06666666666666665</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1.571428571428571</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-1.428571428571428</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.533333333333333</v>
-      </c>
       <c r="AM2" t="n">
-        <v>-1.466666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2.034314495028782</v>
+        <v>1.486771561771562</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.123851148851149</v>
+        <v>-2.383333333333332</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.950862637362638</v>
+        <v>1.114844950371266</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.035535261839611</v>
+        <v>-0.7444739609130364</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-20.80000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.200000000000003</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-15.69230769230769</v>
+        <v>7.272727272727266</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.15384615384616</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.399999999999999</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15</v>
-      </c>
+        <v>-12.27272727272728</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>0.8461538461538467</v>
+        <v>-3.63636363636364</v>
       </c>
       <c r="BC2" t="n">
-        <v>18.84615384615385</v>
+        <v>0.818181818181813</v>
       </c>
       <c r="BD2" t="n">
-        <v>-7.285714285714285</v>
+        <v>-6.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>-2.857142857142854</v>
+        <v>10.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>-11.06666666666667</v>
+        <v>-1.533333333333339</v>
       </c>
       <c r="BG2" t="n">
-        <v>-3.133333333333333</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="BH2" t="n">
-        <v>-15.14285714285715</v>
+        <v>-15.66666666666666</v>
       </c>
       <c r="BI2" t="n">
-        <v>15.14285714285715</v>
+        <v>15.66666666666666</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-13.06666666666666</v>
+        <v>-8.857142857142854</v>
       </c>
       <c r="BK2" t="n">
-        <v>13.06666666666666</v>
+        <v>8.857142857142854</v>
       </c>
       <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>0.1685714285714285</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.5285714285714285</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.5166666666666666</v>
+        <v>0.2252747252747251</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1173333333333333</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.4835164835164836</v>
+      </c>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.6666666666666665</v>
+        <v>-0.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.5</v>
+        <v>-8.75</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>-1.571428571428571</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.7142857142857153</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0.8666666666666671</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.2000000000000011</v>
-      </c>
+        <v>-3.866666666666667</v>
+      </c>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
-      <c r="CI2" t="inlineStr"/>
+      <c r="CH2" t="n">
+        <v>0.01142048147838962</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.007851362214019726</v>
+      </c>
       <c r="CJ2" t="n">
-        <v>-0.03170512089554403</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0307723137296308</v>
+        <v>0.25</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0.03290441104613708</v>
+        <v>-0.2</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.03492332572775557</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>-0.5285714285714285</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>-0.1685714285714285</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>-0.1173333333333333</v>
-      </c>
+        <v>-1.876174134507465</v>
+      </c>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="n">
-        <v>-0.5166666666666666</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>-0.3600000000000001</v>
-      </c>
+        <v>4.038327163999568</v>
+      </c>
+      <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="n">
-        <v>0.3600000000000001</v>
+        <v>-3.786240009667779</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.3993333333333333</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>-0.3993333333333333</v>
-      </c>
+        <v>1.096373909565656</v>
+      </c>
+      <c r="CY2" t="inlineStr"/>
       <c r="CZ2" t="n">
-        <v>76.11559829059829</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>76.52563131313131</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>157</v>
-      </c>
+        <v>-0.01935579255625686</v>
+      </c>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
       <c r="DC2" t="n">
-        <v>17920.47950759251</v>
-      </c>
-      <c r="DD2" t="inlineStr"/>
-      <c r="DE2" t="n">
-        <v>1.500334648029252</v>
-      </c>
+        <v>4294.081184875493</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-741537.0562905874</v>
+      </c>
+      <c r="DE2" t="inlineStr"/>
       <c r="DF2" t="inlineStr"/>
       <c r="DG2" t="inlineStr"/>
-      <c r="DH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>3</v>
-      </c>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
       <c r="DJ2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-23750</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>2.757691301891896</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.1261600794163833</v>
-      </c>
-      <c r="DO2" t="inlineStr"/>
-      <c r="DP2" t="n">
-        <v>0</v>
+        <v>-3.99199044312239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45584.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1434,334 +1348,288 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8399999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1214285714285713</v>
+        <v>-2.006666666666666</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.524</v>
+        <v>-0.2402857142857144</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.09799999999999986</v>
+        <v>-0.1504285714285716</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2857142857142856</v>
+        <v>0.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1428571428571428</v>
+        <v>-1</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2666666666666666</v>
+        <v>-0.3157894736842106</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.04210526315789465</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.142857142857143</v>
+        <v>3.666666666666666</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-6.666666666666666</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3.2</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.4666666666666663</v>
+        <v>-0.7301587301587302</v>
       </c>
       <c r="AB3" t="n">
-        <v>-6.857142857142856</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2857142857142847</v>
+        <v>-9.333333333333334</v>
       </c>
       <c r="AD3" t="n">
-        <v>-4.066666666666668</v>
+        <v>-0.8809523809523796</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.600000000000001</v>
+        <v>-1.079365079365079</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.7142857142857142</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.2857142857142858</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.8</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.1825396825396826</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.2857142857142856</v>
+        <v>1.75</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1428571428571428</v>
+        <v>-2</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.2666666666666666</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.249122807017544</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.822343224679901</v>
+        <v>2.790675990675991</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.59143475572047</v>
+        <v>-2.729953917050691</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3922600651565</v>
+        <v>1.007340780680379</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.75034151034151</v>
+        <v>1.243160309064348</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-36.60000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>45.8</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-26.61538461538461</v>
+        <v>23.37575757575758</v>
       </c>
       <c r="AY3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-1.399999999999999</v>
-      </c>
+        <v>2.787878787878782</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-16.92307692307693</v>
+        <v>6.672727272727272</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.6923076923076934</v>
+        <v>1.612121212121217</v>
       </c>
       <c r="BD3" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.714285714285712</v>
+        <v>8.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1.266666666666666</v>
+        <v>0.5824561403508781</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.066666666666663</v>
+        <v>2.824561403508767</v>
       </c>
       <c r="BH3" t="n">
-        <v>-13.57142857142857</v>
+        <v>-2</v>
       </c>
       <c r="BI3" t="n">
-        <v>13.57142857142857</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-10.66666666666667</v>
+        <v>0.8174603174603163</v>
       </c>
       <c r="BK3" t="n">
-        <v>10.66666666666667</v>
+        <v>-0.8174603174603163</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="n">
-        <v>0.1257142857142857</v>
+        <v>-3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.1642857142857143</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.276</v>
+        <v>-1.031746031746032</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.09799999999999993</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0.8809523809523807</v>
-      </c>
+        <v>-0.0952380952380949</v>
+      </c>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8952380952380949</v>
-      </c>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>-2.25</v>
+      </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-2.287719298245616</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>-0.1428571428571423</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>-3.142857142857144</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>1.466666666666667</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>-1.200000000000001</v>
-      </c>
+        <v>-3.094736842105263</v>
+      </c>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
+      <c r="CH3" t="n">
+        <v>0.01273282718499661</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.004787163086764135</v>
+      </c>
       <c r="CJ3" t="n">
-        <v>0.003340163581037951</v>
+        <v>0.25</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.02123992540509204</v>
+        <v>-0.25</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.008195299532143305</v>
+        <v>-0.08771929824561403</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.008746191925054582</v>
+        <v>-0.4070175438596491</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.2857142857142858</v>
+        <v>2.146260471781304</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.8269886363636365</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>1.257733585858631</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>0.1642857142857143</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>-0.1257142857142857</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>-0.09799999999999993</v>
-      </c>
+        <v>11488.5101010101</v>
+      </c>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
       <c r="CU3" t="n">
-        <v>0.276</v>
+        <v>0.3525982955597939</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.29</v>
+        <v>5.269065656565644</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.29</v>
+        <v>2.066200244436544</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.3739999999999999</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>0.3739999999999999</v>
-      </c>
+        <v>4.739282046320554</v>
+      </c>
+      <c r="CY3" t="inlineStr"/>
       <c r="CZ3" t="n">
-        <v>77.25222222222223</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>75.56241582491582</v>
-      </c>
+        <v>0.5153691520467834</v>
+      </c>
+      <c r="DA3" t="inlineStr"/>
       <c r="DB3" t="n">
-        <v>-173</v>
+        <v>5.490625000000009</v>
       </c>
       <c r="DC3" t="n">
-        <v>-66446.71466488691</v>
+        <v>11664.21841509884</v>
       </c>
       <c r="DD3" t="n">
-        <v>-1.281385281385298</v>
+        <v>13141873.53222328</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2027003738558335</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>1.567821067821068</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>-3.888455988456002</v>
-      </c>
+        <v>18021868.68686868</v>
+      </c>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
       <c r="DH3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>-5</v>
-      </c>
+        <v>0.1691287878787833</v>
+      </c>
+      <c r="DI3" t="inlineStr"/>
       <c r="DJ3" t="n">
-        <v>8.666666666666668</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>-120666.6666666667</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>1.060068880699077</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>1.360771126632471</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>-134701.443001443</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>0</v>
+        <v>4.2808238486015</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45583.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1788,334 +1656,288 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5371428571428571</v>
+        <v>0.2433333333333334</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.055714285714286</v>
+        <v>-0.2833333333333332</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2690196078431371</v>
+        <v>0.5114285714285715</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1759607843137254</v>
+        <v>-0.05999999999999983</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.5333333333333332</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1166666666666667</v>
+        <v>-0.4666666666666666</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.714285714285715</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.933333333333334</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.04999999999999982</v>
+        <v>-0.5714285714285712</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.142857142857144</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7.714285714285714</v>
+        <v>-7.000000000000002</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.966666666666667</v>
+        <v>1.071428571428573</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.083333333333332</v>
+        <v>-2.214285714285714</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.2166666666666667</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1500000000000001</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-0.2666666666666668</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1.770281452048369</v>
+        <v>-3.64017094017094</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.745486663873761</v>
+        <v>7.15930735930736</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.7707600927337772</v>
+        <v>-2.400218035932322</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.348876820312304</v>
+        <v>0.4909276840360142</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.400000000000006</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>0.5726495726495813</v>
+        <v>5.36363636363636</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.230769230769226</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-2.200000000000003</v>
-      </c>
+        <v>-7.36363636363636</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>10.64957264957265</v>
+        <v>1.545454545454547</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.952991452991455</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.714285714285708</v>
+        <v>-3</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.4285714285714306</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.300000000000004</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.3833333333333329</v>
+        <v>2.733333333333334</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.85714285714285</v>
+        <v>-3.333333333333336</v>
       </c>
       <c r="BI4" t="n">
-        <v>-11.85714285714285</v>
+        <v>3.333333333333336</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4.68333333333333</v>
+        <v>-7.857142857142854</v>
       </c>
       <c r="BK4" t="n">
-        <v>-4.68333333333333</v>
+        <v>7.857142857142854</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>-0.5371428571428571</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.4842857142857143</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.06117647058823535</v>
+        <v>-0.4285714285714284</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.3014509803921568</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>-0.5714285714285716</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="n">
-        <v>-0.9166666666666667</v>
+        <v>-0.06666666666666671</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.04999999999999982</v>
-      </c>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="BZ4" t="n">
-        <v>-1</v>
+        <v>0.2666666666666675</v>
       </c>
       <c r="CA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>2.857142857142856</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>-0.1428571428571459</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>-0.1333333333333329</v>
-      </c>
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr"/>
-      <c r="CI4" t="inlineStr"/>
+      <c r="CH4" t="n">
+        <v>0.003909028004727429</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.006629056116554177</v>
+      </c>
       <c r="CJ4" t="n">
-        <v>-0.0009254475193338357</v>
+        <v>-0.25</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0.04791991598381529</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.008012871480320136</v>
+        <v>-0.06666666666666671</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.007041766262958236</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1428571428571428</v>
+        <v>5.585369568702902</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.001984126984127199</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1833333333333333</v>
+        <v>1.952380952380963</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1833333333333333</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>-0.4842857142857143</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>0.5371428571428571</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>-0.3014509803921568</v>
-      </c>
+        <v>3163.492063492064</v>
+      </c>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>0.06117647058823535</v>
+        <v>-1.731866458704694</v>
       </c>
       <c r="CV4" t="n">
-        <v>-1.021428571428571</v>
+        <v>1.596825396825395</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.021428571428571</v>
+        <v>0.266459821568219</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0.3626274509803921</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>0.3626274509803921</v>
-      </c>
+        <v>0.7892043779234115</v>
+      </c>
+      <c r="CY4" t="inlineStr"/>
       <c r="CZ4" t="n">
-        <v>77.25481902356903</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>73.59467592592593</v>
-      </c>
+        <v>-0.02377875392581252</v>
+      </c>
+      <c r="DA4" t="inlineStr"/>
       <c r="DB4" t="n">
-        <v>93</v>
+        <v>0.7357142857142804</v>
       </c>
       <c r="DC4" t="n">
-        <v>31384.1136135475</v>
+        <v>5823.062837575217</v>
       </c>
       <c r="DD4" t="n">
-        <v>-2.630555555555475</v>
+        <v>1411480.013257296</v>
       </c>
       <c r="DE4" t="n">
-        <v>3.36374437334743</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.851388888888881</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>4.906944444444449</v>
-      </c>
+        <v>1164047.619047619</v>
+      </c>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
       <c r="DH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>6.666666666666671</v>
-      </c>
+        <v>-0.8964285714285758</v>
+      </c>
+      <c r="DI4" t="inlineStr"/>
       <c r="DJ4" t="n">
-        <v>1.666666666666668</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>19000</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>-3.833333333333343</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>-0.7678837324402821</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>-1.038183271713784</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>27802.77777777777</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>0</v>
+        <v>2.072960950727975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,338 +1964,316 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.05857142857142872</v>
+        <v>0.03249999999999975</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.05571428571428583</v>
+        <v>0.3050000000000002</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2847083333333333</v>
+        <v>-0.4668749999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09579166666666672</v>
+        <v>0.375</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4285714285714286</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1208333333333333</v>
+        <v>-0.6875</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.07916666666666661</v>
+        <v>0.625</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2.4375</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-1</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-0.5291666666666668</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1.295833333333333</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-5.714285714285714</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1.808333333333334</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.4625000000000004</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.2857142857142858</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.2041666666666666</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.7142857142857144</v>
-      </c>
       <c r="AK5" t="n">
-        <v>-0.5714285714285714</v>
+        <v>1.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.55</v>
+        <v>-0.9375</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.6000000000000001</v>
+        <v>0.9375</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.491528114742401</v>
+        <v>-2.749458874458875</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.41698063840921</v>
+        <v>-1.739583333333333</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.910733241431771</v>
+        <v>0.6812062855445209</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.8642909574086044</v>
+        <v>-0.2742721688034191</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>23.20000000000002</v>
+        <v>19.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.400000000000006</v>
+        <v>-40.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>31.81318681318682</v>
+        <v>9.972527472527474</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.05494505494506541</v>
+        <v>-21.96703296703296</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-5.800000000000004</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.200000000000003</v>
+        <v>-2.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.08791208791209</v>
+        <v>0.9065934065934087</v>
       </c>
       <c r="BC5" t="n">
-        <v>-2.098901098901102</v>
+        <v>-9.082417582417584</v>
       </c>
       <c r="BD5" t="n">
-        <v>-2.428571428571431</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.05833333333333</v>
+        <v>7.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.5083333333333329</v>
+        <v>8.4375</v>
       </c>
       <c r="BH5" t="n">
-        <v>-10</v>
+        <v>10.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>10</v>
+        <v>-10.75</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.9874999999999972</v>
+        <v>4.9375</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.9874999999999972</v>
+        <v>-4.9375</v>
       </c>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.23</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.5847083333333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.108375</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>-0.4285714285714284</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-0.4285714285714288</v>
-      </c>
+        <v>0.06666666666666643</v>
+      </c>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="n">
-        <v>-0.875</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.2708333333333335</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.25</v>
+        <v>1.625</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.08333333333333331</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>-0.4285714285714306</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>-2.142857142857144</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0.8583333333333325</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0.6083333333333325</v>
-      </c>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
+        <v>1.1875</v>
+      </c>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="n">
+        <v>0.0350595238095238</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.05159504704072043</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.02194506396887187</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.02204850453484599</v>
+      </c>
       <c r="CJ5" t="n">
-        <v>-0.009217170619331291</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.02270822911424415</v>
+        <v>0.75</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.003651736827716842</v>
+        <v>-0.125</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0005207966501886638</v>
+        <v>0.3125</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>-0.7975631313131402</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.7567460317460317</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.04583333333333334</v>
+        <v>-0.714682539682542</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.2041666666666667</v>
+        <v>-41908.33333333334</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.23</v>
+        <v>-79000</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.63</v>
+        <v>-22500000</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.108375</v>
+        <v>-4</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.5847083333333334</v>
+        <v>-3.624668226150803</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.8600000000000001</v>
+        <v>-2.180952380952391</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.8600000000000001</v>
+        <v>2.672679364894805</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.6930833333333333</v>
+        <v>-7.794263060131826</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.6930833333333333</v>
+        <v>-8</v>
       </c>
       <c r="CZ5" t="n">
-        <v>75.81342592592593</v>
+        <v>-0.7697822903865101</v>
       </c>
       <c r="DA5" t="n">
-        <v>75.90694444444445</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>84</v>
+        <v>-4.121031746031747</v>
       </c>
       <c r="DC5" t="n">
-        <v>490.9188555805158</v>
+        <v>-43322.13929461771</v>
       </c>
       <c r="DD5" t="n">
-        <v>-1.668518518518539</v>
+        <v>-12499511.56846138</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2451335377782016</v>
+        <v>-9341865.079365075</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1062962962962928</v>
+        <v>0</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.678148148148139</v>
+        <v>-3</v>
       </c>
       <c r="DH5" t="n">
-        <v>1</v>
+        <v>-2.714285714285715</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.333333333333329</v>
+        <v>-4</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>-7916.666666666664</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.6666666666666572</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>2.29413683370862</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>-1.104828582844277</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2038.518518518515</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>0</v>
+        <v>-3.694314260618626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.375</v>
+        <v>45571.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2500,307 +2300,2935 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.332857142857143</v>
+        <v>-1.0035</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4085714285714287</v>
+        <v>0.3075000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.222</v>
+        <v>-0.1481249999999998</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1286666666666669</v>
+        <v>0.2581249999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1428571428571428</v>
+        <v>-1.85</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2857142857142857</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2000000000000002</v>
+        <v>-0.5625</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="X6" t="n">
-        <v>1.714285714285714</v>
+        <v>-3.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5714285714285712</v>
+        <v>0.9500000000000002</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5333333333333332</v>
+        <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.2666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7142857142857153</v>
+        <v>-3.149999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.7142857142857135</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.6666666666666661</v>
+        <v>-1.3125</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2000000000000011</v>
+        <v>1.6875</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.8571428571428572</v>
+        <v>-0.1499999999999999</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.2000000000000002</v>
+        <v>-0.0625</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.4666666666666668</v>
+        <v>0.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.142857142857143</v>
+        <v>-0.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.1333333333333335</v>
+        <v>-0.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.6634302205730771</v>
+        <v>-1.887099567099567</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.850233945252742</v>
+        <v>0.2634615384615389</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.339222870527218</v>
+        <v>-0.6263018459975696</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.05827741144304577</v>
+        <v>-0.1721004516317022</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-9.799999999999997</v>
+        <v>-28</v>
       </c>
       <c r="AW6" t="n">
-        <v>23.60000000000001</v>
+        <v>-15</v>
       </c>
       <c r="AX6" t="n">
-        <v>-4.15384615384616</v>
+        <v>-3.769230769230774</v>
       </c>
       <c r="AY6" t="n">
-        <v>18.84615384615384</v>
+        <v>-8.384615384615387</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-10.2</v>
+        <v>-12</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.400000000000006</v>
+        <v>-7.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>-5.46153846153846</v>
+        <v>-7.384615384615387</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.230769230769226</v>
+        <v>-5.153846153846153</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.7142857142857153</v>
+        <v>-4.899999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>-1.285714285714285</v>
+        <v>8.200000000000003</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.799999999999997</v>
+        <v>-2.5625</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.599999999999994</v>
+        <v>1.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>-2</v>
+        <v>2.700000000000003</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>-2.700000000000003</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-4.399999999999999</v>
+        <v>0.1875</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.399999999999999</v>
+        <v>-0.1875</v>
       </c>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="n">
-        <v>0.5242857142857142</v>
+        <v>1.55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1628571428571429</v>
+        <v>-1.35</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0220000000000001</v>
+        <v>1.0625</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.5953333333333333</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.1190476190476191</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0.07142857142857162</v>
-      </c>
+        <v>-0.3125</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="n">
-        <v>0.2142857142857142</v>
+        <v>0.6</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.6</v>
       </c>
       <c r="BX6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-6.149999999999999</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-2.9375</v>
+      </c>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="n">
+        <v>-0.01173245614035087</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-0.008844460443607566</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.002932486858592022</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.004100327410668195</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-1.367803030303023</v>
+      </c>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="n">
+        <v>-73000</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-29500000</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>2.064516212953713</v>
+      </c>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="n">
+        <v>-0.2374406843156294</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.693787982850466</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-161</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.08079732767232817</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="n">
+        <v>3138.657176157169</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>2538440.751956377</v>
+      </c>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="n">
+        <v>-160</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="n">
+        <v>5.333333333333343</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-1.209041999666994</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>148</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.2175</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.2150000000000003</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.8343749999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1656250000000004</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-4.375</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.9375</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.5416666666666661</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.05702908202908197</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.585274631266479</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.6813499000999</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-29.07692307692308</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>29.23076923076923</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>9.384615384615387</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-1.9375</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>12.1875</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-24.625</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BS7" t="n">
         <v>0.5</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0.04307909604519774</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.00950867805630707</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-0.01799150139258565</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.19653379028378</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-1.761507936507937</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.575396825396837</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-96707.53968253967</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-405000</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-158000000</v>
+      </c>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="n">
+        <v>3.848781518189409</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>-10.13293650793651</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-1.470561346548152</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.210655901116425</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-255</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.5466374269005847</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-8.189682539682522</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-38499.49494949495</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-13530164.30754917</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>-35913968.25396825</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-264</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.556349206349207</v>
+      </c>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="n">
+        <v>-4.158890123034851</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.3699999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.1199999999999999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.811875</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1037500000000002</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.3125</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.5601787101787101</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.080952380952381</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-2.835984899495929</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.4616115220241577</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-15.92307692307692</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-17.84615384615384</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.692307692307693</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-1.38461538461538</v>
+      </c>
+      <c r="BD8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>-0.2857142857142847</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>4.142857142857141</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.066666666666668</v>
-      </c>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr"/>
-      <c r="CH6" t="inlineStr"/>
-      <c r="CI6" t="inlineStr"/>
-      <c r="CJ6" t="n">
-        <v>0.008041519219204374</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0.03060205977597281</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>0.005728090949074657</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>-0.003233568779033053</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>-0.4285714285714285</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>-0.2857142857142857</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>-0.06666666666666665</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.1628571428571429</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>-0.5242857142857142</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-0.5953333333333333</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>-0.0220000000000001</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0.3614285714285714</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>-0.3614285714285714</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>-0.5733333333333333</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>0.5733333333333333</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>75.40757575757576</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>76.93124999999999</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>97</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-10991.53708962422</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>-1.87291666666664</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>-1.631050909506229</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>2.008333333333326</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>-2.253240740740736</v>
-      </c>
-      <c r="DH6" t="n">
+      <c r="BE8" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-4.9375</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-8.1875</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-19</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-8.625</v>
+      </c>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-0.3958333333333333</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.5416666666666665</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BU8" t="n">
         <v>1</v>
       </c>
-      <c r="DI6" t="n">
-        <v>11.33333333333333</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>6.833333333333332</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>16166.66666666667</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>-2.833333333333343</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>0.2381243431000257</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0.555957303790116</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>-7898.611111111117</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>0</v>
+      <c r="BV8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="n">
+        <v>0.04188861985472155</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>-0.06944444444444445</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.001951674614775238</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.01238267971249583</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.03557692307693117</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.02221771284271301</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-1.932336760461766</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>8019.42640692641</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>114000</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-38100000</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0.06666666666666643</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0.03844755605591388</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.4436327561327573</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-2.548638669981585</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>-1.000321813334594</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>124</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>-0.1145224497294928</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.6554067460317299</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>2580.165040497854</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>-6095524.586030586</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>-2763932.178932179</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>145</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-0.4564303751803784</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-5.933333333333337</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0.07552303217937606</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5699999999999998</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.2825</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.5706250000000002</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.4375</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-2.125</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.9375</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.801861042183623</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.2810606060606062</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.2988397310955797</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.6194861222714483</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>28.23076923076923</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-19.46153846153847</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>19.46153846153847</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-6.615384615384613</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-3.1875</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-18.75</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-14.625</v>
+      </c>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-1.3125</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-1.3125</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-2.1875</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="n">
+        <v>-0.01816911250873515</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>-0.002380952380952386</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.01678756958995798</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>-0.01654058809071059</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.7347337006427921</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.697222222222222</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>-0.4232638888888687</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>195505.2083333333</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>199000</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0.2003937303666454</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>8.316666666666663</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.7673425468365451</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>5.450012013914858</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>-145</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.7072602497476725</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>7.990277777777777</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>103893.0756909714</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>29834877.65357492</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>56989062.5</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-144</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-1.678472222222222</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>5.771847747196034</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1475</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.69625</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5799999999999998</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.9375</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.8125</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.6875</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-1.0625</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1.275595238095238</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.007692307692307665</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.2528710533126297</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.9279673451548454</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.846153846153854</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-7.15384615384616</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>31</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-5.769230769230774</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-8.692307692307693</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5.0625</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-5.0625</v>
+      </c>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0.1833333333333333</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="n">
+        <v>0.07371794871794872</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0.0597069597069597</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.02215132632296486</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-0.02626166347673529</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.115860990860995</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0.1841269841269841</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-1.015873015873012</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-1556.746031746032</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-23000</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.3143575292956058</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.5734126984126959</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-1.780012873370993</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.330286367936324</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-69</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.1914776566527725</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>2.324206349206349</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-1027.429025437927</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>-695807.303184431</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>873244.0476190476</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-68</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.7853174603174615</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>-0.7901626978542566</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.2006250000000001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.3125</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.0625</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.1875</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-2.318278657616893</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1.167207792207792</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1138305771384331</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.04617878702357547</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-4.538461538461533</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.15384615384616</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-6.846153846153847</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.307692307692314</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-3.3125</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-3.6875</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.1416666666666666</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.7374999999999998</v>
+      </c>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>-1.4375</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="n">
+        <v>0.04700854700854701</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0.02014652014652014</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.008923391396155271</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.009374193155685856</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0.1875</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-5.291999050332365</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0.3297619047619045</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0.5912698412698774</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>780.9523809523816</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-8350000</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-2.590059093812965</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-1.50793650793652</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1.857133014689111</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-3.43252052814745</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-69</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.4428093546030856</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-2.169047619047618</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-1977.735385422107</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-4096142.593002114</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-2519603.174603175</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-81</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-1.820238095238093</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-1.573175264922554</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.46875</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.2909999999999999</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05649999999999999</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.07125000000000004</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.9000000000000004</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-2.0625</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.5625</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-3.945138195138195</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.116176470588235</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.483190017702885</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.416248416616064</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.3076923076923066</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-3.461538461538467</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-7.846153846153847</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-9.07692307692308</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.149999999999999</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.2000000000000028</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8.3125</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.6916666666666667</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.7916666666666665</v>
+      </c>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>5.949999999999999</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>7.699999999999999</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>5.8125</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="n">
+        <v>-0.02374768089053803</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0.02326388888888889</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.000538330537886586</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-0.006092098253704402</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.7011724386724438</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.1427083333333334</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-1.308564814814872</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-3499.074074074077</v>
+      </c>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="n">
+        <v>-1.47153442854875</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-2.373495370370364</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>2.249502574309076</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>-0.5402389599564543</v>
+      </c>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="n">
+        <v>-0.03133083699066663</v>
+      </c>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="n">
+        <v>-1.118518518518528</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-2932.486798869344</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>286845.308087809</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-3110995.370370368</v>
+      </c>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="n">
+        <v>0.764930555555555</v>
+      </c>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="n">
+        <v>0.06360745968426329</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.2725</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1148529411764709</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5014338235294116</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-1.3875</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.3250000000000002</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.1500000000000004</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.137499999999999</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.08750000000000002</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1375</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.8065656565656569</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.4956110421836231</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.1346884421033692</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.4146536769681939</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-1.424369747899163</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-8.096638655462172</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-27</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-6.268907563025209</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-1.268907563025209</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.450000000000003</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-3.125</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.7250000000000014</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0.7250000000000014</v>
+      </c>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.8875000000000002</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.8624999999999998</v>
+      </c>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>3.649999999999999</v>
+      </c>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="n">
+        <v>0.008730158730158727</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.2002314814814815</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.01253896485564531</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.01451162408652944</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-3.202709636042968</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0.46875</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-2.388888888888914</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-9364.583333333328</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-8200000</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0.3273019362173777</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-2.256944444444443</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.7661856117738637</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-3.669911787558831</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.2630390442890445</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-3.6875</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-8779.323923625394</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-5594533.392465377</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-7249652.777777778</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-10</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-1.413194444444439</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-2.666666666666686</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-2.651655840074966</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45569.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.07750000000000012</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.4824999999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.1975</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1.9375</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1.364285714285714</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.966233766233766</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.713076506826507</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.9468608937358942</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>47</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.0769230769230802</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-2.92307692307692</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-31</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-9.230769230769234</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-4.307692307692307</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-2.625</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0.3125</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.4642857142857142</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.1339285714285714</v>
+      </c>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="n">
+        <v>-0.02418939783839424</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.03263157894736841</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.01342409519685678</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.003246381826031181</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="n">
+        <v>-123000</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-50100000</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>2.458585155706864</v>
+      </c>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="n">
+        <v>2.683161201006612</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-1.260588808121696</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>-241</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.01680559024309058</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="n">
+        <v>-226.1712519936191</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-3323253.966884723</v>
+      </c>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="n">
+        <v>-242</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-4.175497519658691</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -890,144 +890,144 @@
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1059,95 +1059,95 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3800000000000001</v>
+        <v>1.503333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4366666666666666</v>
+        <v>0.8466666666666669</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.3399999999999999</v>
+        <v>0.8421428571428571</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3964285714285711</v>
+        <v>-0.1549999999999998</v>
       </c>
       <c r="T2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U2" t="n">
         <v>-1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-3.642857142857142</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.2142857142857144</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0.5</v>
       </c>
-      <c r="V2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-1.928571428571428</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.4285714285714284</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-5.666666666666668</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-3.428571428571429</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.6428571428571428</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AK2" t="n">
-        <v>-0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.06666666666666665</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.1333333333333333</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.486771561771562</v>
+        <v>-1.001010101010102</v>
       </c>
       <c r="AO2" t="n">
-        <v>-2.383333333333332</v>
+        <v>0.05151515151515129</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.114844950371266</v>
+        <v>-2.478224862036973</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.7444739609130364</v>
+        <v>1.711118326118326</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -1156,78 +1156,78 @@
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>7.272727272727266</v>
+        <v>29.72727272727272</v>
       </c>
       <c r="AY2" t="n">
-        <v>-12.27272727272728</v>
+        <v>-37.72727272727273</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>-3.63636363636364</v>
+        <v>10.90909090909091</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.818181818181813</v>
+        <v>-13.81818181818181</v>
       </c>
       <c r="BD2" t="n">
-        <v>-6.25</v>
+        <v>-0.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.75</v>
+        <v>-4.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1.533333333333339</v>
+        <v>2.066666666666663</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.133333333333333</v>
+        <v>-7.93333333333333</v>
       </c>
       <c r="BH2" t="n">
-        <v>-15.66666666666666</v>
+        <v>11.66666666666666</v>
       </c>
       <c r="BI2" t="n">
-        <v>15.66666666666666</v>
+        <v>-11.66666666666667</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-8.857142857142854</v>
+        <v>13.14285714285715</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.857142857142854</v>
+        <v>-13.14285714285715</v>
       </c>
       <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.6666666666666665</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.2252747252747251</v>
+        <v>-1.357142857142857</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.4835164835164836</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>-1</v>
+        <v>-4.75</v>
       </c>
       <c r="BY2" t="n">
-        <v>-8.75</v>
+        <v>2.25</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-1</v>
+        <v>-2.133333333333335</v>
       </c>
       <c r="CA2" t="n">
-        <v>-3.866666666666667</v>
+        <v>-0.5333333333333332</v>
       </c>
       <c r="CB2" t="inlineStr"/>
       <c r="CC2" t="inlineStr"/>
@@ -1236,92 +1236,92 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr"/>
       <c r="CH2" t="n">
-        <v>0.01142048147838962</v>
+        <v>0.01840877662422498</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.007851362214019726</v>
+        <v>0.0227685815200746</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="CM2" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="CN2" t="n">
-        <v>-1.876174134507465</v>
+        <v>-0.4795260295260277</v>
       </c>
       <c r="CO2" t="inlineStr"/>
       <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
+      <c r="CQ2" t="n">
+        <v>-0.4752431413616023</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-3.691973048880943</v>
+      </c>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="n">
-        <v>4.038327163999568</v>
-      </c>
+      <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="n">
-        <v>-3.786240009667779</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.096373909565656</v>
-      </c>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="n">
-        <v>-0.01935579255625686</v>
-      </c>
+      <c r="CZ2" t="inlineStr"/>
       <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="n">
-        <v>4294.081184875493</v>
-      </c>
+      <c r="DB2" t="n">
+        <v>36922.05637929323</v>
+      </c>
+      <c r="DC2" t="inlineStr"/>
       <c r="DD2" t="n">
-        <v>-741537.0562905874</v>
+        <v>0.3224568560094871</v>
       </c>
       <c r="DE2" t="inlineStr"/>
       <c r="DF2" t="inlineStr"/>
-      <c r="DG2" t="inlineStr"/>
-      <c r="DH2" t="inlineStr"/>
-      <c r="DI2" t="inlineStr"/>
-      <c r="DJ2" t="n">
-        <v>-3.99199044312239</v>
-      </c>
+      <c r="DG2" t="n">
+        <v>1.55464917027416</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-2.454151002506251</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>8420367.627620915</v>
+      </c>
+      <c r="DJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45584.375</v>
+        <v>45585.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1348,100 +1348,100 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.23</v>
+        <v>0.9308333333333332</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.006666666666666</v>
+        <v>0.7058333333333333</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2402857142857144</v>
+        <v>0.6109047619047621</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1504285714285716</v>
+        <v>0.4232857142857145</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="U3" t="n">
-        <v>-1</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3157894736842106</v>
+        <v>0.2190476190476192</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04210526315789465</v>
+        <v>-0.1952380952380952</v>
       </c>
       <c r="X3" t="n">
-        <v>3.666666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>-6.666666666666666</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6666666666666665</v>
+        <v>1.061904761904762</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.7301587301587302</v>
+        <v>2.047619047619048</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.333333333333334</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>-9.333333333333334</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8809523809523796</v>
+        <v>2.080952380952381</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.079365079365079</v>
+        <v>5.528571428571428</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.666666666666667</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5555555555555556</v>
+        <v>1.547619047619048</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1825396825396826</v>
+        <v>0.6523809523809525</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2</v>
+        <v>-0.25</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.3508771929824561</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.249122807017544</v>
+        <v>-1.219047619047619</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.790675990675991</v>
+        <v>-2.522743922743923</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2.729953917050691</v>
+        <v>-1.306060606060606</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.007340780680379</v>
+        <v>-0.6782290398676949</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.243160309064348</v>
+        <v>-2.875437465111378</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -1450,78 +1450,78 @@
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>23.37575757575758</v>
+        <v>-13.18181818181819</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.787878787878782</v>
+        <v>12.18181818181817</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>6.672727272727272</v>
+        <v>2.181818181818187</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.612121212121217</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>-19.66666666666666</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.75</v>
+        <v>-17.33333333333334</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.5824561403508781</v>
+        <v>-13.35238095238095</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.824561403508767</v>
+        <v>-13.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>-2</v>
+        <v>-0.8333333333333357</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>0.8333333333333357</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.8174603174603163</v>
+        <v>-0.7380952380952337</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.8174603174603163</v>
+        <v>0.7380952380952337</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="n">
-        <v>-3</v>
+        <v>0.75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-0.25</v>
       </c>
       <c r="BR3" t="n">
-        <v>-1.031746031746032</v>
+        <v>0.4666666666666668</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0952380952380949</v>
+        <v>-0.2714285714285718</v>
       </c>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="BX3" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="BY3" t="n">
-        <v>-2.25</v>
+        <v>-1.583333333333334</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-2.287719298245616</v>
+        <v>-5.461904761904764</v>
       </c>
       <c r="CA3" t="n">
-        <v>-3.094736842105263</v>
+        <v>-1.699999999999999</v>
       </c>
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="inlineStr"/>
@@ -1530,106 +1530,106 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
       <c r="CH3" t="n">
-        <v>0.01273282718499661</v>
+        <v>-0.01212574865551905</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.004787163086764135</v>
+        <v>0.0305725186780594</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="CK3" t="n">
         <v>-0.25</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.08771929824561403</v>
+        <v>-0.05714285714285716</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.4070175438596491</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.146260471781304</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0.8269886363636365</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1.257733585858631</v>
-      </c>
+        <v>0.6381172839506206</v>
+      </c>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
       <c r="CQ3" t="n">
-        <v>11488.5101010101</v>
-      </c>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="n">
-        <v>0.3525982955597939</v>
-      </c>
+        <v>0.02938368629801857</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0.6501828482930208</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>4229320.987654322</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>7612.345679012345</v>
+      </c>
+      <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>5.269065656565644</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>2.066200244436544</v>
-      </c>
+        <v>2.568827160493825</v>
+      </c>
+      <c r="CW3" t="inlineStr"/>
       <c r="CX3" t="n">
-        <v>4.739282046320554</v>
-      </c>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="n">
-        <v>0.5153691520467834</v>
-      </c>
-      <c r="DA3" t="inlineStr"/>
+        <v>2.361728395061732</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>1.4141975308642</v>
+      </c>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="n">
+        <v>2.521296296296285</v>
+      </c>
       <c r="DB3" t="n">
-        <v>5.490625000000009</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>11664.21841509884</v>
-      </c>
+        <v>8273.674508039832</v>
+      </c>
+      <c r="DC3" t="inlineStr"/>
       <c r="DD3" t="n">
-        <v>13141873.53222328</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>18021868.68686868</v>
-      </c>
+        <v>0.3848012098076599</v>
+      </c>
+      <c r="DE3" t="inlineStr"/>
       <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
+      <c r="DG3" t="n">
+        <v>2.901643957177996</v>
+      </c>
       <c r="DH3" t="n">
-        <v>0.1691287878787833</v>
-      </c>
-      <c r="DI3" t="inlineStr"/>
+        <v>2.214992210709454</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>2031404.109664559</v>
+      </c>
       <c r="DJ3" t="n">
-        <v>4.2808238486015</v>
+        <v>0.5444444444444447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45585.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1656,76 +1656,76 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2433333333333334</v>
+        <v>0.1766666666666665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2833333333333332</v>
+        <v>0.2566666666666667</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5114285714285715</v>
+        <v>0.6562380952380955</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.05999999999999983</v>
+        <v>-0.2007619047619049</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5333333333333332</v>
+        <v>0.5333333333333334</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4666666666666666</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9999999999999998</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.333333333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.714285714285714</v>
+        <v>1.352380952380952</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.5714285714285712</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7.000000000000002</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.071428571428573</v>
+        <v>2.72857142857143</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.214285714285714</v>
+        <v>-1.009523809523809</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.7095238095238094</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.3571428571428571</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.5</v>
@@ -1734,22 +1734,22 @@
         <v>-0.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.2666666666666668</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="AN4" t="n">
-        <v>-3.64017094017094</v>
+        <v>0.3472222222222214</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.15930735930736</v>
+        <v>-1.691666666666667</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2.400218035932322</v>
+        <v>1.099512313083742</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.4909276840360142</v>
+        <v>0.2215627362055934</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -1758,78 +1758,78 @@
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>5.36363636363636</v>
+        <v>-2.27272727272728</v>
       </c>
       <c r="AY4" t="n">
-        <v>-7.36363636363636</v>
+        <v>9.181818181818187</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>1.545454545454547</v>
+        <v>3</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.909090909090907</v>
       </c>
       <c r="BD4" t="n">
+        <v>-15.33333333333334</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-30.25</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-3.533333333333331</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="BH4" t="n">
         <v>-3</v>
       </c>
-      <c r="BE4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.399999999999999</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.733333333333334</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>-3.333333333333336</v>
-      </c>
       <c r="BI4" t="n">
-        <v>3.333333333333336</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-7.857142857142854</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.857142857142854</v>
+        <v>-4.399999999999999</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>-1.333333333333333</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.4285714285714284</v>
+        <v>-0.3435897435897435</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.1538461538461537</v>
       </c>
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="n">
-        <v>-0.06666666666666671</v>
+        <v>0.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.06666666666666665</v>
+        <v>-0.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>-4.833333333333332</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.75</v>
+        <v>-7.583333333333332</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.2666666666666675</v>
+        <v>-2.666666666666668</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.4666666666666668</v>
+        <v>-3.599999999999998</v>
       </c>
       <c r="CB4" t="inlineStr"/>
       <c r="CC4" t="inlineStr"/>
@@ -1838,106 +1838,90 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
       <c r="CH4" t="n">
-        <v>0.003909028004727429</v>
+        <v>-0.0153523598376037</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.006629056116554177</v>
+        <v>0.01569763733121778</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0.25</v>
+        <v>-0.08333333333333331</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.06666666666666671</v>
+        <v>0.4</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.1333333333333333</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>5.585369568702902</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0.001984126984127199</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>1.952380952380963</v>
-      </c>
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
       <c r="CQ4" t="n">
-        <v>3163.492063492064</v>
-      </c>
-      <c r="CR4" t="inlineStr"/>
+        <v>-2.905136926754494</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.8520597745175849</v>
+      </c>
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="n">
-        <v>-1.731866458704694</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>1.596825396825395</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>0.266459821568219</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>0.7892043779234115</v>
-      </c>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
       <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="n">
-        <v>-0.02377875392581252</v>
-      </c>
+      <c r="CZ4" t="inlineStr"/>
       <c r="DA4" t="inlineStr"/>
       <c r="DB4" t="n">
-        <v>0.7357142857142804</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>5823.062837575217</v>
-      </c>
+        <v>45602.7172760761</v>
+      </c>
+      <c r="DC4" t="inlineStr"/>
       <c r="DD4" t="n">
-        <v>1411480.013257296</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>1164047.619047619</v>
-      </c>
+        <v>1.252978435773058</v>
+      </c>
+      <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="inlineStr"/>
-      <c r="DG4" t="inlineStr"/>
+      <c r="DG4" t="n">
+        <v>7.916886267072201</v>
+      </c>
       <c r="DH4" t="n">
-        <v>-0.8964285714285758</v>
-      </c>
-      <c r="DI4" t="inlineStr"/>
-      <c r="DJ4" t="n">
-        <v>2.072960950727975</v>
-      </c>
+        <v>8.47680525850221</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>19553618.11955419</v>
+      </c>
+      <c r="DJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.66666666666</v>
+        <v>45585.375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1964,316 +1948,288 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03249999999999975</v>
+        <v>0.1933333333333336</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3050000000000002</v>
+        <v>-0.1758333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.4668749999999999</v>
+        <v>-0.08066666666666666</v>
       </c>
       <c r="S5" t="n">
-        <v>0.375</v>
+        <v>-0.3533333333333335</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6875</v>
+        <v>-0.2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.625</v>
+        <v>0.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.875</v>
+        <v>-0.1333333333333329</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8125</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>-0.5833333333333339</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.75</v>
+        <v>0.5833333333333339</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.4375</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3125</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.75</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AG5" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK5" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH5" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL5" t="n">
-        <v>-0.9375</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9375</v>
+        <v>-0.4000000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>-2.749458874458875</v>
+        <v>-5.564583333333333</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.739583333333333</v>
+        <v>4.906759906759907</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.6812062855445209</v>
+        <v>1.078391001355842</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.2742721688034191</v>
+        <v>-0.9251354201354203</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-40.5</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>9.972527472527474</v>
+        <v>2.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>-21.96703296703296</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>4.681818181818187</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>0.9065934065934087</v>
+        <v>-5.212121212121211</v>
       </c>
       <c r="BC5" t="n">
-        <v>-9.082417582417584</v>
+        <v>4.93181818181818</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>6.333333333333336</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.5</v>
+        <v>-3.666666666666671</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.4375</v>
+        <v>-3.533333333333331</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.75</v>
+        <v>0.4166666666666643</v>
       </c>
       <c r="BI5" t="n">
-        <v>-10.75</v>
+        <v>-0.4166666666666643</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4.9375</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>-4.9375</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.3999999999999999</v>
+        <v>-0.2333333333333334</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.06666666666666643</v>
+        <v>-0.6095238095238094</v>
       </c>
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="BX5" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.5</v>
+        <v>3.583333333333332</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.625</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.1875</v>
+        <v>-3.066666666666665</v>
       </c>
       <c r="CB5" t="inlineStr"/>
       <c r="CC5" t="inlineStr"/>
       <c r="CD5" t="inlineStr"/>
       <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="n">
-        <v>0.0350595238095238</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>-0.05159504704072043</v>
-      </c>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="n">
-        <v>0.02194506396887187</v>
+        <v>-0.01643228294216253</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.02204850453484599</v>
+        <v>0.005748529422383589</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.125</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.3125</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.7975631313131402</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>-0.7567460317460317</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>-0.714682539682542</v>
-      </c>
+        <v>0.7606361231361092</v>
+      </c>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
       <c r="CQ5" t="n">
-        <v>-41908.33333333334</v>
+        <v>3.022652453134896</v>
       </c>
       <c r="CR5" t="n">
-        <v>-79000</v>
+        <v>-2.778389300757723</v>
       </c>
       <c r="CS5" t="n">
-        <v>-22500000</v>
+        <v>5572722.222222222</v>
       </c>
       <c r="CT5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>-3.624668226150803</v>
-      </c>
+        <v>11267.22222222222</v>
+      </c>
+      <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>-2.180952380952391</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>2.672679364894805</v>
-      </c>
+        <v>1.973333333333329</v>
+      </c>
+      <c r="CW5" t="inlineStr"/>
       <c r="CX5" t="n">
-        <v>-7.794263060131826</v>
+        <v>4.19999999999996</v>
       </c>
       <c r="CY5" t="n">
-        <v>-8</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>-0.7697822903865101</v>
-      </c>
+        <v>-0.7033333333333331</v>
+      </c>
+      <c r="CZ5" t="inlineStr"/>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>2.118333333333339</v>
       </c>
       <c r="DB5" t="n">
-        <v>-4.121031746031747</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-43322.13929461771</v>
-      </c>
+        <v>6744.220537422287</v>
+      </c>
+      <c r="DC5" t="inlineStr"/>
       <c r="DD5" t="n">
-        <v>-12499511.56846138</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>-9341865.079365075</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.2502100725784935</v>
+      </c>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
       <c r="DG5" t="n">
-        <v>-3</v>
+        <v>1.931668258641949</v>
       </c>
       <c r="DH5" t="n">
-        <v>-2.714285714285715</v>
+        <v>-0.009098171159578783</v>
       </c>
       <c r="DI5" t="n">
-        <v>-4</v>
+        <v>1681289.410719234</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-3.694314260618626</v>
+        <v>0.0338888888888893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.5625</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2300,302 +2256,292 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0035</v>
+        <v>-1.554166666666666</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3075000000000001</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1481249999999998</v>
+        <v>-0.518904761904762</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2581249999999999</v>
+        <v>0.3426666666666666</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.85</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5625</v>
+        <v>-0.5904761904761906</v>
       </c>
       <c r="W6" t="n">
-        <v>0.375</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.7</v>
+        <v>-4.583333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9500000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1</v>
+        <v>-3.071428571428571</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.875</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.149999999999999</v>
+        <v>-8.166666666666668</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.300000000000001</v>
+        <v>-1.583333333333334</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.3125</v>
+        <v>-5.96190476190476</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6875</v>
+        <v>0.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-1.916666666666667</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0625</v>
+        <v>-0.7619047619047616</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.25</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.25</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.5</v>
+        <v>-0.7523809523809522</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.625</v>
+        <v>0.9761904761904761</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1.887099567099567</v>
+        <v>0.212903225806452</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2634615384615389</v>
+        <v>2.481944444444444</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.6263018459975696</v>
+        <v>2.079228149896324</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.1721004516317022</v>
+        <v>0.945355596784168</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-15</v>
-      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-3.769230769230774</v>
+        <v>-20.36363636363636</v>
       </c>
       <c r="AY6" t="n">
-        <v>-8.384615384615387</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-12</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-7.5</v>
-      </c>
+        <v>11.63636363636364</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-7.384615384615387</v>
+        <v>-17.81818181818181</v>
       </c>
       <c r="BC6" t="n">
-        <v>-5.153846153846153</v>
+        <v>-5.636363636363633</v>
       </c>
       <c r="BD6" t="n">
-        <v>-4.899999999999999</v>
+        <v>5.833333333333332</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.200000000000003</v>
+        <v>5.083333333333332</v>
       </c>
       <c r="BF6" t="n">
-        <v>-2.5625</v>
+        <v>0.08095238095238244</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.5</v>
+        <v>3.676190476190474</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.700000000000003</v>
+        <v>-9.666666666666664</v>
       </c>
       <c r="BI6" t="n">
-        <v>-2.700000000000003</v>
+        <v>9.666666666666664</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1875</v>
+        <v>-6.919047619047618</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.1875</v>
+        <v>6.919047619047618</v>
       </c>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="n">
-        <v>1.55</v>
+        <v>0.25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1.0625</v>
+        <v>0.8571428571428574</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.3125</v>
-      </c>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-1</v>
+      </c>
       <c r="BV6" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="BY6" t="n">
-        <v>-6.149999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.25</v>
+        <v>0.05714285714285694</v>
       </c>
       <c r="CA6" t="n">
-        <v>-2.9375</v>
+        <v>0.1761904761904756</v>
       </c>
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="n">
-        <v>-0.01173245614035087</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>-0.008844460443607566</v>
-      </c>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="n">
-        <v>0.002932486858592022</v>
+        <v>0.03163283548068595</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.004100327410668195</v>
+        <v>0.005735573344559375</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.15</v>
+        <v>0.25</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0625</v>
+        <v>-0.5047619047619047</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="CN6" t="n">
-        <v>-1.367803030303023</v>
+        <v>0.9934615384615313</v>
       </c>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
+      <c r="CQ6" t="n">
+        <v>-0.1616614829027867</v>
+      </c>
       <c r="CR6" t="n">
-        <v>-73000</v>
+        <v>0.5359984901006563</v>
       </c>
       <c r="CS6" t="n">
-        <v>-29500000</v>
+        <v>-62889019.09722222</v>
       </c>
       <c r="CT6" t="n">
-        <v>-4.666666666666668</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>2.064516212953713</v>
-      </c>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="n">
-        <v>-0.2374406843156294</v>
-      </c>
+        <v>-209116.3194444444</v>
+      </c>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="n">
+        <v>-12.46770833333333</v>
+      </c>
+      <c r="CW6" t="inlineStr"/>
       <c r="CX6" t="n">
-        <v>1.693787982850466</v>
+        <v>-2.160069444444474</v>
       </c>
       <c r="CY6" t="n">
-        <v>-161</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>0.08079732767232817</v>
-      </c>
+        <v>0.1263888888888864</v>
+      </c>
+      <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="n">
-        <v>3138.657176157169</v>
-      </c>
+        <v>-11.09097222222222</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-114791.4631222536</v>
+      </c>
+      <c r="DC6" t="inlineStr"/>
       <c r="DD6" t="n">
-        <v>2538440.751956377</v>
+        <v>-0.9598897316921702</v>
       </c>
       <c r="DE6" t="inlineStr"/>
-      <c r="DF6" t="n">
-        <v>-160</v>
-      </c>
+      <c r="DF6" t="inlineStr"/>
       <c r="DG6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="DH6" t="inlineStr"/>
+        <v>-9.368032147018198</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-8.632473606902778</v>
+      </c>
       <c r="DI6" t="n">
-        <v>5.333333333333343</v>
+        <v>-32835469.54462734</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-1.209041999666994</v>
+        <v>-2.188541666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.46875</v>
+        <v>45584.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2622,312 +2568,288 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2175</v>
+        <v>-0.9083333333333333</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2150000000000003</v>
+        <v>0.07166666666666666</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.8343749999999999</v>
+        <v>0.8321428571428573</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1656250000000004</v>
+        <v>0.06142857142857139</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.25</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="U7" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.9999999999999996</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2142857142857144</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-3.166666666666666</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.428571428571429</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2142857142857135</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-4.375</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AH7" t="n">
-        <v>-1.375</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1875</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-1.5</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.9375</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.75</v>
+        <v>-0.4666666666666668</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.5416666666666661</v>
+        <v>1.681818181818183</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.05702908202908197</v>
+        <v>3.831746031746032</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.585274631266479</v>
+        <v>-2.259863945578231</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.6813499000999</v>
+        <v>1.204642308401707</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-6</v>
-      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-29.07692307692308</v>
+        <v>0.3636363636363598</v>
       </c>
       <c r="AY7" t="n">
-        <v>29.23076923076923</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-20</v>
-      </c>
+        <v>-11.38636363636364</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-6</v>
+        <v>5.909090909090907</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.384615384615387</v>
+        <v>0.5151515151515156</v>
       </c>
       <c r="BD7" t="n">
-        <v>-6</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>14.25</v>
+        <v>-5.333333333333336</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1.9375</v>
+        <v>-8.266666666666666</v>
       </c>
       <c r="BG7" t="n">
-        <v>12.1875</v>
+        <v>-8.400000000000002</v>
       </c>
       <c r="BH7" t="n">
-        <v>-22.5</v>
+        <v>0.6666666666666643</v>
       </c>
       <c r="BI7" t="n">
-        <v>22.5</v>
+        <v>-0.6666666666666643</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-24.625</v>
+        <v>2.785714285714285</v>
       </c>
       <c r="BK7" t="n">
-        <v>24.625</v>
+        <v>-2.785714285714285</v>
       </c>
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="n">
-        <v>1</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.25</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.75</v>
+        <v>-0.846153846153846</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.5</v>
+        <v>0.07692307692307709</v>
       </c>
       <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>9.25</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.25</v>
+        <v>0.5833333333333339</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.75</v>
+        <v>-3.6</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.25</v>
+        <v>-2.533333333333333</v>
       </c>
       <c r="CB7" t="inlineStr"/>
       <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="n">
-        <v>0.1944444444444444</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>-0.04307909604519774</v>
-      </c>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
       <c r="CH7" t="n">
-        <v>-0.00950867805630707</v>
+        <v>-0.002136586577308586</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.01799150139258565</v>
+        <v>0.02939031265072215</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.25</v>
+        <v>-0.4166666666666666</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0.1333333333333334</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.19653379028378</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>-1.761507936507937</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.575396825396837</v>
-      </c>
+        <v>-1.266981947450688</v>
+      </c>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
       <c r="CQ7" t="n">
-        <v>-96707.53968253967</v>
+        <v>-0.8876668470418281</v>
       </c>
       <c r="CR7" t="n">
-        <v>-405000</v>
+        <v>2.69795327221798</v>
       </c>
       <c r="CS7" t="n">
-        <v>-158000000</v>
-      </c>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="n">
-        <v>3.848781518189409</v>
-      </c>
+        <v>-2057341.269841276</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1180.158730158742</v>
+      </c>
+      <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>-10.13293650793651</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>-1.470561346548152</v>
-      </c>
+        <v>0.7738095238095184</v>
+      </c>
+      <c r="CW7" t="inlineStr"/>
       <c r="CX7" t="n">
-        <v>1.210655901116425</v>
+        <v>0.4976190476190254</v>
       </c>
       <c r="CY7" t="n">
-        <v>-255</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>-0.5466374269005847</v>
-      </c>
+        <v>-0.3567460317460345</v>
+      </c>
+      <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>-3</v>
+        <v>0.5043650793650727</v>
       </c>
       <c r="DB7" t="n">
-        <v>-8.189682539682522</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-38499.49494949495</v>
-      </c>
+        <v>3807.516605126897</v>
+      </c>
+      <c r="DC7" t="inlineStr"/>
       <c r="DD7" t="n">
-        <v>-13530164.30754917</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>-35913968.25396825</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>-264</v>
-      </c>
+        <v>-0.1301438757321112</v>
+      </c>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
       <c r="DG7" t="n">
-        <v>-11</v>
+        <v>1.352002695017404</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.556349206349207</v>
-      </c>
-      <c r="DI7" t="inlineStr"/>
+        <v>3.460671844495366</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-746075.5400645118</v>
+      </c>
       <c r="DJ7" t="n">
-        <v>-4.158890123034851</v>
+        <v>-0.234126984126984</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.375</v>
+        <v>45584.46875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2954,320 +2876,274 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3699999999999999</v>
+        <v>-0.6258333333333335</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.3975000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.811875</v>
+        <v>-0.3787142857142858</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1037500000000002</v>
+        <v>0.3749523809523807</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
         <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>-0.8</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3125</v>
+        <v>0.6</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.25</v>
+        <v>-4.416666666666667</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-2.033333333333333</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-6.916666666666668</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-3.757142857142858</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.947619047619046</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK8" t="n">
         <v>-0.75</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5625</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL8" t="n">
-        <v>-0.0625</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.125</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.5601787101787101</v>
+        <v>1.096328671328672</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.080952380952381</v>
+        <v>-0.8462121212121212</v>
       </c>
       <c r="AP8" t="n">
-        <v>-2.835984899495929</v>
+        <v>1.034875197901514</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.4616115220241577</v>
+        <v>-0.4109788659053359</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-27</v>
-      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>-15.92307692307692</v>
+        <v>7.272727272727266</v>
       </c>
       <c r="AY8" t="n">
-        <v>-17.84615384615384</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-11</v>
-      </c>
+        <v>-12.27272727272728</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>2.692307692307693</v>
+        <v>-3.63636363636364</v>
       </c>
       <c r="BC8" t="n">
-        <v>-1.38461538461538</v>
+        <v>0.818181818181813</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.5</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>-6.5</v>
+        <v>22.25</v>
       </c>
       <c r="BF8" t="n">
-        <v>-4.9375</v>
+        <v>2.266666666666666</v>
       </c>
       <c r="BG8" t="n">
-        <v>-8.1875</v>
+        <v>4.200000000000003</v>
       </c>
       <c r="BH8" t="n">
-        <v>19</v>
+        <v>-10</v>
       </c>
       <c r="BI8" t="n">
-        <v>-19</v>
+        <v>10</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.625</v>
+        <v>-7.799999999999997</v>
       </c>
       <c r="BK8" t="n">
-        <v>-8.625</v>
+        <v>7.799999999999997</v>
       </c>
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="n">
-        <v>0.75</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.25</v>
+        <v>-0.9166666666666665</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.3958333333333333</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.5416666666666665</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.25</v>
+        <v>-4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-3.25</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.125</v>
+        <v>-2.600000000000001</v>
       </c>
       <c r="CB8" t="inlineStr"/>
       <c r="CC8" t="inlineStr"/>
       <c r="CD8" t="inlineStr"/>
       <c r="CE8" t="inlineStr"/>
-      <c r="CF8" t="n">
-        <v>0.04188861985472155</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>-0.06944444444444445</v>
-      </c>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
       <c r="CH8" t="n">
-        <v>0.001951674614775238</v>
+        <v>0.01142048147838962</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01238267971249583</v>
+        <v>0.007851362214019726</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.03557692307693117</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.02221771284271301</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>-1.932336760461766</v>
-      </c>
+        <v>-1.806516014849336</v>
+      </c>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
       <c r="CQ8" t="n">
-        <v>8019.42640692641</v>
+        <v>-3.831995851084429</v>
       </c>
       <c r="CR8" t="n">
-        <v>114000</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>-38100000</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0.06666666666666643</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0.03844755605591388</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>0.4436327561327573</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>-2.548638669981585</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>-1.000321813334594</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>124</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>-0.1145224497294928</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>2</v>
-      </c>
+        <v>4.08175626134701</v>
+      </c>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
       <c r="DB8" t="n">
-        <v>0.6554067460317299</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>2580.165040497854</v>
-      </c>
+        <v>4470.098656360264</v>
+      </c>
+      <c r="DC8" t="inlineStr"/>
       <c r="DD8" t="n">
-        <v>-6095524.586030586</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>-2763932.178932179</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>145</v>
-      </c>
+        <v>-0.02958871444746047</v>
+      </c>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
       <c r="DG8" t="n">
-        <v>3</v>
+        <v>-3.879222061478231</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0.4564303751803784</v>
+        <v>1.249008662297157</v>
       </c>
       <c r="DI8" t="n">
-        <v>-5.933333333333337</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>-0.07552303217937606</v>
-      </c>
+        <v>-547215.304591707</v>
+      </c>
+      <c r="DJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45584.375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3294,320 +3170,288 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5699999999999998</v>
+        <v>0.1916666666666665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2825</v>
+        <v>-1.508333333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>0.16875</v>
+        <v>-0.2130357142857144</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5706250000000002</v>
+        <v>-0.1239285714285716</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="V9" t="n">
+        <v>-0.3157894736842106</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.04210526315789465</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-5.166666666666666</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.7067669172932334</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-6.583333333333334</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.7406015037593985</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.9360902255639107</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0.5</v>
       </c>
-      <c r="W9" t="n">
-        <v>-0.4375</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-2.125</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AI9" t="n">
-        <v>-0.9375</v>
+        <v>0.1766917293233082</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.5</v>
+        <v>-1.75</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.375</v>
+        <v>0.2456140350877194</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.375</v>
+        <v>-0.1964912280701754</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.801861042183623</v>
+        <v>1.462077505827506</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.2810606060606062</v>
+        <v>-1.458179723502304</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.2988397310955797</v>
+        <v>0.7974371553566248</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.6194861222714483</v>
+        <v>1.457394101430568</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>13</v>
-      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>28.23076923076923</v>
+        <v>23.37575757575758</v>
       </c>
       <c r="AY9" t="n">
-        <v>-19.46153846153847</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-1</v>
-      </c>
+        <v>2.787878787878782</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>19.46153846153847</v>
+        <v>6.672727272727272</v>
       </c>
       <c r="BC9" t="n">
-        <v>-6.615384615384613</v>
+        <v>1.612121212121217</v>
       </c>
       <c r="BD9" t="n">
-        <v>-2.5</v>
+        <v>-4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>-4.75</v>
+        <v>-5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.625</v>
+        <v>-1.838596491228074</v>
       </c>
       <c r="BG9" t="n">
-        <v>-3.1875</v>
+        <v>-0.07017543859649322</v>
       </c>
       <c r="BH9" t="n">
-        <v>18.75</v>
+        <v>-1.166666666666664</v>
       </c>
       <c r="BI9" t="n">
-        <v>-18.75</v>
+        <v>1.166666666666664</v>
       </c>
       <c r="BJ9" t="n">
-        <v>14.625</v>
+        <v>1.165413533834588</v>
       </c>
       <c r="BK9" t="n">
-        <v>-14.625</v>
+        <v>-1.165413533834588</v>
       </c>
       <c r="BL9" t="inlineStr"/>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="n">
-        <v>-0.5</v>
+        <v>-2.25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0.5</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="BR9" t="n">
-        <v>-1.3125</v>
+        <v>-0.9323308270676689</v>
       </c>
       <c r="BS9" t="n">
-        <v>-1.3125</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.244360902255639</v>
+      </c>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="n">
-        <v>-0.1666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
         <v>-5.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>-1.5</v>
+        <v>-8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-2.1875</v>
+        <v>-3.024561403508773</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.875</v>
+        <v>-4.305263157894736</v>
       </c>
       <c r="CB9" t="inlineStr"/>
       <c r="CC9" t="inlineStr"/>
       <c r="CD9" t="inlineStr"/>
       <c r="CE9" t="inlineStr"/>
-      <c r="CF9" t="n">
-        <v>-0.01816911250873515</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>-0.002380952380952386</v>
-      </c>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
       <c r="CH9" t="n">
-        <v>-0.01678756958995798</v>
+        <v>0.01273282718499661</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0.01654058809071059</v>
+        <v>0.004787163086764135</v>
       </c>
       <c r="CJ9" t="n">
         <v>0.25</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.4375</v>
+        <v>-0.08771929824561403</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0625</v>
+        <v>-0.4070175438596491</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.7347337006427921</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.697222222222222</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>-0.4232638888888687</v>
-      </c>
+        <v>2.263447971781304</v>
+      </c>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
       <c r="CQ9" t="n">
-        <v>195505.2083333333</v>
+        <v>2.166524161396495</v>
       </c>
       <c r="CR9" t="n">
-        <v>199000</v>
+        <v>0.3908167435515217</v>
       </c>
       <c r="CS9" t="n">
-        <v>21500000</v>
+        <v>18021868.68686868</v>
       </c>
       <c r="CT9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>-0.2003937303666454</v>
-      </c>
+        <v>11488.5101010101</v>
+      </c>
+      <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>8.316666666666663</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>-0.7673425468365451</v>
-      </c>
+        <v>5.490625000000009</v>
+      </c>
+      <c r="CW9" t="inlineStr"/>
       <c r="CX9" t="n">
-        <v>5.450012013914858</v>
+        <v>1.257733585858631</v>
       </c>
       <c r="CY9" t="n">
-        <v>-145</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>0.7072602497476725</v>
-      </c>
+        <v>0.1691287878787833</v>
+      </c>
+      <c r="CZ9" t="inlineStr"/>
       <c r="DA9" t="n">
-        <v>-2</v>
+        <v>5.269065656565644</v>
       </c>
       <c r="DB9" t="n">
-        <v>7.990277777777777</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>103893.0756909714</v>
-      </c>
+        <v>11732.00181407096</v>
+      </c>
+      <c r="DC9" t="inlineStr"/>
       <c r="DD9" t="n">
-        <v>29834877.65357492</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>56989062.5</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>-144</v>
-      </c>
+        <v>0.5153691520467834</v>
+      </c>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
       <c r="DG9" t="n">
-        <v>1</v>
+        <v>4.355257975884896</v>
       </c>
       <c r="DH9" t="n">
-        <v>-1.678472222222222</v>
+        <v>4.887035227008795</v>
       </c>
       <c r="DI9" t="n">
-        <v>2.75</v>
+        <v>13219613.9081101</v>
       </c>
       <c r="DJ9" t="n">
-        <v>5.771847747196034</v>
+        <v>0.8269886363636365</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45583.66666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3634,320 +3478,288 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1475</v>
+        <v>-0.09083333333333343</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.51</v>
+        <v>-0.3700000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.69625</v>
+        <v>0.4294285714285714</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.1043809523809525</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>-0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9375</v>
+        <v>0.5333333333333332</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9375</v>
+        <v>-0.4666666666666666</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.8125</v>
+        <v>1.566666666666667</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8125</v>
+        <v>-0.4571428571428564</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.5</v>
+        <v>-1.916666666666666</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.75</v>
+        <v>-6.583333333333334</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.6875</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9375</v>
+        <v>-2.38095238095238</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AG10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.5571428571428572</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.1714285714285715</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.75</v>
       </c>
-      <c r="AH10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AK10" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AL10" t="n">
-        <v>-1.0625</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.8125</v>
+        <v>-0.4000000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1.275595238095238</v>
+        <v>-4.160256410256411</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.007692307692307665</v>
+        <v>8.170670995670996</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.2528710533126297</v>
+        <v>-2.686714634571778</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.9279673451548454</v>
+        <v>1.073953364663997</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>28</v>
-      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>5.846153846153854</v>
+        <v>5.36363636363636</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.15384615384616</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>31</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-7</v>
-      </c>
+        <v>-7.36363636363636</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>-5.769230769230774</v>
+        <v>1.545454545454547</v>
       </c>
       <c r="BC10" t="n">
-        <v>-8.692307692307693</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.75</v>
+        <v>-15.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.75</v>
+        <v>-9.25</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.375</v>
+        <v>-2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.25</v>
+        <v>-0.1999999999999957</v>
       </c>
       <c r="BH10" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="BI10" t="n">
         <v>2.25</v>
       </c>
-      <c r="BI10" t="n">
-        <v>-2.25</v>
-      </c>
       <c r="BJ10" t="n">
-        <v>5.0625</v>
+        <v>-7.271428571428572</v>
       </c>
       <c r="BK10" t="n">
-        <v>-5.0625</v>
+        <v>7.271428571428572</v>
       </c>
       <c r="BL10" t="inlineStr"/>
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="n">
-        <v>1.25</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="BQ10" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0.4952380952380953</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0.07619047619047592</v>
+      </c>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="n">
+        <v>-0.06666666666666671</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.8000000000000007</v>
+      </c>
+      <c r="CA10" t="n">
         <v>-1</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-0.1833333333333333</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0.4583333333333333</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>-0.125</v>
       </c>
       <c r="CB10" t="inlineStr"/>
       <c r="CC10" t="inlineStr"/>
       <c r="CD10" t="inlineStr"/>
       <c r="CE10" t="inlineStr"/>
-      <c r="CF10" t="n">
-        <v>0.07371794871794872</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>-0.0597069597069597</v>
-      </c>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
       <c r="CH10" t="n">
-        <v>0.02215132632296486</v>
+        <v>0.003909028004727429</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.02626166347673529</v>
+        <v>0.006629056116554177</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0625</v>
+        <v>-0.06666666666666671</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.1875</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.115860990860995</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>-0.1841269841269841</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>-1.015873015873012</v>
-      </c>
+        <v>5.50419672919675</v>
+      </c>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
       <c r="CQ10" t="n">
-        <v>-1556.746031746032</v>
+        <v>0.3330021623331731</v>
       </c>
       <c r="CR10" t="n">
-        <v>-23000</v>
+        <v>-1.79502081464997</v>
       </c>
       <c r="CS10" t="n">
-        <v>-800000</v>
+        <v>1164047.619047619</v>
       </c>
       <c r="CT10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>0.3143575292956058</v>
-      </c>
+        <v>3163.492063492064</v>
+      </c>
+      <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="n">
-        <v>0.5734126984126959</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>-1.780012873370993</v>
-      </c>
+        <v>0.7357142857142804</v>
+      </c>
+      <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.330286367936324</v>
+        <v>1.952380952380963</v>
       </c>
       <c r="CY10" t="n">
-        <v>-69</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>-0.1914776566527725</v>
-      </c>
+        <v>-0.8964285714285758</v>
+      </c>
+      <c r="CZ10" t="inlineStr"/>
       <c r="DA10" t="n">
-        <v>-1</v>
+        <v>1.596825396825395</v>
       </c>
       <c r="DB10" t="n">
-        <v>2.324206349206349</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>-1027.429025437927</v>
-      </c>
+        <v>5833.464281165856</v>
+      </c>
+      <c r="DC10" t="inlineStr"/>
       <c r="DD10" t="n">
-        <v>-695807.303184431</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>873244.0476190476</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>-68</v>
-      </c>
+        <v>-0.0225710495464162</v>
+      </c>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
       <c r="DG10" t="n">
-        <v>-1</v>
+        <v>2.188427691882055</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.7853174603174615</v>
+        <v>0.7802335655848935</v>
       </c>
       <c r="DI10" t="n">
-        <v>-4</v>
+        <v>1433523.602845432</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.7901626978542566</v>
+        <v>0.001984126984127199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3974,152 +3786,152 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5</v>
+        <v>0.03249999999999975</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7</v>
+        <v>0.3050000000000002</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.2006250000000001</v>
+        <v>-0.4668749999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.12125</v>
+        <v>0.375</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-2.4375</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>-1</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AK11" t="n">
         <v>1.25</v>
       </c>
-      <c r="V11" t="n">
-        <v>-0.3125</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1.0625</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.875</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1875</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL11" t="n">
-        <v>0.25</v>
+        <v>-0.9375</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.125</v>
+        <v>0.9375</v>
       </c>
       <c r="AN11" t="n">
-        <v>-2.318278657616893</v>
+        <v>-2.749458874458875</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1.167207792207792</v>
+        <v>-1.739583333333333</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.1138305771384331</v>
+        <v>0.6812062855445209</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.04617878702357547</v>
+        <v>-0.2742721688034191</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>-26</v>
+        <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>-40.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>-4.538461538461533</v>
+        <v>9.972527472527474</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.15384615384616</v>
+        <v>-21.96703296703296</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>-2.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>-6.846153846153847</v>
+        <v>0.9065934065934087</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.307692307692314</v>
+        <v>-9.082417582417584</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.5</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>-3.3125</v>
+        <v>7.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>-3.6875</v>
+        <v>8.4375</v>
       </c>
       <c r="BH11" t="n">
-        <v>-6.5</v>
+        <v>10.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.5</v>
+        <v>-10.75</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-0.375</v>
+        <v>4.9375</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.375</v>
+        <v>-4.9375</v>
       </c>
       <c r="BL11" t="inlineStr"/>
       <c r="BM11" t="inlineStr"/>
@@ -4129,161 +3941,161 @@
         <v>1</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.1416666666666666</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.7374999999999998</v>
+        <v>0.06666666666666643</v>
       </c>
       <c r="BT11" t="inlineStr"/>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BX11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BY11" t="n">
         <v>1.5</v>
       </c>
-      <c r="BY11" t="n">
-        <v>4</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>-1.4375</v>
+        <v>1.625</v>
       </c>
       <c r="CA11" t="n">
-        <v>-2</v>
+        <v>1.1875</v>
       </c>
       <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="inlineStr"/>
       <c r="CD11" t="inlineStr"/>
       <c r="CE11" t="inlineStr"/>
       <c r="CF11" t="n">
-        <v>0.04700854700854701</v>
+        <v>0.0350595238095238</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.02014652014652014</v>
+        <v>-0.05159504704072043</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.008923391396155271</v>
+        <v>0.02194506396887187</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.009374193155685856</v>
+        <v>-0.02204850453484599</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.25</v>
+        <v>-0.125</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.1875</v>
+        <v>0.3125</v>
       </c>
       <c r="CN11" t="n">
-        <v>-5.291999050332365</v>
+        <v>-0.7975631313131402</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0.3297619047619045</v>
+        <v>-79000</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.5912698412698774</v>
+        <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>780.9523809523816</v>
+        <v>2.672679364894805</v>
       </c>
       <c r="CR11" t="n">
-        <v>-13000</v>
+        <v>-3.624668226150803</v>
       </c>
       <c r="CS11" t="n">
-        <v>-8350000</v>
+        <v>-9341865.079365075</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-41908.33333333334</v>
       </c>
       <c r="CU11" t="n">
-        <v>-2.590059093812965</v>
+        <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-1.50793650793652</v>
+        <v>-4.121031746031747</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.857133014689111</v>
+        <v>-22500000</v>
       </c>
       <c r="CX11" t="n">
-        <v>-3.43252052814745</v>
+        <v>-0.714682539682542</v>
       </c>
       <c r="CY11" t="n">
-        <v>-69</v>
+        <v>-2.714285714285715</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.4428093546030856</v>
+        <v>-8</v>
       </c>
       <c r="DA11" t="n">
-        <v>-1</v>
+        <v>-2.180952380952391</v>
       </c>
       <c r="DB11" t="n">
-        <v>-2.169047619047618</v>
+        <v>-43322.13929461771</v>
       </c>
       <c r="DC11" t="n">
-        <v>-1977.735385422107</v>
+        <v>-4</v>
       </c>
       <c r="DD11" t="n">
-        <v>-4096142.593002114</v>
+        <v>-0.7697822903865101</v>
       </c>
       <c r="DE11" t="n">
-        <v>-2519603.174603175</v>
+        <v>-3</v>
       </c>
       <c r="DF11" t="n">
-        <v>-81</v>
+        <v>-4</v>
       </c>
       <c r="DG11" t="n">
-        <v>-2</v>
+        <v>-3.694314260618626</v>
       </c>
       <c r="DH11" t="n">
-        <v>-1.820238095238093</v>
+        <v>-7.794263060131826</v>
       </c>
       <c r="DI11" t="n">
-        <v>4.5</v>
+        <v>-12499511.56846138</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-1.573175264922554</v>
+        <v>-0.7567460317460317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45570.46875</v>
+        <v>45571.5625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4310,300 +4122,302 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2909999999999999</v>
+        <v>-1.0035</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05649999999999999</v>
+        <v>0.3075000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.175</v>
+        <v>-0.1481249999999998</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.07125000000000004</v>
+        <v>0.2581249999999999</v>
       </c>
       <c r="T12" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.5625</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-3.149999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.3125</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="AI12" t="n">
         <v>0.25</v>
       </c>
-      <c r="U12" t="n">
-        <v>0.1000000000000001</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.9500000000000002</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.9000000000000004</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.6875</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-2.0625</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-0.6875</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-0.5625</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>-0.95</v>
+        <v>-0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AL12" t="n">
         <v>-0.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4375</v>
+        <v>0.625</v>
       </c>
       <c r="AN12" t="n">
-        <v>-3.945138195138195</v>
+        <v>-1.887099567099567</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.116176470588235</v>
+        <v>0.2634615384615389</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1.483190017702885</v>
+        <v>-0.6263018459975696</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.416248416616064</v>
+        <v>-0.1721004516317022</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="n">
-        <v>-10</v>
+        <v>-28</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>-15</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.3076923076923066</v>
+        <v>-3.769230769230774</v>
       </c>
       <c r="AY12" t="n">
-        <v>-3.461538461538467</v>
+        <v>-8.384615384615387</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="BA12" t="n">
-        <v>-4</v>
+        <v>-7.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>-7.846153846153847</v>
+        <v>-7.384615384615387</v>
       </c>
       <c r="BC12" t="n">
-        <v>-9.07692307692308</v>
+        <v>-5.153846153846153</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.149999999999999</v>
+        <v>-4.899999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.2000000000000028</v>
+        <v>8.200000000000003</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.625</v>
+        <v>-2.5625</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.3125</v>
+        <v>1.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.5</v>
+        <v>2.700000000000003</v>
       </c>
       <c r="BI12" t="n">
-        <v>-3.5</v>
+        <v>-2.700000000000003</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.125</v>
+        <v>0.1875</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0.125</v>
+        <v>-0.1875</v>
       </c>
       <c r="BL12" t="inlineStr"/>
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="n">
-        <v>0.9500000000000002</v>
+        <v>1.55</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.6916666666666667</v>
+        <v>1.0625</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.7916666666666665</v>
+        <v>-0.3125</v>
       </c>
       <c r="BT12" t="inlineStr"/>
       <c r="BU12" t="inlineStr"/>
       <c r="BV12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-6.149999999999999</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BW12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>5.949999999999999</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>7.699999999999999</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>5.8125</v>
-      </c>
       <c r="CA12" t="n">
-        <v>4.25</v>
+        <v>-2.9375</v>
       </c>
       <c r="CB12" t="inlineStr"/>
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
       <c r="CE12" t="inlineStr"/>
       <c r="CF12" t="n">
-        <v>-0.02374768089053803</v>
+        <v>-0.01173245614035087</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.02326388888888889</v>
+        <v>-0.008844460443607566</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.000538330537886586</v>
+        <v>0.002932486858592022</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0.006092098253704402</v>
+        <v>0.004100327410668195</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0.04999999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.125</v>
+        <v>-0.0625</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.7011724386724438</v>
+        <v>-1.367803030303023</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.1427083333333334</v>
+        <v>-73000</v>
       </c>
       <c r="CP12" t="n">
-        <v>-1.308564814814872</v>
+        <v>-160</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-3499.074074074077</v>
-      </c>
-      <c r="CR12" t="inlineStr"/>
+        <v>-0.2374406843156294</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>2.064516212953713</v>
+      </c>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="n">
-        <v>-1.47153442854875</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>-2.373495370370364</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="n">
-        <v>2.249502574309076</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>-0.5402389599564543</v>
-      </c>
+        <v>-29500000</v>
+      </c>
+      <c r="CX12" t="inlineStr"/>
       <c r="CY12" t="inlineStr"/>
       <c r="CZ12" t="n">
-        <v>-0.03133083699066663</v>
+        <v>-161</v>
       </c>
       <c r="DA12" t="inlineStr"/>
       <c r="DB12" t="n">
-        <v>-1.118518518518528</v>
+        <v>3138.657176157169</v>
       </c>
       <c r="DC12" t="n">
-        <v>-2932.486798869344</v>
+        <v>-4.666666666666668</v>
       </c>
       <c r="DD12" t="n">
-        <v>286845.308087809</v>
+        <v>0.08079732767232817</v>
       </c>
       <c r="DE12" t="n">
-        <v>-3110995.370370368</v>
-      </c>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>5.333333333333343</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>-1.209041999666994</v>
+      </c>
       <c r="DH12" t="n">
-        <v>0.764930555555555</v>
-      </c>
-      <c r="DI12" t="inlineStr"/>
-      <c r="DJ12" t="n">
-        <v>0.06360745968426329</v>
-      </c>
+        <v>1.693787982850466</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2538440.751956377</v>
+      </c>
+      <c r="DJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45570.375</v>
+        <v>45571.46875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4630,76 +4444,76 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2725</v>
+        <v>-1.2175</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.63</v>
+        <v>-0.2150000000000003</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1148529411764709</v>
+        <v>-0.8343749999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5014338235294116</v>
+        <v>-0.1656250000000004</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.75</v>
+        <v>-1.25</v>
       </c>
       <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-4.375</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0.75</v>
       </c>
-      <c r="V13" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-1.3875</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.3250000000000002</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.1500000000000004</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.137499999999999</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH13" t="n">
-        <v>-0.09999999999999998</v>
+        <v>-1.375</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.08750000000000002</v>
+        <v>0.1875</v>
       </c>
       <c r="AJ13" t="n">
         <v>-1.5</v>
@@ -4708,126 +4522,126 @@
         <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.1375</v>
+        <v>-0.9375</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.75</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.8065656565656569</v>
+        <v>0.5416666666666661</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.4956110421836231</v>
+        <v>0.05702908202908197</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1346884421033692</v>
+        <v>1.585274631266479</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.4146536769681939</v>
+        <v>-1.6813499000999</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="n">
-        <v>-34</v>
+        <v>-8</v>
       </c>
       <c r="AW13" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="AX13" t="n">
-        <v>-1.424369747899163</v>
+        <v>-29.07692307692308</v>
       </c>
       <c r="AY13" t="n">
-        <v>-8.096638655462172</v>
+        <v>29.23076923076923</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-27</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.5</v>
+        <v>-20</v>
       </c>
       <c r="BB13" t="n">
-        <v>-6.268907563025209</v>
+        <v>-6</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.268907563025209</v>
+        <v>9.384615384615387</v>
       </c>
       <c r="BD13" t="n">
-        <v>-1.25</v>
+        <v>-6</v>
       </c>
       <c r="BE13" t="n">
-        <v>-6.5</v>
+        <v>14.25</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.450000000000003</v>
+        <v>-1.9375</v>
       </c>
       <c r="BG13" t="n">
-        <v>-3.125</v>
+        <v>12.1875</v>
       </c>
       <c r="BH13" t="n">
-        <v>-3.75</v>
+        <v>-22.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.75</v>
+        <v>22.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7250000000000014</v>
+        <v>-24.625</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.7250000000000014</v>
+        <v>24.625</v>
       </c>
       <c r="BL13" t="inlineStr"/>
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BQ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BS13" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0.8875000000000002</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>0.8624999999999998</v>
       </c>
       <c r="BT13" t="inlineStr"/>
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="BX13" t="n">
-        <v>5</v>
+        <v>9.25</v>
       </c>
       <c r="BY13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.125</v>
+        <v>3.75</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.649999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="CB13" t="inlineStr"/>
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>0.008730158730158727</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.2002314814814815</v>
+        <v>-0.04307909604519774</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01253896485564531</v>
+        <v>-0.00950867805630707</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01451162408652944</v>
+        <v>-0.01799150139258565</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0.25</v>
@@ -4836,110 +4650,106 @@
         <v>0.25</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>0.25</v>
       </c>
       <c r="CN13" t="n">
-        <v>-3.202709636042968</v>
+        <v>1.19653379028378</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0.46875</v>
+        <v>-405000</v>
       </c>
       <c r="CP13" t="n">
-        <v>-2.388888888888914</v>
+        <v>-264</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-9364.583333333328</v>
+        <v>-1.470561346548152</v>
       </c>
       <c r="CR13" t="n">
-        <v>-20000</v>
+        <v>3.848781518189409</v>
       </c>
       <c r="CS13" t="n">
-        <v>-8200000</v>
+        <v>-35913968.25396825</v>
       </c>
       <c r="CT13" t="n">
-        <v>3</v>
+        <v>-96707.53968253967</v>
       </c>
       <c r="CU13" t="n">
-        <v>-0.3273019362173777</v>
+        <v>-3</v>
       </c>
       <c r="CV13" t="n">
-        <v>-2.256944444444443</v>
+        <v>-8.189682539682522</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.7661856117738637</v>
+        <v>-158000000</v>
       </c>
       <c r="CX13" t="n">
-        <v>-3.669911787558831</v>
+        <v>1.575396825396837</v>
       </c>
       <c r="CY13" t="n">
-        <v>3</v>
+        <v>0.556349206349207</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.2630390442890445</v>
+        <v>-255</v>
       </c>
       <c r="DA13" t="n">
-        <v>0</v>
+        <v>-10.13293650793651</v>
       </c>
       <c r="DB13" t="n">
-        <v>-3.6875</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>-8779.323923625394</v>
-      </c>
+        <v>-38499.49494949495</v>
+      </c>
+      <c r="DC13" t="inlineStr"/>
       <c r="DD13" t="n">
-        <v>-5594533.392465377</v>
+        <v>-0.5466374269005847</v>
       </c>
       <c r="DE13" t="n">
-        <v>-7249652.777777778</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>-10</v>
-      </c>
+        <v>-11</v>
+      </c>
+      <c r="DF13" t="inlineStr"/>
       <c r="DG13" t="n">
-        <v>-1</v>
+        <v>-4.158890123034851</v>
       </c>
       <c r="DH13" t="n">
-        <v>-1.413194444444439</v>
+        <v>1.210655901116425</v>
       </c>
       <c r="DI13" t="n">
-        <v>-2.666666666666686</v>
+        <v>-13530164.30754917</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-2.651655840074966</v>
+        <v>-1.761507936507937</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45569.66666666666</v>
+        <v>45571.375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4966,269 +4776,289 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.07750000000000012</v>
+        <v>-0.3699999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.4824999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1975</v>
+        <v>0.811875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5899999999999999</v>
+        <v>0.1037500000000002</v>
       </c>
       <c r="T14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V14" t="n">
         <v>0.25</v>
       </c>
-      <c r="U14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.5</v>
-      </c>
       <c r="W14" t="n">
-        <v>-0.625</v>
+        <v>-0.3125</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="Z14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="AM14" t="n">
         <v>0.125</v>
       </c>
-      <c r="AA14" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-1.9375</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-0.6875</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-0.875</v>
-      </c>
       <c r="AN14" t="n">
-        <v>-1.364285714285714</v>
+        <v>-0.5601787101787101</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.966233766233766</v>
+        <v>1.080952380952381</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1.713076506826507</v>
+        <v>-2.835984899495929</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.9468608937358942</v>
+        <v>0.4616115220241577</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="n">
-        <v>-59</v>
+        <v>-33</v>
       </c>
       <c r="AW14" t="n">
-        <v>47</v>
+        <v>-27</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0769230769230802</v>
+        <v>-15.92307692307692</v>
       </c>
       <c r="AY14" t="n">
-        <v>-2.92307692307692</v>
+        <v>-17.84615384615384</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-31</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>-11</v>
       </c>
       <c r="BB14" t="n">
-        <v>-9.230769230769234</v>
+        <v>2.692307692307693</v>
       </c>
       <c r="BC14" t="n">
-        <v>-4.307692307692307</v>
+        <v>-1.38461538461538</v>
       </c>
       <c r="BD14" t="n">
-        <v>-3.75</v>
+        <v>-0.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>-2.625</v>
+        <v>-4.9375</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.375</v>
+        <v>-8.1875</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.25</v>
+        <v>19</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0.25</v>
+        <v>-19</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0.3125</v>
+        <v>8.625</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.3125</v>
+        <v>-8.625</v>
       </c>
       <c r="BL14" t="inlineStr"/>
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.75</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.4642857142857142</v>
+        <v>-0.3958333333333333</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.1339285714285714</v>
-      </c>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
+        <v>0.5416666666666665</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1</v>
+      </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="BX14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.25</v>
+        <v>-0.25</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.9375</v>
+        <v>-3.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.25</v>
+        <v>0.125</v>
       </c>
       <c r="CB14" t="inlineStr"/>
       <c r="CC14" t="inlineStr"/>
       <c r="CD14" t="inlineStr"/>
       <c r="CE14" t="inlineStr"/>
       <c r="CF14" t="n">
-        <v>-0.02418939783839424</v>
+        <v>0.04188861985472155</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.03263157894736841</v>
+        <v>-0.06944444444444445</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01342409519685678</v>
+        <v>0.001951674614775238</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.003246381826031181</v>
+        <v>0.01238267971249583</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN14" t="inlineStr"/>
-      <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
+        <v>0.1875</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.03557692307693117</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>114000</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>145</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-2.548638669981585</v>
+      </c>
       <c r="CR14" t="n">
-        <v>-123000</v>
+        <v>0.03844755605591388</v>
       </c>
       <c r="CS14" t="n">
-        <v>-50100000</v>
+        <v>-2763932.178932179</v>
       </c>
       <c r="CT14" t="n">
-        <v>-4</v>
+        <v>8019.42640692641</v>
       </c>
       <c r="CU14" t="n">
-        <v>2.458585155706864</v>
-      </c>
-      <c r="CV14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.6554067460317299</v>
+      </c>
       <c r="CW14" t="n">
-        <v>2.683161201006612</v>
+        <v>-38100000</v>
       </c>
       <c r="CX14" t="n">
-        <v>-1.260588808121696</v>
+        <v>-1.932336760461766</v>
       </c>
       <c r="CY14" t="n">
-        <v>-241</v>
+        <v>-0.4564303751803784</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01680559024309058</v>
+        <v>124</v>
       </c>
       <c r="DA14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="DB14" t="inlineStr"/>
+        <v>0.4436327561327573</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>2580.165040497854</v>
+      </c>
       <c r="DC14" t="n">
-        <v>-226.1712519936191</v>
+        <v>0.06666666666666643</v>
       </c>
       <c r="DD14" t="n">
-        <v>-3323253.966884723</v>
-      </c>
-      <c r="DE14" t="inlineStr"/>
+        <v>-0.1145224497294928</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>3</v>
+      </c>
       <c r="DF14" t="n">
-        <v>-242</v>
+        <v>-5.933333333333337</v>
       </c>
       <c r="DG14" t="n">
-        <v>-6</v>
-      </c>
-      <c r="DH14" t="inlineStr"/>
+        <v>-0.07552303217937606</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-1.000321813334594</v>
+      </c>
       <c r="DI14" t="n">
-        <v>-1</v>
+        <v>-6095524.586030586</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-4.175497519658691</v>
+        <v>0.02221771284271301</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ14"/>
+  <dimension ref="A1:DJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,144 +890,144 @@
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>E595Qvn9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.66666666666</v>
+        <v>45593.70833333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1054,100 +1054,100 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.503333333333333</v>
+        <v>-0.6299999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8466666666666669</v>
+        <v>-0.915</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8421428571428571</v>
+        <v>0.04428571428571426</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1549999999999998</v>
+        <v>-0.5535714285714286</v>
       </c>
       <c r="T2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="X2" t="n">
-        <v>3.333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.714285714285714</v>
+        <v>0.6428571428571423</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.07142857142857117</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3333333333333321</v>
+        <v>-2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.714285714285714</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3.642857142857142</v>
+        <v>-1.071428571428571</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3333333333333335</v>
+        <v>0.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.785714285714286</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.2142857142857144</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.5</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.533333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1.266666666666667</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1.001010101010102</v>
+        <v>-3.576923076923077</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.05151515151515129</v>
+        <v>5.767857142857143</v>
       </c>
       <c r="AP2" t="n">
-        <v>-2.478224862036973</v>
+        <v>-1.238313349212364</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.711118326118326</v>
+        <v>-1.410181380244406</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -1156,78 +1156,78 @@
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>29.72727272727272</v>
+        <v>-18.53636363636365</v>
       </c>
       <c r="AY2" t="n">
-        <v>-37.72727272727273</v>
+        <v>0.681818181818187</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>10.90909090909091</v>
+        <v>2.709090909090904</v>
       </c>
       <c r="BC2" t="n">
-        <v>-13.81818181818181</v>
+        <v>-1.036363636363632</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.75</v>
+        <v>5.833333333333332</v>
       </c>
       <c r="BE2" t="n">
-        <v>-4.75</v>
+        <v>-4.333333333333332</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.066666666666663</v>
+        <v>-0.5333333333333314</v>
       </c>
       <c r="BG2" t="n">
-        <v>-7.93333333333333</v>
+        <v>-1.466666666666669</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.66666666666666</v>
+        <v>23.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>-11.66666666666667</v>
+        <v>-23.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.14285714285715</v>
+        <v>2.142857142857139</v>
       </c>
       <c r="BK2" t="n">
-        <v>-13.14285714285715</v>
+        <v>-2.142857142857139</v>
       </c>
       <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>-2.666666666666667</v>
+        <v>3.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.333333333333333</v>
+        <v>-2.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>-1.357142857142857</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.7142857142857142</v>
       </c>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="n">
-        <v>-0.25</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="BX2" t="n">
-        <v>-4.75</v>
+        <v>3.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.25</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-2.133333333333335</v>
+        <v>-0.3333333333333321</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.5333333333333332</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="CB2" t="inlineStr"/>
       <c r="CC2" t="inlineStr"/>
@@ -1236,71 +1236,85 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr"/>
       <c r="CH2" t="n">
-        <v>0.01840877662422498</v>
+        <v>0.001211204572177348</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0227685815200746</v>
+        <v>-0.02496244407688095</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1333333333333334</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.4795260295260277</v>
-      </c>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
+        <v>1.952127525252536</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.050315656565658</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-0.1217169144542751</v>
+      </c>
       <c r="CQ2" t="n">
-        <v>-0.4752431413616023</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>-3.691973048880943</v>
-      </c>
-      <c r="CS2" t="inlineStr"/>
+        <v>-1.464007722631322</v>
+      </c>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="n">
+        <v>-0.4269886363636364</v>
+      </c>
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
+      <c r="CV2" t="n">
+        <v>-2.065625000000011</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-6027509.463850085</v>
+      </c>
       <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
+      <c r="CY2" t="n">
+        <v>-1.394177128245744</v>
+      </c>
       <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="n">
-        <v>36922.05637929323</v>
-      </c>
+      <c r="DA2" t="n">
+        <v>-0.7150932275642106</v>
+      </c>
+      <c r="DB2" t="inlineStr"/>
       <c r="DC2" t="inlineStr"/>
       <c r="DD2" t="n">
-        <v>0.3224568560094871</v>
+        <v>0.9811553030302775</v>
       </c>
       <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="inlineStr"/>
+      <c r="DF2" t="n">
+        <v>-2630.17676767677</v>
+      </c>
       <c r="DG2" t="n">
-        <v>1.55464917027416</v>
+        <v>-3.124621212121212</v>
       </c>
       <c r="DH2" t="n">
-        <v>-2.454151002506251</v>
+        <v>-0.1923839816157924</v>
       </c>
       <c r="DI2" t="n">
-        <v>8420367.627620915</v>
-      </c>
-      <c r="DJ2" t="inlineStr"/>
+        <v>-2550.131150621353</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-11240340.90909091</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>jiAoNQdE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.5625</v>
+        <v>45592.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1310,18 +1324,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1348,7 +1362,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1360,88 +1374,88 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9308333333333332</v>
+        <v>-0.08000000000000007</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7058333333333333</v>
+        <v>-1.095</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6109047619047621</v>
+        <v>-0.2464285714285716</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4232857142857145</v>
+        <v>-0.07214285714285684</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08333333333333326</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08333333333333326</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2190476190476192</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1952380952380952</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>-2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.061904761904762</v>
+        <v>0.07142857142857117</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.047619047619048</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="AB3" t="n">
         <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.666666666666666</v>
+        <v>-5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.080952380952381</v>
+        <v>-0.3571428571428577</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.528571428571428</v>
+        <v>0.07142857142857295</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.583333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.547619047619048</v>
+        <v>-0.6428571428571429</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6523809523809525</v>
+        <v>-0.6428571428571429</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.266666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.219047619047619</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>-2.522743922743923</v>
+        <v>2.017045454545455</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1.306060606060606</v>
+        <v>-0.5909090909090908</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.6782290398676949</v>
+        <v>-0.5162516055373199</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2.875437465111378</v>
+        <v>0.4511401122220446</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -1450,78 +1464,78 @@
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-13.18181818181819</v>
+        <v>2.027272727272731</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.18181818181817</v>
+        <v>-3.163636363636357</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>2.181818181818187</v>
+        <v>-0.3454545454545439</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>-5.981818181818177</v>
       </c>
       <c r="BD3" t="n">
-        <v>-19.66666666666666</v>
+        <v>-1</v>
       </c>
       <c r="BE3" t="n">
-        <v>-17.33333333333334</v>
+        <v>-4.666666666666664</v>
       </c>
       <c r="BF3" t="n">
-        <v>-13.35238095238095</v>
+        <v>0.4666666666666615</v>
       </c>
       <c r="BG3" t="n">
-        <v>-13.6</v>
+        <v>0.1333333333333329</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.8333333333333357</v>
+        <v>21.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.8333333333333357</v>
+        <v>-21.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.7380952380952337</v>
+        <v>11.57142857142857</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.7380952380952337</v>
+        <v>-11.57142857142857</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="n">
-        <v>0.75</v>
+        <v>-3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.4666666666666668</v>
+        <v>-0.1538461538461542</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.2714285714285718</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="BY3" t="n">
-        <v>-1.583333333333334</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-5.461904761904764</v>
+        <v>0.9333333333333336</v>
       </c>
       <c r="CA3" t="n">
-        <v>-1.699999999999999</v>
+        <v>2.733333333333333</v>
       </c>
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="inlineStr"/>
@@ -1530,106 +1544,106 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
       <c r="CH3" t="n">
-        <v>-0.01212574865551905</v>
+        <v>-0.005689444030122441</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0305725186780594</v>
+        <v>-0.01223606889403565</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.05714285714285716</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.5333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.6381172839506206</v>
-      </c>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
+        <v>0.964877946127956</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>-0.2698412698412689</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>-2.704222192973482</v>
+      </c>
       <c r="CQ3" t="n">
-        <v>0.02938368629801857</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>0.6501828482930208</v>
-      </c>
+        <v>3.105038891468183</v>
+      </c>
+      <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="n">
-        <v>4229320.987654322</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>7612.345679012345</v>
-      </c>
+        <v>0.890873015873016</v>
+      </c>
+      <c r="CT3" t="inlineStr"/>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>2.568827160493825</v>
-      </c>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="n">
-        <v>2.361728395061732</v>
-      </c>
+        <v>2.126190476190487</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>4594889.493318287</v>
+      </c>
+      <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.4141975308642</v>
+        <v>1.491166213005727</v>
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.521296296296285</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>8273.674508039832</v>
-      </c>
+        <v>-1.491784968461957</v>
+      </c>
+      <c r="DB3" t="inlineStr"/>
       <c r="DC3" t="inlineStr"/>
       <c r="DD3" t="n">
-        <v>0.3848012098076599</v>
+        <v>-1.751587301587278</v>
       </c>
       <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
+      <c r="DF3" t="n">
+        <v>8351.587301587297</v>
+      </c>
       <c r="DG3" t="n">
-        <v>2.901643957177996</v>
+        <v>2.061507936507923</v>
       </c>
       <c r="DH3" t="n">
-        <v>2.214992210709454</v>
+        <v>0.4084363306112533</v>
       </c>
       <c r="DI3" t="n">
-        <v>2031404.109664559</v>
+        <v>2010.029349257933</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.5444444444444447</v>
+        <v>11127380.95238096</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>842EOIGL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.46875</v>
+        <v>45592.60416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1656,100 +1670,100 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>AZ18LjKN</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1766666666666665</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2566666666666667</v>
+        <v>0.22</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6562380952380955</v>
+        <v>0.06214285714285706</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2007619047619049</v>
+        <v>0.2492857142857144</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5333333333333334</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4666666666666667</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="X4" t="n">
-        <v>1.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.333333333333333</v>
+        <v>-2.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.352380952380952</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.2000000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.666666666666666</v>
+        <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.72857142857143</v>
+        <v>2.428571428571429</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.009523809523809</v>
+        <v>0.5714285714285712</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3333333333333334</v>
+        <v>-0.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.7095238095238094</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.3571428571428571</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8666666666666667</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.3472222222222214</v>
+        <v>-4.033333333333333</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1.691666666666667</v>
+        <v>1.508928571428572</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.099512313083742</v>
+        <v>-1.431544798142542</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.2215627362055934</v>
+        <v>-0.1479029898672755</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -1758,78 +1772,82 @@
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-2.27272727272728</v>
+        <v>4.400000000000006</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.181818181818187</v>
+        <v>-5.799999999999997</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>3</v>
+        <v>6.399999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.909090909090907</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-15.33333333333334</v>
+        <v>6.333333333333332</v>
       </c>
       <c r="BE4" t="n">
-        <v>-30.25</v>
+        <v>2</v>
       </c>
       <c r="BF4" t="n">
-        <v>-3.533333333333331</v>
+        <v>6.466666666666669</v>
       </c>
       <c r="BG4" t="n">
-        <v>-14.6</v>
+        <v>4.066666666666666</v>
       </c>
       <c r="BH4" t="n">
-        <v>-3</v>
+        <v>8.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>-8.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4.399999999999999</v>
+        <v>4.428571428571431</v>
       </c>
       <c r="BK4" t="n">
-        <v>-4.399999999999999</v>
+        <v>-4.428571428571431</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>0.8333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0.8333333333333335</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.3435897435897435</v>
+        <v>0.08241758241758235</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1538461538461537</v>
-      </c>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
+        <v>0.7857142857142856</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1</v>
+      </c>
       <c r="BV4" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="BX4" t="n">
-        <v>-4.833333333333332</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="BY4" t="n">
-        <v>-7.583333333333332</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-2.666666666666668</v>
+        <v>2.6</v>
       </c>
       <c r="CA4" t="n">
-        <v>-3.599999999999998</v>
+        <v>3.133333333333333</v>
       </c>
       <c r="CB4" t="inlineStr"/>
       <c r="CC4" t="inlineStr"/>
@@ -1838,90 +1856,92 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
       <c r="CH4" t="n">
-        <v>-0.0153523598376037</v>
+        <v>0.01163916070996808</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01569763733121778</v>
+        <v>-0.02288424412588812</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0.08333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.4</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="CN4" t="inlineStr"/>
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.1260804473304518</v>
+      </c>
       <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
+      <c r="CP4" t="n">
+        <v>-4.672619431606805</v>
+      </c>
       <c r="CQ4" t="n">
-        <v>-2.905136926754494</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>0.8520597745175849</v>
-      </c>
+        <v>3.058702847841261</v>
+      </c>
+      <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
+      <c r="CW4" t="n">
+        <v>-17113749.79414442</v>
+      </c>
       <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
+      <c r="CY4" t="n">
+        <v>-1.647580149082714</v>
+      </c>
       <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="n">
-        <v>45602.7172760761</v>
-      </c>
+      <c r="DA4" t="n">
+        <v>-7.690118101415266</v>
+      </c>
+      <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="n">
-        <v>1.252978435773058</v>
-      </c>
+      <c r="DD4" t="inlineStr"/>
       <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="inlineStr"/>
-      <c r="DG4" t="n">
-        <v>7.916886267072201</v>
-      </c>
+      <c r="DG4" t="inlineStr"/>
       <c r="DH4" t="n">
-        <v>8.47680525850221</v>
+        <v>-1.084414643150257</v>
       </c>
       <c r="DI4" t="n">
-        <v>19553618.11955419</v>
+        <v>-49423.54103874246</v>
       </c>
       <c r="DJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>naHJ2yf2</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.375</v>
+        <v>45592.51041666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1948,100 +1968,100 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1933333333333336</v>
+        <v>0.995</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1758333333333333</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.08066666666666666</v>
+        <v>0.1028571428571429</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3533333333333335</v>
+        <v>-0.2685714285714287</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-1</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2</v>
+        <v>-0.4000000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08333333333333348</v>
+        <v>-1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1333333333333329</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2666666666666666</v>
+        <v>-0.7857142857142856</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.5833333333333339</v>
+        <v>5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5833333333333339</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.800000000000001</v>
+        <v>3.142857142857142</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3333333333333339</v>
+        <v>-2.857142857142858</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5833333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.2666666666666666</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.25</v>
+        <v>-1</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.4000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-5.564583333333333</v>
+        <v>6.698051948051948</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.906759906759907</v>
+        <v>-6.244318181818182</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.078391001355842</v>
+        <v>-1.015617453275016</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.9251354201354203</v>
+        <v>3.009201710987425</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -2050,78 +2070,78 @@
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>2.75</v>
+        <v>7.400000000000006</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.681818181818187</v>
+        <v>-12.19999999999999</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-5.212121212121211</v>
+        <v>-8.800000000000004</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.93181818181818</v>
+        <v>-5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.333333333333336</v>
+        <v>2.333333333333336</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>10.33333333333334</v>
       </c>
       <c r="BF5" t="n">
-        <v>-3.666666666666671</v>
+        <v>3.333333333333329</v>
       </c>
       <c r="BG5" t="n">
-        <v>-3.533333333333331</v>
+        <v>8.466666666666669</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.4166666666666643</v>
+        <v>2.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.4166666666666643</v>
+        <v>-2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-1.600000000000001</v>
+        <v>0.4285714285714306</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.600000000000001</v>
+        <v>-0.4285714285714306</v>
       </c>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>0.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.2333333333333334</v>
+        <v>0.5119047619047616</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.6095238095238094</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.583333333333332</v>
+        <v>3</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-2.333333333333334</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="CA5" t="n">
-        <v>-3.066666666666665</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="CB5" t="inlineStr"/>
       <c r="CC5" t="inlineStr"/>
@@ -2130,106 +2150,106 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="n">
-        <v>-0.01643228294216253</v>
+        <v>0.00160421600193246</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.005748529422383589</v>
+        <v>0.003423476942068175</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.25</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.06666666666666665</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.7606361231361092</v>
-      </c>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
+        <v>-0.3277777777777686</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>3.647955246913579</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1.116784813101891</v>
+      </c>
       <c r="CQ5" t="n">
-        <v>3.022652453134896</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>-2.778389300757723</v>
-      </c>
+        <v>2.481331327830617</v>
+      </c>
+      <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="n">
-        <v>5572722.222222222</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>11267.22222222222</v>
-      </c>
+        <v>0.08746141975308608</v>
+      </c>
+      <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.973333333333329</v>
-      </c>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="n">
-        <v>4.19999999999996</v>
-      </c>
+        <v>-0.8259259259259295</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-1199146.081890938</v>
+      </c>
+      <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
-        <v>-0.7033333333333331</v>
+        <v>-2.219579242507194</v>
       </c>
       <c r="CZ5" t="inlineStr"/>
       <c r="DA5" t="n">
-        <v>2.118333333333339</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>6744.220537422287</v>
-      </c>
+        <v>-0.2893650152164042</v>
+      </c>
+      <c r="DB5" t="inlineStr"/>
       <c r="DC5" t="inlineStr"/>
       <c r="DD5" t="n">
-        <v>-0.2502100725784935</v>
+        <v>-0.884953703703701</v>
       </c>
       <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
+      <c r="DF5" t="n">
+        <v>-7563.734567901236</v>
+      </c>
       <c r="DG5" t="n">
-        <v>1.931668258641949</v>
+        <v>-3.772415123456781</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.009098171159578783</v>
+        <v>0.1181871075833927</v>
       </c>
       <c r="DI5" t="n">
-        <v>1681289.410719234</v>
+        <v>-3595.902921754314</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0338888888888893</v>
+        <v>-9414371.14197531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45592.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2256,100 +2276,100 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.554166666666666</v>
+        <v>-0.215</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.02000000000000013</v>
+        <v>-0.4350000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.518904761904762</v>
+        <v>-0.6699999999999997</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3426666666666666</v>
+        <v>-0.279285714285714</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.8571428571428572</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1.285714285714285</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.8571428571428572</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AK6" t="n">
         <v>0.3333333333333334</v>
       </c>
-      <c r="V6" t="n">
-        <v>-0.5904761904761906</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.4952380952380953</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-4.583333333333333</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-3.071428571428571</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.7666666666666666</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-8.166666666666668</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1.583333333333334</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-5.96190476190476</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1.916666666666667</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.08333333333333326</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.7619047619047616</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.9523809523809524</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.416666666666667</v>
-      </c>
       <c r="AL6" t="n">
-        <v>-0.7523809523809522</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.9761904761904761</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.212903225806452</v>
+        <v>-4.020833333333333</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.481944444444444</v>
+        <v>1.025</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.079228149896324</v>
+        <v>-1.287520476417992</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.945355596784168</v>
+        <v>0.9012703566274989</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -2358,82 +2378,78 @@
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-20.36363636363636</v>
+        <v>-5.099999999999994</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.63636363636364</v>
+        <v>9.400000000000006</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-17.81818181818181</v>
+        <v>-7.300000000000004</v>
       </c>
       <c r="BC6" t="n">
-        <v>-5.636363636363633</v>
+        <v>3.899999999999999</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.833333333333332</v>
+        <v>-1</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.083333333333332</v>
+        <v>5.666666666666664</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.08095238095238244</v>
+        <v>-0.1333333333333329</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.676190476190474</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="BH6" t="n">
-        <v>-9.666666666666664</v>
+        <v>8.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>9.666666666666664</v>
+        <v>-8.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-6.919047619047618</v>
+        <v>-8.142857142857146</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.919047619047618</v>
+        <v>8.142857142857146</v>
       </c>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="n">
-        <v>0.25</v>
+        <v>-3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.8571428571428574</v>
+        <v>-0.2527472527472527</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-1</v>
-      </c>
+        <v>0.1538461538461537</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1</v>
+        <v>0.6666666666666661</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.25</v>
+        <v>0.6666666666666679</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.05714285714285694</v>
+        <v>1.933333333333334</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.1761904761904756</v>
+        <v>0.2000000000000011</v>
       </c>
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
@@ -2442,106 +2458,90 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="n">
-        <v>0.03163283548068595</v>
+        <v>-0.01172540956133454</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.005735573344559375</v>
+        <v>-0.01066149322241685</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.5047619047619047</v>
+        <v>0.1333333333333334</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1285714285714286</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>0.9934615384615313</v>
-      </c>
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CN6" t="inlineStr"/>
       <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="inlineStr"/>
+      <c r="CP6" t="n">
+        <v>0.5102070343943446</v>
+      </c>
       <c r="CQ6" t="n">
-        <v>-0.1616614829027867</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>0.5359984901006563</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>-62889019.09722222</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-209116.3194444444</v>
-      </c>
+        <v>1.49437009069365</v>
+      </c>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
       <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="n">
-        <v>-12.46770833333333</v>
-      </c>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="n">
-        <v>-2.160069444444474</v>
-      </c>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="n">
+        <v>-1439063.827397806</v>
+      </c>
+      <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>0.1263888888888864</v>
+        <v>-1.659219207864723</v>
       </c>
       <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
-        <v>-11.09097222222222</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>-114791.4631222536</v>
-      </c>
+        <v>-0.2976906793470278</v>
+      </c>
+      <c r="DB6" t="inlineStr"/>
       <c r="DC6" t="inlineStr"/>
-      <c r="DD6" t="n">
-        <v>-0.9598897316921702</v>
-      </c>
+      <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="inlineStr"/>
       <c r="DF6" t="inlineStr"/>
-      <c r="DG6" t="n">
-        <v>-9.368032147018198</v>
-      </c>
+      <c r="DG6" t="inlineStr"/>
       <c r="DH6" t="n">
-        <v>-8.632473606902778</v>
+        <v>-0.2186379510295919</v>
       </c>
       <c r="DI6" t="n">
-        <v>-32835469.54462734</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>-2.188541666666667</v>
-      </c>
+        <v>5680.385381159376</v>
+      </c>
+      <c r="DJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2568,100 +2568,100 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9083333333333333</v>
+        <v>-1.165</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07166666666666666</v>
+        <v>-0.9850000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8321428571428573</v>
+        <v>-0.2094285714285711</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06142857142857139</v>
+        <v>-0.2811904761904763</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3999999999999999</v>
+        <v>-0.02500000000000002</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.666666666666667</v>
+        <v>-4.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9999999999999996</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2142857142857144</v>
+        <v>-0.0428571428571427</v>
       </c>
       <c r="AB7" t="n">
-        <v>-3.166666666666666</v>
+        <v>-2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.428571428571429</v>
+        <v>-0.00952380952380949</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2142857142857135</v>
+        <v>2.047619047619047</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.166666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.142857142857143</v>
+        <v>-0.3666666666666667</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.3571428571428571</v>
+        <v>-0.3523809523809524</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.9166666666666667</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.8333333333333334</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.3333333333333335</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.4666666666666668</v>
+        <v>-0.03749999999999998</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.681818181818183</v>
+        <v>5.136363636363637</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.831746031746032</v>
+        <v>-5.689393939393939</v>
       </c>
       <c r="AP7" t="n">
-        <v>-2.259863945578231</v>
+        <v>2.490134221495031</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.204642308401707</v>
+        <v>-2.849563425991997</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
@@ -2670,78 +2670,78 @@
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>0.3636363636363598</v>
+        <v>2.345454545454558</v>
       </c>
       <c r="AY7" t="n">
-        <v>-11.38636363636364</v>
+        <v>19.83636363636364</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>5.909090909090907</v>
+        <v>16.13636363636363</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.5151515151515156</v>
+        <v>15.68181818181818</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>-15</v>
       </c>
       <c r="BE7" t="n">
-        <v>-5.333333333333336</v>
+        <v>-3.666666666666664</v>
       </c>
       <c r="BF7" t="n">
-        <v>-8.266666666666666</v>
+        <v>-6.508333333333333</v>
       </c>
       <c r="BG7" t="n">
-        <v>-8.400000000000002</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.6666666666666643</v>
+        <v>-22</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.6666666666666643</v>
+        <v>22</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2.785714285714285</v>
+        <v>-5.361904761904768</v>
       </c>
       <c r="BK7" t="n">
-        <v>-2.785714285714285</v>
+        <v>5.361904761904761</v>
       </c>
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="n">
-        <v>-2.333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.846153846153846</v>
+        <v>-0.4380952380952381</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.07692307692307709</v>
+        <v>-0.838095238095238</v>
       </c>
       <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.166666666666666</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.5833333333333339</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-3.6</v>
+        <v>0.07083333333333286</v>
       </c>
       <c r="CA7" t="n">
-        <v>-2.533333333333333</v>
+        <v>1.141666666666667</v>
       </c>
       <c r="CB7" t="inlineStr"/>
       <c r="CC7" t="inlineStr"/>
@@ -2750,106 +2750,106 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr"/>
       <c r="CH7" t="n">
-        <v>-0.002136586577308586</v>
+        <v>-0.03764650946538886</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.02939031265072215</v>
+        <v>-0.01669084681906393</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.4166666666666666</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.1333333333333334</v>
+        <v>0.1583333333333333</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="CN7" t="n">
-        <v>-1.266981947450688</v>
-      </c>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
+        <v>-0.8730130633255442</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>2.407908950617283</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>4.291484368458057</v>
+      </c>
       <c r="CQ7" t="n">
-        <v>-0.8876668470418281</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>2.69795327221798</v>
-      </c>
+        <v>-1.289074830302894</v>
+      </c>
+      <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>-2057341.269841276</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>1180.158730158742</v>
-      </c>
+        <v>0.7887345679012343</v>
+      </c>
+      <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>0.7738095238095184</v>
-      </c>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="n">
-        <v>0.4976190476190254</v>
-      </c>
+        <v>5.129668209876556</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>19089465.20260116</v>
+      </c>
+      <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>-0.3567460317460345</v>
+        <v>3.976846610179933</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>0.5043650793650727</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>3807.516605126897</v>
-      </c>
+        <v>8.137524618007063</v>
+      </c>
+      <c r="DB7" t="inlineStr"/>
       <c r="DC7" t="inlineStr"/>
       <c r="DD7" t="n">
-        <v>-0.1301438757321112</v>
+        <v>3.163117283950612</v>
       </c>
       <c r="DE7" t="inlineStr"/>
-      <c r="DF7" t="inlineStr"/>
+      <c r="DF7" t="n">
+        <v>113549.5756172839</v>
+      </c>
       <c r="DG7" t="n">
-        <v>1.352002695017404</v>
+        <v>1.759490740740745</v>
       </c>
       <c r="DH7" t="n">
-        <v>3.460671844495366</v>
+        <v>0.5739054399142121</v>
       </c>
       <c r="DI7" t="n">
-        <v>-746075.5400645118</v>
+        <v>69125.44233706512</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.234126984126984</v>
+        <v>30112789.35185187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45591.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2876,100 +2876,100 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6258333333333335</v>
+        <v>-0.4200000000000002</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3975000000000001</v>
+        <v>0.2516666666666669</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.3787142857142858</v>
+        <v>-0.7778571428571429</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3749523809523807</v>
+        <v>0.2507142857142859</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.4285714285714279</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2142857142857135</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.5</v>
       </c>
-      <c r="V8" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-4.416666666666667</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-2.033333333333333</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-6.916666666666668</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.333333333333333</v>
-      </c>
       <c r="AD8" t="n">
-        <v>-3.757142857142858</v>
+        <v>-2.285714285714285</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.947619047619046</v>
+        <v>0.2142857142857135</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.75</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2571428571428571</v>
+        <v>-1.071428571428572</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.75</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.06666666666666665</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.9333333333333336</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.096328671328672</v>
+        <v>1.837301587301587</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.8462121212121212</v>
+        <v>0.4833333333333334</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.034875197901514</v>
+        <v>1.234151463615749</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.4109788659053359</v>
+        <v>-1.056507605802719</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
@@ -2978,78 +2978,82 @@
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>7.272727272727266</v>
+        <v>-1.700000000000003</v>
       </c>
       <c r="AY8" t="n">
-        <v>-12.27272727272728</v>
+        <v>21.39999999999999</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-3.63636363636364</v>
+        <v>-14.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.818181818181813</v>
+        <v>-3</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
-        <v>22.25</v>
+        <v>4.166666666666668</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.266666666666666</v>
+        <v>8.133333333333333</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.200000000000003</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="BH8" t="n">
-        <v>-10</v>
+        <v>-1.666666666666664</v>
       </c>
       <c r="BI8" t="n">
-        <v>10</v>
+        <v>1.666666666666664</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-7.799999999999997</v>
+        <v>-2.428571428571431</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.799999999999997</v>
+        <v>2.428571428571431</v>
       </c>
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="n">
-        <v>0.4166666666666665</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0.9166666666666665</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.357142857142857</v>
+        <v>0.1593406593406594</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
+        <v>-0.3461538461538463</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
       <c r="BV8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BX8" t="n">
-        <v>1.5</v>
+        <v>1.083333333333334</v>
       </c>
       <c r="BY8" t="n">
-        <v>-4</v>
+        <v>2.75</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.3333333333333339</v>
+        <v>1.4</v>
       </c>
       <c r="CA8" t="n">
-        <v>-2.600000000000001</v>
+        <v>2.266666666666666</v>
       </c>
       <c r="CB8" t="inlineStr"/>
       <c r="CC8" t="inlineStr"/>
@@ -3058,10 +3062,10 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr"/>
       <c r="CH8" t="n">
-        <v>0.01142048147838962</v>
+        <v>0.01681808427849318</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.007851362214019726</v>
+        <v>-0.02360492083723476</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
@@ -3073,77 +3077,91 @@
         <v>-0.2</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="CN8" t="n">
-        <v>-1.806516014849336</v>
-      </c>
-      <c r="CO8" t="inlineStr"/>
-      <c r="CP8" t="inlineStr"/>
+        <v>0.5701914983164897</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.94537037037037</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.0459000913851213</v>
+      </c>
       <c r="CQ8" t="n">
-        <v>-3.831995851084429</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>4.08175626134701</v>
-      </c>
-      <c r="CS8" t="inlineStr"/>
+        <v>-2.14164507997063</v>
+      </c>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="n">
+        <v>-0.6990740740740742</v>
+      </c>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
+      <c r="CV8" t="n">
+        <v>-3.82037037037037</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-5704867.248334739</v>
+      </c>
       <c r="CX8" t="inlineStr"/>
-      <c r="CY8" t="inlineStr"/>
+      <c r="CY8" t="n">
+        <v>-4.759326755688974</v>
+      </c>
       <c r="CZ8" t="inlineStr"/>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="n">
-        <v>4470.098656360264</v>
-      </c>
+      <c r="DA8" t="n">
+        <v>-2.562941550002932</v>
+      </c>
+      <c r="DB8" t="inlineStr"/>
       <c r="DC8" t="inlineStr"/>
       <c r="DD8" t="n">
-        <v>-0.02958871444746047</v>
+        <v>-1.592592592592609</v>
       </c>
       <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
+      <c r="DF8" t="n">
+        <v>-20278.70370370371</v>
+      </c>
       <c r="DG8" t="n">
-        <v>-3.879222061478231</v>
+        <v>-4.754629629629633</v>
       </c>
       <c r="DH8" t="n">
-        <v>1.249008662297157</v>
+        <v>-0.2736331755810599</v>
       </c>
       <c r="DI8" t="n">
-        <v>-547215.304591707</v>
-      </c>
-      <c r="DJ8" t="inlineStr"/>
+        <v>-13008.46655408575</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-13212685.18518519</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.375</v>
+        <v>45591.46875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3170,100 +3188,100 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1916666666666665</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.508333333333333</v>
+        <v>-0.4949999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.2130357142857144</v>
+        <v>-0.00714285714285734</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1239285714285716</v>
+        <v>-0.1149999999999998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3157894736842106</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04210526315789465</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.166666666666666</v>
+        <v>-4.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.7067669172932334</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.583333333333334</v>
+        <v>-1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.7406015037593985</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.9360902255639107</v>
+        <v>-0.7857142857142847</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.5</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.1766917293233082</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.75</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2456140350877194</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.1964912280701754</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.462077505827506</v>
+        <v>-2.478787878787879</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1.458179723502304</v>
+        <v>-0.03021978021978011</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.7974371553566248</v>
+        <v>1.984195546905631</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.457394101430568</v>
+        <v>0.2045831152974014</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
@@ -3272,78 +3290,78 @@
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>23.37575757575758</v>
+        <v>0.9000000000000057</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.787878787878782</v>
+        <v>9.599999999999994</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>6.672727272727272</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.612121212121217</v>
+        <v>-0.8000000000000043</v>
       </c>
       <c r="BD9" t="n">
-        <v>-4.5</v>
+        <v>-4.666666666666668</v>
       </c>
       <c r="BE9" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1.838596491228074</v>
+        <v>1.266666666666666</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07017543859649322</v>
+        <v>1.533333333333331</v>
       </c>
       <c r="BH9" t="n">
-        <v>-1.166666666666664</v>
+        <v>16</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.166666666666664</v>
+        <v>-16</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.165413533834588</v>
+        <v>9.428571428571431</v>
       </c>
       <c r="BK9" t="n">
-        <v>-1.165413533834588</v>
+        <v>-9.428571428571431</v>
       </c>
       <c r="BL9" t="inlineStr"/>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="n">
-        <v>-2.25</v>
+        <v>-2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0.8333333333333335</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0.9323308270676689</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0.244360902255639</v>
+        <v>-0.6318681318681318</v>
       </c>
       <c r="BT9" t="inlineStr"/>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="BX9" t="n">
-        <v>-5.5</v>
+        <v>-2</v>
       </c>
       <c r="BY9" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-3.024561403508773</v>
+        <v>0.6666666666666679</v>
       </c>
       <c r="CA9" t="n">
-        <v>-4.305263157894736</v>
+        <v>0.8666666666666671</v>
       </c>
       <c r="CB9" t="inlineStr"/>
       <c r="CC9" t="inlineStr"/>
@@ -3352,106 +3370,106 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr"/>
       <c r="CH9" t="n">
-        <v>0.01273282718499661</v>
+        <v>-0.007095342909798963</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.004787163086764135</v>
+        <v>-0.008696876274300075</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0.25</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.08771929824561403</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0.4070175438596491</v>
+        <v>0.1333333333333334</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.263447971781304</v>
-      </c>
-      <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="inlineStr"/>
+        <v>-0.5433651996151951</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>2.801018518518521</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>4.380210627579046</v>
+      </c>
       <c r="CQ9" t="n">
-        <v>2.166524161396495</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.3908167435515217</v>
-      </c>
+        <v>-1.96512345679011</v>
+      </c>
+      <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="n">
-        <v>18021868.68686868</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>11488.5101010101</v>
-      </c>
+        <v>0.349444444444444</v>
+      </c>
+      <c r="CT9" t="inlineStr"/>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>5.490625000000009</v>
-      </c>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="n">
-        <v>1.257733585858631</v>
-      </c>
+        <v>1.60768518518519</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>2492409.622541202</v>
+      </c>
+      <c r="CX9" t="inlineStr"/>
       <c r="CY9" t="n">
-        <v>0.1691287878787833</v>
+        <v>-0.637723728513194</v>
       </c>
       <c r="CZ9" t="inlineStr"/>
       <c r="DA9" t="n">
-        <v>5.269065656565644</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>11732.00181407096</v>
-      </c>
+        <v>2.55234340058901</v>
+      </c>
+      <c r="DB9" t="inlineStr"/>
       <c r="DC9" t="inlineStr"/>
       <c r="DD9" t="n">
-        <v>0.5153691520467834</v>
+        <v>-1.736111111111057</v>
       </c>
       <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
+      <c r="DF9" t="n">
+        <v>-3381.111111111113</v>
+      </c>
       <c r="DG9" t="n">
-        <v>4.355257975884896</v>
+        <v>0.02564814814813587</v>
       </c>
       <c r="DH9" t="n">
-        <v>4.887035227008795</v>
+        <v>0.4512946929613595</v>
       </c>
       <c r="DI9" t="n">
-        <v>13219613.9081101</v>
+        <v>-3966.314460393405</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.8269886363636365</v>
+        <v>1622462.962962964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45591.375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3478,100 +3496,100 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.09083333333333343</v>
+        <v>-0.07333333333333347</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3700000000000001</v>
+        <v>1.246666666666667</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4294285714285714</v>
+        <v>-0.7721428571428572</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1043809523809525</v>
+        <v>-0.2578571428571428</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.25</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5333333333333332</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4666666666666666</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1666666666666665</v>
+        <v>-1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.166666666666667</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.566666666666667</v>
+        <v>-1.642857142857143</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.4571428571428564</v>
+        <v>-0.6428571428571423</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.916666666666666</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AC10" t="n">
-        <v>-6.583333333333334</v>
+        <v>6.833333333333334</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9857142857142858</v>
+        <v>-3.214285714285714</v>
       </c>
       <c r="AE10" t="n">
-        <v>-2.38095238095238</v>
+        <v>-0.1428571428571441</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5833333333333333</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.5571428571428572</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1714285714285715</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.75</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.3999999999999999</v>
+        <v>-0.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.4000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>-4.160256410256411</v>
+        <v>7.753846153846155</v>
       </c>
       <c r="AO10" t="n">
-        <v>8.170670995670996</v>
+        <v>-11.98484848484848</v>
       </c>
       <c r="AP10" t="n">
-        <v>-2.686714634571778</v>
+        <v>1.405937990580847</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.073953364663997</v>
+        <v>-1.272935419226979</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
@@ -3580,78 +3598,78 @@
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>5.36363636363636</v>
+        <v>-6.400000000000006</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.36363636363636</v>
+        <v>-2.299999999999997</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>1.545454545454547</v>
+        <v>-0.1000000000000014</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-12.59999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>-15.75</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="BE10" t="n">
-        <v>-9.25</v>
+        <v>0.1666666666666679</v>
       </c>
       <c r="BF10" t="n">
-        <v>-2</v>
+        <v>6.266666666666666</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1999999999999957</v>
+        <v>6.533333333333331</v>
       </c>
       <c r="BH10" t="n">
-        <v>-2.25</v>
+        <v>0.8333333333333357</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.25</v>
+        <v>-0.8333333333333357</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-7.271428571428572</v>
+        <v>2.214285714285715</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.271428571428572</v>
+        <v>-2.214285714285715</v>
       </c>
       <c r="BL10" t="inlineStr"/>
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="n">
-        <v>-1.416666666666667</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.4166666666666665</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0.4952380952380953</v>
+        <v>0.07142857142857162</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0.07619047619047592</v>
+        <v>0.07142857142857117</v>
       </c>
       <c r="BT10" t="inlineStr"/>
       <c r="BU10" t="inlineStr"/>
       <c r="BV10" t="n">
-        <v>-0.06666666666666671</v>
+        <v>-0.35</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>-4</v>
+        <v>-2.916666666666666</v>
       </c>
       <c r="BY10" t="n">
-        <v>-6.25</v>
+        <v>2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.8000000000000007</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="CA10" t="n">
-        <v>-1</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="CB10" t="inlineStr"/>
       <c r="CC10" t="inlineStr"/>
@@ -3660,106 +3678,106 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr"/>
       <c r="CH10" t="n">
-        <v>0.003909028004727429</v>
+        <v>0.005109552916032371</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.006629056116554177</v>
+        <v>-0.02939614806409017</v>
       </c>
       <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
         <v>-0.25</v>
       </c>
-      <c r="CK10" t="n">
-        <v>0</v>
-      </c>
       <c r="CL10" t="n">
-        <v>-0.06666666666666671</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="CN10" t="n">
-        <v>5.50419672919675</v>
-      </c>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
+        <v>-4.888631687242807</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-2.392460317460316</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.6919975250167703</v>
+      </c>
       <c r="CQ10" t="n">
-        <v>0.3330021623331731</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>-1.79502081464997</v>
-      </c>
+        <v>-1.073288524291371</v>
+      </c>
+      <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">
-        <v>1164047.619047619</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>3163.492063492064</v>
-      </c>
+        <v>-0.8269841269841272</v>
+      </c>
+      <c r="CT10" t="inlineStr"/>
       <c r="CU10" t="inlineStr"/>
       <c r="CV10" t="n">
-        <v>0.7357142857142804</v>
-      </c>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="n">
-        <v>1.952380952380963</v>
-      </c>
+        <v>-5.663492063492058</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-5414173.775614414</v>
+      </c>
+      <c r="CX10" t="inlineStr"/>
       <c r="CY10" t="n">
-        <v>-0.8964285714285758</v>
+        <v>-4.722458168056505</v>
       </c>
       <c r="CZ10" t="inlineStr"/>
       <c r="DA10" t="n">
-        <v>1.596825396825395</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>5833.464281165856</v>
-      </c>
+        <v>-2.934594366462719</v>
+      </c>
+      <c r="DB10" t="inlineStr"/>
       <c r="DC10" t="inlineStr"/>
       <c r="DD10" t="n">
-        <v>-0.0225710495464162</v>
+        <v>-3.952380952380963</v>
       </c>
       <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
+      <c r="DF10" t="n">
+        <v>-16174.60317460317</v>
+      </c>
       <c r="DG10" t="n">
-        <v>2.188427691882055</v>
+        <v>-5.055158730158738</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.7802335655848935</v>
+        <v>-0.4736079062300629</v>
       </c>
       <c r="DI10" t="n">
-        <v>1433523.602845432</v>
+        <v>-13871.46429714575</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.001984126984127199</v>
+        <v>-9049047.619047619</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.66666666666</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3786,316 +3804,274 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03249999999999975</v>
+        <v>-0.8033333333333332</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3050000000000002</v>
+        <v>0.6483333333333332</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.4668749999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0.375</v>
+        <v>0.05800000000000005</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6875</v>
+        <v>0.2730263157894737</v>
       </c>
       <c r="W11" t="n">
-        <v>0.625</v>
+        <v>-0.1019736842105263</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.875</v>
+        <v>-1.755555555555556</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.8125</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>-4.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="AD11" t="n">
-        <v>-2.4375</v>
+        <v>-2.722222222222223</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3125</v>
+        <v>0.7111111111111121</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.25</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.75</v>
+        <v>-0.1222222222222222</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1875</v>
+        <v>-0.4333333333333332</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-1</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.25</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.9375</v>
+        <v>0.3585526315789473</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.9375</v>
+        <v>-0.361842105263158</v>
       </c>
       <c r="AN11" t="n">
-        <v>-2.749458874458875</v>
+        <v>3.280844155844156</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1.739583333333333</v>
+        <v>-2.043589743589743</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.6812062855445209</v>
+        <v>1.191989849007393</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.2742721688034191</v>
+        <v>-0.5282587997426704</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-40.5</v>
-      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>9.972527472527474</v>
+        <v>2.201298701298697</v>
       </c>
       <c r="AY11" t="n">
-        <v>-21.96703296703296</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>-0.8766233766233853</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>0.9065934065934087</v>
+        <v>-4.311688311688307</v>
       </c>
       <c r="BC11" t="n">
-        <v>-9.082417582417584</v>
+        <v>-0.4935064935064872</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>3.333333333333332</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>4.333333333333332</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.5</v>
+        <v>-1.309210526315788</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4375</v>
+        <v>-0.1315789473684177</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.75</v>
+        <v>-8.833333333333336</v>
       </c>
       <c r="BI11" t="n">
-        <v>-10.75</v>
+        <v>8.833333333333336</v>
       </c>
       <c r="BJ11" t="n">
-        <v>4.9375</v>
+        <v>-6.766666666666666</v>
       </c>
       <c r="BK11" t="n">
-        <v>-4.9375</v>
+        <v>6.766666666666666</v>
       </c>
       <c r="BL11" t="inlineStr"/>
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="n">
-        <v>1</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.3999999999999999</v>
+        <v>-0.6777777777777776</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.06666666666666643</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="BT11" t="inlineStr"/>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="n">
-        <v>-0.3333333333333334</v>
+        <v>0.2</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="BX11" t="n">
-        <v>-1.5</v>
+        <v>4.083333333333334</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.625</v>
+        <v>1.217105263157896</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.1875</v>
+        <v>2.648026315789473</v>
       </c>
       <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="inlineStr"/>
       <c r="CD11" t="inlineStr"/>
       <c r="CE11" t="inlineStr"/>
-      <c r="CF11" t="n">
-        <v>0.0350595238095238</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>-0.05159504704072043</v>
-      </c>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
       <c r="CH11" t="n">
-        <v>0.02194506396887187</v>
+        <v>-0.01854574715721258</v>
       </c>
       <c r="CI11" t="n">
-        <v>-0.02204850453484599</v>
+        <v>0.009465698732532481</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="CL11" t="n">
-        <v>-0.125</v>
+        <v>0.1710526315789473</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.3125</v>
+        <v>0.2236842105263158</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.7975631313131402</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>-79000</v>
-      </c>
+        <v>-0.5590926001082295</v>
+      </c>
+      <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>1.471171049357327</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.672679364894805</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>-3.624668226150803</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>-9341865.079365075</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>-41908.33333333334</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>-4.121031746031747</v>
-      </c>
+        <v>-1.130642097553874</v>
+      </c>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="n">
-        <v>-22500000</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>-0.714682539682542</v>
-      </c>
+        <v>-6266816.586645018</v>
+      </c>
+      <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>-2.714285714285715</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>-8</v>
-      </c>
+        <v>-4.007857910063791</v>
+      </c>
+      <c r="CZ11" t="inlineStr"/>
       <c r="DA11" t="n">
-        <v>-2.180952380952391</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>-43322.13929461771</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>-0.7697822903865101</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>-3.694314260618626</v>
-      </c>
+        <v>-2.433486820006422</v>
+      </c>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
       <c r="DH11" t="n">
-        <v>-7.794263060131826</v>
+        <v>-0.2264439264439266</v>
       </c>
       <c r="DI11" t="n">
-        <v>-12499511.56846138</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>-0.7567460317460317</v>
-      </c>
+        <v>-7351.914552404749</v>
+      </c>
+      <c r="DJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45571.5625</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4122,302 +4098,288 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0035</v>
+        <v>-0.4899999999999998</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3075000000000001</v>
+        <v>-0.7033333333333336</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.1481249999999998</v>
+        <v>0.01666666666666683</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2581249999999999</v>
+        <v>-0.2233333333333334</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.85</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5625</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7</v>
+        <v>-1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.9500000000000002</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.875</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3.149999999999999</v>
+        <v>-0.6666666666666661</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.300000000000001</v>
+        <v>-3.666666666666666</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.3125</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6875</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.0625</v>
+        <v>-0.1333333333333334</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.25</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.2</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.5</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.625</v>
+        <v>-0.06666666666666687</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1.887099567099567</v>
+        <v>-2.744444444444444</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.2634615384615389</v>
+        <v>2.429545454545455</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.6263018459975696</v>
+        <v>0.4466741591741594</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.1721004516317022</v>
+        <v>0.1712218028884696</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-15</v>
-      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>-3.769230769230774</v>
+        <v>-11.45454545454545</v>
       </c>
       <c r="AY12" t="n">
-        <v>-8.384615384615387</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-12</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-7.5</v>
-      </c>
+        <v>11.54545454545455</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>-7.384615384615387</v>
+        <v>7.090909090909093</v>
       </c>
       <c r="BC12" t="n">
-        <v>-5.153846153846153</v>
+        <v>7.63636363636364</v>
       </c>
       <c r="BD12" t="n">
-        <v>-4.899999999999999</v>
+        <v>9.333333333333336</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.200000000000003</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
-        <v>-2.5625</v>
+        <v>-1.800000000000004</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.700000000000003</v>
+        <v>-13.33333333333334</v>
       </c>
       <c r="BI12" t="n">
-        <v>-2.700000000000003</v>
+        <v>13.33333333333334</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.1875</v>
+        <v>-13.66666666666666</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0.1875</v>
+        <v>13.66666666666666</v>
       </c>
       <c r="BL12" t="inlineStr"/>
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="n">
-        <v>1.55</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-1.35</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="BR12" t="n">
-        <v>1.0625</v>
+        <v>-0.09743589743589753</v>
       </c>
       <c r="BS12" t="n">
-        <v>-0.3125</v>
+        <v>-0.5333333333333332</v>
       </c>
       <c r="BT12" t="inlineStr"/>
       <c r="BU12" t="inlineStr"/>
       <c r="BV12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>-0.6</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="BX12" t="n">
-        <v>2.25</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="BY12" t="n">
-        <v>-6.149999999999999</v>
+        <v>-3.333333333333334</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.25</v>
+        <v>-0.2666666666666675</v>
       </c>
       <c r="CA12" t="n">
-        <v>-2.9375</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="CB12" t="inlineStr"/>
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
       <c r="CE12" t="inlineStr"/>
-      <c r="CF12" t="n">
-        <v>-0.01173245614035087</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>-0.008844460443607566</v>
-      </c>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
       <c r="CH12" t="n">
-        <v>0.002932486858592022</v>
+        <v>-0.01177850786289869</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.004100327410668195</v>
+        <v>0.005999152381633309</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0.15</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="CL12" t="n">
-        <v>-0.0625</v>
+        <v>0.2</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="CN12" t="n">
-        <v>-1.367803030303023</v>
+        <v>0.5913825757575637</v>
       </c>
       <c r="CO12" t="n">
-        <v>-73000</v>
+        <v>-3.985802469135802</v>
       </c>
       <c r="CP12" t="n">
-        <v>-160</v>
+        <v>-2.61891662211579</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.2374406843156294</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>2.064516212953713</v>
-      </c>
-      <c r="CS12" t="inlineStr"/>
+        <v>0.1995080851762907</v>
+      </c>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="n">
+        <v>0.07191358024691352</v>
+      </c>
       <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="CV12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="n">
+        <v>0.8703703703703809</v>
+      </c>
       <c r="CW12" t="n">
-        <v>-29500000</v>
+        <v>2953117.619012871</v>
       </c>
       <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="n">
-        <v>-161</v>
-      </c>
-      <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="n">
-        <v>3138.657176157169</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>-4.666666666666668</v>
-      </c>
+      <c r="CY12" t="n">
+        <v>3.688827969607118</v>
+      </c>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="n">
+        <v>-0.3628186690235395</v>
+      </c>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
       <c r="DD12" t="n">
-        <v>0.08079732767232817</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>-5</v>
-      </c>
+        <v>2.334259259259255</v>
+      </c>
+      <c r="DE12" t="inlineStr"/>
       <c r="DF12" t="n">
-        <v>5.333333333333343</v>
+        <v>15487.34567901235</v>
       </c>
       <c r="DG12" t="n">
-        <v>-1.209041999666994</v>
+        <v>3.698456790123444</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.693787982850466</v>
+        <v>-0.07474955337442468</v>
       </c>
       <c r="DI12" t="n">
-        <v>2538440.751956377</v>
-      </c>
-      <c r="DJ12" t="inlineStr"/>
+        <v>7025.922106216221</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>10354197.5308642</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45571.46875</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4444,312 +4406,274 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2175</v>
+        <v>1.115</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2150000000000003</v>
+        <v>0.6450000000000002</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.8343749999999999</v>
+        <v>0.7826666666666664</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1656250000000004</v>
+        <v>-0.1419999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.25</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.375</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="W13" t="n">
-        <v>0.375</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.3125</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.5</v>
+        <v>0.5</v>
       </c>
       <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD13" t="n">
-        <v>-4.375</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AH13" t="n">
-        <v>-1.375</v>
+        <v>1.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1875</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>-0.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.9375</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.75</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.5416666666666661</v>
+        <v>-3.536471861471862</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.05702908202908197</v>
+        <v>2.561363636363637</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.585274631266479</v>
+        <v>-3.055867014091652</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.6813499000999</v>
+        <v>2.269771043771044</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="n">
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>29.72727272727272</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-37.72727272727273</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>10.90909090909091</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-13.81818181818181</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.933333333333337</v>
+      </c>
+      <c r="BG13" t="n">
         <v>-8</v>
       </c>
-      <c r="AW13" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-29.07692307692308</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>29.23076923076923</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-20</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>9.384615384615387</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-1.9375</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>12.1875</v>
-      </c>
       <c r="BH13" t="n">
-        <v>-22.5</v>
+        <v>14</v>
       </c>
       <c r="BI13" t="n">
-        <v>22.5</v>
+        <v>-14</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-24.625</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="BK13" t="n">
-        <v>24.625</v>
+        <v>-13.66666666666666</v>
       </c>
       <c r="BL13" t="inlineStr"/>
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.75</v>
+        <v>-1.533333333333333</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.5</v>
+        <v>0.06666666666666643</v>
       </c>
       <c r="BT13" t="inlineStr"/>
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.3</v>
       </c>
       <c r="BX13" t="n">
-        <v>9.25</v>
+        <v>-7</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.75</v>
+        <v>-2.733333333333333</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.25</v>
+        <v>-0.4666666666666668</v>
       </c>
       <c r="CB13" t="inlineStr"/>
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
       <c r="CE13" t="inlineStr"/>
-      <c r="CF13" t="n">
-        <v>0.1944444444444444</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>-0.04307909604519774</v>
-      </c>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
       <c r="CH13" t="n">
-        <v>-0.00950867805630707</v>
+        <v>0.01840877662422498</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.01799150139258565</v>
+        <v>0.0227685815200746</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>0.1333333333333334</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.25</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.19653379028378</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>-405000</v>
-      </c>
+        <v>-0.4925602175602108</v>
+      </c>
+      <c r="CO13" t="inlineStr"/>
       <c r="CP13" t="n">
-        <v>-264</v>
+        <v>-3.551595091068776</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-1.470561346548152</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>3.848781518189409</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>-35913968.25396825</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>-96707.53968253967</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>-8.189682539682522</v>
-      </c>
+        <v>-0.3227910815630253</v>
+      </c>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="n">
-        <v>-158000000</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.575396825396837</v>
-      </c>
+        <v>10430141.59492229</v>
+      </c>
+      <c r="CX13" t="inlineStr"/>
       <c r="CY13" t="n">
-        <v>0.556349206349207</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>-255</v>
-      </c>
+        <v>1.813127304793966</v>
+      </c>
+      <c r="CZ13" t="inlineStr"/>
       <c r="DA13" t="n">
-        <v>-10.13293650793651</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>-38499.49494949495</v>
-      </c>
+        <v>-1.934553977536424</v>
+      </c>
+      <c r="DB13" t="inlineStr"/>
       <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="n">
-        <v>-0.5466374269005847</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>-11</v>
-      </c>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
       <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="n">
-        <v>-4.158890123034851</v>
-      </c>
+      <c r="DG13" t="inlineStr"/>
       <c r="DH13" t="n">
-        <v>1.210655901116425</v>
+        <v>0.4286036250948531</v>
       </c>
       <c r="DI13" t="n">
-        <v>-13530164.30754917</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>-1.761507936507937</v>
-      </c>
+        <v>40653.82083803137</v>
+      </c>
+      <c r="DJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45571.375</v>
+        <v>45585.5625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4776,289 +4700,2387 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3699999999999999</v>
+        <v>0.5349999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.4124999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>0.811875</v>
+        <v>0.5313333333333332</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1037500000000002</v>
+        <v>0.3500000000000005</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.8000000000000003</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.866666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5.266666666666666</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.5</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AG14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>0.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>-0.3125</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.5625</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
         <v>0.25</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL14" t="n">
-        <v>-0.0625</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.125</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.5601787101787101</v>
+        <v>-4.302231102231103</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.080952380952381</v>
+        <v>0.08030303030303054</v>
       </c>
       <c r="AP14" t="n">
-        <v>-2.835984899495929</v>
+        <v>-1.09518272903567</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.4616115220241577</v>
+        <v>-2.533368797064449</v>
       </c>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-27</v>
-      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="n">
-        <v>-15.92307692307692</v>
+        <v>-13.18181818181819</v>
       </c>
       <c r="AY14" t="n">
-        <v>-17.84615384615384</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-11</v>
-      </c>
+        <v>12.18181818181817</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>2.692307692307693</v>
+        <v>2.181818181818187</v>
       </c>
       <c r="BC14" t="n">
-        <v>-1.38461538461538</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.5</v>
+        <v>-20.25</v>
       </c>
       <c r="BE14" t="n">
-        <v>-6.5</v>
+        <v>-19.25</v>
       </c>
       <c r="BF14" t="n">
-        <v>-4.9375</v>
+        <v>-13.53333333333334</v>
       </c>
       <c r="BG14" t="n">
-        <v>-8.1875</v>
+        <v>-13.93333333333334</v>
       </c>
       <c r="BH14" t="n">
-        <v>19</v>
+        <v>0.25</v>
       </c>
       <c r="BI14" t="n">
-        <v>-19</v>
+        <v>-0.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>8.625</v>
+        <v>-0.7333333333333343</v>
       </c>
       <c r="BK14" t="n">
-        <v>-8.625</v>
+        <v>0.7333333333333343</v>
       </c>
       <c r="BL14" t="inlineStr"/>
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.25</v>
+        <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0.3958333333333333</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.5416666666666665</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
       <c r="BV14" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>-1.75</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.25</v>
+        <v>-2.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-3.25</v>
+        <v>-5.533333333333335</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.125</v>
+        <v>-1.933333333333332</v>
       </c>
       <c r="CB14" t="inlineStr"/>
       <c r="CC14" t="inlineStr"/>
       <c r="CD14" t="inlineStr"/>
       <c r="CE14" t="inlineStr"/>
-      <c r="CF14" t="n">
-        <v>0.04188861985472155</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>-0.06944444444444445</v>
-      </c>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
       <c r="CH14" t="n">
-        <v>0.001951674614775238</v>
+        <v>-0.01212574865551905</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01238267971249583</v>
+        <v>0.0305725186780594</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0.06666666666666668</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1.464166666666685</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1.387847222222224</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.6547774586667785</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.2339991526862661</v>
+      </c>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="n">
+        <v>0.5406250000000004</v>
+      </c>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="n">
+        <v>2.480555555555554</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1753673.492999878</v>
+      </c>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="n">
+        <v>2.936630507184887</v>
+      </c>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="n">
+        <v>2.326296510507035</v>
+      </c>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="n">
+        <v>2.300694444444446</v>
+      </c>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="n">
+        <v>7601.388888888891</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>2.448958333333337</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.3757045643268555</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>8473.179791484748</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>4237673.611111111</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.46875</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>148</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.07166666666666666</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5860000000000003</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.1906666666666668</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5333333333333334</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.06666666666666643</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0.5</v>
       </c>
-      <c r="CL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>0.03557692307693117</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>114000</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>145</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>-2.548638669981585</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>0.03844755605591388</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>-2763932.178932179</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>8019.42640692641</v>
-      </c>
-      <c r="CU14" t="n">
+      <c r="AK15" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.9999999999999996</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.8458333333333334</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.168111777111778</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.4774074074074077</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>-2.27272727272728</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.181818181818187</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.909090909090907</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-6.333333333333336</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-12.13333333333333</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>3.333333333333329</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-3.333333333333329</v>
+      </c>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-0.338095238095238</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-2.583333333333332</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-5.083333333333332</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-2.066666666666666</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-2.933333333333332</v>
+      </c>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="n">
+        <v>-0.0153523598376037</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.01569763733121778</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="n">
+        <v>0.8504299951903924</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-2.630428168086354</v>
+      </c>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="n">
+        <v>19752263.93366596</v>
+      </c>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="n">
+        <v>7.917771896906032</v>
+      </c>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="n">
+        <v>8.513256600951792</v>
+      </c>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="n">
+        <v>1.25223896673116</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>45872.71315074351</v>
+      </c>
+      <c r="DJ15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45585.375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1933333333333336</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.1758333333333333</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.08066666666666666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.3533333333333335</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.5833333333333339</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5833333333333339</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-2.800000000000001</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-5.564583333333333</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4.906759906759907</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.078391001355842</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.9251354201354203</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4.681818181818187</v>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>-5.212121212121211</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.93181818181818</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6.333333333333336</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-3.666666666666671</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-3.533333333333331</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.4166666666666643</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0.4166666666666643</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-0.2333333333333334</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0.6095238095238094</v>
+      </c>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>3.583333333333332</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-3.066666666666665</v>
+      </c>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="n">
+        <v>-0.01643228294216253</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.005748529422383589</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0.7606361231361092</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>-0.7033333333333331</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-2.778389300757723</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>3.022652453134896</v>
+      </c>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="n">
+        <v>0.0338888888888893</v>
+      </c>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="n">
+        <v>1.973333333333329</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1681289.410719234</v>
+      </c>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="n">
+        <v>1.931668258641949</v>
+      </c>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="n">
+        <v>-0.009098171159578783</v>
+      </c>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="n">
+        <v>4.199999999999932</v>
+      </c>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="n">
+        <v>11267.22222222222</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>2.118333333333339</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-0.2502100725784935</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>6744.220537422287</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>5572722.222222222</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.0375</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.08499999999999996</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.4233333333333338</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.5333333333333334</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2</v>
       </c>
-      <c r="CV14" t="n">
-        <v>0.6554067460317299</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>-38100000</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>-1.932336760461766</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>-0.4564303751803784</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>124</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>0.4436327561327573</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>2580.165040497854</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>0.06666666666666643</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>-0.1145224497294928</v>
-      </c>
-      <c r="DE14" t="n">
+      <c r="Z17" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.9333333333333331</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.7333333333333332</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.6418377321603126</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3.829166666666666</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.711013592390845</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.36508177008177</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>-20.36363636363636</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11.63636363636364</v>
+      </c>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>-17.81818181818181</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-5.636363636363633</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.5333333333333314</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.799999999999997</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-6.533333333333331</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.533333333333331</v>
+      </c>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.9714285714285715</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.3952380952380952</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.2666666666666657</v>
+      </c>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="n">
+        <v>0.03163283548068595</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.005735573344559375</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0.9934615384615313</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0.1389660493827165</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.7249942165963787</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0.275136376065177</v>
+      </c>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="n">
+        <v>-2.161998456790124</v>
+      </c>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="n">
+        <v>-12.44564043209877</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-33531301.24571946</v>
+      </c>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="n">
+        <v>-9.433452374938426</v>
+      </c>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="n">
+        <v>-8.595267410321583</v>
+      </c>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="n">
+        <v>-2.086728395061726</v>
+      </c>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="n">
+        <v>-208270.0617283951</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-11.09282407407407</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-0.9625206077605462</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-114587.4908406771</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>-63086530.67129631</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2NyhKup</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45584.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.2625</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5575000000000001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8673333333333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1873333333333336</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-2.416666666666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-3.166666666666666</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.8333333333333339</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.133333333333335</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.7999999999999989</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.5833333333333333</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.5333333333333334</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.7467532467532472</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.4599206349206351</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-2.103253968253968</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.524332821174927</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>0.3636363636363598</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-11.38636363636364</v>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>5.909090909090907</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.5151515151515156</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.6666666666666643</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-11.08333333333334</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-8.200000000000003</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-9.133333333333333</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-0.0833333333333286</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.0833333333333357</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2.533333333333339</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-2.533333333333339</v>
+      </c>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1.583333333333334</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.583333333333334</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-3.266666666666666</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>-2.066666666666666</v>
+      </c>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="n">
+        <v>-0.002136586577308586</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.02939031265072215</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0.4166666666666666</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0.1333333333333334</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>-1.217824074074073</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>-0.4953703703703702</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>2.74826816248385</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-1.021197031000952</v>
+      </c>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="n">
+        <v>-0.2092592592592593</v>
+      </c>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="n">
+        <v>0.7981481481481438</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-441157.7257165518</v>
+      </c>
+      <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="n">
+        <v>1.462250893623434</v>
+      </c>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="n">
+        <v>3.736258712239106</v>
+      </c>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="inlineStr"/>
+      <c r="DD18" t="n">
+        <v>0.6537037037036839</v>
+      </c>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="n">
+        <v>759.25925925927</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0.6157407407407476</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0.1715608465608467</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>4224.358194456236</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-1702314.814814817</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45584.46875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>148</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.3275000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.3286666666666667</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.327333333333333</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1.866666666666666</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-3.533333333333333</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.7333333333333325</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.615078671328671</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1.77775974025974</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.440521953679849</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.6922449609214314</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>7.272727272727266</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-12.27272727272728</v>
+      </c>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>-3.63636363636364</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.818181818181813</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.7999999999999972</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.800000000000004</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-7.466666666666661</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>7.466666666666661</v>
+      </c>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.2857142857142856</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.7190476190476187</v>
+      </c>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>-3.866666666666667</v>
+      </c>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
+      <c r="CH19" t="n">
+        <v>0.01142048147838962</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.007851362214019726</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>-1.806516014849336</v>
+      </c>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="n">
+        <v>3.790089594680346</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-3.498662517751114</v>
+      </c>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="n">
+        <v>-218569.471258373</v>
+      </c>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="n">
+        <v>-3.618805394811559</v>
+      </c>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="n">
+        <v>1.3635919956305</v>
+      </c>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="inlineStr"/>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="n">
+        <v>-0.07125538111412721</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>3918.015323026935</v>
+      </c>
+      <c r="DJ19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45584.375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>148</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.1825</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.1220833333333335</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.05616666666666648</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.3157894736842106</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.04210526315789465</v>
+      </c>
+      <c r="X20" t="n">
         <v>3</v>
       </c>
-      <c r="DF14" t="n">
-        <v>-5.933333333333337</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>-0.07552303217937606</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>-1.000321813334594</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>-6095524.586030586</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>0.02221771284271301</v>
+      <c r="Y20" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.6912280701754385</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.5543859649122811</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.526315789473685</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.8456140350877206</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.2385964912280701</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.1789473684210527</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0.06315789473684208</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-0.7507430069930066</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.2561059907834098</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.2378256953880222</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.717439658114781</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>23.37575757575758</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>2.787878787878782</v>
+      </c>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="n">
+        <v>6.672727272727272</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.612121212121217</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-0.1719298245614098</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.463157894736845</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.270175438596489</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-0.270175438596489</v>
+      </c>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-0.8561403508771928</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-0.1157894736842104</v>
+      </c>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>-1.957894736842107</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>-3.305263157894736</v>
+      </c>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="inlineStr"/>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr"/>
+      <c r="CH20" t="n">
+        <v>0.01273282718499661</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>0.004787163086764135</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>-0.08771929824561403</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>-0.4070175438596491</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>2.047569444444449</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>0.2441287878787826</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>0.3904297466474951</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>2.037654192356229</v>
+      </c>
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="n">
+        <v>0.8519886363636364</v>
+      </c>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="n">
+        <v>5.565625000000011</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>11633390.99789338</v>
+      </c>
+      <c r="CX20" t="inlineStr"/>
+      <c r="CY20" t="n">
+        <v>4.191945282386456</v>
+      </c>
+      <c r="CZ20" t="inlineStr"/>
+      <c r="DA20" t="n">
+        <v>4.512422223912807</v>
+      </c>
+      <c r="DB20" t="inlineStr"/>
+      <c r="DC20" t="inlineStr"/>
+      <c r="DD20" t="n">
+        <v>1.107733585858625</v>
+      </c>
+      <c r="DE20" t="inlineStr"/>
+      <c r="DF20" t="n">
+        <v>11488.5101010101</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>5.29406565656565</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>0.4484186876504985</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>11226.19686051059</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>18140618.68686868</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>148</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3966666666666666</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.07133333333333325</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5333333333333332</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.4666666666666666</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8666666666666654</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-2.133333333333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.2666666666666668</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-2.745862470862471</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>5.86948051948052</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-2.244399304399304</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.5915325051002798</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>5.36363636363636</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-7.36363636363636</v>
+      </c>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="n">
+        <v>1.545454545454547</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>3.06666666666667</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-8.133333333333333</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>8.133333333333333</v>
+      </c>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-0.5333333333333337</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="n">
+        <v>-0.06666666666666671</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>-0.3333333333333321</v>
+      </c>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr"/>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr"/>
+      <c r="CG21" t="inlineStr"/>
+      <c r="CH21" t="n">
+        <v>0.003909028004727429</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.006629056116554177</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>-0.06666666666666671</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>5.19629629629631</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>-0.9802248677248713</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>-1.739517367479852</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>0.5327468945340286</v>
+      </c>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="n">
+        <v>-0.006349206349206105</v>
+      </c>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="n">
+        <v>0.7074735449735385</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>1653843.747694086</v>
+      </c>
+      <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="n">
+        <v>2.269765611597165</v>
+      </c>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="n">
+        <v>0.9028032473650995</v>
+      </c>
+      <c r="DB21" t="inlineStr"/>
+      <c r="DC21" t="inlineStr"/>
+      <c r="DD21" t="n">
+        <v>1.938492063492077</v>
+      </c>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="n">
+        <v>2813.492063492064</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>1.636177248677257</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>0.001810189747103896</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>6049.244261419513</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>1176362.433862434</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -890,112 +890,112 @@
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -1256,55 +1256,55 @@
       <c r="CN2" t="n">
         <v>1.952127525252536</v>
       </c>
-      <c r="CO2" t="n">
-        <v>1.050315656565658</v>
-      </c>
+      <c r="CO2" t="inlineStr"/>
       <c r="CP2" t="n">
-        <v>-0.1217169144542751</v>
+        <v>-6027509.463850085</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-1.464007722631322</v>
+        <v>-0.7150932275642106</v>
       </c>
       <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="n">
+        <v>-1.394177128245744</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>1.050315656565658</v>
+      </c>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="n">
+        <v>-2550.131150621353</v>
+      </c>
+      <c r="CY2" t="n">
         <v>-0.4269886363636364</v>
       </c>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="n">
+      <c r="CZ2" t="n">
         <v>-2.065625000000011</v>
       </c>
-      <c r="CW2" t="n">
-        <v>-6027509.463850085</v>
-      </c>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="n">
-        <v>-1.394177128245744</v>
-      </c>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="n">
-        <v>-0.7150932275642106</v>
-      </c>
-      <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="n">
+        <v>-11240340.90909091</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.1217169144542751</v>
+      </c>
       <c r="DD2" t="n">
-        <v>0.9811553030302775</v>
+        <v>-2630.17676767677</v>
       </c>
       <c r="DE2" t="inlineStr"/>
       <c r="DF2" t="n">
-        <v>-2630.17676767677</v>
+        <v>-0.1923839816157924</v>
       </c>
       <c r="DG2" t="n">
+        <v>0.9811553030302775</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-1.464007722631322</v>
+      </c>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="n">
         <v>-3.124621212121212</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.1923839816157924</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-2550.131150621353</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-11240340.90909091</v>
       </c>
     </row>
     <row r="3">
@@ -1564,55 +1564,55 @@
       <c r="CN3" t="n">
         <v>0.964877946127956</v>
       </c>
-      <c r="CO3" t="n">
-        <v>-0.2698412698412689</v>
-      </c>
+      <c r="CO3" t="inlineStr"/>
       <c r="CP3" t="n">
-        <v>-2.704222192973482</v>
+        <v>4594889.493318287</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.105038891468183</v>
+        <v>-1.491784968461957</v>
       </c>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="n">
+        <v>1.491166213005727</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>-0.2698412698412689</v>
+      </c>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="n">
+        <v>2010.029349257933</v>
+      </c>
+      <c r="CY3" t="n">
         <v>0.890873015873016</v>
       </c>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="n">
+      <c r="CZ3" t="n">
         <v>2.126190476190487</v>
       </c>
-      <c r="CW3" t="n">
-        <v>4594889.493318287</v>
-      </c>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="n">
-        <v>1.491166213005727</v>
-      </c>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="n">
-        <v>-1.491784968461957</v>
-      </c>
-      <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="n">
+        <v>11127380.95238096</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>-2.704222192973482</v>
+      </c>
       <c r="DD3" t="n">
-        <v>-1.751587301587278</v>
+        <v>8351.587301587297</v>
       </c>
       <c r="DE3" t="inlineStr"/>
       <c r="DF3" t="n">
-        <v>8351.587301587297</v>
+        <v>0.4084363306112533</v>
       </c>
       <c r="DG3" t="n">
+        <v>-1.751587301587278</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>3.105038891468183</v>
+      </c>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="n">
         <v>2.061507936507923</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>0.4084363306112533</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>2010.029349257933</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>11127380.95238096</v>
       </c>
     </row>
     <row r="4">
@@ -1878,39 +1878,39 @@
       </c>
       <c r="CO4" t="inlineStr"/>
       <c r="CP4" t="n">
-        <v>-4.672619431606805</v>
+        <v>-17113749.79414442</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.058702847841261</v>
+        <v>-7.690118101415266</v>
       </c>
       <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
+      <c r="CS4" t="n">
+        <v>-1.647580149082714</v>
+      </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="n">
-        <v>-17113749.79414442</v>
-      </c>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="n">
-        <v>-1.647580149082714</v>
-      </c>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="n">
+        <v>-49423.54103874246</v>
+      </c>
+      <c r="CY4" t="inlineStr"/>
       <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="n">
-        <v>-7.690118101415266</v>
-      </c>
+      <c r="DA4" t="inlineStr"/>
       <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
+      <c r="DC4" t="n">
+        <v>-4.672619431606805</v>
+      </c>
       <c r="DD4" t="inlineStr"/>
       <c r="DE4" t="inlineStr"/>
-      <c r="DF4" t="inlineStr"/>
+      <c r="DF4" t="n">
+        <v>-1.084414643150257</v>
+      </c>
       <c r="DG4" t="inlineStr"/>
       <c r="DH4" t="n">
-        <v>-1.084414643150257</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>-49423.54103874246</v>
-      </c>
+        <v>3.058702847841261</v>
+      </c>
+      <c r="DI4" t="inlineStr"/>
       <c r="DJ4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -2170,55 +2170,55 @@
       <c r="CN5" t="n">
         <v>-0.3277777777777686</v>
       </c>
-      <c r="CO5" t="n">
-        <v>3.647955246913579</v>
-      </c>
+      <c r="CO5" t="inlineStr"/>
       <c r="CP5" t="n">
-        <v>1.116784813101891</v>
+        <v>-1199146.081890938</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.481331327830617</v>
+        <v>-0.2893650152164042</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="n">
+        <v>-2.219579242507194</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>3.647955246913579</v>
+      </c>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="n">
+        <v>-3595.902921754314</v>
+      </c>
+      <c r="CY5" t="n">
         <v>0.08746141975308608</v>
       </c>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="n">
+      <c r="CZ5" t="n">
         <v>-0.8259259259259295</v>
       </c>
-      <c r="CW5" t="n">
-        <v>-1199146.081890938</v>
-      </c>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="n">
-        <v>-2.219579242507194</v>
-      </c>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="n">
-        <v>-0.2893650152164042</v>
-      </c>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="n">
+        <v>-9414371.14197531</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.116784813101891</v>
+      </c>
       <c r="DD5" t="n">
-        <v>-0.884953703703701</v>
+        <v>-7563.734567901236</v>
       </c>
       <c r="DE5" t="inlineStr"/>
       <c r="DF5" t="n">
-        <v>-7563.734567901236</v>
+        <v>0.1181871075833927</v>
       </c>
       <c r="DG5" t="n">
+        <v>-0.884953703703701</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>2.481331327830617</v>
+      </c>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="n">
         <v>-3.772415123456781</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>0.1181871075833927</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-3595.902921754314</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>-9414371.14197531</v>
       </c>
     </row>
     <row r="6">
@@ -2478,39 +2478,39 @@
       <c r="CN6" t="inlineStr"/>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="n">
-        <v>0.5102070343943446</v>
+        <v>-1439063.827397806</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.49437009069365</v>
+        <v>-0.2976906793470278</v>
       </c>
       <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
+      <c r="CS6" t="n">
+        <v>-1.659219207864723</v>
+      </c>
       <c r="CT6" t="inlineStr"/>
       <c r="CU6" t="inlineStr"/>
       <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="n">
-        <v>-1439063.827397806</v>
-      </c>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="n">
-        <v>-1.659219207864723</v>
-      </c>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="n">
+        <v>5680.385381159376</v>
+      </c>
+      <c r="CY6" t="inlineStr"/>
       <c r="CZ6" t="inlineStr"/>
-      <c r="DA6" t="n">
-        <v>-0.2976906793470278</v>
-      </c>
+      <c r="DA6" t="inlineStr"/>
       <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="inlineStr"/>
+      <c r="DC6" t="n">
+        <v>0.5102070343943446</v>
+      </c>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="inlineStr"/>
-      <c r="DF6" t="inlineStr"/>
+      <c r="DF6" t="n">
+        <v>-0.2186379510295919</v>
+      </c>
       <c r="DG6" t="inlineStr"/>
       <c r="DH6" t="n">
-        <v>-0.2186379510295919</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>5680.385381159376</v>
-      </c>
+        <v>1.49437009069365</v>
+      </c>
+      <c r="DI6" t="inlineStr"/>
       <c r="DJ6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2770,55 +2770,55 @@
       <c r="CN7" t="n">
         <v>-0.8730130633255442</v>
       </c>
-      <c r="CO7" t="n">
-        <v>2.407908950617283</v>
-      </c>
+      <c r="CO7" t="inlineStr"/>
       <c r="CP7" t="n">
-        <v>4.291484368458057</v>
+        <v>19089465.20260116</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-1.289074830302894</v>
+        <v>8.137524618007063</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
+        <v>3.976846610179933</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>2.407908950617283</v>
+      </c>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="n">
+        <v>69125.44233706512</v>
+      </c>
+      <c r="CY7" t="n">
         <v>0.7887345679012343</v>
       </c>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="n">
+      <c r="CZ7" t="n">
         <v>5.129668209876556</v>
       </c>
-      <c r="CW7" t="n">
-        <v>19089465.20260116</v>
-      </c>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="n">
-        <v>3.976846610179933</v>
-      </c>
-      <c r="CZ7" t="inlineStr"/>
-      <c r="DA7" t="n">
-        <v>8.137524618007063</v>
-      </c>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="n">
+        <v>30112789.35185187</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>4.291484368458057</v>
+      </c>
       <c r="DD7" t="n">
-        <v>3.163117283950612</v>
+        <v>113549.5756172839</v>
       </c>
       <c r="DE7" t="inlineStr"/>
       <c r="DF7" t="n">
-        <v>113549.5756172839</v>
+        <v>0.5739054399142121</v>
       </c>
       <c r="DG7" t="n">
+        <v>3.163117283950612</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-1.289074830302894</v>
+      </c>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="n">
         <v>1.759490740740745</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>0.5739054399142121</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>69125.44233706512</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>30112789.35185187</v>
       </c>
     </row>
     <row r="8">
@@ -3082,55 +3082,55 @@
       <c r="CN8" t="n">
         <v>0.5701914983164897</v>
       </c>
-      <c r="CO8" t="n">
-        <v>1.94537037037037</v>
-      </c>
+      <c r="CO8" t="inlineStr"/>
       <c r="CP8" t="n">
-        <v>0.0459000913851213</v>
+        <v>-5704867.248334739</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-2.14164507997063</v>
+        <v>-2.562941550002932</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="n">
+        <v>-4.759326755688974</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1.94537037037037</v>
+      </c>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="n">
+        <v>-13008.46655408575</v>
+      </c>
+      <c r="CY8" t="n">
         <v>-0.6990740740740742</v>
       </c>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="n">
+      <c r="CZ8" t="n">
         <v>-3.82037037037037</v>
       </c>
-      <c r="CW8" t="n">
-        <v>-5704867.248334739</v>
-      </c>
-      <c r="CX8" t="inlineStr"/>
-      <c r="CY8" t="n">
-        <v>-4.759326755688974</v>
-      </c>
-      <c r="CZ8" t="inlineStr"/>
-      <c r="DA8" t="n">
-        <v>-2.562941550002932</v>
-      </c>
-      <c r="DB8" t="inlineStr"/>
-      <c r="DC8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="n">
+        <v>-13212685.18518519</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.0459000913851213</v>
+      </c>
       <c r="DD8" t="n">
-        <v>-1.592592592592609</v>
+        <v>-20278.70370370371</v>
       </c>
       <c r="DE8" t="inlineStr"/>
       <c r="DF8" t="n">
-        <v>-20278.70370370371</v>
+        <v>-0.2736331755810599</v>
       </c>
       <c r="DG8" t="n">
+        <v>-1.592592592592609</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-2.14164507997063</v>
+      </c>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="n">
         <v>-4.754629629629633</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>-0.2736331755810599</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>-13008.46655408575</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>-13212685.18518519</v>
       </c>
     </row>
     <row r="9">
@@ -3390,55 +3390,55 @@
       <c r="CN9" t="n">
         <v>-0.5433651996151951</v>
       </c>
-      <c r="CO9" t="n">
-        <v>2.801018518518521</v>
-      </c>
+      <c r="CO9" t="inlineStr"/>
       <c r="CP9" t="n">
-        <v>4.380210627579046</v>
+        <v>2492409.622541202</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-1.96512345679011</v>
+        <v>2.55234340058901</v>
       </c>
       <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="n">
+        <v>-0.637723728513194</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2.801018518518521</v>
+      </c>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="n">
+        <v>-3966.314460393405</v>
+      </c>
+      <c r="CY9" t="n">
         <v>0.349444444444444</v>
       </c>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="n">
+      <c r="CZ9" t="n">
         <v>1.60768518518519</v>
       </c>
-      <c r="CW9" t="n">
-        <v>2492409.622541202</v>
-      </c>
-      <c r="CX9" t="inlineStr"/>
-      <c r="CY9" t="n">
-        <v>-0.637723728513194</v>
-      </c>
-      <c r="CZ9" t="inlineStr"/>
-      <c r="DA9" t="n">
-        <v>2.55234340058901</v>
-      </c>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="n">
+        <v>1622462.962962964</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>4.380210627579046</v>
+      </c>
       <c r="DD9" t="n">
-        <v>-1.736111111111057</v>
+        <v>-3381.111111111113</v>
       </c>
       <c r="DE9" t="inlineStr"/>
       <c r="DF9" t="n">
-        <v>-3381.111111111113</v>
+        <v>0.4512946929613595</v>
       </c>
       <c r="DG9" t="n">
+        <v>-1.736111111111057</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-1.96512345679011</v>
+      </c>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="n">
         <v>0.02564814814813587</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>0.4512946929613595</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>-3966.314460393405</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>1622462.962962964</v>
       </c>
     </row>
     <row r="10">
@@ -3698,55 +3698,55 @@
       <c r="CN10" t="n">
         <v>-4.888631687242807</v>
       </c>
-      <c r="CO10" t="n">
-        <v>-2.392460317460316</v>
-      </c>
+      <c r="CO10" t="inlineStr"/>
       <c r="CP10" t="n">
-        <v>0.6919975250167703</v>
+        <v>-5414173.775614414</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-1.073288524291371</v>
+        <v>-2.934594366462719</v>
       </c>
       <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">
+        <v>-4.722458168056505</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-2.392460317460316</v>
+      </c>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="n">
+        <v>-13871.46429714575</v>
+      </c>
+      <c r="CY10" t="n">
         <v>-0.8269841269841272</v>
       </c>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="n">
+      <c r="CZ10" t="n">
         <v>-5.663492063492058</v>
       </c>
-      <c r="CW10" t="n">
-        <v>-5414173.775614414</v>
-      </c>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="n">
-        <v>-4.722458168056505</v>
-      </c>
-      <c r="CZ10" t="inlineStr"/>
-      <c r="DA10" t="n">
-        <v>-2.934594366462719</v>
-      </c>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="n">
+        <v>-9049047.619047619</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.6919975250167703</v>
+      </c>
       <c r="DD10" t="n">
-        <v>-3.952380952380963</v>
+        <v>-16174.60317460317</v>
       </c>
       <c r="DE10" t="inlineStr"/>
       <c r="DF10" t="n">
-        <v>-16174.60317460317</v>
+        <v>-0.4736079062300629</v>
       </c>
       <c r="DG10" t="n">
+        <v>-3.952380952380963</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-1.073288524291371</v>
+      </c>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="n">
         <v>-5.055158730158738</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>-0.4736079062300629</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>-13871.46429714575</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>-9049047.619047619</v>
       </c>
     </row>
     <row r="11">
@@ -4008,39 +4008,39 @@
       </c>
       <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="n">
-        <v>1.471171049357327</v>
+        <v>-6266816.586645018</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-1.130642097553874</v>
+        <v>-2.433486820006422</v>
       </c>
       <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
+      <c r="CS11" t="n">
+        <v>-4.007857910063791</v>
+      </c>
       <c r="CT11" t="inlineStr"/>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="n">
-        <v>-6266816.586645018</v>
-      </c>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="n">
-        <v>-4.007857910063791</v>
-      </c>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="n">
+        <v>-7351.914552404749</v>
+      </c>
+      <c r="CY11" t="inlineStr"/>
       <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="n">
-        <v>-2.433486820006422</v>
-      </c>
+      <c r="DA11" t="inlineStr"/>
       <c r="DB11" t="inlineStr"/>
-      <c r="DC11" t="inlineStr"/>
+      <c r="DC11" t="n">
+        <v>1.471171049357327</v>
+      </c>
       <c r="DD11" t="inlineStr"/>
       <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
+      <c r="DF11" t="n">
+        <v>-0.2264439264439266</v>
+      </c>
       <c r="DG11" t="inlineStr"/>
       <c r="DH11" t="n">
-        <v>-0.2264439264439266</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>-7351.914552404749</v>
-      </c>
+        <v>-1.130642097553874</v>
+      </c>
+      <c r="DI11" t="inlineStr"/>
       <c r="DJ11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4300,55 +4300,55 @@
       <c r="CN12" t="n">
         <v>0.5913825757575637</v>
       </c>
-      <c r="CO12" t="n">
-        <v>-3.985802469135802</v>
-      </c>
+      <c r="CO12" t="inlineStr"/>
       <c r="CP12" t="n">
-        <v>-2.61891662211579</v>
+        <v>2953117.619012871</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.1995080851762907</v>
+        <v>-0.3628186690235395</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="n">
+        <v>3.688827969607118</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-3.985802469135802</v>
+      </c>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="n">
+        <v>7025.922106216221</v>
+      </c>
+      <c r="CY12" t="n">
         <v>0.07191358024691352</v>
       </c>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="n">
+      <c r="CZ12" t="n">
         <v>0.8703703703703809</v>
       </c>
-      <c r="CW12" t="n">
-        <v>2953117.619012871</v>
-      </c>
-      <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="n">
-        <v>3.688827969607118</v>
-      </c>
-      <c r="CZ12" t="inlineStr"/>
-      <c r="DA12" t="n">
-        <v>-0.3628186690235395</v>
-      </c>
-      <c r="DB12" t="inlineStr"/>
-      <c r="DC12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="n">
+        <v>10354197.5308642</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-2.61891662211579</v>
+      </c>
       <c r="DD12" t="n">
-        <v>2.334259259259255</v>
+        <v>15487.34567901235</v>
       </c>
       <c r="DE12" t="inlineStr"/>
       <c r="DF12" t="n">
-        <v>15487.34567901235</v>
+        <v>-0.07474955337442468</v>
       </c>
       <c r="DG12" t="n">
+        <v>2.334259259259255</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.1995080851762907</v>
+      </c>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="n">
         <v>3.698456790123444</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>-0.07474955337442468</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>7025.922106216221</v>
-      </c>
-      <c r="DJ12" t="n">
-        <v>10354197.5308642</v>
       </c>
     </row>
     <row r="13">
@@ -4610,39 +4610,39 @@
       </c>
       <c r="CO13" t="inlineStr"/>
       <c r="CP13" t="n">
-        <v>-3.551595091068776</v>
+        <v>10430141.59492229</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.3227910815630253</v>
+        <v>-1.934553977536424</v>
       </c>
       <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
+      <c r="CS13" t="n">
+        <v>1.813127304793966</v>
+      </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="n">
-        <v>10430141.59492229</v>
-      </c>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="n">
-        <v>1.813127304793966</v>
-      </c>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="n">
+        <v>40653.82083803137</v>
+      </c>
+      <c r="CY13" t="inlineStr"/>
       <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="n">
-        <v>-1.934553977536424</v>
-      </c>
+      <c r="DA13" t="inlineStr"/>
       <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
+      <c r="DC13" t="n">
+        <v>-3.551595091068776</v>
+      </c>
       <c r="DD13" t="inlineStr"/>
       <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
+      <c r="DF13" t="n">
+        <v>0.4286036250948531</v>
+      </c>
       <c r="DG13" t="inlineStr"/>
       <c r="DH13" t="n">
-        <v>0.4286036250948531</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>40653.82083803137</v>
-      </c>
+        <v>-0.3227910815630253</v>
+      </c>
+      <c r="DI13" t="inlineStr"/>
       <c r="DJ13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4902,55 +4902,55 @@
       <c r="CN14" t="n">
         <v>1.464166666666685</v>
       </c>
-      <c r="CO14" t="n">
-        <v>1.387847222222224</v>
-      </c>
+      <c r="CO14" t="inlineStr"/>
       <c r="CP14" t="n">
-        <v>0.6547774586667785</v>
+        <v>1753673.492999878</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.2339991526862661</v>
+        <v>2.326296510507035</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
+        <v>2.936630507184887</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>1.387847222222224</v>
+      </c>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="n">
+        <v>8473.179791484748</v>
+      </c>
+      <c r="CY14" t="n">
         <v>0.5406250000000004</v>
       </c>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="inlineStr"/>
-      <c r="CV14" t="n">
+      <c r="CZ14" t="n">
         <v>2.480555555555554</v>
       </c>
-      <c r="CW14" t="n">
-        <v>1753673.492999878</v>
-      </c>
-      <c r="CX14" t="inlineStr"/>
-      <c r="CY14" t="n">
-        <v>2.936630507184887</v>
-      </c>
-      <c r="CZ14" t="inlineStr"/>
-      <c r="DA14" t="n">
-        <v>2.326296510507035</v>
-      </c>
-      <c r="DB14" t="inlineStr"/>
-      <c r="DC14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="n">
+        <v>4237673.611111111</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.6547774586667785</v>
+      </c>
       <c r="DD14" t="n">
-        <v>2.300694444444446</v>
+        <v>7601.388888888891</v>
       </c>
       <c r="DE14" t="inlineStr"/>
       <c r="DF14" t="n">
-        <v>7601.388888888891</v>
+        <v>0.3757045643268555</v>
       </c>
       <c r="DG14" t="n">
+        <v>2.300694444444446</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0.2339991526862661</v>
+      </c>
+      <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="n">
         <v>2.448958333333337</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>0.3757045643268555</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>8473.179791484748</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>4237673.611111111</v>
       </c>
     </row>
     <row r="15">
@@ -5210,39 +5210,39 @@
       <c r="CN15" t="inlineStr"/>
       <c r="CO15" t="inlineStr"/>
       <c r="CP15" t="n">
-        <v>0.8504299951903924</v>
+        <v>19752263.93366596</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-2.630428168086354</v>
+        <v>8.513256600951792</v>
       </c>
       <c r="CR15" t="inlineStr"/>
-      <c r="CS15" t="inlineStr"/>
+      <c r="CS15" t="n">
+        <v>7.917771896906032</v>
+      </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="n">
-        <v>19752263.93366596</v>
-      </c>
-      <c r="CX15" t="inlineStr"/>
-      <c r="CY15" t="n">
-        <v>7.917771896906032</v>
-      </c>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="n">
+        <v>45872.71315074351</v>
+      </c>
+      <c r="CY15" t="inlineStr"/>
       <c r="CZ15" t="inlineStr"/>
-      <c r="DA15" t="n">
-        <v>8.513256600951792</v>
-      </c>
+      <c r="DA15" t="inlineStr"/>
       <c r="DB15" t="inlineStr"/>
-      <c r="DC15" t="inlineStr"/>
+      <c r="DC15" t="n">
+        <v>0.8504299951903924</v>
+      </c>
       <c r="DD15" t="inlineStr"/>
       <c r="DE15" t="inlineStr"/>
-      <c r="DF15" t="inlineStr"/>
+      <c r="DF15" t="n">
+        <v>1.25223896673116</v>
+      </c>
       <c r="DG15" t="inlineStr"/>
       <c r="DH15" t="n">
-        <v>1.25223896673116</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>45872.71315074351</v>
-      </c>
+        <v>-2.630428168086354</v>
+      </c>
+      <c r="DI15" t="inlineStr"/>
       <c r="DJ15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -5502,55 +5502,55 @@
       <c r="CN16" t="n">
         <v>0.7606361231361092</v>
       </c>
-      <c r="CO16" t="n">
-        <v>-0.7033333333333331</v>
-      </c>
+      <c r="CO16" t="inlineStr"/>
       <c r="CP16" t="n">
-        <v>-2.778389300757723</v>
+        <v>1681289.410719234</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.022652453134896</v>
+        <v>-0.009098171159578783</v>
       </c>
       <c r="CR16" t="inlineStr"/>
       <c r="CS16" t="n">
+        <v>1.931668258641949</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0.7033333333333331</v>
+      </c>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="n">
+        <v>6744.220537422287</v>
+      </c>
+      <c r="CY16" t="n">
         <v>0.0338888888888893</v>
       </c>
-      <c r="CT16" t="inlineStr"/>
-      <c r="CU16" t="inlineStr"/>
-      <c r="CV16" t="n">
+      <c r="CZ16" t="n">
         <v>1.973333333333329</v>
       </c>
-      <c r="CW16" t="n">
-        <v>1681289.410719234</v>
-      </c>
-      <c r="CX16" t="inlineStr"/>
-      <c r="CY16" t="n">
-        <v>1.931668258641949</v>
-      </c>
-      <c r="CZ16" t="inlineStr"/>
-      <c r="DA16" t="n">
-        <v>-0.009098171159578783</v>
-      </c>
-      <c r="DB16" t="inlineStr"/>
-      <c r="DC16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="n">
+        <v>5572722.222222222</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>-2.778389300757723</v>
+      </c>
       <c r="DD16" t="n">
-        <v>4.199999999999932</v>
+        <v>11267.22222222222</v>
       </c>
       <c r="DE16" t="inlineStr"/>
       <c r="DF16" t="n">
-        <v>11267.22222222222</v>
+        <v>-0.2502100725784935</v>
       </c>
       <c r="DG16" t="n">
+        <v>4.199999999999932</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>3.022652453134896</v>
+      </c>
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="n">
         <v>2.118333333333339</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>-0.2502100725784935</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>6744.220537422287</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>5572722.222222222</v>
       </c>
     </row>
     <row r="17">
@@ -5814,55 +5814,55 @@
       <c r="CN17" t="n">
         <v>0.9934615384615313</v>
       </c>
-      <c r="CO17" t="n">
-        <v>0.1389660493827165</v>
-      </c>
+      <c r="CO17" t="inlineStr"/>
       <c r="CP17" t="n">
-        <v>0.7249942165963787</v>
+        <v>-33531301.24571946</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.275136376065177</v>
+        <v>-8.595267410321583</v>
       </c>
       <c r="CR17" t="inlineStr"/>
       <c r="CS17" t="n">
+        <v>-9.433452374938426</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0.1389660493827165</v>
+      </c>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="n">
+        <v>-114587.4908406771</v>
+      </c>
+      <c r="CY17" t="n">
         <v>-2.161998456790124</v>
       </c>
-      <c r="CT17" t="inlineStr"/>
-      <c r="CU17" t="inlineStr"/>
-      <c r="CV17" t="n">
+      <c r="CZ17" t="n">
         <v>-12.44564043209877</v>
       </c>
-      <c r="CW17" t="n">
-        <v>-33531301.24571946</v>
-      </c>
-      <c r="CX17" t="inlineStr"/>
-      <c r="CY17" t="n">
-        <v>-9.433452374938426</v>
-      </c>
-      <c r="CZ17" t="inlineStr"/>
-      <c r="DA17" t="n">
-        <v>-8.595267410321583</v>
-      </c>
-      <c r="DB17" t="inlineStr"/>
-      <c r="DC17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="n">
+        <v>-63086530.67129631</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0.7249942165963787</v>
+      </c>
       <c r="DD17" t="n">
-        <v>-2.086728395061726</v>
+        <v>-208270.0617283951</v>
       </c>
       <c r="DE17" t="inlineStr"/>
       <c r="DF17" t="n">
-        <v>-208270.0617283951</v>
+        <v>-0.9625206077605462</v>
       </c>
       <c r="DG17" t="n">
+        <v>-2.086728395061726</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-0.275136376065177</v>
+      </c>
+      <c r="DI17" t="inlineStr"/>
+      <c r="DJ17" t="n">
         <v>-11.09282407407407</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>-0.9625206077605462</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>-114587.4908406771</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>-63086530.67129631</v>
       </c>
     </row>
     <row r="18">
@@ -6122,55 +6122,55 @@
       <c r="CN18" t="n">
         <v>-1.217824074074073</v>
       </c>
-      <c r="CO18" t="n">
-        <v>-0.4953703703703702</v>
-      </c>
+      <c r="CO18" t="inlineStr"/>
       <c r="CP18" t="n">
-        <v>2.74826816248385</v>
+        <v>-441157.7257165518</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-1.021197031000952</v>
+        <v>3.736258712239106</v>
       </c>
       <c r="CR18" t="inlineStr"/>
       <c r="CS18" t="n">
+        <v>1.462250893623434</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-0.4953703703703702</v>
+      </c>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="n">
+        <v>4224.358194456236</v>
+      </c>
+      <c r="CY18" t="n">
         <v>-0.2092592592592593</v>
       </c>
-      <c r="CT18" t="inlineStr"/>
-      <c r="CU18" t="inlineStr"/>
-      <c r="CV18" t="n">
+      <c r="CZ18" t="n">
         <v>0.7981481481481438</v>
       </c>
-      <c r="CW18" t="n">
-        <v>-441157.7257165518</v>
-      </c>
-      <c r="CX18" t="inlineStr"/>
-      <c r="CY18" t="n">
-        <v>1.462250893623434</v>
-      </c>
-      <c r="CZ18" t="inlineStr"/>
-      <c r="DA18" t="n">
-        <v>3.736258712239106</v>
-      </c>
-      <c r="DB18" t="inlineStr"/>
-      <c r="DC18" t="inlineStr"/>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="n">
+        <v>-1702314.814814817</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>2.74826816248385</v>
+      </c>
       <c r="DD18" t="n">
-        <v>0.6537037037036839</v>
+        <v>759.25925925927</v>
       </c>
       <c r="DE18" t="inlineStr"/>
       <c r="DF18" t="n">
-        <v>759.25925925927</v>
+        <v>-0.1715608465608467</v>
       </c>
       <c r="DG18" t="n">
+        <v>0.6537037037036839</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-1.021197031000952</v>
+      </c>
+      <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="n">
         <v>0.6157407407407476</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>-0.1715608465608467</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>4224.358194456236</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>-1702314.814814817</v>
       </c>
     </row>
     <row r="19">
@@ -6432,39 +6432,39 @@
       </c>
       <c r="CO19" t="inlineStr"/>
       <c r="CP19" t="n">
-        <v>3.790089594680346</v>
+        <v>-218569.471258373</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-3.498662517751114</v>
+        <v>1.3635919956305</v>
       </c>
       <c r="CR19" t="inlineStr"/>
-      <c r="CS19" t="inlineStr"/>
+      <c r="CS19" t="n">
+        <v>-3.618805394811559</v>
+      </c>
       <c r="CT19" t="inlineStr"/>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="inlineStr"/>
-      <c r="CW19" t="n">
-        <v>-218569.471258373</v>
-      </c>
-      <c r="CX19" t="inlineStr"/>
-      <c r="CY19" t="n">
-        <v>-3.618805394811559</v>
-      </c>
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="n">
+        <v>3918.015323026935</v>
+      </c>
+      <c r="CY19" t="inlineStr"/>
       <c r="CZ19" t="inlineStr"/>
-      <c r="DA19" t="n">
-        <v>1.3635919956305</v>
-      </c>
+      <c r="DA19" t="inlineStr"/>
       <c r="DB19" t="inlineStr"/>
-      <c r="DC19" t="inlineStr"/>
+      <c r="DC19" t="n">
+        <v>3.790089594680346</v>
+      </c>
       <c r="DD19" t="inlineStr"/>
       <c r="DE19" t="inlineStr"/>
-      <c r="DF19" t="inlineStr"/>
+      <c r="DF19" t="n">
+        <v>-0.07125538111412721</v>
+      </c>
       <c r="DG19" t="inlineStr"/>
       <c r="DH19" t="n">
-        <v>-0.07125538111412721</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>3918.015323026935</v>
-      </c>
+        <v>-3.498662517751114</v>
+      </c>
+      <c r="DI19" t="inlineStr"/>
       <c r="DJ19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -6724,55 +6724,55 @@
       <c r="CN20" t="n">
         <v>2.047569444444449</v>
       </c>
-      <c r="CO20" t="n">
-        <v>0.2441287878787826</v>
-      </c>
+      <c r="CO20" t="inlineStr"/>
       <c r="CP20" t="n">
-        <v>0.3904297466474951</v>
+        <v>11633390.99789338</v>
       </c>
       <c r="CQ20" t="n">
-        <v>2.037654192356229</v>
+        <v>4.512422223912807</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="n">
+        <v>4.191945282386456</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>0.2441287878787826</v>
+      </c>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr"/>
+      <c r="CW20" t="inlineStr"/>
+      <c r="CX20" t="n">
+        <v>11226.19686051059</v>
+      </c>
+      <c r="CY20" t="n">
         <v>0.8519886363636364</v>
       </c>
-      <c r="CT20" t="inlineStr"/>
-      <c r="CU20" t="inlineStr"/>
-      <c r="CV20" t="n">
+      <c r="CZ20" t="n">
         <v>5.565625000000011</v>
       </c>
-      <c r="CW20" t="n">
-        <v>11633390.99789338</v>
-      </c>
-      <c r="CX20" t="inlineStr"/>
-      <c r="CY20" t="n">
-        <v>4.191945282386456</v>
-      </c>
-      <c r="CZ20" t="inlineStr"/>
-      <c r="DA20" t="n">
-        <v>4.512422223912807</v>
-      </c>
-      <c r="DB20" t="inlineStr"/>
-      <c r="DC20" t="inlineStr"/>
+      <c r="DA20" t="inlineStr"/>
+      <c r="DB20" t="n">
+        <v>18140618.68686868</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>0.3904297466474951</v>
+      </c>
       <c r="DD20" t="n">
-        <v>1.107733585858625</v>
+        <v>11488.5101010101</v>
       </c>
       <c r="DE20" t="inlineStr"/>
       <c r="DF20" t="n">
-        <v>11488.5101010101</v>
+        <v>0.4484186876504985</v>
       </c>
       <c r="DG20" t="n">
+        <v>1.107733585858625</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>2.037654192356229</v>
+      </c>
+      <c r="DI20" t="inlineStr"/>
+      <c r="DJ20" t="n">
         <v>5.29406565656565</v>
-      </c>
-      <c r="DH20" t="n">
-        <v>0.4484186876504985</v>
-      </c>
-      <c r="DI20" t="n">
-        <v>11226.19686051059</v>
-      </c>
-      <c r="DJ20" t="n">
-        <v>18140618.68686868</v>
       </c>
     </row>
     <row r="21">
@@ -7032,55 +7032,55 @@
       <c r="CN21" t="n">
         <v>5.19629629629631</v>
       </c>
-      <c r="CO21" t="n">
-        <v>-0.9802248677248713</v>
-      </c>
+      <c r="CO21" t="inlineStr"/>
       <c r="CP21" t="n">
-        <v>-1.739517367479852</v>
+        <v>1653843.747694086</v>
       </c>
       <c r="CQ21" t="n">
-        <v>0.5327468945340286</v>
+        <v>0.9028032473650995</v>
       </c>
       <c r="CR21" t="inlineStr"/>
       <c r="CS21" t="n">
+        <v>2.269765611597165</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>-0.9802248677248713</v>
+      </c>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="inlineStr"/>
+      <c r="CX21" t="n">
+        <v>6049.244261419513</v>
+      </c>
+      <c r="CY21" t="n">
         <v>-0.006349206349206105</v>
       </c>
-      <c r="CT21" t="inlineStr"/>
-      <c r="CU21" t="inlineStr"/>
-      <c r="CV21" t="n">
+      <c r="CZ21" t="n">
         <v>0.7074735449735385</v>
       </c>
-      <c r="CW21" t="n">
-        <v>1653843.747694086</v>
-      </c>
-      <c r="CX21" t="inlineStr"/>
-      <c r="CY21" t="n">
-        <v>2.269765611597165</v>
-      </c>
-      <c r="CZ21" t="inlineStr"/>
-      <c r="DA21" t="n">
-        <v>0.9028032473650995</v>
-      </c>
-      <c r="DB21" t="inlineStr"/>
-      <c r="DC21" t="inlineStr"/>
+      <c r="DA21" t="inlineStr"/>
+      <c r="DB21" t="n">
+        <v>1176362.433862434</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>-1.739517367479852</v>
+      </c>
       <c r="DD21" t="n">
-        <v>1.938492063492077</v>
+        <v>2813.492063492064</v>
       </c>
       <c r="DE21" t="inlineStr"/>
       <c r="DF21" t="n">
-        <v>2813.492063492064</v>
+        <v>0.001810189747103896</v>
       </c>
       <c r="DG21" t="n">
+        <v>1.938492063492077</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>0.5327468945340286</v>
+      </c>
+      <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="n">
         <v>1.636177248677257</v>
-      </c>
-      <c r="DH21" t="n">
-        <v>0.001810189747103896</v>
-      </c>
-      <c r="DI21" t="n">
-        <v>6049.244261419513</v>
-      </c>
-      <c r="DJ21" t="n">
-        <v>1176362.433862434</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -890,112 +890,112 @@
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
@@ -1256,55 +1256,71 @@
       <c r="CN2" t="n">
         <v>1.952127525252536</v>
       </c>
-      <c r="CO2" t="inlineStr"/>
+      <c r="CO2" t="n">
+        <v>-5.775231481481484</v>
+      </c>
       <c r="CP2" t="n">
+        <v>-2630.17676767677</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-72555.55555555556</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-121.9444444444445</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-5.347222222222222</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>-3.771759259259259</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>-1.394177128245744</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>-98876388.8888889</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-117.1805555555555</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.9811553030302775</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-1.464007722631322</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.7150932275642106</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.1923839816157924</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-3.124621212121212</v>
+      </c>
+      <c r="DC2" t="n">
         <v>-6027509.463850085</v>
       </c>
-      <c r="CQ2" t="n">
-        <v>-0.7150932275642106</v>
-      </c>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="n">
-        <v>-1.394177128245744</v>
-      </c>
-      <c r="CT2" t="n">
+      <c r="DD2" t="n">
+        <v>-0.4269886363636364</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-2.065625000000011</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-1.291666666666667</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.1217169144542751</v>
+      </c>
+      <c r="DH2" t="n">
         <v>1.050315656565658</v>
       </c>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="n">
+      <c r="DI2" t="n">
         <v>-2550.131150621353</v>
       </c>
-      <c r="CY2" t="n">
-        <v>-0.4269886363636364</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>-2.065625000000011</v>
-      </c>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="n">
+      <c r="DJ2" t="n">
         <v>-11240340.90909091</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.1217169144542751</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-2630.17676767677</v>
-      </c>
-      <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="n">
-        <v>-0.1923839816157924</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.9811553030302775</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-1.464007722631322</v>
-      </c>
-      <c r="DI2" t="inlineStr"/>
-      <c r="DJ2" t="n">
-        <v>-3.124621212121212</v>
       </c>
     </row>
     <row r="3">
@@ -1564,55 +1580,71 @@
       <c r="CN3" t="n">
         <v>0.964877946127956</v>
       </c>
-      <c r="CO3" t="inlineStr"/>
+      <c r="CO3" t="n">
+        <v>3.111111111111086</v>
+      </c>
       <c r="CP3" t="n">
-        <v>4594889.493318287</v>
+        <v>8351.587301587297</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-1.491784968461957</v>
-      </c>
-      <c r="CR3" t="inlineStr"/>
+        <v>62500</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>111.75</v>
+      </c>
       <c r="CS3" t="n">
-        <v>1.491166213005727</v>
+        <v>3.055555555555555</v>
       </c>
       <c r="CT3" t="n">
+        <v>-1.532407407407405</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.665055918179306</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>38430555.55555555</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>124.7083333333333</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>-1.751587301587278</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>2.802389667698606</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>-1.414517862789282</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>0.3977438498965202</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>2.061507936507923</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>4833053.156781873</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>0.890873015873016</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>2.126190476190487</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>1.388888888888889</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>-2.794065154449569</v>
+      </c>
+      <c r="DH3" t="n">
         <v>-0.2698412698412689</v>
       </c>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="n">
-        <v>2010.029349257933</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>0.890873015873016</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>2.126190476190487</v>
-      </c>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="n">
+      <c r="DI3" t="n">
+        <v>2225.568879566232</v>
+      </c>
+      <c r="DJ3" t="n">
         <v>11127380.95238096</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>-2.704222192973482</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>8351.587301587297</v>
-      </c>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="n">
-        <v>0.4084363306112533</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>-1.751587301587278</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>3.105038891468183</v>
-      </c>
-      <c r="DI3" t="inlineStr"/>
-      <c r="DJ3" t="n">
-        <v>2.061507936507923</v>
       </c>
     </row>
     <row r="4">
@@ -1876,41 +1908,57 @@
       <c r="CN4" t="n">
         <v>0.1260804473304518</v>
       </c>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="n">
-        <v>-17113749.79414442</v>
-      </c>
+      <c r="CO4" t="n">
+        <v>3.762499999999989</v>
+      </c>
+      <c r="CP4" t="inlineStr"/>
       <c r="CQ4" t="n">
+        <v>5875</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>149.875</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>3.149999999999999</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-1.647580149082714</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>10031250</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>152.375</v>
+      </c>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="n">
+        <v>3.058702847841261</v>
+      </c>
+      <c r="CZ4" t="n">
         <v>-7.690118101415266</v>
       </c>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="n">
-        <v>-1.647580149082714</v>
-      </c>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="n">
-        <v>-49423.54103874246</v>
-      </c>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
+      <c r="DA4" t="n">
+        <v>-1.084414643150257</v>
+      </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
-        <v>-4.672619431606805</v>
+        <v>-17113749.79414442</v>
       </c>
       <c r="DD4" t="inlineStr"/>
       <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="n">
-        <v>-1.084414643150257</v>
-      </c>
-      <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="n">
-        <v>3.058702847841261</v>
-      </c>
-      <c r="DI4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-4.672619431606805</v>
+      </c>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="n">
+        <v>-49423.54103874246</v>
+      </c>
       <c r="DJ4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -2168,57 +2216,73 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.3277777777777686</v>
-      </c>
-      <c r="CO5" t="inlineStr"/>
+        <v>-0.3270833333333343</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.2083333333333144</v>
+      </c>
       <c r="CP5" t="n">
+        <v>-7563.734567901236</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-115222.2222222222</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-158.7777777777778</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-1.009259259259263</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-2.219579242507194</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-43577777.77777778</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-155.7222222222222</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.884953703703701</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>2.481331327830617</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>-0.2893650152164042</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0.1181871075833927</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-3.772415123456781</v>
+      </c>
+      <c r="DC5" t="n">
         <v>-1199146.081890938</v>
       </c>
-      <c r="CQ5" t="n">
-        <v>-0.2893650152164042</v>
-      </c>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="n">
-        <v>-2.219579242507194</v>
-      </c>
-      <c r="CT5" t="n">
+      <c r="DD5" t="n">
+        <v>0.08746141975308608</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.8259259259259295</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-1.777777777777778</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.116784813101891</v>
+      </c>
+      <c r="DH5" t="n">
         <v>3.647955246913579</v>
       </c>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="n">
+      <c r="DI5" t="n">
         <v>-3595.902921754314</v>
       </c>
-      <c r="CY5" t="n">
-        <v>0.08746141975308608</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>-0.8259259259259295</v>
-      </c>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="n">
+      <c r="DJ5" t="n">
         <v>-9414371.14197531</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>1.116784813101891</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>-7563.734567901236</v>
-      </c>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="n">
-        <v>0.1181871075833927</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.884953703703701</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>2.481331327830617</v>
-      </c>
-      <c r="DI5" t="inlineStr"/>
-      <c r="DJ5" t="n">
-        <v>-3.772415123456781</v>
       </c>
     </row>
     <row r="6">
@@ -2476,41 +2540,57 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="n">
-        <v>-1439063.827397806</v>
-      </c>
+      <c r="CO6" t="n">
+        <v>1.504166666666663</v>
+      </c>
+      <c r="CP6" t="inlineStr"/>
       <c r="CQ6" t="n">
-        <v>-0.2976906793470278</v>
-      </c>
-      <c r="CR6" t="inlineStr"/>
+        <v>-30425</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-119.65</v>
+      </c>
       <c r="CS6" t="n">
-        <v>-1.659219207864723</v>
-      </c>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="n">
-        <v>5680.385381159376</v>
-      </c>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="inlineStr"/>
-      <c r="DA6" t="inlineStr"/>
+        <v>-1.775</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-3.581249999999997</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-1.863562168288382</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-8748750</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-112.35</v>
+      </c>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="n">
+        <v>1.280816701680692</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.6552691471325431</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>-0.2328558067964026</v>
+      </c>
       <c r="DB6" t="inlineStr"/>
       <c r="DC6" t="n">
-        <v>0.5102070343943446</v>
+        <v>-1713898.728899455</v>
       </c>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="inlineStr"/>
       <c r="DF6" t="n">
-        <v>-0.2186379510295919</v>
-      </c>
-      <c r="DG6" t="inlineStr"/>
-      <c r="DH6" t="n">
-        <v>1.49437009069365</v>
-      </c>
-      <c r="DI6" t="inlineStr"/>
+        <v>-1.525</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.3690003962111206</v>
+      </c>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="n">
+        <v>5129.069917440662</v>
+      </c>
       <c r="DJ6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2768,57 +2848,73 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.8730130633255442</v>
-      </c>
-      <c r="CO7" t="inlineStr"/>
+        <v>-0.9012620712620532</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0.04259259259259807</v>
+      </c>
       <c r="CP7" t="n">
+        <v>113549.5756172839</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-115583.3333333333</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-145.4305555555555</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-5.819444444444445</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>-1.596296296296295</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>3.976846610179933</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>-45188888.8888889</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-150.9444444444445</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>3.163117283950612</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-1.289074830302894</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>8.137524618007063</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.5739054399142121</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.759490740740745</v>
+      </c>
+      <c r="DC7" t="n">
         <v>19089465.20260116</v>
       </c>
-      <c r="CQ7" t="n">
-        <v>8.137524618007063</v>
-      </c>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="n">
-        <v>3.976846610179933</v>
-      </c>
-      <c r="CT7" t="n">
+      <c r="DD7" t="n">
+        <v>0.7887345679012343</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>5.129668209876556</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-1.777777777777778</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>4.291484368458057</v>
+      </c>
+      <c r="DH7" t="n">
         <v>2.407908950617283</v>
       </c>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="n">
+      <c r="DI7" t="n">
         <v>69125.44233706512</v>
       </c>
-      <c r="CY7" t="n">
-        <v>0.7887345679012343</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>5.129668209876556</v>
-      </c>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="n">
+      <c r="DJ7" t="n">
         <v>30112789.35185187</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>4.291484368458057</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>113549.5756172839</v>
-      </c>
-      <c r="DE7" t="inlineStr"/>
-      <c r="DF7" t="n">
-        <v>0.5739054399142121</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>3.163117283950612</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>-1.289074830302894</v>
-      </c>
-      <c r="DI7" t="inlineStr"/>
-      <c r="DJ7" t="n">
-        <v>1.759490740740745</v>
       </c>
     </row>
     <row r="8">
@@ -3082,55 +3178,71 @@
       <c r="CN8" t="n">
         <v>0.5701914983164897</v>
       </c>
-      <c r="CO8" t="inlineStr"/>
+      <c r="CO8" t="n">
+        <v>1.3125</v>
+      </c>
       <c r="CP8" t="n">
-        <v>-5704867.248334739</v>
+        <v>-20128.70370370371</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-2.562941550002932</v>
-      </c>
-      <c r="CR8" t="inlineStr"/>
+        <v>-4625</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-17.25</v>
+      </c>
       <c r="CS8" t="n">
-        <v>-4.759326755688974</v>
+        <v>-0.375</v>
       </c>
       <c r="CT8" t="n">
-        <v>1.94537037037037</v>
-      </c>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
+        <v>6.020833333333336</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>-4.753563010132282</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>237500</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-43</v>
+      </c>
       <c r="CX8" t="n">
-        <v>-13008.46655408575</v>
+        <v>-1.655092592592609</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0.6990740740740742</v>
+        <v>-2.069260474325262</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-3.82037037037037</v>
-      </c>
-      <c r="DA8" t="inlineStr"/>
+        <v>-2.599134778512664</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>-0.2685157984645212</v>
+      </c>
       <c r="DB8" t="n">
-        <v>-13212685.18518519</v>
+        <v>-4.910879629629633</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0459000913851213</v>
+        <v>-5667768.435125245</v>
       </c>
       <c r="DD8" t="n">
-        <v>-20278.70370370371</v>
-      </c>
-      <c r="DE8" t="inlineStr"/>
+        <v>-0.6865740740740742</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>-3.826620370370364</v>
+      </c>
       <c r="DF8" t="n">
-        <v>-0.2736331755810599</v>
+        <v>-0.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>-1.592592592592609</v>
+        <v>0.06267258498295192</v>
       </c>
       <c r="DH8" t="n">
-        <v>-2.14164507997063</v>
-      </c>
-      <c r="DI8" t="inlineStr"/>
+        <v>2.02662037037037</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-13014.43791631485</v>
+      </c>
       <c r="DJ8" t="n">
-        <v>-4.754629629629633</v>
+        <v>-13303935.18518519</v>
       </c>
     </row>
     <row r="9">
@@ -3390,55 +3502,71 @@
       <c r="CN9" t="n">
         <v>-0.5433651996151951</v>
       </c>
-      <c r="CO9" t="inlineStr"/>
+      <c r="CO9" t="n">
+        <v>-1.712962962962962</v>
+      </c>
       <c r="CP9" t="n">
-        <v>2492409.622541202</v>
+        <v>-2858.888888888891</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.55234340058901</v>
-      </c>
-      <c r="CR9" t="inlineStr"/>
+        <v>14833.33333333333</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>69.22222222222223</v>
+      </c>
       <c r="CS9" t="n">
-        <v>-0.637723728513194</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.801018518518521</v>
-      </c>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
+        <v>-1.138888888888889</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0.7871972123068502</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>6044444.444444444</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>79.22222222222223</v>
+      </c>
       <c r="CX9" t="n">
-        <v>-3966.314460393405</v>
+        <v>-2.258333333333297</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.349444444444444</v>
+        <v>-1.898602408799746</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.60768518518519</v>
-      </c>
-      <c r="DA9" t="inlineStr"/>
+        <v>2.383246415702544</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.4444259322548796</v>
+      </c>
       <c r="DB9" t="n">
-        <v>1622462.962962964</v>
+        <v>0.1594444444444321</v>
       </c>
       <c r="DC9" t="n">
-        <v>4.380210627579046</v>
+        <v>2319363.53931968</v>
       </c>
       <c r="DD9" t="n">
-        <v>-3381.111111111113</v>
-      </c>
-      <c r="DE9" t="inlineStr"/>
+        <v>0.3411111111111107</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1.673888888888882</v>
+      </c>
       <c r="DF9" t="n">
-        <v>0.4512946929613595</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="DG9" t="n">
-        <v>-1.736111111111057</v>
+        <v>4.416525478257931</v>
       </c>
       <c r="DH9" t="n">
-        <v>-1.96512345679011</v>
-      </c>
-      <c r="DI9" t="inlineStr"/>
+        <v>2.700555555555557</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-4123.889743297637</v>
+      </c>
       <c r="DJ9" t="n">
-        <v>0.02564814814813587</v>
+        <v>1674500</v>
       </c>
     </row>
     <row r="10">
@@ -3696,57 +3824,73 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="CN10" t="n">
-        <v>-4.888631687242807</v>
-      </c>
-      <c r="CO10" t="inlineStr"/>
+        <v>-4.89598765432099</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-5.508101851851876</v>
+      </c>
       <c r="CP10" t="n">
+        <v>-16174.60317460317</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-125513.8888888889</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-161.9444444444445</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-3.847222222222222</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.2673611111111072</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-4.722458168056505</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-62220833.33333334</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-163.9583333333333</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-3.952380952380963</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-1.073288524291371</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-2.934594366462719</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-0.4736079062300629</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-5.055158730158738</v>
+      </c>
+      <c r="DC10" t="n">
         <v>-5414173.775614414</v>
       </c>
-      <c r="CQ10" t="n">
-        <v>-2.934594366462719</v>
-      </c>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="n">
-        <v>-4.722458168056505</v>
-      </c>
-      <c r="CT10" t="n">
+      <c r="DD10" t="n">
+        <v>-0.8269841269841272</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-5.663492063492058</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-1.847222222222222</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.6919975250167703</v>
+      </c>
+      <c r="DH10" t="n">
         <v>-2.392460317460316</v>
       </c>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="n">
+      <c r="DI10" t="n">
         <v>-13871.46429714575</v>
       </c>
-      <c r="CY10" t="n">
-        <v>-0.8269841269841272</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>-5.663492063492058</v>
-      </c>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="n">
+      <c r="DJ10" t="n">
         <v>-9049047.619047619</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>0.6919975250167703</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>-16174.60317460317</v>
-      </c>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="n">
-        <v>-0.4736079062300629</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>-3.952380952380963</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>-1.073288524291371</v>
-      </c>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="n">
-        <v>-5.055158730158738</v>
       </c>
     </row>
     <row r="11">
@@ -4006,41 +4150,57 @@
       <c r="CN11" t="n">
         <v>-0.5590926001082295</v>
       </c>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="n">
-        <v>-6266816.586645018</v>
-      </c>
+      <c r="CO11" t="n">
+        <v>-4.655092592592581</v>
+      </c>
+      <c r="CP11" t="inlineStr"/>
       <c r="CQ11" t="n">
-        <v>-2.433486820006422</v>
-      </c>
-      <c r="CR11" t="inlineStr"/>
+        <v>-11138.88888888889</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>17.81944444444444</v>
+      </c>
       <c r="CS11" t="n">
-        <v>-4.007857910063791</v>
-      </c>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
-      <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="n">
-        <v>-7351.914552404749</v>
-      </c>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="inlineStr"/>
+        <v>-0.4444444444444444</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.9351851851851869</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-3.916607609438486</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-13097222.22222222</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>16.05555555555556</v>
+      </c>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="n">
+        <v>-1.038962943374713</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-2.5625091865288</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.2339160839160841</v>
+      </c>
       <c r="DB11" t="inlineStr"/>
       <c r="DC11" t="n">
-        <v>1.471171049357327</v>
+        <v>-6134159.035862468</v>
       </c>
       <c r="DD11" t="inlineStr"/>
       <c r="DE11" t="inlineStr"/>
       <c r="DF11" t="n">
-        <v>-0.2264439264439266</v>
-      </c>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="n">
-        <v>-1.130642097553874</v>
-      </c>
-      <c r="DI11" t="inlineStr"/>
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>1.366848982535259</v>
+      </c>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="n">
+        <v>-7578.270603760797</v>
+      </c>
       <c r="DJ11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4300,55 +4460,71 @@
       <c r="CN12" t="n">
         <v>0.5913825757575637</v>
       </c>
-      <c r="CO12" t="inlineStr"/>
+      <c r="CO12" t="n">
+        <v>0.3333333333333144</v>
+      </c>
       <c r="CP12" t="n">
-        <v>2953117.619012871</v>
+        <v>15337.34567901235</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.3628186690235395</v>
-      </c>
-      <c r="CR12" t="inlineStr"/>
+        <v>97972.22222222222</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>114.7777777777778</v>
+      </c>
       <c r="CS12" t="n">
-        <v>3.688827969607118</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="CT12" t="n">
-        <v>-3.985802469135802</v>
-      </c>
-      <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr"/>
-      <c r="CW12" t="inlineStr"/>
+        <v>-0.5949074074074048</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>3.683064224050426</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>38711111.11111111</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>115.5972222222222</v>
+      </c>
       <c r="CX12" t="n">
-        <v>7025.922106216221</v>
+        <v>2.396759259259255</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.07191358024691352</v>
+        <v>0.1271234795309226</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.8703703703703809</v>
-      </c>
-      <c r="DA12" t="inlineStr"/>
+        <v>-0.3266254405138085</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>-0.07986693049096338</v>
+      </c>
       <c r="DB12" t="n">
-        <v>10354197.5308642</v>
+        <v>3.854706790123444</v>
       </c>
       <c r="DC12" t="n">
-        <v>-2.61891662211579</v>
+        <v>2916018.805803376</v>
       </c>
       <c r="DD12" t="n">
-        <v>15487.34567901235</v>
-      </c>
-      <c r="DE12" t="inlineStr"/>
+        <v>0.05941358024691357</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.8766203703703752</v>
+      </c>
       <c r="DF12" t="n">
-        <v>-0.07474955337442468</v>
+        <v>1.402777777777778</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.334259259259255</v>
+        <v>-2.635689115713621</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1995080851762907</v>
-      </c>
-      <c r="DI12" t="inlineStr"/>
+        <v>-4.067052469135803</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>7031.893468445323</v>
+      </c>
       <c r="DJ12" t="n">
-        <v>3.698456790123444</v>
+        <v>10445447.5308642</v>
       </c>
     </row>
     <row r="13">
@@ -4608,41 +4784,57 @@
       <c r="CN13" t="n">
         <v>-0.4925602175602108</v>
       </c>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="n">
-        <v>10430141.59492229</v>
-      </c>
+      <c r="CO13" t="n">
+        <v>-4.445833333333326</v>
+      </c>
+      <c r="CP13" t="inlineStr"/>
       <c r="CQ13" t="n">
-        <v>-1.934553977536424</v>
-      </c>
-      <c r="CR13" t="inlineStr"/>
+        <v>492000</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>234.25</v>
+      </c>
       <c r="CS13" t="n">
-        <v>1.813127304793966</v>
-      </c>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="n">
-        <v>40653.82083803137</v>
-      </c>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
+        <v>11.375</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-2.533333333333335</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.90437760541927</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>202825000</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>249</v>
+      </c>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="n">
+        <v>-0.2311119273838642</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-2.063576344058802</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.4211314676226956</v>
+      </c>
       <c r="DB13" t="inlineStr"/>
       <c r="DC13" t="n">
-        <v>-3.551595091068776</v>
+        <v>10562799.14570484</v>
       </c>
       <c r="DD13" t="inlineStr"/>
       <c r="DE13" t="inlineStr"/>
       <c r="DF13" t="n">
-        <v>0.4286036250948531</v>
-      </c>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="n">
-        <v>-0.3227910815630253</v>
-      </c>
-      <c r="DI13" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-3.655917157890844</v>
+      </c>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="n">
+        <v>40427.46478667533</v>
+      </c>
       <c r="DJ13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4902,55 +5094,71 @@
       <c r="CN14" t="n">
         <v>1.464166666666685</v>
       </c>
-      <c r="CO14" t="inlineStr"/>
+      <c r="CO14" t="n">
+        <v>1.947916666666686</v>
+      </c>
       <c r="CP14" t="n">
+        <v>7601.388888888891</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>123625</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>3.291666666666667</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>2.093750000000004</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>2.936630507184887</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>55229166.66666666</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>147.125</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>2.300694444444446</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>-0.2339991526862661</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.326296510507035</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.3757045643268555</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>2.448958333333337</v>
+      </c>
+      <c r="DC14" t="n">
         <v>1753673.492999878</v>
       </c>
-      <c r="CQ14" t="n">
-        <v>2.326296510507035</v>
-      </c>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="n">
-        <v>2.936630507184887</v>
-      </c>
-      <c r="CT14" t="n">
+      <c r="DD14" t="n">
+        <v>0.5406250000000004</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>2.480555555555554</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.6547774586667785</v>
+      </c>
+      <c r="DH14" t="n">
         <v>1.387847222222224</v>
       </c>
-      <c r="CU14" t="inlineStr"/>
-      <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr"/>
-      <c r="CX14" t="n">
+      <c r="DI14" t="n">
         <v>8473.179791484748</v>
       </c>
-      <c r="CY14" t="n">
-        <v>0.5406250000000004</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.480555555555554</v>
-      </c>
-      <c r="DA14" t="inlineStr"/>
-      <c r="DB14" t="n">
+      <c r="DJ14" t="n">
         <v>4237673.611111111</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>0.6547774586667785</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>7601.388888888891</v>
-      </c>
-      <c r="DE14" t="inlineStr"/>
-      <c r="DF14" t="n">
-        <v>0.3757045643268555</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>2.300694444444446</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>-0.2339991526862661</v>
-      </c>
-      <c r="DI14" t="inlineStr"/>
-      <c r="DJ14" t="n">
-        <v>2.448958333333337</v>
       </c>
     </row>
     <row r="15">
@@ -5208,41 +5416,57 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="CN15" t="inlineStr"/>
-      <c r="CO15" t="inlineStr"/>
-      <c r="CP15" t="n">
-        <v>19752263.93366596</v>
-      </c>
+      <c r="CO15" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="CP15" t="inlineStr"/>
       <c r="CQ15" t="n">
-        <v>8.513256600951792</v>
-      </c>
-      <c r="CR15" t="inlineStr"/>
+        <v>87300</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>59.15000000000001</v>
+      </c>
       <c r="CS15" t="n">
-        <v>7.917771896906032</v>
-      </c>
-      <c r="CT15" t="inlineStr"/>
-      <c r="CU15" t="inlineStr"/>
-      <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="inlineStr"/>
-      <c r="CX15" t="n">
-        <v>45872.71315074351</v>
-      </c>
-      <c r="CY15" t="inlineStr"/>
-      <c r="CZ15" t="inlineStr"/>
-      <c r="DA15" t="inlineStr"/>
+        <v>3.275</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>3.3125</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>7.949102995753591</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>34655000</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>53.72499999999999</v>
+      </c>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="n">
+        <v>-2.254093066175585</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>8.677213434809943</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>1.255880047263688</v>
+      </c>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>0.8504299951903924</v>
+        <v>19933093.19197466</v>
       </c>
       <c r="DD15" t="inlineStr"/>
       <c r="DE15" t="inlineStr"/>
       <c r="DF15" t="n">
-        <v>1.25223896673116</v>
-      </c>
-      <c r="DG15" t="inlineStr"/>
-      <c r="DH15" t="n">
-        <v>-2.630428168086354</v>
-      </c>
-      <c r="DI15" t="inlineStr"/>
+        <v>0.5249999999999999</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.903067766166977</v>
+      </c>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="n">
+        <v>46266.50405160678</v>
+      </c>
       <c r="DJ15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -5502,55 +5726,71 @@
       <c r="CN16" t="n">
         <v>0.7606361231361092</v>
       </c>
-      <c r="CO16" t="inlineStr"/>
+      <c r="CO16" t="n">
+        <v>-1.18518518518519</v>
+      </c>
       <c r="CP16" t="n">
+        <v>11267.22222222222</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>19777.77777777778</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>18.33333333333331</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0.2222222222222223</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-1.37037037037037</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>1.931668258641949</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>8683333.333333334</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>17.22222222222223</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>4.199999999999932</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>3.022652453134896</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>-0.009098171159578783</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>-0.2502100725784935</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>2.118333333333339</v>
+      </c>
+      <c r="DC16" t="n">
         <v>1681289.410719234</v>
       </c>
-      <c r="CQ16" t="n">
-        <v>-0.009098171159578783</v>
-      </c>
-      <c r="CR16" t="inlineStr"/>
-      <c r="CS16" t="n">
-        <v>1.931668258641949</v>
-      </c>
-      <c r="CT16" t="n">
+      <c r="DD16" t="n">
+        <v>0.0338888888888893</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>1.973333333333329</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>-2.778389300757723</v>
+      </c>
+      <c r="DH16" t="n">
         <v>-0.7033333333333331</v>
       </c>
-      <c r="CU16" t="inlineStr"/>
-      <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr"/>
-      <c r="CX16" t="n">
+      <c r="DI16" t="n">
         <v>6744.220537422287</v>
       </c>
-      <c r="CY16" t="n">
-        <v>0.0338888888888893</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>1.973333333333329</v>
-      </c>
-      <c r="DA16" t="inlineStr"/>
-      <c r="DB16" t="n">
+      <c r="DJ16" t="n">
         <v>5572722.222222222</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>-2.778389300757723</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>11267.22222222222</v>
-      </c>
-      <c r="DE16" t="inlineStr"/>
-      <c r="DF16" t="n">
-        <v>-0.2502100725784935</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>4.199999999999932</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>3.022652453134896</v>
-      </c>
-      <c r="DI16" t="inlineStr"/>
-      <c r="DJ16" t="n">
-        <v>2.118333333333339</v>
       </c>
     </row>
     <row r="17">
@@ -5814,55 +6054,71 @@
       <c r="CN17" t="n">
         <v>0.9934615384615313</v>
       </c>
-      <c r="CO17" t="inlineStr"/>
+      <c r="CO17" t="n">
+        <v>-1</v>
+      </c>
       <c r="CP17" t="n">
-        <v>-33531301.24571946</v>
+        <v>-208535.934744268</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-8.595267410321583</v>
-      </c>
-      <c r="CR17" t="inlineStr"/>
+        <v>-559000</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>-32</v>
+      </c>
       <c r="CS17" t="n">
-        <v>-9.433452374938426</v>
+        <v>-6</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.1389660493827165</v>
-      </c>
-      <c r="CU17" t="inlineStr"/>
-      <c r="CV17" t="inlineStr"/>
-      <c r="CW17" t="inlineStr"/>
+        <v>0.6666666666666679</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-9.260440513362326</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-122700000</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-32</v>
+      </c>
       <c r="CX17" t="n">
-        <v>-114587.4908406771</v>
+        <v>-1.884347442680763</v>
       </c>
       <c r="CY17" t="n">
-        <v>-2.161998456790124</v>
+        <v>-0.4379180889629879</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-12.44564043209877</v>
-      </c>
-      <c r="DA17" t="inlineStr"/>
+        <v>-8.401645776394219</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>-0.9519438325262632</v>
+      </c>
       <c r="DB17" t="n">
-        <v>-63086530.67129631</v>
+        <v>-11.2212962962963</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.7249942165963787</v>
+        <v>-33437295.6025265</v>
       </c>
       <c r="DD17" t="n">
-        <v>-208270.0617283951</v>
-      </c>
-      <c r="DE17" t="inlineStr"/>
+        <v>-2.160758377425044</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>-12.72813051146385</v>
+      </c>
       <c r="DF17" t="n">
-        <v>-0.9625206077605462</v>
+        <v>0</v>
       </c>
       <c r="DG17" t="n">
-        <v>-2.086728395061726</v>
+        <v>0.8135630838030181</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0.275136376065177</v>
-      </c>
-      <c r="DI17" t="inlineStr"/>
+        <v>0.1136684303350961</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-114429.9662778217</v>
+      </c>
       <c r="DJ17" t="n">
-        <v>-11.09282407407407</v>
+        <v>-63297238.75661377</v>
       </c>
     </row>
     <row r="18">
@@ -6122,55 +6378,71 @@
       <c r="CN18" t="n">
         <v>-1.217824074074073</v>
       </c>
-      <c r="CO18" t="inlineStr"/>
+      <c r="CO18" t="n">
+        <v>-0.8000000000000114</v>
+      </c>
       <c r="CP18" t="n">
+        <v>759.25925925927</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>128</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-0.06666666666666643</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>1.462250893623434</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-12100000</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>147</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0.6537037037036839</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-1.021197031000952</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>3.736258712239106</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.1715608465608467</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0.6157407407407476</v>
+      </c>
+      <c r="DC18" t="n">
         <v>-441157.7257165518</v>
       </c>
-      <c r="CQ18" t="n">
-        <v>3.736258712239106</v>
-      </c>
-      <c r="CR18" t="inlineStr"/>
-      <c r="CS18" t="n">
-        <v>1.462250893623434</v>
-      </c>
-      <c r="CT18" t="n">
+      <c r="DD18" t="n">
+        <v>-0.2092592592592593</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0.7981481481481438</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>2.74826816248385</v>
+      </c>
+      <c r="DH18" t="n">
         <v>-0.4953703703703702</v>
       </c>
-      <c r="CU18" t="inlineStr"/>
-      <c r="CV18" t="inlineStr"/>
-      <c r="CW18" t="inlineStr"/>
-      <c r="CX18" t="n">
+      <c r="DI18" t="n">
         <v>4224.358194456236</v>
       </c>
-      <c r="CY18" t="n">
-        <v>-0.2092592592592593</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>0.7981481481481438</v>
-      </c>
-      <c r="DA18" t="inlineStr"/>
-      <c r="DB18" t="n">
+      <c r="DJ18" t="n">
         <v>-1702314.814814817</v>
-      </c>
-      <c r="DC18" t="n">
-        <v>2.74826816248385</v>
-      </c>
-      <c r="DD18" t="n">
-        <v>759.25925925927</v>
-      </c>
-      <c r="DE18" t="inlineStr"/>
-      <c r="DF18" t="n">
-        <v>-0.1715608465608467</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>0.6537037037036839</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>-1.021197031000952</v>
-      </c>
-      <c r="DI18" t="inlineStr"/>
-      <c r="DJ18" t="n">
-        <v>0.6157407407407476</v>
       </c>
     </row>
     <row r="19">
@@ -6430,41 +6702,57 @@
       <c r="CN19" t="n">
         <v>-1.806516014849336</v>
       </c>
-      <c r="CO19" t="inlineStr"/>
-      <c r="CP19" t="n">
-        <v>-218569.471258373</v>
-      </c>
+      <c r="CO19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="CP19" t="inlineStr"/>
       <c r="CQ19" t="n">
-        <v>1.3635919956305</v>
-      </c>
-      <c r="CR19" t="inlineStr"/>
+        <v>-49000</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-87</v>
+      </c>
       <c r="CS19" t="n">
-        <v>-3.618805394811559</v>
-      </c>
-      <c r="CT19" t="inlineStr"/>
-      <c r="CU19" t="inlineStr"/>
-      <c r="CV19" t="inlineStr"/>
-      <c r="CW19" t="inlineStr"/>
-      <c r="CX19" t="n">
-        <v>3918.015323026935</v>
-      </c>
-      <c r="CY19" t="inlineStr"/>
-      <c r="CZ19" t="inlineStr"/>
-      <c r="DA19" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>-3.792695099985139</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>-87</v>
+      </c>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="n">
+        <v>-3.196013293981537</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>1.286324889957825</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>-0.06056290039939416</v>
+      </c>
       <c r="DB19" t="inlineStr"/>
       <c r="DC19" t="n">
-        <v>3.790089594680346</v>
+        <v>-456733.134721959</v>
       </c>
       <c r="DD19" t="inlineStr"/>
       <c r="DE19" t="inlineStr"/>
       <c r="DF19" t="n">
-        <v>-0.07125538111412721</v>
-      </c>
-      <c r="DG19" t="inlineStr"/>
-      <c r="DH19" t="n">
-        <v>-3.498662517751114</v>
-      </c>
-      <c r="DI19" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>3.879932556156433</v>
+      </c>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="n">
+        <v>3702.475792718637</v>
+      </c>
       <c r="DJ19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -6724,55 +7012,71 @@
       <c r="CN20" t="n">
         <v>2.047569444444449</v>
       </c>
-      <c r="CO20" t="inlineStr"/>
+      <c r="CO20" t="n">
+        <v>7.592592592592581</v>
+      </c>
       <c r="CP20" t="n">
+        <v>11488.5101010101</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>34888.88888888889</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>47.55555555555556</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>2.444444444444445</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>-2.685185185185187</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>4.191945282386456</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>64722222.22222222</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>52.44444444444444</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>1.107733585858625</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>2.037654192356229</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>4.512422223912807</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0.4484186876504985</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>5.29406565656565</v>
+      </c>
+      <c r="DC20" t="n">
         <v>11633390.99789338</v>
       </c>
-      <c r="CQ20" t="n">
-        <v>4.512422223912807</v>
-      </c>
-      <c r="CR20" t="inlineStr"/>
-      <c r="CS20" t="n">
-        <v>4.191945282386456</v>
-      </c>
-      <c r="CT20" t="n">
+      <c r="DD20" t="n">
+        <v>0.8519886363636364</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>5.565625000000011</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0.3904297466474951</v>
+      </c>
+      <c r="DH20" t="n">
         <v>0.2441287878787826</v>
       </c>
-      <c r="CU20" t="inlineStr"/>
-      <c r="CV20" t="inlineStr"/>
-      <c r="CW20" t="inlineStr"/>
-      <c r="CX20" t="n">
+      <c r="DI20" t="n">
         <v>11226.19686051059</v>
       </c>
-      <c r="CY20" t="n">
-        <v>0.8519886363636364</v>
-      </c>
-      <c r="CZ20" t="n">
-        <v>5.565625000000011</v>
-      </c>
-      <c r="DA20" t="inlineStr"/>
-      <c r="DB20" t="n">
+      <c r="DJ20" t="n">
         <v>18140618.68686868</v>
-      </c>
-      <c r="DC20" t="n">
-        <v>0.3904297466474951</v>
-      </c>
-      <c r="DD20" t="n">
-        <v>11488.5101010101</v>
-      </c>
-      <c r="DE20" t="inlineStr"/>
-      <c r="DF20" t="n">
-        <v>0.4484186876504985</v>
-      </c>
-      <c r="DG20" t="n">
-        <v>1.107733585858625</v>
-      </c>
-      <c r="DH20" t="n">
-        <v>2.037654192356229</v>
-      </c>
-      <c r="DI20" t="inlineStr"/>
-      <c r="DJ20" t="n">
-        <v>5.29406565656565</v>
       </c>
     </row>
     <row r="21">
@@ -7032,55 +7336,71 @@
       <c r="CN21" t="n">
         <v>5.19629629629631</v>
       </c>
-      <c r="CO21" t="inlineStr"/>
+      <c r="CO21" t="n">
+        <v>3.916666666666657</v>
+      </c>
       <c r="CP21" t="n">
-        <v>1653843.747694086</v>
+        <v>2291.269841269841</v>
       </c>
       <c r="CQ21" t="n">
-        <v>0.9028032473650995</v>
-      </c>
-      <c r="CR21" t="inlineStr"/>
+        <v>7833.333333333332</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>13</v>
+      </c>
       <c r="CS21" t="n">
-        <v>2.269765611597165</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CT21" t="n">
-        <v>-0.9802248677248713</v>
-      </c>
-      <c r="CU21" t="inlineStr"/>
-      <c r="CV21" t="inlineStr"/>
-      <c r="CW21" t="inlineStr"/>
+        <v>1.916666666666668</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>2.419239095390822</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>1083333.333333333</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>13</v>
+      </c>
       <c r="CX21" t="n">
-        <v>6049.244261419513</v>
+        <v>2.460714285714317</v>
       </c>
       <c r="CY21" t="n">
-        <v>-0.006349206349206105</v>
+        <v>0.4662258465436651</v>
       </c>
       <c r="CZ21" t="n">
-        <v>0.7074735449735385</v>
-      </c>
-      <c r="DA21" t="inlineStr"/>
+        <v>1.071900232251565</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>0.0086789504535838</v>
+      </c>
       <c r="DB21" t="n">
-        <v>1176362.433862434</v>
+        <v>1.50238095238096</v>
       </c>
       <c r="DC21" t="n">
-        <v>-1.739517367479852</v>
+        <v>1826889.830915608</v>
       </c>
       <c r="DD21" t="n">
-        <v>2813.492063492064</v>
-      </c>
-      <c r="DE21" t="inlineStr"/>
+        <v>0.001984126984127199</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>0.6412698412698461</v>
+      </c>
       <c r="DF21" t="n">
-        <v>0.001810189747103896</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.938492063492077</v>
+        <v>-1.775832218158737</v>
       </c>
       <c r="DH21" t="n">
-        <v>0.5327468945340286</v>
-      </c>
-      <c r="DI21" t="inlineStr"/>
+        <v>-0.8797619047619065</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>6206.819544323746</v>
+      </c>
       <c r="DJ21" t="n">
-        <v>1.636177248677257</v>
+        <v>1124325.396825397</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -890,112 +890,112 @@
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -1257,70 +1257,70 @@
         <v>1.952127525252536</v>
       </c>
       <c r="CO2" t="n">
-        <v>-5.775231481481484</v>
+        <v>-2630.17676767677</v>
       </c>
       <c r="CP2" t="n">
-        <v>-2630.17676767677</v>
+        <v>-72555.55555555556</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-72555.55555555556</v>
+        <v>-1.464007722631322</v>
       </c>
       <c r="CR2" t="n">
-        <v>-121.9444444444445</v>
+        <v>-0.1923839816157924</v>
       </c>
       <c r="CS2" t="n">
-        <v>-5.347222222222222</v>
+        <v>-2550.131150621353</v>
       </c>
       <c r="CT2" t="n">
-        <v>-3.771759259259259</v>
+        <v>-3.124621212121212</v>
       </c>
       <c r="CU2" t="n">
-        <v>-1.394177128245744</v>
+        <v>-117.1805555555555</v>
       </c>
       <c r="CV2" t="n">
         <v>-98876388.8888889</v>
       </c>
       <c r="CW2" t="n">
-        <v>-117.1805555555555</v>
+        <v>-3.771759259259259</v>
       </c>
       <c r="CX2" t="n">
+        <v>-121.9444444444445</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-11240340.90909091</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.4269886363636364</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.050315656565658</v>
+      </c>
+      <c r="DB2" t="n">
         <v>0.9811553030302775</v>
       </c>
-      <c r="CY2" t="n">
-        <v>-1.464007722631322</v>
-      </c>
-      <c r="CZ2" t="n">
+      <c r="DC2" t="n">
+        <v>-5.347222222222222</v>
+      </c>
+      <c r="DD2" t="n">
         <v>-0.7150932275642106</v>
       </c>
-      <c r="DA2" t="n">
-        <v>-0.1923839816157924</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-3.124621212121212</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-6027509.463850085</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.4269886363636364</v>
-      </c>
       <c r="DE2" t="n">
-        <v>-2.065625000000011</v>
+        <v>-0.1217169144542751</v>
       </c>
       <c r="DF2" t="n">
         <v>-1.291666666666667</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0.1217169144542751</v>
+        <v>-2.065625000000011</v>
       </c>
       <c r="DH2" t="n">
-        <v>1.050315656565658</v>
+        <v>-1.394177128245744</v>
       </c>
       <c r="DI2" t="n">
-        <v>-2550.131150621353</v>
+        <v>-6027509.463850085</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-11240340.90909091</v>
+        <v>-5.775231481481484</v>
       </c>
     </row>
     <row r="3">
@@ -1581,70 +1581,70 @@
         <v>0.964877946127956</v>
       </c>
       <c r="CO3" t="n">
-        <v>3.111111111111086</v>
+        <v>8351.587301587297</v>
       </c>
       <c r="CP3" t="n">
-        <v>8351.587301587297</v>
+        <v>62500</v>
       </c>
       <c r="CQ3" t="n">
-        <v>62500</v>
+        <v>2.802389667698606</v>
       </c>
       <c r="CR3" t="n">
-        <v>111.75</v>
+        <v>0.3977438498965202</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.055555555555555</v>
+        <v>2225.568879566232</v>
       </c>
       <c r="CT3" t="n">
-        <v>-1.532407407407405</v>
+        <v>2.061507936507923</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.665055918179306</v>
+        <v>124.7083333333333</v>
       </c>
       <c r="CV3" t="n">
         <v>38430555.55555555</v>
       </c>
       <c r="CW3" t="n">
-        <v>124.7083333333333</v>
+        <v>-1.532407407407405</v>
       </c>
       <c r="CX3" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>11127380.95238096</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0.890873015873016</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>-0.2698412698412689</v>
+      </c>
+      <c r="DB3" t="n">
         <v>-1.751587301587278</v>
       </c>
-      <c r="CY3" t="n">
-        <v>2.802389667698606</v>
-      </c>
-      <c r="CZ3" t="n">
+      <c r="DC3" t="n">
+        <v>3.055555555555555</v>
+      </c>
+      <c r="DD3" t="n">
         <v>-1.414517862789282</v>
       </c>
-      <c r="DA3" t="n">
-        <v>0.3977438498965202</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>2.061507936507923</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>4833053.156781873</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>0.890873015873016</v>
-      </c>
       <c r="DE3" t="n">
-        <v>2.126190476190487</v>
+        <v>-2.794065154449569</v>
       </c>
       <c r="DF3" t="n">
         <v>1.388888888888889</v>
       </c>
       <c r="DG3" t="n">
-        <v>-2.794065154449569</v>
+        <v>2.126190476190487</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.2698412698412689</v>
+        <v>1.665055918179306</v>
       </c>
       <c r="DI3" t="n">
-        <v>2225.568879566232</v>
+        <v>4833053.156781873</v>
       </c>
       <c r="DJ3" t="n">
-        <v>11127380.95238096</v>
+        <v>3.111111111111086</v>
       </c>
     </row>
     <row r="4">
@@ -1908,58 +1908,58 @@
       <c r="CN4" t="n">
         <v>0.1260804473304518</v>
       </c>
-      <c r="CO4" t="n">
-        <v>3.762499999999989</v>
-      </c>
-      <c r="CP4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="n">
+        <v>5875</v>
+      </c>
       <c r="CQ4" t="n">
-        <v>5875</v>
+        <v>3.058702847841261</v>
       </c>
       <c r="CR4" t="n">
-        <v>149.875</v>
+        <v>-1.084414643150257</v>
       </c>
       <c r="CS4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>3.149999999999999</v>
-      </c>
+        <v>-49423.54103874246</v>
+      </c>
+      <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>-1.647580149082714</v>
+        <v>152.375</v>
       </c>
       <c r="CV4" t="n">
         <v>10031250</v>
       </c>
       <c r="CW4" t="n">
-        <v>152.375</v>
-      </c>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="n">
-        <v>3.058702847841261</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>-7.690118101415266</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>-1.084414643150257</v>
-      </c>
+        <v>3.149999999999999</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>149.875</v>
+      </c>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
-        <v>-17113749.79414442</v>
-      </c>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-7.690118101415266</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-4.672619431606805</v>
+      </c>
       <c r="DF4" t="n">
         <v>2</v>
       </c>
-      <c r="DG4" t="n">
-        <v>-4.672619431606805</v>
-      </c>
-      <c r="DH4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="n">
+        <v>-1.647580149082714</v>
+      </c>
       <c r="DI4" t="n">
-        <v>-49423.54103874246</v>
-      </c>
-      <c r="DJ4" t="inlineStr"/>
+        <v>-17113749.79414442</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>3.762499999999989</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2219,70 +2219,70 @@
         <v>-0.3270833333333343</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.2083333333333144</v>
+        <v>-7609.027777777781</v>
       </c>
       <c r="CP5" t="n">
-        <v>-7563.734567901236</v>
+        <v>-114750</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-115222.2222222222</v>
+        <v>2.629622246625928</v>
       </c>
       <c r="CR5" t="n">
-        <v>-158.7777777777778</v>
+        <v>0.1206590386737445</v>
       </c>
       <c r="CS5" t="n">
-        <v>-4.333333333333334</v>
+        <v>-3917.648731986963</v>
       </c>
       <c r="CT5" t="n">
-        <v>-1.009259259259263</v>
+        <v>-3.600347222222226</v>
       </c>
       <c r="CU5" t="n">
-        <v>-2.219579242507194</v>
+        <v>-154.375</v>
       </c>
       <c r="CV5" t="n">
-        <v>-43577777.77777778</v>
+        <v>-44729166.66666666</v>
       </c>
       <c r="CW5" t="n">
-        <v>-155.7222222222222</v>
+        <v>-0.9375000000000036</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.884953703703701</v>
+        <v>-157</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.481331327830617</v>
+        <v>-9206458.333333336</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.2893650152164042</v>
+        <v>0.09409722222222205</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.1181871075833927</v>
+        <v>3.524305555555554</v>
       </c>
       <c r="DB5" t="n">
-        <v>-3.772415123456781</v>
+        <v>-0.8517361111111086</v>
       </c>
       <c r="DC5" t="n">
-        <v>-1199146.081890938</v>
+        <v>-4.291666666666666</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.08746141975308608</v>
+        <v>-0.470977347815591</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.8259259259259295</v>
+        <v>1.098868125338711</v>
       </c>
       <c r="DF5" t="n">
-        <v>-1.777777777777778</v>
+        <v>-1.75</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.116784813101891</v>
+        <v>-0.8034722222222115</v>
       </c>
       <c r="DH5" t="n">
-        <v>3.647955246913579</v>
+        <v>-2.342586835141972</v>
       </c>
       <c r="DI5" t="n">
-        <v>-3595.902921754314</v>
+        <v>-1479003.018529673</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-9414371.14197531</v>
+        <v>-0.4479166666666572</v>
       </c>
     </row>
     <row r="6">
@@ -2540,58 +2540,58 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="n">
-        <v>1.504166666666663</v>
-      </c>
-      <c r="CP6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="n">
+        <v>-30425</v>
+      </c>
       <c r="CQ6" t="n">
-        <v>-30425</v>
+        <v>1.280816701680692</v>
       </c>
       <c r="CR6" t="n">
-        <v>-119.65</v>
+        <v>-0.2328558067964026</v>
       </c>
       <c r="CS6" t="n">
-        <v>-1.775</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-3.581249999999997</v>
-      </c>
+        <v>5129.069917440662</v>
+      </c>
+      <c r="CT6" t="inlineStr"/>
       <c r="CU6" t="n">
-        <v>-1.863562168288382</v>
+        <v>-112.35</v>
       </c>
       <c r="CV6" t="n">
         <v>-8748750</v>
       </c>
       <c r="CW6" t="n">
-        <v>-112.35</v>
-      </c>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="n">
-        <v>1.280816701680692</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>-0.6552691471325431</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>-0.2328558067964026</v>
-      </c>
+        <v>-3.581249999999997</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-119.65</v>
+      </c>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
       <c r="DB6" t="inlineStr"/>
       <c r="DC6" t="n">
-        <v>-1713898.728899455</v>
-      </c>
-      <c r="DD6" t="inlineStr"/>
-      <c r="DE6" t="inlineStr"/>
+        <v>-1.775</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0.6552691471325431</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.3690003962111206</v>
+      </c>
       <c r="DF6" t="n">
         <v>-1.525</v>
       </c>
-      <c r="DG6" t="n">
-        <v>0.3690003962111206</v>
-      </c>
-      <c r="DH6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="n">
+        <v>-1.863562168288382</v>
+      </c>
       <c r="DI6" t="n">
-        <v>5129.069917440662</v>
-      </c>
-      <c r="DJ6" t="inlineStr"/>
+        <v>-1713898.728899455</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>1.504166666666663</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2851,70 +2851,70 @@
         <v>-0.9012620712620532</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.04259259259259807</v>
+        <v>113623.2363315696</v>
       </c>
       <c r="CP7" t="n">
-        <v>113549.5756172839</v>
+        <v>-106761.9047619048</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-115583.3333333333</v>
+        <v>-1.150102346483919</v>
       </c>
       <c r="CR7" t="n">
-        <v>-145.4305555555555</v>
+        <v>0.5961911626385312</v>
       </c>
       <c r="CS7" t="n">
-        <v>-5.819444444444445</v>
+        <v>70268.74756984405</v>
       </c>
       <c r="CT7" t="n">
-        <v>-1.596296296296295</v>
+        <v>1.7510582010582</v>
       </c>
       <c r="CU7" t="n">
-        <v>3.976846610179933</v>
+        <v>-139.5873015873016</v>
       </c>
       <c r="CV7" t="n">
-        <v>-45188888.8888889</v>
+        <v>-42774603.17460319</v>
       </c>
       <c r="CW7" t="n">
-        <v>-150.9444444444445</v>
+        <v>-1.784391534391531</v>
       </c>
       <c r="CX7" t="n">
-        <v>3.163117283950612</v>
+        <v>-136.2698412698413</v>
       </c>
       <c r="CY7" t="n">
-        <v>-1.289074830302894</v>
+        <v>29520105.82010584</v>
       </c>
       <c r="CZ7" t="n">
-        <v>8.137524618007063</v>
+        <v>0.7877425044091706</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.5739054399142121</v>
+        <v>2.493474426807762</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.759490740740745</v>
+        <v>3.221649029982359</v>
       </c>
       <c r="DC7" t="n">
-        <v>19089465.20260116</v>
+        <v>-5.730158730158731</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.7887345679012343</v>
+        <v>8.347543720898983</v>
       </c>
       <c r="DE7" t="n">
-        <v>5.129668209876556</v>
+        <v>4.332500576908473</v>
       </c>
       <c r="DF7" t="n">
-        <v>-1.777777777777778</v>
+        <v>-1.634920634920635</v>
       </c>
       <c r="DG7" t="n">
-        <v>4.291484368458057</v>
+        <v>5.117019400352746</v>
       </c>
       <c r="DH7" t="n">
-        <v>2.407908950617283</v>
+        <v>3.994233775483764</v>
       </c>
       <c r="DI7" t="n">
-        <v>69125.44233706512</v>
+        <v>20010368.94290731</v>
       </c>
       <c r="DJ7" t="n">
-        <v>30112789.35185187</v>
+        <v>-0.187830687830683</v>
       </c>
     </row>
     <row r="8">
@@ -3176,73 +3176,73 @@
         <v>0.06666666666666665</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.5701914983164897</v>
+        <v>0.5673847853535392</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3125</v>
+        <v>-20128.70370370371</v>
       </c>
       <c r="CP8" t="n">
-        <v>-20128.70370370371</v>
+        <v>-4625</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-4625</v>
+        <v>-2.069260474325262</v>
       </c>
       <c r="CR8" t="n">
-        <v>-17.25</v>
+        <v>-0.2685157984645212</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0.375</v>
+        <v>-13014.43791631485</v>
       </c>
       <c r="CT8" t="n">
-        <v>6.020833333333336</v>
+        <v>-4.910879629629633</v>
       </c>
       <c r="CU8" t="n">
-        <v>-4.753563010132282</v>
+        <v>-43</v>
       </c>
       <c r="CV8" t="n">
         <v>237500</v>
       </c>
       <c r="CW8" t="n">
-        <v>-43</v>
+        <v>6.020833333333336</v>
       </c>
       <c r="CX8" t="n">
+        <v>-17.25</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>-13303935.18518519</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>-0.6865740740740742</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>2.02662037037037</v>
+      </c>
+      <c r="DB8" t="n">
         <v>-1.655092592592609</v>
       </c>
-      <c r="CY8" t="n">
-        <v>-2.069260474325262</v>
-      </c>
-      <c r="CZ8" t="n">
+      <c r="DC8" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="DD8" t="n">
         <v>-2.599134778512664</v>
       </c>
-      <c r="DA8" t="n">
-        <v>-0.2685157984645212</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>-4.910879629629633</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>-5667768.435125245</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>-0.6865740740740742</v>
-      </c>
       <c r="DE8" t="n">
-        <v>-3.826620370370364</v>
+        <v>0.06267258498295192</v>
       </c>
       <c r="DF8" t="n">
         <v>-0.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.06267258498295192</v>
+        <v>-3.826620370370364</v>
       </c>
       <c r="DH8" t="n">
-        <v>2.02662037037037</v>
+        <v>-4.753563010132282</v>
       </c>
       <c r="DI8" t="n">
-        <v>-13014.43791631485</v>
+        <v>-5667768.435125245</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-13303935.18518519</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="9">
@@ -3503,70 +3503,70 @@
         <v>-0.5433651996151951</v>
       </c>
       <c r="CO9" t="n">
-        <v>-1.712962962962962</v>
+        <v>-2858.888888888891</v>
       </c>
       <c r="CP9" t="n">
-        <v>-2858.888888888891</v>
+        <v>14833.33333333333</v>
       </c>
       <c r="CQ9" t="n">
-        <v>14833.33333333333</v>
+        <v>-1.898602408799746</v>
       </c>
       <c r="CR9" t="n">
-        <v>69.22222222222223</v>
+        <v>0.4444259322548796</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.833333333333333</v>
+        <v>-4123.889743297637</v>
       </c>
       <c r="CT9" t="n">
-        <v>-1.138888888888889</v>
+        <v>0.1594444444444321</v>
       </c>
       <c r="CU9" t="n">
-        <v>-0.7871972123068502</v>
+        <v>79.22222222222223</v>
       </c>
       <c r="CV9" t="n">
         <v>6044444.444444444</v>
       </c>
       <c r="CW9" t="n">
-        <v>79.22222222222223</v>
+        <v>-1.138888888888889</v>
       </c>
       <c r="CX9" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1674500</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.3411111111111107</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>2.700555555555557</v>
+      </c>
+      <c r="DB9" t="n">
         <v>-2.258333333333297</v>
       </c>
-      <c r="CY9" t="n">
-        <v>-1.898602408799746</v>
-      </c>
-      <c r="CZ9" t="n">
+      <c r="DC9" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="DD9" t="n">
         <v>2.383246415702544</v>
       </c>
-      <c r="DA9" t="n">
-        <v>0.4444259322548796</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>0.1594444444444321</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>2319363.53931968</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0.3411111111111107</v>
-      </c>
       <c r="DE9" t="n">
-        <v>1.673888888888882</v>
+        <v>4.416525478257931</v>
       </c>
       <c r="DF9" t="n">
         <v>1.055555555555556</v>
       </c>
       <c r="DG9" t="n">
-        <v>4.416525478257931</v>
+        <v>1.673888888888882</v>
       </c>
       <c r="DH9" t="n">
-        <v>2.700555555555557</v>
+        <v>-0.7871972123068502</v>
       </c>
       <c r="DI9" t="n">
-        <v>-4123.889743297637</v>
+        <v>2319363.53931968</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1674500</v>
+        <v>-1.712962962962962</v>
       </c>
     </row>
     <row r="10">
@@ -3827,70 +3827,70 @@
         <v>-4.89598765432099</v>
       </c>
       <c r="CO10" t="n">
-        <v>-5.508101851851876</v>
+        <v>-16174.60317460317</v>
       </c>
       <c r="CP10" t="n">
-        <v>-16174.60317460317</v>
+        <v>-125513.8888888889</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-125513.8888888889</v>
+        <v>-1.073288524291371</v>
       </c>
       <c r="CR10" t="n">
-        <v>-161.9444444444445</v>
+        <v>-0.4736079062300629</v>
       </c>
       <c r="CS10" t="n">
-        <v>-3.847222222222222</v>
+        <v>-13871.46429714575</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.2673611111111072</v>
+        <v>-5.055158730158738</v>
       </c>
       <c r="CU10" t="n">
-        <v>-4.722458168056505</v>
+        <v>-163.9583333333333</v>
       </c>
       <c r="CV10" t="n">
         <v>-62220833.33333334</v>
       </c>
       <c r="CW10" t="n">
-        <v>-163.9583333333333</v>
+        <v>0.2673611111111072</v>
       </c>
       <c r="CX10" t="n">
+        <v>-161.9444444444445</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-9049047.619047619</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.8269841269841272</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-2.392460317460316</v>
+      </c>
+      <c r="DB10" t="n">
         <v>-3.952380952380963</v>
       </c>
-      <c r="CY10" t="n">
-        <v>-1.073288524291371</v>
-      </c>
-      <c r="CZ10" t="n">
+      <c r="DC10" t="n">
+        <v>-3.847222222222222</v>
+      </c>
+      <c r="DD10" t="n">
         <v>-2.934594366462719</v>
       </c>
-      <c r="DA10" t="n">
-        <v>-0.4736079062300629</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>-5.055158730158738</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>-5414173.775614414</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>-0.8269841269841272</v>
-      </c>
       <c r="DE10" t="n">
-        <v>-5.663492063492058</v>
+        <v>0.6919975250167703</v>
       </c>
       <c r="DF10" t="n">
         <v>-1.847222222222222</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.6919975250167703</v>
+        <v>-5.663492063492058</v>
       </c>
       <c r="DH10" t="n">
-        <v>-2.392460317460316</v>
+        <v>-4.722458168056505</v>
       </c>
       <c r="DI10" t="n">
-        <v>-13871.46429714575</v>
+        <v>-5414173.775614414</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-9049047.619047619</v>
+        <v>-5.508101851851876</v>
       </c>
     </row>
     <row r="11">
@@ -4148,60 +4148,60 @@
         <v>0.2236842105263158</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.5590926001082295</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>-4.655092592592581</v>
-      </c>
-      <c r="CP11" t="inlineStr"/>
+        <v>-0.5599960865027924</v>
+      </c>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="n">
+        <v>-11138.88888888889</v>
+      </c>
       <c r="CQ11" t="n">
-        <v>-11138.88888888889</v>
+        <v>-1.038962943374713</v>
       </c>
       <c r="CR11" t="n">
-        <v>17.81944444444444</v>
+        <v>-0.2339160839160841</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0.4444444444444444</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>0.9351851851851869</v>
-      </c>
+        <v>-7578.270603760797</v>
+      </c>
+      <c r="CT11" t="inlineStr"/>
       <c r="CU11" t="n">
-        <v>-3.916607609438486</v>
+        <v>16.05555555555556</v>
       </c>
       <c r="CV11" t="n">
         <v>-13097222.22222222</v>
       </c>
       <c r="CW11" t="n">
-        <v>16.05555555555556</v>
-      </c>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="n">
-        <v>-1.038962943374713</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>-2.5625091865288</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>-0.2339160839160841</v>
-      </c>
+        <v>0.9351851851851869</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>17.81944444444444</v>
+      </c>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
       <c r="DB11" t="inlineStr"/>
       <c r="DC11" t="n">
-        <v>-6134159.035862468</v>
-      </c>
-      <c r="DD11" t="inlineStr"/>
-      <c r="DE11" t="inlineStr"/>
+        <v>-0.4444444444444444</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-2.5625091865288</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>1.366848982535259</v>
+      </c>
       <c r="DF11" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="DG11" t="n">
-        <v>1.366848982535259</v>
-      </c>
-      <c r="DH11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="n">
+        <v>-3.916607609438486</v>
+      </c>
       <c r="DI11" t="n">
-        <v>-7578.270603760797</v>
-      </c>
-      <c r="DJ11" t="inlineStr"/>
+        <v>-6134159.035862468</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-4.655092592592581</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
@@ -4461,70 +4461,70 @@
         <v>0.5913825757575637</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.3333333333333144</v>
+        <v>15382.63888888889</v>
       </c>
       <c r="CP12" t="n">
-        <v>15337.34567901235</v>
+        <v>97500</v>
       </c>
       <c r="CQ12" t="n">
-        <v>97972.22222222222</v>
+        <v>-0.02116743926438858</v>
       </c>
       <c r="CR12" t="n">
-        <v>114.7777777777778</v>
+        <v>-0.0823388615813152</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.541666666666667</v>
+        <v>7353.639278677972</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0.5949074074074048</v>
+        <v>3.682638888888889</v>
       </c>
       <c r="CU12" t="n">
-        <v>3.683064224050426</v>
+        <v>114.25</v>
       </c>
       <c r="CV12" t="n">
-        <v>38711111.11111111</v>
+        <v>39862500</v>
       </c>
       <c r="CW12" t="n">
-        <v>115.5972222222222</v>
+        <v>-0.6666666666666643</v>
       </c>
       <c r="CX12" t="n">
-        <v>2.396759259259255</v>
+        <v>113</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1271234795309226</v>
+        <v>10237534.72222222</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.3266254405138085</v>
+        <v>0.05277777777777759</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0.07986693049096338</v>
+        <v>-3.943402777777777</v>
       </c>
       <c r="DB12" t="n">
-        <v>3.854706790123444</v>
+        <v>2.363541666666663</v>
       </c>
       <c r="DC12" t="n">
-        <v>2916018.805803376</v>
+        <v>3.5</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.05941358024691357</v>
+        <v>-0.1450131079146217</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.8766203703703752</v>
+        <v>-2.617772427950442</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.402777777777778</v>
+        <v>1.375</v>
       </c>
       <c r="DG12" t="n">
-        <v>-2.635689115713621</v>
+        <v>0.8541666666666572</v>
       </c>
       <c r="DH12" t="n">
-        <v>-4.067052469135803</v>
+        <v>3.806071816685204</v>
       </c>
       <c r="DI12" t="n">
-        <v>7031.893468445323</v>
+        <v>3195875.742442111</v>
       </c>
       <c r="DJ12" t="n">
-        <v>10445447.5308642</v>
+        <v>0.5729166666666572</v>
       </c>
     </row>
     <row r="13">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
@@ -4784,58 +4784,58 @@
       <c r="CN13" t="n">
         <v>-0.4925602175602108</v>
       </c>
-      <c r="CO13" t="n">
-        <v>-4.445833333333326</v>
-      </c>
-      <c r="CP13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="n">
+        <v>483178.5714285715</v>
+      </c>
       <c r="CQ13" t="n">
-        <v>492000</v>
+        <v>-0.3700844112028392</v>
       </c>
       <c r="CR13" t="n">
-        <v>234.25</v>
+        <v>0.3988457448983764</v>
       </c>
       <c r="CS13" t="n">
-        <v>11.375</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>-2.533333333333335</v>
-      </c>
+        <v>39284.1595538964</v>
+      </c>
+      <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>1.90437760541927</v>
+        <v>237.6428571428572</v>
       </c>
       <c r="CV13" t="n">
-        <v>202825000</v>
+        <v>200410714.2857143</v>
       </c>
       <c r="CW13" t="n">
-        <v>249</v>
-      </c>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="n">
-        <v>-0.2311119273838642</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>-2.063576344058802</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>0.4211314676226956</v>
-      </c>
+        <v>-2.345238095238098</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>225.0892857142857</v>
+      </c>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
       <c r="DB13" t="inlineStr"/>
       <c r="DC13" t="n">
-        <v>10562799.14570484</v>
-      </c>
-      <c r="DD13" t="inlineStr"/>
-      <c r="DE13" t="inlineStr"/>
+        <v>11.28571428571429</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-2.273595446950722</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-3.696933366341259</v>
+      </c>
       <c r="DF13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>-3.655917157890844</v>
-      </c>
-      <c r="DH13" t="inlineStr"/>
+        <v>2.607142857142857</v>
+      </c>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="n">
+        <v>1.88699044011544</v>
+      </c>
       <c r="DI13" t="n">
-        <v>40427.46478667533</v>
-      </c>
-      <c r="DJ13" t="inlineStr"/>
+        <v>9641895.405398695</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-4.300595238095241</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
@@ -5095,70 +5095,70 @@
         <v>1.464166666666685</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.947916666666686</v>
+        <v>7601.388888888891</v>
       </c>
       <c r="CP14" t="n">
-        <v>7601.388888888891</v>
+        <v>123625</v>
       </c>
       <c r="CQ14" t="n">
-        <v>123625</v>
+        <v>-0.2339991526862661</v>
       </c>
       <c r="CR14" t="n">
-        <v>152.5</v>
+        <v>0.3757045643268555</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.291666666666667</v>
+        <v>8473.179791484748</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.093750000000004</v>
+        <v>2.448958333333337</v>
       </c>
       <c r="CU14" t="n">
-        <v>2.936630507184887</v>
+        <v>147.125</v>
       </c>
       <c r="CV14" t="n">
         <v>55229166.66666666</v>
       </c>
       <c r="CW14" t="n">
-        <v>147.125</v>
+        <v>2.093750000000004</v>
       </c>
       <c r="CX14" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>4237673.611111111</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.5406250000000004</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>1.387847222222224</v>
+      </c>
+      <c r="DB14" t="n">
         <v>2.300694444444446</v>
       </c>
-      <c r="CY14" t="n">
-        <v>-0.2339991526862661</v>
-      </c>
-      <c r="CZ14" t="n">
+      <c r="DC14" t="n">
+        <v>3.291666666666667</v>
+      </c>
+      <c r="DD14" t="n">
         <v>2.326296510507035</v>
       </c>
-      <c r="DA14" t="n">
-        <v>0.3757045643268555</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>2.448958333333337</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1753673.492999878</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>0.5406250000000004</v>
-      </c>
       <c r="DE14" t="n">
-        <v>2.480555555555554</v>
+        <v>0.6547774586667785</v>
       </c>
       <c r="DF14" t="n">
         <v>1.625</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.6547774586667785</v>
+        <v>2.480555555555554</v>
       </c>
       <c r="DH14" t="n">
-        <v>1.387847222222224</v>
+        <v>2.936630507184887</v>
       </c>
       <c r="DI14" t="n">
-        <v>8473.179791484748</v>
+        <v>1753673.492999878</v>
       </c>
       <c r="DJ14" t="n">
-        <v>4237673.611111111</v>
+        <v>1.947916666666686</v>
       </c>
     </row>
     <row r="15">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
@@ -5416,58 +5416,58 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="CN15" t="inlineStr"/>
-      <c r="CO15" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="CP15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="n">
+        <v>87300</v>
+      </c>
       <c r="CQ15" t="n">
-        <v>87300</v>
+        <v>-2.254093066175585</v>
       </c>
       <c r="CR15" t="n">
-        <v>59.15000000000001</v>
+        <v>1.255880047263688</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>3.3125</v>
-      </c>
+        <v>46266.50405160678</v>
+      </c>
+      <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
-        <v>7.949102995753591</v>
+        <v>53.72499999999999</v>
       </c>
       <c r="CV15" t="n">
         <v>34655000</v>
       </c>
       <c r="CW15" t="n">
-        <v>53.72499999999999</v>
-      </c>
-      <c r="CX15" t="inlineStr"/>
-      <c r="CY15" t="n">
-        <v>-2.254093066175585</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>8.677213434809943</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>1.255880047263688</v>
-      </c>
+        <v>3.3125</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>59.15000000000001</v>
+      </c>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="n">
-        <v>19933093.19197466</v>
-      </c>
-      <c r="DD15" t="inlineStr"/>
-      <c r="DE15" t="inlineStr"/>
+        <v>3.275</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>8.677213434809943</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.903067766166977</v>
+      </c>
       <c r="DF15" t="n">
         <v>0.5249999999999999</v>
       </c>
-      <c r="DG15" t="n">
-        <v>0.903067766166977</v>
-      </c>
-      <c r="DH15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="n">
+        <v>7.949102995753591</v>
+      </c>
       <c r="DI15" t="n">
-        <v>46266.50405160678</v>
-      </c>
-      <c r="DJ15" t="inlineStr"/>
+        <v>19933093.19197466</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-2.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
@@ -5727,70 +5727,70 @@
         <v>0.7606361231361092</v>
       </c>
       <c r="CO16" t="n">
-        <v>-1.18518518518519</v>
+        <v>11267.22222222222</v>
       </c>
       <c r="CP16" t="n">
-        <v>11267.22222222222</v>
+        <v>30000</v>
       </c>
       <c r="CQ16" t="n">
-        <v>19777.77777777778</v>
+        <v>3.022652453134896</v>
       </c>
       <c r="CR16" t="n">
-        <v>18.33333333333331</v>
+        <v>-0.2502100725784935</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0.2222222222222223</v>
+        <v>6744.220537422287</v>
       </c>
       <c r="CT16" t="n">
-        <v>-1.37037037037037</v>
+        <v>2.118333333333339</v>
       </c>
       <c r="CU16" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>15250000</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.3333333333333321</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>5572722.222222222</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.0338888888888893</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>-0.7033333333333331</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>4.199999999999932</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>-0.009098171159578783</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>-2.778389300757723</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>1.973333333333329</v>
+      </c>
+      <c r="DH16" t="n">
         <v>1.931668258641949</v>
       </c>
-      <c r="CV16" t="n">
-        <v>8683333.333333334</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>17.22222222222223</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>4.199999999999932</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>3.022652453134896</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>-0.009098171159578783</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>-0.2502100725784935</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>2.118333333333339</v>
-      </c>
-      <c r="DC16" t="n">
+      <c r="DI16" t="n">
         <v>1681289.410719234</v>
       </c>
-      <c r="DD16" t="n">
-        <v>0.0338888888888893</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>1.973333333333329</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>0.1111111111111112</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>-2.778389300757723</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>-0.7033333333333331</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>6744.220537422287</v>
-      </c>
       <c r="DJ16" t="n">
-        <v>5572722.222222222</v>
+        <v>8.333333333333343</v>
       </c>
     </row>
     <row r="17">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
@@ -6055,70 +6055,70 @@
         <v>0.9934615384615313</v>
       </c>
       <c r="CO17" t="n">
-        <v>-1</v>
+        <v>-208535.934744268</v>
       </c>
       <c r="CP17" t="n">
-        <v>-208535.934744268</v>
+        <v>-200000</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-559000</v>
+        <v>-0.4379180889629879</v>
       </c>
       <c r="CR17" t="n">
-        <v>-32</v>
+        <v>-0.9519438325262632</v>
       </c>
       <c r="CS17" t="n">
-        <v>-6</v>
+        <v>-114429.9662778217</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.6666666666666679</v>
+        <v>-11.2212962962963</v>
       </c>
       <c r="CU17" t="n">
+        <v>68</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-31200000</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>67</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-63297238.75661377</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>-2.160758377425044</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.1136684303350961</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-1.884347442680763</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>-8.401645776394219</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.8135630838030181</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-12.72813051146385</v>
+      </c>
+      <c r="DH17" t="n">
         <v>-9.260440513362326</v>
       </c>
-      <c r="CV17" t="n">
-        <v>-122700000</v>
-      </c>
-      <c r="CW17" t="n">
-        <v>-32</v>
-      </c>
-      <c r="CX17" t="n">
-        <v>-1.884347442680763</v>
-      </c>
-      <c r="CY17" t="n">
-        <v>-0.4379180889629879</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>-8.401645776394219</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>-0.9519438325262632</v>
-      </c>
-      <c r="DB17" t="n">
-        <v>-11.2212962962963</v>
-      </c>
-      <c r="DC17" t="n">
+      <c r="DI17" t="n">
         <v>-33437295.6025265</v>
       </c>
-      <c r="DD17" t="n">
-        <v>-2.160758377425044</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>-12.72813051146385</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>0.8135630838030181</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>0.1136684303350961</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>-114429.9662778217</v>
-      </c>
       <c r="DJ17" t="n">
-        <v>-63297238.75661377</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
@@ -6379,70 +6379,70 @@
         <v>-1.217824074074073</v>
       </c>
       <c r="CO18" t="n">
-        <v>-0.8000000000000114</v>
+        <v>759.25925925927</v>
       </c>
       <c r="CP18" t="n">
-        <v>759.25925925927</v>
+        <v>210000</v>
       </c>
       <c r="CQ18" t="n">
-        <v>81000</v>
+        <v>-1.021197031000952</v>
       </c>
       <c r="CR18" t="n">
-        <v>128</v>
+        <v>-0.1715608465608467</v>
       </c>
       <c r="CS18" t="n">
-        <v>4</v>
+        <v>4224.358194456236</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0.06666666666666643</v>
+        <v>0.6157407407407476</v>
       </c>
       <c r="CU18" t="n">
+        <v>477</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>59200000</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-5.857142857142858</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>435</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-1702314.814814817</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.2092592592592593</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.4953703703703702</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0.6537037037036839</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>3.736258712239106</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>2.74826816248385</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>6</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0.7981481481481438</v>
+      </c>
+      <c r="DH18" t="n">
         <v>1.462250893623434</v>
       </c>
-      <c r="CV18" t="n">
-        <v>-12100000</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>147</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>0.6537037037036839</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>-1.021197031000952</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>3.736258712239106</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>-0.1715608465608467</v>
-      </c>
-      <c r="DB18" t="n">
-        <v>0.6157407407407476</v>
-      </c>
-      <c r="DC18" t="n">
+      <c r="DI18" t="n">
         <v>-441157.7257165518</v>
       </c>
-      <c r="DD18" t="n">
-        <v>-0.2092592592592593</v>
-      </c>
-      <c r="DE18" t="n">
-        <v>0.7981481481481438</v>
-      </c>
-      <c r="DF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>2.74826816248385</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>-0.4953703703703702</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>4224.358194456236</v>
-      </c>
       <c r="DJ18" t="n">
-        <v>-1702314.814814817</v>
+        <v>4.714285714285722</v>
       </c>
     </row>
     <row r="19">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
@@ -6702,58 +6702,58 @@
       <c r="CN19" t="n">
         <v>-1.806516014849336</v>
       </c>
-      <c r="CO19" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="CP19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="n">
+        <v>-34500</v>
+      </c>
       <c r="CQ19" t="n">
-        <v>-49000</v>
+        <v>-3.196013293981537</v>
       </c>
       <c r="CR19" t="n">
-        <v>-87</v>
+        <v>-0.06056290039939416</v>
       </c>
       <c r="CS19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>-5</v>
-      </c>
+        <v>3702.475792718637</v>
+      </c>
+      <c r="CT19" t="inlineStr"/>
       <c r="CU19" t="n">
-        <v>-3.792695099985139</v>
+        <v>-49.375</v>
       </c>
       <c r="CV19" t="n">
-        <v>-32000000</v>
+        <v>-28575000</v>
       </c>
       <c r="CW19" t="n">
-        <v>-87</v>
-      </c>
-      <c r="CX19" t="inlineStr"/>
-      <c r="CY19" t="n">
-        <v>-3.196013293981537</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>1.286324889957825</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>-0.06056290039939416</v>
-      </c>
+        <v>-4.458333333333336</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>-49.75</v>
+      </c>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="inlineStr"/>
       <c r="DB19" t="inlineStr"/>
       <c r="DC19" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>1.286324889957825</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>3.879932556156433</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="n">
+        <v>-3.792695099985139</v>
+      </c>
+      <c r="DI19" t="n">
         <v>-456733.134721959</v>
       </c>
-      <c r="DD19" t="inlineStr"/>
-      <c r="DE19" t="inlineStr"/>
-      <c r="DF19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DG19" t="n">
-        <v>3.879932556156433</v>
-      </c>
-      <c r="DH19" t="inlineStr"/>
-      <c r="DI19" t="n">
-        <v>3702.475792718637</v>
-      </c>
-      <c r="DJ19" t="inlineStr"/>
+      <c r="DJ19" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
@@ -7013,70 +7013,70 @@
         <v>2.047569444444449</v>
       </c>
       <c r="CO20" t="n">
-        <v>7.592592592592581</v>
+        <v>11488.5101010101</v>
       </c>
       <c r="CP20" t="n">
-        <v>11488.5101010101</v>
+        <v>34888.88888888889</v>
       </c>
       <c r="CQ20" t="n">
-        <v>34888.88888888889</v>
+        <v>2.037654192356229</v>
       </c>
       <c r="CR20" t="n">
-        <v>47.55555555555556</v>
+        <v>0.4484186876504985</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.444444444444445</v>
+        <v>11226.19686051059</v>
       </c>
       <c r="CT20" t="n">
-        <v>-2.685185185185187</v>
+        <v>5.29406565656565</v>
       </c>
       <c r="CU20" t="n">
-        <v>4.191945282386456</v>
+        <v>52.44444444444444</v>
       </c>
       <c r="CV20" t="n">
         <v>64722222.22222222</v>
       </c>
       <c r="CW20" t="n">
-        <v>52.44444444444444</v>
+        <v>-2.685185185185187</v>
       </c>
       <c r="CX20" t="n">
+        <v>47.55555555555556</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>18140618.68686868</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0.8519886363636364</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0.2441287878787826</v>
+      </c>
+      <c r="DB20" t="n">
         <v>1.107733585858625</v>
       </c>
-      <c r="CY20" t="n">
-        <v>2.037654192356229</v>
-      </c>
-      <c r="CZ20" t="n">
+      <c r="DC20" t="n">
+        <v>2.444444444444445</v>
+      </c>
+      <c r="DD20" t="n">
         <v>4.512422223912807</v>
       </c>
-      <c r="DA20" t="n">
-        <v>0.4484186876504985</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>5.29406565656565</v>
-      </c>
-      <c r="DC20" t="n">
-        <v>11633390.99789338</v>
-      </c>
-      <c r="DD20" t="n">
-        <v>0.8519886363636364</v>
-      </c>
       <c r="DE20" t="n">
-        <v>5.565625000000011</v>
+        <v>0.3904297466474951</v>
       </c>
       <c r="DF20" t="n">
         <v>0.4444444444444444</v>
       </c>
       <c r="DG20" t="n">
-        <v>0.3904297466474951</v>
+        <v>5.565625000000011</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.2441287878787826</v>
+        <v>4.191945282386456</v>
       </c>
       <c r="DI20" t="n">
-        <v>11226.19686051059</v>
+        <v>11633390.99789338</v>
       </c>
       <c r="DJ20" t="n">
-        <v>18140618.68686868</v>
+        <v>7.592592592592581</v>
       </c>
     </row>
     <row r="21">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
@@ -7337,70 +7337,70 @@
         <v>5.19629629629631</v>
       </c>
       <c r="CO21" t="n">
-        <v>3.916666666666657</v>
+        <v>2291.269841269841</v>
       </c>
       <c r="CP21" t="n">
-        <v>2291.269841269841</v>
+        <v>7833.333333333332</v>
       </c>
       <c r="CQ21" t="n">
-        <v>7833.333333333332</v>
+        <v>0.4662258465436651</v>
       </c>
       <c r="CR21" t="n">
+        <v>0.0086789504535838</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>6206.819544323746</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>1.50238095238096</v>
+      </c>
+      <c r="CU21" t="n">
         <v>13</v>
-      </c>
-      <c r="CS21" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="CT21" t="n">
-        <v>1.916666666666668</v>
-      </c>
-      <c r="CU21" t="n">
-        <v>2.419239095390822</v>
       </c>
       <c r="CV21" t="n">
         <v>1083333.333333333</v>
       </c>
       <c r="CW21" t="n">
+        <v>1.916666666666668</v>
+      </c>
+      <c r="CX21" t="n">
         <v>13</v>
       </c>
-      <c r="CX21" t="n">
+      <c r="CY21" t="n">
+        <v>1124325.396825397</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>0.001984126984127199</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>-0.8797619047619065</v>
+      </c>
+      <c r="DB21" t="n">
         <v>2.460714285714317</v>
       </c>
-      <c r="CY21" t="n">
-        <v>0.4662258465436651</v>
-      </c>
-      <c r="CZ21" t="n">
+      <c r="DC21" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="DD21" t="n">
         <v>1.071900232251565</v>
       </c>
-      <c r="DA21" t="n">
-        <v>0.0086789504535838</v>
-      </c>
-      <c r="DB21" t="n">
-        <v>1.50238095238096</v>
-      </c>
-      <c r="DC21" t="n">
-        <v>1826889.830915608</v>
-      </c>
-      <c r="DD21" t="n">
-        <v>0.001984126984127199</v>
-      </c>
       <c r="DE21" t="n">
-        <v>0.6412698412698461</v>
+        <v>-1.775832218158737</v>
       </c>
       <c r="DF21" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="DG21" t="n">
-        <v>-1.775832218158737</v>
+        <v>0.6412698412698461</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0.8797619047619065</v>
+        <v>2.419239095390822</v>
       </c>
       <c r="DI21" t="n">
-        <v>6206.819544323746</v>
+        <v>1826889.830915608</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1124325.396825397</v>
+        <v>3.916666666666657</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ6"/>
+  <dimension ref="A1:DJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,144 +890,144 @@
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1054,160 +1054,176 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4899999999999998</v>
+        <v>-0.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7033333333333336</v>
+        <v>-0.17</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01666666666666683</v>
+        <v>0.399285714285714</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2233333333333334</v>
+        <v>0.155</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.2666666666666666</v>
       </c>
       <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>-1</v>
       </c>
-      <c r="Y2" t="n">
-        <v>-1.666666666666667</v>
-      </c>
       <c r="Z2" t="n">
-        <v>-1.466666666666667</v>
+        <v>0.7142857142857149</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.7142857142857144</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.6666666666666661</v>
+        <v>-8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.4000000000000004</v>
+        <v>-2.357142857142858</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4000000000000004</v>
+        <v>2.857142857142856</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.1333333333333334</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.06666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.06666666666666687</v>
+        <v>-0.4666666666666668</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2.744444444444444</v>
+        <v>19.15384615384615</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.429545454545455</v>
+        <v>-7.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4466741591741594</v>
+        <v>2.246598936777509</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1712218028884696</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>-2.142361408432837</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>246.0264150943396</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-597.0299727520436</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>246.0264150943396</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-597.0299727520436</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-11.45454545454545</v>
+        <v>-2.222222222222229</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.54545454545455</v>
+        <v>8.444444444444443</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>7.090909090909093</v>
+        <v>5.888888888888893</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.63636363636364</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.333333333333336</v>
+        <v>-9</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1.800000000000004</v>
+        <v>-8.06666666666667</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>-11.73333333333333</v>
       </c>
       <c r="BH2" t="n">
-        <v>-13.33333333333334</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
-        <v>13.33333333333334</v>
+        <v>-4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-13.66666666666666</v>
+        <v>8.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>13.66666666666666</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
+        <v>-8.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>262</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>241</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>262</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>241</v>
+      </c>
       <c r="BP2" t="n">
-        <v>-1.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.8333333333333335</v>
+        <v>-3</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.09743589743589753</v>
+        <v>-0.2582417582417582</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.5333333333333332</v>
+        <v>-1.291208791208791</v>
       </c>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
@@ -1215,143 +1231,151 @@
         <v>0.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.8333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BX2" t="n">
-        <v>-2.666666666666666</v>
+        <v>-11</v>
       </c>
       <c r="BY2" t="n">
-        <v>-3.333333333333334</v>
+        <v>-2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.2666666666666675</v>
+        <v>-7.133333333333333</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.4000000000000004</v>
-      </c>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>16.51148936170213</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>12.51190476190476</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>16.51148936170213</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>12.51190476190476</v>
+      </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr"/>
       <c r="CH2" t="n">
-        <v>-0.01177850786289869</v>
+        <v>0.0018336132785024</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.005999152381633309</v>
+        <v>0.03187305759219961</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.2</v>
+        <v>-0.1333333333333334</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.5913825757575637</v>
+        <v>0.7906552706552787</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.8541666666666572</v>
+        <v>-0.1035493827160536</v>
       </c>
       <c r="CP2" t="n">
-        <v>7353.639278677972</v>
+        <v>0.05810185185185213</v>
       </c>
       <c r="CQ2" t="n">
-        <v>83</v>
+        <v>0.8173091728819273</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.1450131079146217</v>
+        <v>-2894.470181234887</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.05277777777777759</v>
+        <v>0.1225517182431528</v>
       </c>
       <c r="CT2" t="n">
-        <v>2</v>
+        <v>-3.047354497354519</v>
       </c>
       <c r="CU2" t="n">
-        <v>1</v>
+        <v>-0.3954861111111256</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.0823388615813152</v>
+        <v>-6300.694444444442</v>
       </c>
       <c r="CW2" t="n">
-        <v>10237534.72222222</v>
+        <v>692857.1428571437</v>
       </c>
       <c r="CX2" t="n">
-        <v>3.806071816685204</v>
+        <v>0.06242283950615501</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.363541666666663</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.02116743926438858</v>
+        <v>-2.144984567901247</v>
       </c>
       <c r="DA2" t="n">
-        <v>-2.617772427950442</v>
+        <v>-0.6010271825029179</v>
       </c>
       <c r="DB2" t="n">
-        <v>3195875.742442111</v>
+        <v>31936.50793650794</v>
       </c>
       <c r="DC2" t="n">
-        <v>14900000</v>
+        <v>1.158730158730159</v>
       </c>
       <c r="DD2" t="n">
-        <v>15382.63888888889</v>
+        <v>1.230952380952381</v>
       </c>
       <c r="DE2" t="n">
-        <v>3.682638888888889</v>
+        <v>-0.4077198558235722</v>
       </c>
       <c r="DF2" t="n">
-        <v>-3.943402777777777</v>
+        <v>93.15873015873017</v>
       </c>
       <c r="DG2" t="n">
-        <v>76</v>
+        <v>-1875689.62191358</v>
       </c>
       <c r="DH2" t="n">
-        <v>-1</v>
+        <v>90.09523809523807</v>
       </c>
       <c r="DI2" t="n">
-        <v>7.5</v>
+        <v>-1.57096874812305</v>
       </c>
       <c r="DJ2" t="n">
-        <v>46000</v>
+        <v>-798350.0388834495</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.66666666666</v>
+        <v>45599.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1378,7 +1402,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1390,278 +1414,304 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.115</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6450000000000002</v>
+        <v>-0.5700000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7826666666666664</v>
+        <v>-0.4728571428571426</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1419999999999999</v>
+        <v>0.01500000000000035</v>
       </c>
       <c r="T3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8666666666666667</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="X3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.8</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.266666666666667</v>
+        <v>-0.785714285714286</v>
       </c>
       <c r="AB3" t="n">
         <v>0.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.533333333333333</v>
+        <v>-3.714285714285714</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3.4</v>
+        <v>-0.5714285714285712</v>
       </c>
       <c r="AF3" t="n">
         <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.533333333333333</v>
+        <v>0.2666666666666668</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.266666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="AN3" t="n">
-        <v>-3.536471861471862</v>
+        <v>3.75</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.561363636363637</v>
+        <v>-1.516917293233083</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3.055867014091652</v>
+        <v>1.997565800949259</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.269771043771044</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+        <v>-0.4302571405816651</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>310.0229166666667</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-343.0536193029491</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>310.0229166666667</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-343.0536193029491</v>
+      </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>29.72727272727272</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AY3" t="n">
-        <v>-37.72727272727273</v>
+        <v>-9.888888888888886</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>10.90909090909091</v>
+        <v>-4.666666666666664</v>
       </c>
       <c r="BC3" t="n">
-        <v>-13.81818181818181</v>
+        <v>-4.55555555555555</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.5</v>
+        <v>-2</v>
       </c>
       <c r="BE3" t="n">
-        <v>-5</v>
+        <v>0.6666666666666643</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.933333333333337</v>
+        <v>-3.266666666666666</v>
       </c>
       <c r="BG3" t="n">
-        <v>-8</v>
+        <v>4.200000000000003</v>
       </c>
       <c r="BH3" t="n">
-        <v>14</v>
+        <v>-1.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.66666666666667</v>
+        <v>-4.642857142857139</v>
       </c>
       <c r="BK3" t="n">
-        <v>-13.66666666666666</v>
-      </c>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
+        <v>4.642857142857139</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>158</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-24</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>158</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-24</v>
+      </c>
       <c r="BP3" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>-1.533333333333333</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.06666666666666643</v>
-      </c>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
+        <v>-0.4285714285714284</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="BV3" t="n">
-        <v>-0.3</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.3</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="BX3" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.5</v>
+        <v>0.6666666666666661</v>
       </c>
       <c r="BZ3" t="n">
+        <v>-0.3333333333333321</v>
+      </c>
+      <c r="CA3" t="n">
         <v>-2.733333333333333</v>
       </c>
-      <c r="CA3" t="n">
-        <v>-0.4666666666666668</v>
-      </c>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
+      <c r="CB3" t="n">
+        <v>-1.142857142857142</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>2.619528619528619</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-1.142857142857142</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>2.619528619528619</v>
+      </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
       <c r="CH3" t="n">
-        <v>0.01840877662422498</v>
+        <v>-0.003308154147895905</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0227685815200746</v>
+        <v>0.01546041931248696</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1333333333333334</v>
+        <v>0</v>
       </c>
       <c r="CM3" t="n">
         <v>-0.2666666666666667</v>
       </c>
-      <c r="CN3" t="n">
-        <v>-0.4925602175602108</v>
-      </c>
+      <c r="CN3" t="inlineStr"/>
       <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="n">
-        <v>39284.1595538964</v>
-      </c>
+      <c r="CP3" t="inlineStr"/>
       <c r="CQ3" t="n">
-        <v>185</v>
+        <v>3.571621959147759</v>
       </c>
       <c r="CR3" t="n">
-        <v>-2.273595446950722</v>
-      </c>
-      <c r="CS3" t="inlineStr"/>
+        <v>6577.624427134229</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>0.2360999390282152</v>
+      </c>
       <c r="CT3" t="n">
-        <v>9</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0.3988457448983764</v>
-      </c>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="n">
-        <v>1.88699044011544</v>
-      </c>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="n">
-        <v>-0.3700844112028392</v>
-      </c>
+        <v>3.222222222222229</v>
+      </c>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="n">
+        <v>69016666.66666666</v>
+      </c>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="n">
+        <v>-0.4444444444444442</v>
+      </c>
+      <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>-3.696933366341259</v>
+        <v>3.953197203171399</v>
       </c>
       <c r="DB3" t="n">
-        <v>9641895.405398695</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>142000000</v>
-      </c>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="n">
-        <v>177</v>
-      </c>
+        <v>-0.8888888888888893</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>-2.918518518518521</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>-0.6741392957079029</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="DG3" t="inlineStr"/>
       <c r="DH3" t="n">
-        <v>-0.6666666666666679</v>
+        <v>-19.88888888888891</v>
       </c>
       <c r="DI3" t="n">
-        <v>-1.666666666666657</v>
+        <v>0.7287174331421511</v>
       </c>
       <c r="DJ3" t="n">
-        <v>372000</v>
+        <v>8393255.375396114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.5625</v>
+        <v>45599.60416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1688,304 +1738,314 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5349999999999999</v>
+        <v>-0.125</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4124999999999999</v>
+        <v>2.095</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5313333333333332</v>
+        <v>0.2764285714285715</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3500000000000005</v>
+        <v>0.4071428571428573</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2</v>
+        <v>0.2666666666666668</v>
       </c>
       <c r="X4" t="n">
-        <v>0.25</v>
+        <v>-2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8000000000000003</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>-4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.866666666666667</v>
+        <v>2.714285714285715</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.266666666666666</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.25</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.133333333333333</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1.066666666666667</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>-4.302231102231103</v>
+        <v>3.508928571428572</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08030303030303054</v>
+        <v>-3.919642857142857</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1.09518272903567</v>
+        <v>-0.8115221088435378</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2.533368797064449</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
+        <v>-0.8155740886098033</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>195</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.01480258150933058</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>195</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.01480258150933058</v>
+      </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-13.18181818181819</v>
+        <v>-9.333333333333329</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.18181818181817</v>
+        <v>6.51111111111112</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>2.181818181818187</v>
+        <v>-0.74444444444444</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>1.966666666666661</v>
       </c>
       <c r="BD4" t="n">
-        <v>-20.25</v>
+        <v>-4.333333333333332</v>
       </c>
       <c r="BE4" t="n">
-        <v>-19.25</v>
+        <v>2.666666666666664</v>
       </c>
       <c r="BF4" t="n">
-        <v>-13.53333333333334</v>
+        <v>-2.799999999999997</v>
       </c>
       <c r="BG4" t="n">
-        <v>-13.93333333333334</v>
+        <v>-1.466666666666669</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.25</v>
+        <v>-17.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.25</v>
+        <v>17.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.7333333333333343</v>
+        <v>-3.928571428571423</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.7333333333333343</v>
-      </c>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
+        <v>3.928571428571423</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-202</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>186</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-202</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>186</v>
+      </c>
       <c r="BP4" t="n">
-        <v>0.25</v>
+        <v>3.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.3333333333333335</v>
+        <v>1.054945054945055</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.4666666666666668</v>
+        <v>-0.4670329670329667</v>
       </c>
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.75</v>
+        <v>-0.3</v>
       </c>
       <c r="BX4" t="n">
-        <v>-1.75</v>
+        <v>6.666666666666668</v>
       </c>
       <c r="BY4" t="n">
-        <v>-2.5</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-5.533333333333335</v>
+        <v>0.1333333333333329</v>
       </c>
       <c r="CA4" t="n">
-        <v>-1.933333333333332</v>
-      </c>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
+        <v>-0.9333333333333318</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-1.593548387096774</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-13.71323529411765</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-1.593548387096774</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-13.71323529411765</v>
+      </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr"/>
       <c r="CH4" t="n">
-        <v>-0.01212574865551905</v>
+        <v>0.00364464958517495</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0305725186780594</v>
+        <v>-0.0004976324132801996</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.06666666666666668</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.1333333333333334</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.464166666666685</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>2.480555555555554</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>9103.55791439383</v>
-      </c>
+        <v>-0.5582533670033598</v>
+      </c>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
       <c r="CQ4" t="n">
-        <v>331.5</v>
+        <v>0.6680942514275827</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.399367385280698</v>
+        <v>-3743.201660358518</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.5406250000000004</v>
+        <v>-0.3345257139374787</v>
       </c>
       <c r="CT4" t="n">
-        <v>9.666666666666666</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>0.408214706260372</v>
-      </c>
+        <v>4.673611111111143</v>
+      </c>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
       <c r="CW4" t="n">
-        <v>4237673.611111111</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>2.793129157027195</v>
-      </c>
+        <v>-22280555.55555555</v>
+      </c>
+      <c r="CX4" t="inlineStr"/>
       <c r="CY4" t="n">
-        <v>2.300694444444446</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>-0.3557595145008463</v>
-      </c>
+        <v>-1.75</v>
+      </c>
+      <c r="CZ4" t="inlineStr"/>
       <c r="DA4" t="n">
-        <v>0.9489639918045469</v>
+        <v>1.798418828810995</v>
       </c>
       <c r="DB4" t="n">
-        <v>1560894.601641264</v>
+        <v>-63972.22222222222</v>
       </c>
       <c r="DC4" t="n">
-        <v>72266666.66666667</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="DD4" t="n">
-        <v>7601.388888888891</v>
+        <v>1.268518518518519</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.448958333333337</v>
+        <v>1.071183591281624</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.387847222222224</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>338</v>
-      </c>
+        <v>-132.4861111111111</v>
+      </c>
+      <c r="DG4" t="inlineStr"/>
       <c r="DH4" t="n">
-        <v>4.5</v>
+        <v>-145.1666666666667</v>
       </c>
       <c r="DI4" t="n">
-        <v>3.125</v>
+        <v>-0.2462309114270056</v>
       </c>
       <c r="DJ4" t="n">
-        <v>214000</v>
+        <v>-2184636.888166299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.46875</v>
+        <v>45599.51041666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2012,288 +2072,314 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07166666666666666</v>
+        <v>2.385</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2025</v>
+        <v>-0.145</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5860000000000003</v>
+        <v>1.176095238095238</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1906666666666668</v>
+        <v>-0.3856190476190475</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5333333333333334</v>
+        <v>0.8280701754385964</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7298245614035087</v>
       </c>
       <c r="X5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.293650793650793</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>6.388888888888889</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-4.253968253968253</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.2698412698412699</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.06666666666666643</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.200000000000001</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.5999999999999996</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.08333333333333337</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AK5" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8666666666666667</v>
+        <v>1.298245614035088</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-1.101754385964912</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9999999999999996</v>
+        <v>-4.044642857142857</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.8458333333333334</v>
+        <v>1.795454545454545</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.168111777111778</v>
+        <v>-3.677674083682311</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.4774074074074077</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+        <v>2.160460375944247</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>343.0358306188925</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-288.0229166666667</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>343.0358306188925</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-288.0229166666667</v>
+      </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-2.27272727272728</v>
+        <v>25.13675213675214</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.181818181818187</v>
+        <v>-36.04273504273505</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>3</v>
+        <v>14.44444444444444</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.909090909090907</v>
+        <v>-13.57264957264957</v>
       </c>
       <c r="BD5" t="n">
-        <v>-6.333333333333336</v>
+        <v>-1.666666666666668</v>
       </c>
       <c r="BE5" t="n">
-        <v>-21</v>
+        <v>-11.66666666666667</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1.133333333333333</v>
+        <v>3.992982456140354</v>
       </c>
       <c r="BG5" t="n">
-        <v>-12.13333333333333</v>
+        <v>-8.428070175438595</v>
       </c>
       <c r="BH5" t="n">
-        <v>-6.25</v>
+        <v>28.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>6.25</v>
+        <v>-28.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3.333333333333329</v>
+        <v>20.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>-3.333333333333329</v>
-      </c>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
+        <v>-20.5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>265</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-184</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>265</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-184</v>
+      </c>
       <c r="BP5" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-1.333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.338095238095238</v>
+        <v>-0.8809523809523807</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>0.2936507936507939</v>
       </c>
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-2.583333333333332</v>
+        <v>-6.666666666666666</v>
       </c>
       <c r="BY5" t="n">
-        <v>-5.083333333333332</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-2.066666666666666</v>
+        <v>-4.635087719298246</v>
       </c>
       <c r="CA5" t="n">
-        <v>-2.933333333333332</v>
-      </c>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
+        <v>-1.831578947368421</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>2.866310160427807</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>3.187403993855604</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>2.866310160427807</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>3.187403993855604</v>
+      </c>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="n">
-        <v>-0.0153523598376037</v>
+        <v>0.01351418202566566</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01569763733121778</v>
+        <v>0.01231768384485873</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.08333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.4</v>
+        <v>0.0315789473684211</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="CN5" t="inlineStr"/>
+        <v>-0.4210526315789473</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.2904332678638326</v>
+      </c>
       <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="n">
-        <v>46318.75881632557</v>
-      </c>
+      <c r="CP5" t="inlineStr"/>
       <c r="CQ5" t="n">
-        <v>90</v>
+        <v>-5.343104022167491</v>
       </c>
       <c r="CR5" t="n">
-        <v>8.591209662692847</v>
-      </c>
-      <c r="CS5" t="inlineStr"/>
+        <v>48874.96865879219</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0.6794140232736725</v>
+      </c>
       <c r="CT5" t="n">
-        <v>5</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1.233601613492287</v>
-      </c>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="n">
-        <v>7.852309437531005</v>
-      </c>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="n">
-        <v>-2.400285200802813</v>
-      </c>
+        <v>1.18981481481481</v>
+      </c>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="n">
+        <v>195520833.3333333</v>
+      </c>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="n">
+        <v>1.958333333333333</v>
+      </c>
+      <c r="CZ5" t="inlineStr"/>
       <c r="DA5" t="n">
-        <v>0.9094929419136051</v>
+        <v>0.4118308281749989</v>
       </c>
       <c r="DB5" t="n">
-        <v>19628341.23975547</v>
+        <v>464222.2222222222</v>
       </c>
       <c r="DC5" t="n">
-        <v>45200000</v>
-      </c>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="n">
-        <v>98</v>
-      </c>
+        <v>10.95833333333333</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-2.587962962962969</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>6.105553116092338</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="DG5" t="inlineStr"/>
       <c r="DH5" t="n">
-        <v>8.5</v>
+        <v>192.5277777777778</v>
       </c>
       <c r="DI5" t="n">
-        <v>2.5</v>
+        <v>0.2200992291162436</v>
       </c>
       <c r="DJ5" t="n">
-        <v>126000</v>
+        <v>17199680.72867583</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.375</v>
+        <v>45599.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2320,28 +2406,28 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>tI57YghG</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1933333333333336</v>
+        <v>0.5950000000000002</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1758333333333333</v>
+        <v>-0.5900000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.08066666666666666</v>
+        <v>0.5828571428571427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3533333333333335</v>
+        <v>-0.9149999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>0.6666666666666667</v>
@@ -2350,243 +2436,5471 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.08333333333333348</v>
+        <v>0.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1333333333333329</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2666666666666666</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.5833333333333339</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5833333333333339</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.3333333333333339</v>
+        <v>-2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5833333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2666666666666666</v>
+        <v>-0.9285714285714285</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.25</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.4000000000000001</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.4000000000000001</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AN6" t="n">
-        <v>-5.564583333333333</v>
+        <v>2.541666666666667</v>
       </c>
       <c r="AO6" t="n">
-        <v>4.906759906759907</v>
+        <v>-0.04464285714285721</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.078391001355842</v>
+        <v>1.061016542980829</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.9251354201354203</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+        <v>1.533856619570905</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>478.0440140845071</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-336.0365853658537</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>478.0440140845071</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-336.0365853658537</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>2.75</v>
+        <v>-13.66666666666666</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.681818181818187</v>
+        <v>14.55555555555556</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-5.212121212121211</v>
+        <v>3.777777777777771</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.93181818181818</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.333333333333336</v>
+        <v>-3.333333333333332</v>
       </c>
       <c r="BE6" t="n">
-        <v>1</v>
+        <v>-2.666666666666668</v>
       </c>
       <c r="BF6" t="n">
-        <v>-3.666666666666671</v>
+        <v>-6.866666666666667</v>
       </c>
       <c r="BG6" t="n">
-        <v>-3.533333333333331</v>
+        <v>-4.133333333333333</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.4166666666666643</v>
+        <v>-8</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.4166666666666643</v>
+        <v>8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-1.600000000000001</v>
+        <v>-7.428571428571423</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.600000000000001</v>
-      </c>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
+        <v>7.428571428571423</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-68</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>78</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-68</v>
+      </c>
       <c r="BP6" t="n">
-        <v>0.666666666666667</v>
+        <v>-2.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.333333333333333</v>
+        <v>-5.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.2333333333333334</v>
+        <v>-0.2692307692307692</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.6095238095238094</v>
+        <v>-0.7197802197802197</v>
       </c>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.6666666666666666</v>
+        <v>-1.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.583333333333332</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-2.333333333333334</v>
+        <v>0.2666666666666675</v>
       </c>
       <c r="CA6" t="n">
-        <v>-3.066666666666665</v>
-      </c>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-7.024509803921568</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-1.235690235690235</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-7.024509803921568</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-1.235690235690235</v>
+      </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="n">
-        <v>-0.01643228294216253</v>
+        <v>-0.03180036380556536</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.005748529422383589</v>
+        <v>0.02163923454806881</v>
       </c>
       <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.221317340067344</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.171180555555559</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1.618402777777778</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.715789132417104</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>52165.7883009663</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>1.158975728338473</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-2.666666666666657</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>6.324652777777771</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>61696.875</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>25719444.44444444</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.441319444444446</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.3194444444444446</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>7.047569444444434</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>6.641332584779434</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>79402.77777777778</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>2.013888888888889</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0.1481481481481488</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>7.0204687669858</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-14.29166666666666</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>23877083.33333333</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-13.09722222222223</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.05008014813228101</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>18644525.17583323</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>148</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4900000000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.2750000000000001</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.7914285714285716</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-3.428571428571428</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.4999999999999996</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-5.785714285714286</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.9285714285714288</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.970779220779221</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.985576923076923</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.484906924646692</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.2748376623376636</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>597.0365853658536</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-478.0264150943396</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>597.0365853658536</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-478.0264150943396</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>-24.33333333333333</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>-16.22222222222222</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-7.777777777777779</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>13.33333333333334</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-15.71428571428572</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-198</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-40</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-198</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-40</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.6666666666666679</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.7333333333333325</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.1893939393939412</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>-7.236666666666668</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.1893939393939412</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-7.236666666666668</v>
+      </c>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="n">
+        <v>0.03399765127862761</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-0.02312260921509684</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.333973765432091</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-3.064197530864195</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-2.287345679012346</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-1.425711479878146</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-115637.5548833882</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-1.251888697722031</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>2.509259259259238</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-7.267283950617283</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>-190195.3703703704</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-128188888.8888889</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>-1.129320987654353</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-9.594753086419772</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>-7.44786340203008</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-306666.6666666667</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-1.555555555555556</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2.972222222222225</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>-6.523322356655683</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>86.66666666666666</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-51843873.4567901</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-1.611619861619829</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-32753650.19240019</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.5249999999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.9750000000000001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5528571428571432</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.7857142857142856</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.928571428571428</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.214285714285715</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.7142857142857144</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-9.493191019506808</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.2517493151106596</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.085373680204508</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>360.0299727520436</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-246.0544959128065</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>360.0299727520436</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-246.0544959128065</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.1111111111111143</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>0.7777777777777786</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11.55555555555555</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-4.666666666666664</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-5.333333333333332</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-9.600000000000001</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-1.857142857142861</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.857142857142861</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-99</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-99</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.7527472527472527</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.7087912087912085</v>
+      </c>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>5.999999999999998</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-1.866666666666667</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>-7.904761904761903</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-7.649822695035462</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-7.904761904761903</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-7.649822695035462</v>
+      </c>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="n">
+        <v>0.002064420092261814</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.02803070670750454</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0.1333333333333334</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.8145524691357906</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0.2689814814814859</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.3337962962962968</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-3.649594154650913</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>11829.94018795103</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0.04435356238761812</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>4.30324074074079</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>3.161111111111126</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>13970.37037037037</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>59533333.33333334</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>3.763888888888886</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>1.527777777777778</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2.572685185185193</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>-1.048246517080372</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>128194.4444444444</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>3.440972222222229</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>2.917957359882038</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>143.5416666666667</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>4541851.851851851</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>132.6666666666667</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>2.325283577218556</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>608546.971795165</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45598.51041666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9135714285714286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1142857142857141</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.214285714285714</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2142857142857135</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.607142857142857</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-9.083333333333334</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1.407706975564118</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.7889703289609304</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>336.0210280373832</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-483.0440140845071</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>336.0210280373832</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-483.0440140845071</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>19.66666666666667</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-44</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-9.333333333333336</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-11.66666666666667</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.7999999999999972</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-14.66666666666667</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>17.64285714285715</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-17.64285714285715</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>86</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-70</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>86</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-70</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-0.2197802197802197</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.4780219780219781</v>
+      </c>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-3.200000000000001</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>10.08796296296296</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>11.34117647058823</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>10.08796296296296</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>11.34117647058823</v>
+      </c>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="n">
+        <v>0.01434245842258742</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0005234947851389601</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0.06666666666666671</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.2550110479798064</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0.8703703703703702</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.7490740740740742</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.5148393674322449</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>6145.952931943641</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.3472506094410119</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0.3395061728394921</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>6.504629629629633</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>15003.70370370371</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>20144444.44444444</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>-2.157407407407391</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>2.055555555555555</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>6.795370370370364</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>4.605511141192238</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>51611.11111111111</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>-1.138888888888889</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>5.481758857184559</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>146.1666666666667</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>15685185.18518519</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>168.4444444444445</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.1762050513985685</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>6231386.013868598</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45598.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5900000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2314285714285715</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1164285714285711</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.7857142857142856</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-2.285714285714285</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.3571428571428572</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.5333333333333332</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.975708502024291</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.44090909090909</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.417059851176393</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.1631795999032022</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>234.0536193029491</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-310.0263157894737</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>234.0536193029491</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-310.0263157894737</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>13.33333333333334</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>-2.222222222222221</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.888888888888886</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.866666666666667</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.86666666666666</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1.071428571428577</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.071428571428577</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>126</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-96</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>126</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-96</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0.4670329670329667</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-1.733333333333333</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-3.266666666666666</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-4.150997150997151</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>7.022774327122153</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-4.150997150997151</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>7.022774327122153</v>
+      </c>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="n">
+        <v>-0.009588637332531035</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.02011775127070261</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>2.012089646464631</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.08113425925925455</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.1401620370370369</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.1415258888471946</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>8496.216211706746</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.09609104028440441</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.6296296296296475</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>4.83865740740741</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>11814.81481481482</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>5722222.222222222</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>2.583333333333371</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0.5555555555555556</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>4.044907407407408</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.442986345236534</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>6111.111111111109</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0.5555555555555556</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>-0.8240740740740762</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1.855154943722823</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-31</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>7569548.61111111</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-33.66666666666667</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-1.658069733511695</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>3263739.122070886</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.025</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.05714285714285761</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.5614285714285715</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.3571428571428577</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.4285714285714288</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.07142857142857117</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>4.642822966507177</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-5.1875</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.401214906575291</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.3478055674484244</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.0281801233328553</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>126</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.0281801233328553</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>126</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>-1.933333333333323</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-12.83333333333333</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>-1.111111111111114</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-7.577777777777776</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-5.999999999999996</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.666666666666664</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.799999999999997</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-6.571428571428569</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.571428571428569</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-124</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>51</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-124</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.357142857142857</v>
+      </c>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.933333333333334</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-4.719202898550725</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-1.399267399267398</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-4.719202898550725</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-1.399267399267398</v>
+      </c>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="n">
+        <v>0.02773678164712738</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.005176533553321538</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.8615644540644638</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-1.701018518518516</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0.3633333333333333</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-1.583593940172886</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-2217.679753644661</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0.1871482643412468</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>2.407738095238102</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-2.314814814814824</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-8045.277777777777</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-16294642.85714286</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-1.870555555555541</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-3.358518518518522</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-2.379692407981878</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-37767.85714285714</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>2.291666666666664</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-1.313842760553285</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-91.82142857142857</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-6898935.185185186</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-100.2321428571429</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-1.208094804805341</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-4134132.31343056</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2516666666666667</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5349999999999999</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1300000000000001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.4953333333333334</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.5333333333333337</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.06666666666666643</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.998650472334683</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.2827380952380958</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.182074915405224</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.716169288228112</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.03157924613987284</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.03157924613987284</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>-18.53636363636365</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.681818181818187</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>2.709090909090904</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-1.036363636363632</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>11.33333333333334</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0.86666666666666</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-2.733333333333334</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>11.66666666666666</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-11.66666666666666</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.533333333333331</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-1.533333333333331</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.2666666666666668</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0.8000000000000003</v>
+      </c>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="n">
+        <v>-0.9166666666666667</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-1.833333333333332</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-1.200000000000001</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-1.160714285714286</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>2.93073593073593</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-1.160714285714286</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>2.93073593073593</v>
+      </c>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="n">
+        <v>0.001211204572177348</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-0.02496244407688095</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.58556998556999</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.777856341189672</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0.433131313131313</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-0.08963804799718389</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>-2531.06419724067</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0.2014521793804556</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-5.82361111111112</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-3.075925925925915</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-2993.540965207634</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-98062500</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.9916835016834682</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-2.233484848484849</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>-0.6963438713180636</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-68375</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-5.111111111111111</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-3.395370370370369</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-1.337470236734958</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-112.5277777777778</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>-11478156.56565656</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-107.625</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-1.241889292147306</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>-5935820.534002937</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.07333333333333369</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.433333333333334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.208</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.06666666666666687</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.7333333333333334</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-2.690390749601276</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.314393939393939</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1.288852375694481</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.9627307714072426</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-483.0536193029491</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>310.0210280373832</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-483.0536193029491</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>310.0210280373832</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>2.027272727272731</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-3.163636363636357</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>-0.3454545454545439</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-5.981818181818177</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.6666666666666643</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.73333333333333</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-10.73333333333333</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>125</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>106</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>125</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>106</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-2.166666666666667</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0.214285714285714</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.4285714285714284</v>
+      </c>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>9.474074074074073</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>13.36309523809524</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>9.474074074074073</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>13.36309523809524</v>
+      </c>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="n">
+        <v>-0.005689444030122441</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0.01223606889403565</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.8119149831649821</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0.3350694444444429</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.8802083333333335</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-2.748311173594967</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>2501.219197516919</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.4265535190070795</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>2.277777777777743</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>2.326388888888886</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>8527.777777777774</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>33111111.11111111</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-1.944444444444429</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.416666666666657</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-1.426482824212457</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>63333.33333333333</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>3.222222222222222</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>1.603634202150715</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>122</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>11503298.61111111</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>136.2222222222222</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>3.06947339821437</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>5004591.649034373</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45592.60416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7333333333333335</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.01466666666666661</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.7333333333333329</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-5.411111111111111</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.041040100250627</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.880552922710817</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.06897475331685854</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-310.0440140845071</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>336.0536193029491</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-310.0440140845071</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>336.0536193029491</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>4.400000000000006</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-5.799999999999997</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>6.399999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.866666666666667</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-246</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>31</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-246</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>31</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.2047619047619049</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.8047619047619048</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>6.333333333333332</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>3.133333333333331</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>7.703081232492998</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-9.111111111111112</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>7.703081232492998</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-9.111111111111112</v>
+      </c>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="n">
+        <v>0.01163916070996808</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-0.02288424412588812</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.5002097902097944</v>
+      </c>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="n">
+        <v>-4.524063042793692</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-49134.04071418775</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-1.045290665646703</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>3.122222222222206</v>
+      </c>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="n">
+        <v>8808333.333333336</v>
+      </c>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="n">
+        <v>1.986111111111111</v>
+      </c>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="n">
+        <v>-7.582604550019411</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-625</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>2.522222222222226</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>-1.625845390706075</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>148.4027777777778</v>
+      </c>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="n">
+        <v>150.7638888888889</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>3.213707820673733</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-16960541.94136044</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45592.51041666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>148</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.6499999999999998</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1213333333333334</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.2660000000000002</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.8666666666666663</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.666666666666668</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-2.733333333333334</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1.939393939393939</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1.762878787878788</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-2.228862004009063</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.288588263588264</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-246.0365853658537</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>478.0299727520436</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-246.0365853658537</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>478.0299727520436</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>7.400000000000006</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-12.19999999999999</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>-8.800000000000004</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.333333333333329</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.533333333333331</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.93333333333333</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.3333333333333286</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0.3333333333333286</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.1333333333333329</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-142</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-123</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-142</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-123</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.3897435897435897</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.5179487179487179</v>
+      </c>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>6.866666666666669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.8666666666666671</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-14.4642166344294</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-7.511904761904761</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-14.4642166344294</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-7.511904761904761</v>
+      </c>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="n">
+        <v>0.00160421600193246</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.003423476942068175</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.7444444444444542</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>3.532407407407408</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.09290123456790123</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>1.068241925104669</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-4435.88165646989</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.07694944851807595</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0.5952380952380736</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-3.404012345679007</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-7584.567901234568</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-39853968.25396825</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>-1.034876543209862</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>-1.809523809523809</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>-0.5830246913579913</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>-1.249735195813628</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-106714.2857142857</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-4.047619047619047</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>-0.5846560846560891</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>-2.893747220462899</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-157.2698412698413</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>-9138533.950617287</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>-156.4285714285714</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>2.720719213611375</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-2449237.251038723</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45592.41666666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.6266666666666665</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6566666666666667</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.7220000000000001</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.07133333333333347</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-1.733333333333333</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.2666666666666657</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-3.731837606837607</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3.072222222222222</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1.411942188246536</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.318963443963444</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-336.0264150943396</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>597.044014084507</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-336.0264150943396</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>597.044014084507</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>-5.099999999999994</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.400000000000006</v>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>-7.300000000000004</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.899999999999999</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.666666666666664</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>10.93333333333333</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.333333333333329</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-2.333333333333329</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-8.266666666666666</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>8.266666666666666</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-188</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-40</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-188</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-40</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-0.2999999999999998</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.4142857142857144</v>
+      </c>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="n">
         <v>-0.25</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1.333333333333332</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>2.066666666666666</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.8666666666666671</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>-3.282962962962962</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>-12.02450980392157</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-3.282962962962962</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-12.02450980392157</v>
+      </c>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="n">
+        <v>-0.01172540956133454</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0.01066149322241685</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-2.249412393162402</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>-0.6874999999999964</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-0.2673611111111112</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.3837964079837164</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>4911.746612520608</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0.2175649499565908</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1.725925925925935</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-1.293402777777771</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>3461.805555555555</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-9650000</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>2.288194444444457</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>-1.003472222222229</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>-0.531956413612761</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>-32722.22222222222</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>-1.944444444444445</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>-4.266666666666666</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>-1.694498743144266</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-118.9444444444445</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>-1642057.291666667</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-111.6666666666667</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>1.255867852191386</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-1700846.489180468</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.4156250000000001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.2124999999999999</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.03749999999999998</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.7041666666666666</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.2166666666666668</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.666666666666668</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.7250000000000014</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.5333333333333332</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.3291666666666667</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.2916666666666665</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.04166666666666669</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.9956709956709968</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-2.074980574980574</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.870880043361486</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-2.325801975801976</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-597.0358306188925</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>288.0264150943396</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-597.0358306188925</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>288.0264150943396</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>2.345454545454558</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>19.83636363636364</v>
+      </c>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>16.13636363636363</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>15.68181818181818</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-18</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-6.945833333333333</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.904166666666665</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-19.33333333333334</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-5.9375</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.9375</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>234</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>234</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-0.4125000000000001</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0.7833333333333334</v>
+      </c>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0.6083333333333325</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.8708333333333336</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>4.671568627450981</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>4.513548387096776</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>4.671568627450981</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>4.513548387096776</v>
+      </c>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="n">
+        <v>-0.03764650946538886</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>-0.01669084681906393</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.1583333333333333</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.6905477855477784</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>2.513811728395059</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.7821759259259258</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>4.454177425887952</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>76214.18627668628</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0.6297858817595661</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>-2.134259259259238</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>1.683101851851845</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>110212.5771604938</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-24287500</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>3.688580246913602</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-1.291666666666667</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>5.079706790123467</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>8.449365473707573</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-49333.33333333331</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-4.736111111111111</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>-1.643518518518515</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>4.090806724140052</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-107.9861111111111</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>29280883.48765431</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-110.0833333333333</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-1.122358181130124</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>20907022.80743947</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.0341666666666669</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.07083333333333353</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.6753333333333335</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2113333333333332</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.3999999999999995</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.8333333333333339</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.933333333333334</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.8666666666666666</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0.6964285714285712</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>3.964682539682539</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.6768746993746992</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.1717880511301555</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-478.0210280373832</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>483.0365853658537</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-478.0210280373832</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>483.0365853658537</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>-1.700000000000003</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>21.39999999999999</v>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.083333333333336</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7.733333333333334</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-1.866666666666667</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.866666666666667</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>62</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-88</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>62</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-88</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0.6142857142857141</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0.1142857142857143</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.583333333333332</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.933333333333334</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>-14.04166666666667</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.8727272727272748</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-14.04166666666667</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.8727272727272748</v>
+      </c>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="n">
+        <v>0.01681808427849318</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.02360492083723476</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.6065025252525231</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>2.02662037037037</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0.6865740740740742</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.2855608768405489</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-11846.5818810246</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0.2751886462541775</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1.006172839506149</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>-4.910879629629633</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-20128.70370370371</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-8188888.888888888</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-1.655092592592609</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-3.826620370370364</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-2.415103930106497</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>-33888.88888888889</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>-1.555555555555556</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>5.537037037037038</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-4.484119501069969</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>-64</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>-13303935.18518519</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-93.22222222222223</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>-2.426644231146298</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-4983175.116936726</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45591.46875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>148</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4866666666666665</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.3733333333333329</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.1159999999999999</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.1333333333333337</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.2666666666666657</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-4.752525252525253</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2.681607865818392</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.231915843778588</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.7312951181372234</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-360.0263157894737</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>234.0544959128065</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-360.0263157894737</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>234.0544959128065</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>0.9000000000000057</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.599999999999994</v>
+      </c>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>5.399999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.8000000000000043</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-8</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.533333333333331</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>6.666666666666664</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-6.666666666666664</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-8</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-47</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>120</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-47</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>120</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.2333333333333334</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.6619047619047618</v>
+      </c>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>-2.666666666666664</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.5333333333333314</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0.7333333333333343</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>6.737060041407865</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>-0.6185897435897427</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>6.737060041407865</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-0.6185897435897427</v>
+      </c>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
+      <c r="CH19" t="n">
+        <v>-0.007095342909798963</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>-0.008696876274300075</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>-1.123101851851843</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>2.579166666666669</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0.3398148148148146</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>4.626938558517505</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-3903.657818789397</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0.4874963081103432</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>-2.169312169312178</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0.2370370370370409</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>-2796.759259259259</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>5673809.523809523</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>-2.194444444444429</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>0.9365079365079365</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>1.605555555555554</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>2.536470384715997</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>12698.4126984127</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>-1.055555555555557</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>-0.7516195792511695</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>60.90476190476191</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>1749583.333333335</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>70.1904761904762</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>-1.644878399702947</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>2608108.59218754</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45591.375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>148</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4491666666666667</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.6146666666666665</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.3400000000000001</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.533333333333334</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.6000000000000005</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-1.583333333333334</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-2.866666666666665</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.8666666666666654</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3.085897435897436</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-3.013636363636364</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.765542124542125</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.09859360872148581</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-234.0299727520436</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>246.0263157894737</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-234.0299727520436</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>246.0263157894737</v>
+      </c>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-6.400000000000006</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-2.299999999999997</v>
+      </c>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="n">
+        <v>-0.1000000000000014</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-12.59999999999999</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>13.16666666666666</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.333333333333336</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>5.533333333333339</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-4.666666666666664</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>4.666666666666664</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.8000000000000043</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-0.8000000000000043</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>150</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>150</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-0.06666666666666687</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>-2.083333333333332</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>6.505494505494505</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>2.930619796484737</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>6.505494505494505</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>2.930619796484737</v>
+      </c>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr"/>
+      <c r="CH20" t="n">
+        <v>0.005109552916032371</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>-0.02939614806409017</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK20" t="n">
         <v>-0.25</v>
       </c>
-      <c r="CL6" t="n">
-        <v>0.06666666666666665</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>-0.2666666666666667</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>0.7606361231361092</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.848333333333329</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>6308.027325379298</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>-144</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.151469208788285</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>0.01513888888888926</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>-0.292308842473316</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>5297097.222222222</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.995637613483012</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>4.031249999999943</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>3.16401214830492</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>-2.966055928720404</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1525000.370608924</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-8550000</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>11023.47222222222</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>2.080833333333345</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>-0.8033333333333346</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>-139</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>-37000</v>
+      <c r="CL20" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>-4.9262962962963</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>-1.416203703703697</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>-0.6592592592592597</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>0.854960487979735</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>-14401.22513610421</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>-0.4680523506745073</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>-5.581018518518562</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>-5.043518518518525</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>-13599.53703703704</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>-65427777.77777778</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>-3.729166666666714</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>-5.017129629629636</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>-2.467310415845432</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>-128972.2222222222</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>-0.07986111111111427</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>-4.474927303858976</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>-156.7638888888889</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>-7542638.888888888</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>-157.8888888888889</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>-0.4893379070074104</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>-5068834.269441573</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vymauDyP</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45590.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>148</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.725</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.5724999999999998</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.2281249999999999</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.1412500000000001</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.3355263157894737</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.2269736842105263</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-1.575657894736842</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.3585526315789478</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-2.621710526315789</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.0164473684210531</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.1151315789473685</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.5833333333333333</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.9166666666666667</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.368421052631579</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.381578947368421</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.924918831168831</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1.913186813186813</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.239934540538332</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-0.540529615757757</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-0.01291395222584148</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-0.01291395222584148</v>
+      </c>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>2.201298701298697</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.8766233766233853</v>
+      </c>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="n">
+        <v>-4.311688311688307</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.4935064935064872</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.416666666666664</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-0.2730263157894726</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-0.04276315789473983</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-2.166666666666664</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.166666666666664</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-5.684210526315788</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.684210526315788</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>53</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>-134</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>53</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>-134</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-0.575657894736842</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0.1907894736842106</v>
+      </c>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>6.083333333333334</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1.016447368421051</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>2.690789473684209</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>-5.260997067448679</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>-0.7927170868347311</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>-5.260997067448679</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>-0.7927170868347311</v>
+      </c>
+      <c r="CF21" t="inlineStr"/>
+      <c r="CG21" t="inlineStr"/>
+      <c r="CH21" t="n">
+        <v>-0.01854574715721258</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.009465698732532481</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0.1710526315789473</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0.2236842105263158</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>-0.4913465007215052</v>
+      </c>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="n">
+        <v>1.832282160468438</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>-6972.284922775118</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>-0.2357031857031859</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>-4.710648148148152</v>
+      </c>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="n">
+        <v>-11708333.33333333</v>
+      </c>
+      <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="n">
+        <v>-1.992746079265672</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>-8472.222222222219</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>0.8796296296296333</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>-3.965265317471193</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="n">
+        <v>24.72222222222223</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>-0.4399013568130954</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>-5891631.401459834</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/da